--- a/examples/example_continuous_results.xlsx
+++ b/examples/example_continuous_results.xlsx
@@ -9,15 +9,16 @@
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
     <sheet name="Statistical Tests" sheetId="2" r:id="rId2"/>
-    <sheet name="Estimates" sheetId="3" r:id="rId3"/>
-    <sheet name="Sample" sheetId="4" r:id="rId4"/>
+    <sheet name="Model Performance" sheetId="3" r:id="rId3"/>
+    <sheet name="Estimates" sheetId="4" r:id="rId4"/>
+    <sheet name="Sample" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="112">
   <si>
     <t>Group</t>
   </si>
@@ -205,15 +206,60 @@
     <t>Romano-Wolf (bootstrap tests) / Hommel (other tests)</t>
   </si>
   <si>
-    <t>rho_delta: intraclass correlation of the per-eye difference in loss between the two models; one_eye_factor: patients a one-eye study needs, relative to this analysis (design effect)</t>
+    <t>ρΔ (rho_delta): intraclass correlation of the per-eye difference in loss between the two models; one_eye_factor: patients a one-eye study needs, relative to this analysis (design effect)</t>
   </si>
   <si>
     <t>group</t>
   </si>
   <si>
+    <t>model</t>
+  </si>
+  <si>
     <t>metric</t>
   </si>
   <si>
+    <t>estimate</t>
+  </si>
+  <si>
+    <t>ci_low</t>
+  </si>
+  <si>
+    <t>ci_high</t>
+  </si>
+  <si>
+    <t>n_eyes</t>
+  </si>
+  <si>
+    <t>n_patients</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>bias</t>
+  </si>
+  <si>
+    <t>mae</t>
+  </si>
+  <si>
+    <t>rmse</t>
+  </si>
+  <si>
+    <t>medae</t>
+  </si>
+  <si>
+    <t>sd</t>
+  </si>
+  <si>
+    <t>within</t>
+  </si>
+  <si>
+    <t>patient bootstrap, percentile</t>
+  </si>
+  <si>
+    <t>bootstrap, percentile</t>
+  </si>
+  <si>
     <t>model_a</t>
   </si>
   <si>
@@ -229,12 +275,6 @@
     <t>diff</t>
   </si>
   <si>
-    <t>ci_low</t>
-  </si>
-  <si>
-    <t>ci_high</t>
-  </si>
-  <si>
     <t>p</t>
   </si>
   <si>
@@ -250,24 +290,6 @@
     <t>p_adj</t>
   </si>
   <si>
-    <t>bias</t>
-  </si>
-  <si>
-    <t>mae</t>
-  </si>
-  <si>
-    <t>rmse</t>
-  </si>
-  <si>
-    <t>medae</t>
-  </si>
-  <si>
-    <t>sd</t>
-  </si>
-  <si>
-    <t>within</t>
-  </si>
-  <si>
     <t>bootstrap-t</t>
   </si>
   <si>
@@ -287,12 +309,6 @@
   </si>
   <si>
     <t>truth</t>
-  </si>
-  <si>
-    <t>n_eyes</t>
-  </si>
-  <si>
-    <t>n_patients</t>
   </si>
   <si>
     <t>n_bilateral</t>
@@ -1873,6 +1889,1614 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I55"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="9" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2">
+        <v>0.02049261083743843</v>
+      </c>
+      <c r="E2">
+        <v>-0.03627408686752381</v>
+      </c>
+      <c r="F2">
+        <v>0.07817344322344313</v>
+      </c>
+      <c r="G2">
+        <v>406</v>
+      </c>
+      <c r="H2">
+        <v>250</v>
+      </c>
+      <c r="I2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3">
+        <v>0.02807881773399015</v>
+      </c>
+      <c r="E3">
+        <v>-0.03130163576219235</v>
+      </c>
+      <c r="F3">
+        <v>0.08814663182346116</v>
+      </c>
+      <c r="G3">
+        <v>406</v>
+      </c>
+      <c r="H3">
+        <v>250</v>
+      </c>
+      <c r="I3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4">
+        <v>0.04536945812807881</v>
+      </c>
+      <c r="E4">
+        <v>-0.0227918672839506</v>
+      </c>
+      <c r="F4">
+        <v>0.1117210615626027</v>
+      </c>
+      <c r="G4">
+        <v>406</v>
+      </c>
+      <c r="H4">
+        <v>250</v>
+      </c>
+      <c r="I4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5">
+        <v>0.4010837438423646</v>
+      </c>
+      <c r="E5">
+        <v>0.3695515125104408</v>
+      </c>
+      <c r="F5">
+        <v>0.4314988474459895</v>
+      </c>
+      <c r="G5">
+        <v>406</v>
+      </c>
+      <c r="H5">
+        <v>250</v>
+      </c>
+      <c r="I5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6">
+        <v>0.413743842364532</v>
+      </c>
+      <c r="E6">
+        <v>0.3824580685289189</v>
+      </c>
+      <c r="F6">
+        <v>0.4454042263674867</v>
+      </c>
+      <c r="G6">
+        <v>406</v>
+      </c>
+      <c r="H6">
+        <v>250</v>
+      </c>
+      <c r="I6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7">
+        <v>0.4725615763546798</v>
+      </c>
+      <c r="E7">
+        <v>0.4363228203517588</v>
+      </c>
+      <c r="F7">
+        <v>0.5081824833702879</v>
+      </c>
+      <c r="G7">
+        <v>406</v>
+      </c>
+      <c r="H7">
+        <v>250</v>
+      </c>
+      <c r="I7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8">
+        <v>0.503346436828533</v>
+      </c>
+      <c r="E8">
+        <v>0.467341335102832</v>
+      </c>
+      <c r="F8">
+        <v>0.5381596977405826</v>
+      </c>
+      <c r="G8">
+        <v>406</v>
+      </c>
+      <c r="H8">
+        <v>250</v>
+      </c>
+      <c r="I8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9">
+        <v>0.5190271308530763</v>
+      </c>
+      <c r="E9">
+        <v>0.4829163917076886</v>
+      </c>
+      <c r="F9">
+        <v>0.5537674085132629</v>
+      </c>
+      <c r="G9">
+        <v>406</v>
+      </c>
+      <c r="H9">
+        <v>250</v>
+      </c>
+      <c r="I9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10">
+        <v>0.5875820873372553</v>
+      </c>
+      <c r="E10">
+        <v>0.5463605798821267</v>
+      </c>
+      <c r="F10">
+        <v>0.6266470149182912</v>
+      </c>
+      <c r="G10">
+        <v>406</v>
+      </c>
+      <c r="H10">
+        <v>250</v>
+      </c>
+      <c r="I10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11">
+        <v>0.34</v>
+      </c>
+      <c r="E11">
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="F11">
+        <v>0.38</v>
+      </c>
+      <c r="G11">
+        <v>406</v>
+      </c>
+      <c r="H11">
+        <v>250</v>
+      </c>
+      <c r="I11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12">
+        <v>0.3500000000000001</v>
+      </c>
+      <c r="E12">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="F12">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="G12">
+        <v>406</v>
+      </c>
+      <c r="H12">
+        <v>250</v>
+      </c>
+      <c r="I12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="E13">
+        <v>0.36</v>
+      </c>
+      <c r="F13">
+        <v>0.45</v>
+      </c>
+      <c r="G13">
+        <v>406</v>
+      </c>
+      <c r="H13">
+        <v>250</v>
+      </c>
+      <c r="I13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14">
+        <v>0.5035496260262651</v>
+      </c>
+      <c r="E14">
+        <v>0.4670729663895484</v>
+      </c>
+      <c r="F14">
+        <v>0.5373554039329193</v>
+      </c>
+      <c r="G14">
+        <v>406</v>
+      </c>
+      <c r="H14">
+        <v>250</v>
+      </c>
+      <c r="I14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15">
+        <v>0.5189064985777815</v>
+      </c>
+      <c r="E15">
+        <v>0.481268604979075</v>
+      </c>
+      <c r="F15">
+        <v>0.5530250723007292</v>
+      </c>
+      <c r="G15">
+        <v>406</v>
+      </c>
+      <c r="H15">
+        <v>250</v>
+      </c>
+      <c r="I15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16">
+        <v>0.5865506926221365</v>
+      </c>
+      <c r="E16">
+        <v>0.5442726547777093</v>
+      </c>
+      <c r="F16">
+        <v>0.624844231822534</v>
+      </c>
+      <c r="G16">
+        <v>406</v>
+      </c>
+      <c r="H16">
+        <v>250</v>
+      </c>
+      <c r="I16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17">
+        <v>0.6921182266009852</v>
+      </c>
+      <c r="E17">
+        <v>0.6451574224491374</v>
+      </c>
+      <c r="F17">
+        <v>0.739135938359934</v>
+      </c>
+      <c r="G17">
+        <v>406</v>
+      </c>
+      <c r="H17">
+        <v>250</v>
+      </c>
+      <c r="I17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18">
+        <v>0.6576354679802956</v>
+      </c>
+      <c r="E18">
+        <v>0.6104218362282878</v>
+      </c>
+      <c r="F18">
+        <v>0.7064676616915423</v>
+      </c>
+      <c r="G18">
+        <v>406</v>
+      </c>
+      <c r="H18">
+        <v>250</v>
+      </c>
+      <c r="I18" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19">
+        <v>0.6108374384236454</v>
+      </c>
+      <c r="E19">
+        <v>0.5601965601965602</v>
+      </c>
+      <c r="F19">
+        <v>0.6616933849272157</v>
+      </c>
+      <c r="G19">
+        <v>406</v>
+      </c>
+      <c r="H19">
+        <v>250</v>
+      </c>
+      <c r="I19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20">
+        <v>0.01473429951690822</v>
+      </c>
+      <c r="E20">
+        <v>-0.05386956521739131</v>
+      </c>
+      <c r="F20">
+        <v>0.08382367149758455</v>
+      </c>
+      <c r="G20">
+        <v>207</v>
+      </c>
+      <c r="H20">
+        <v>207</v>
+      </c>
+      <c r="I20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21">
+        <v>0.006376811594202901</v>
+      </c>
+      <c r="E21">
+        <v>-0.06710386473429948</v>
+      </c>
+      <c r="F21">
+        <v>0.07851690821256047</v>
+      </c>
+      <c r="G21">
+        <v>207</v>
+      </c>
+      <c r="H21">
+        <v>207</v>
+      </c>
+      <c r="I21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22">
+        <v>0.002318840579710145</v>
+      </c>
+      <c r="E22">
+        <v>-0.07716183574879226</v>
+      </c>
+      <c r="F22">
+        <v>0.08183816425120778</v>
+      </c>
+      <c r="G22">
+        <v>207</v>
+      </c>
+      <c r="H22">
+        <v>207</v>
+      </c>
+      <c r="I22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23">
+        <v>0.4014975845410628</v>
+      </c>
+      <c r="E23">
+        <v>0.3609106280193235</v>
+      </c>
+      <c r="F23">
+        <v>0.4427584541062801</v>
+      </c>
+      <c r="G23">
+        <v>207</v>
+      </c>
+      <c r="H23">
+        <v>207</v>
+      </c>
+      <c r="I23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24">
+        <v>0.4215458937198068</v>
+      </c>
+      <c r="E24">
+        <v>0.3783091787439615</v>
+      </c>
+      <c r="F24">
+        <v>0.4659565217391309</v>
+      </c>
+      <c r="G24">
+        <v>207</v>
+      </c>
+      <c r="H24">
+        <v>207</v>
+      </c>
+      <c r="I24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25">
+        <v>0.4694685990338164</v>
+      </c>
+      <c r="E25">
+        <v>0.4212487922705314</v>
+      </c>
+      <c r="F25">
+        <v>0.5170048309178744</v>
+      </c>
+      <c r="G25">
+        <v>207</v>
+      </c>
+      <c r="H25">
+        <v>207</v>
+      </c>
+      <c r="I25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26">
+        <v>0.4993498188103143</v>
+      </c>
+      <c r="E26">
+        <v>0.4489748654168933</v>
+      </c>
+      <c r="F26">
+        <v>0.5487215267707212</v>
+      </c>
+      <c r="G26">
+        <v>207</v>
+      </c>
+      <c r="H26">
+        <v>207</v>
+      </c>
+      <c r="I26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27">
+        <v>0.5350976252975095</v>
+      </c>
+      <c r="E27">
+        <v>0.4824960764236936</v>
+      </c>
+      <c r="F27">
+        <v>0.5865781583925679</v>
+      </c>
+      <c r="G27">
+        <v>207</v>
+      </c>
+      <c r="H27">
+        <v>207</v>
+      </c>
+      <c r="I27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28">
+        <v>0.5841530472476332</v>
+      </c>
+      <c r="E28">
+        <v>0.5291510823472348</v>
+      </c>
+      <c r="F28">
+        <v>0.6371627741675031</v>
+      </c>
+      <c r="G28">
+        <v>207</v>
+      </c>
+      <c r="H28">
+        <v>207</v>
+      </c>
+      <c r="I28" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29">
+        <v>0.3599999999999999</v>
+      </c>
+      <c r="E29">
+        <v>0.29</v>
+      </c>
+      <c r="F29">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="G29">
+        <v>207</v>
+      </c>
+      <c r="H29">
+        <v>207</v>
+      </c>
+      <c r="I29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30">
+        <v>0.37</v>
+      </c>
+      <c r="E30">
+        <v>0.3</v>
+      </c>
+      <c r="F30">
+        <v>0.4300000000000002</v>
+      </c>
+      <c r="G30">
+        <v>207</v>
+      </c>
+      <c r="H30">
+        <v>207</v>
+      </c>
+      <c r="I30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31">
+        <v>0.4199999999999999</v>
+      </c>
+      <c r="E31">
+        <v>0.3599999999999994</v>
+      </c>
+      <c r="F31">
+        <v>0.48</v>
+      </c>
+      <c r="G31">
+        <v>207</v>
+      </c>
+      <c r="H31">
+        <v>207</v>
+      </c>
+      <c r="I31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32">
+        <v>0.5003424089040717</v>
+      </c>
+      <c r="E32">
+        <v>0.4484747263872393</v>
+      </c>
+      <c r="F32">
+        <v>0.5472560680830526</v>
+      </c>
+      <c r="G32">
+        <v>207</v>
+      </c>
+      <c r="H32">
+        <v>207</v>
+      </c>
+      <c r="I32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33">
+        <v>0.5363567435512407</v>
+      </c>
+      <c r="E33">
+        <v>0.4821727389220226</v>
+      </c>
+      <c r="F33">
+        <v>0.5863463364422008</v>
+      </c>
+      <c r="G33">
+        <v>207</v>
+      </c>
+      <c r="H33">
+        <v>207</v>
+      </c>
+      <c r="I33" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34">
+        <v>0.5855645643413213</v>
+      </c>
+      <c r="E34">
+        <v>0.529478721324974</v>
+      </c>
+      <c r="F34">
+        <v>0.6374656501091623</v>
+      </c>
+      <c r="G34">
+        <v>207</v>
+      </c>
+      <c r="H34">
+        <v>207</v>
+      </c>
+      <c r="I34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35">
+        <v>0.714975845410628</v>
+      </c>
+      <c r="E35">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="F35">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G35">
+        <v>207</v>
+      </c>
+      <c r="H35">
+        <v>207</v>
+      </c>
+      <c r="I35" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36">
+        <v>0.6473429951690821</v>
+      </c>
+      <c r="E36">
+        <v>0.5797101449275363</v>
+      </c>
+      <c r="F36">
+        <v>0.7101449275362319</v>
+      </c>
+      <c r="G36">
+        <v>207</v>
+      </c>
+      <c r="H36">
+        <v>207</v>
+      </c>
+      <c r="I36" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37">
+        <v>0.6038647342995169</v>
+      </c>
+      <c r="E37">
+        <v>0.5362318840579711</v>
+      </c>
+      <c r="F37">
+        <v>0.6714975845410628</v>
+      </c>
+      <c r="G37">
+        <v>207</v>
+      </c>
+      <c r="H37">
+        <v>207</v>
+      </c>
+      <c r="I37" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38">
+        <v>0.02648241206030149</v>
+      </c>
+      <c r="E38">
+        <v>-0.04417587939698493</v>
+      </c>
+      <c r="F38">
+        <v>0.09693718592964826</v>
+      </c>
+      <c r="G38">
+        <v>199</v>
+      </c>
+      <c r="H38">
+        <v>199</v>
+      </c>
+      <c r="I38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39">
+        <v>0.05065326633165827</v>
+      </c>
+      <c r="E39">
+        <v>-0.01932160804020097</v>
+      </c>
+      <c r="F39">
+        <v>0.1202537688442211</v>
+      </c>
+      <c r="G39">
+        <v>199</v>
+      </c>
+      <c r="H39">
+        <v>199</v>
+      </c>
+      <c r="I39" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" t="s">
+        <v>72</v>
+      </c>
+      <c r="D40">
+        <v>0.09015075376884421</v>
+      </c>
+      <c r="E40">
+        <v>0.005876884422110537</v>
+      </c>
+      <c r="F40">
+        <v>0.1709070351758794</v>
+      </c>
+      <c r="G40">
+        <v>199</v>
+      </c>
+      <c r="H40">
+        <v>199</v>
+      </c>
+      <c r="I40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" t="s">
+        <v>73</v>
+      </c>
+      <c r="D41">
+        <v>0.4006532663316583</v>
+      </c>
+      <c r="E41">
+        <v>0.3574874371859297</v>
+      </c>
+      <c r="F41">
+        <v>0.4432688442211056</v>
+      </c>
+      <c r="G41">
+        <v>199</v>
+      </c>
+      <c r="H41">
+        <v>199</v>
+      </c>
+      <c r="I41" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42">
+        <v>0.4056281407035176</v>
+      </c>
+      <c r="E42">
+        <v>0.3649698492462313</v>
+      </c>
+      <c r="F42">
+        <v>0.4472889447236182</v>
+      </c>
+      <c r="G42">
+        <v>199</v>
+      </c>
+      <c r="H42">
+        <v>199</v>
+      </c>
+      <c r="I42" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43">
+        <v>0.4757788944723618</v>
+      </c>
+      <c r="E43">
+        <v>0.4288944723618093</v>
+      </c>
+      <c r="F43">
+        <v>0.5252286432160804</v>
+      </c>
+      <c r="G43">
+        <v>199</v>
+      </c>
+      <c r="H43">
+        <v>199</v>
+      </c>
+      <c r="I43" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" t="s">
+        <v>74</v>
+      </c>
+      <c r="D44">
+        <v>0.5074703248991672</v>
+      </c>
+      <c r="E44">
+        <v>0.4568519922236322</v>
+      </c>
+      <c r="F44">
+        <v>0.5557394457416932</v>
+      </c>
+      <c r="G44">
+        <v>199</v>
+      </c>
+      <c r="H44">
+        <v>199</v>
+      </c>
+      <c r="I44" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" t="s">
+        <v>74</v>
+      </c>
+      <c r="D45">
+        <v>0.5017647249418594</v>
+      </c>
+      <c r="E45">
+        <v>0.4565332790587962</v>
+      </c>
+      <c r="F45">
+        <v>0.5461399953055275</v>
+      </c>
+      <c r="G45">
+        <v>199</v>
+      </c>
+      <c r="H45">
+        <v>199</v>
+      </c>
+      <c r="I45" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" t="s">
+        <v>74</v>
+      </c>
+      <c r="D46">
+        <v>0.5911278717875009</v>
+      </c>
+      <c r="E46">
+        <v>0.5363117100554832</v>
+      </c>
+      <c r="F46">
+        <v>0.6456197404269474</v>
+      </c>
+      <c r="G46">
+        <v>199</v>
+      </c>
+      <c r="H46">
+        <v>199</v>
+      </c>
+      <c r="I46" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47">
+        <v>0.34</v>
+      </c>
+      <c r="E47">
+        <v>0.29</v>
+      </c>
+      <c r="F47">
+        <v>0.4099999999999999</v>
+      </c>
+      <c r="G47">
+        <v>199</v>
+      </c>
+      <c r="H47">
+        <v>199</v>
+      </c>
+      <c r="I47" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48">
+        <v>0.3500000000000001</v>
+      </c>
+      <c r="E48">
+        <v>0.3099999999999998</v>
+      </c>
+      <c r="F48">
+        <v>0.4</v>
+      </c>
+      <c r="G48">
+        <v>199</v>
+      </c>
+      <c r="H48">
+        <v>199</v>
+      </c>
+      <c r="I48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" t="s">
+        <v>75</v>
+      </c>
+      <c r="D49">
+        <v>0.3900000000000001</v>
+      </c>
+      <c r="E49">
+        <v>0.34</v>
+      </c>
+      <c r="F49">
+        <v>0.4400000000000001</v>
+      </c>
+      <c r="G49">
+        <v>199</v>
+      </c>
+      <c r="H49">
+        <v>199</v>
+      </c>
+      <c r="I49" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50" t="s">
+        <v>76</v>
+      </c>
+      <c r="D50">
+        <v>0.5080569923909963</v>
+      </c>
+      <c r="E50">
+        <v>0.4565598267050878</v>
+      </c>
+      <c r="F50">
+        <v>0.5549796484849452</v>
+      </c>
+      <c r="G50">
+        <v>199</v>
+      </c>
+      <c r="H50">
+        <v>199</v>
+      </c>
+      <c r="I50" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" t="s">
+        <v>76</v>
+      </c>
+      <c r="D51">
+        <v>0.5004604701660993</v>
+      </c>
+      <c r="E51">
+        <v>0.4533062480035989</v>
+      </c>
+      <c r="F51">
+        <v>0.5438143015862841</v>
+      </c>
+      <c r="G51">
+        <v>199</v>
+      </c>
+      <c r="H51">
+        <v>199</v>
+      </c>
+      <c r="I51" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52">
+        <v>0.5856865757701022</v>
+      </c>
+      <c r="E52">
+        <v>0.528603758787536</v>
+      </c>
+      <c r="F52">
+        <v>0.6404274271255828</v>
+      </c>
+      <c r="G52">
+        <v>199</v>
+      </c>
+      <c r="H52">
+        <v>199</v>
+      </c>
+      <c r="I52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" t="s">
+        <v>77</v>
+      </c>
+      <c r="D53">
+        <v>0.6683417085427136</v>
+      </c>
+      <c r="E53">
+        <v>0.6030150753768844</v>
+      </c>
+      <c r="F53">
+        <v>0.7336683417085427</v>
+      </c>
+      <c r="G53">
+        <v>199</v>
+      </c>
+      <c r="H53">
+        <v>199</v>
+      </c>
+      <c r="I53" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" t="s">
+        <v>77</v>
+      </c>
+      <c r="D54">
+        <v>0.6683417085427136</v>
+      </c>
+      <c r="E54">
+        <v>0.5979899497487438</v>
+      </c>
+      <c r="F54">
+        <v>0.7336683417085427</v>
+      </c>
+      <c r="G54">
+        <v>199</v>
+      </c>
+      <c r="H54">
+        <v>199</v>
+      </c>
+      <c r="I54" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55">
+        <v>0.6180904522613065</v>
+      </c>
+      <c r="E55">
+        <v>0.5477386934673367</v>
+      </c>
+      <c r="F55">
+        <v>0.6834170854271356</v>
+      </c>
+      <c r="G55">
+        <v>199</v>
+      </c>
+      <c r="H55">
+        <v>199</v>
+      </c>
+      <c r="I55" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1884,43 +3508,43 @@
         <v>63</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" t="s">
         <v>67</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>68</v>
       </c>
-      <c r="G1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" t="s">
-        <v>71</v>
-      </c>
       <c r="J1" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="K1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="L1" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="M1" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="N1" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1928,7 +3552,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
         <v>38</v>
@@ -1972,7 +3596,7 @@
         <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
         <v>38</v>
@@ -2016,7 +3640,7 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
         <v>38</v>
@@ -2060,7 +3684,7 @@
         <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
         <v>38</v>
@@ -2098,7 +3722,7 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
         <v>38</v>
@@ -2136,7 +3760,7 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
         <v>38</v>
@@ -2180,7 +3804,7 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
         <v>38</v>
@@ -2224,7 +3848,7 @@
         <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
@@ -2268,7 +3892,7 @@
         <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
         <v>38</v>
@@ -2312,7 +3936,7 @@
         <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
         <v>38</v>
@@ -2350,7 +3974,7 @@
         <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
         <v>38</v>
@@ -2388,7 +4012,7 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
         <v>38</v>
@@ -2432,7 +4056,7 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
         <v>39</v>
@@ -2476,7 +4100,7 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
         <v>39</v>
@@ -2520,7 +4144,7 @@
         <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
@@ -2564,7 +4188,7 @@
         <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
         <v>39</v>
@@ -2602,7 +4226,7 @@
         <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
         <v>39</v>
@@ -2640,7 +4264,7 @@
         <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
         <v>39</v>
@@ -2684,7 +4308,7 @@
         <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
         <v>38</v>
@@ -2711,7 +4335,7 @@
         <v>0.7482</v>
       </c>
       <c r="M20" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N20">
         <v>0.9228</v>
@@ -2722,7 +4346,7 @@
         <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
         <v>38</v>
@@ -2749,7 +4373,7 @@
         <v>0.3648</v>
       </c>
       <c r="M21" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N21">
         <v>0.3648</v>
@@ -2760,7 +4384,7 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
         <v>38</v>
@@ -2787,7 +4411,7 @@
         <v>0.1386</v>
       </c>
       <c r="M22" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N22">
         <v>0.2192</v>
@@ -2798,7 +4422,7 @@
         <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
         <v>38</v>
@@ -2825,7 +4449,7 @@
         <v>0.6612</v>
       </c>
       <c r="M23" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N23">
         <v>0.7706</v>
@@ -2836,7 +4460,7 @@
         <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
@@ -2874,7 +4498,7 @@
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
         <v>38</v>
@@ -2901,7 +4525,7 @@
         <v>0.08782509563019504</v>
       </c>
       <c r="M25" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N25">
         <v>0.1756501912603901</v>
@@ -2912,7 +4536,7 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C26" t="s">
         <v>38</v>
@@ -2939,7 +4563,7 @@
         <v>0.6962</v>
       </c>
       <c r="M26" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N26">
         <v>0.9156</v>
@@ -2950,7 +4574,7 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
         <v>38</v>
@@ -2977,7 +4601,7 @@
         <v>0.0066</v>
       </c>
       <c r="M27" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N27">
         <v>0.0182</v>
@@ -2988,7 +4612,7 @@
         <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
         <v>38</v>
@@ -3015,7 +4639,7 @@
         <v>0.004</v>
       </c>
       <c r="M28" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N28">
         <v>0.0112</v>
@@ -3026,7 +4650,7 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
         <v>38</v>
@@ -3053,7 +4677,7 @@
         <v>0.044</v>
       </c>
       <c r="M29" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N29">
         <v>0.3118</v>
@@ -3064,7 +4688,7 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
         <v>38</v>
@@ -3102,7 +4726,7 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
         <v>38</v>
@@ -3129,7 +4753,7 @@
         <v>0.006357215082587968</v>
       </c>
       <c r="M31" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N31">
         <v>0.0190716452477639</v>
@@ -3140,7 +4764,7 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
         <v>39</v>
@@ -3167,7 +4791,7 @@
         <v>0.9026</v>
       </c>
       <c r="M32" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N32">
         <v>0.9228</v>
@@ -3178,7 +4802,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s">
         <v>39</v>
@@ -3205,7 +4829,7 @@
         <v>0.0788</v>
       </c>
       <c r="M33" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N33">
         <v>0.1346</v>
@@ -3216,7 +4840,7 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
         <v>39</v>
@@ -3243,7 +4867,7 @@
         <v>0.1238</v>
       </c>
       <c r="M34" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N34">
         <v>0.2192</v>
@@ -3254,7 +4878,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C35" t="s">
         <v>39</v>
@@ -3281,7 +4905,7 @@
         <v>0.224</v>
       </c>
       <c r="M35" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N35">
         <v>0.4476</v>
@@ -3292,7 +4916,7 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C36" t="s">
         <v>39</v>
@@ -3330,7 +4954,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
         <v>39</v>
@@ -3357,7 +4981,7 @@
         <v>0.3134999455835852</v>
       </c>
       <c r="M37" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N37">
         <v>0.3134999455835852</v>
@@ -3368,7 +4992,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C38" t="s">
         <v>38</v>
@@ -3395,7 +5019,7 @@
         <v>0.3916</v>
       </c>
       <c r="M38" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N38">
         <v>0.4768</v>
@@ -3406,7 +5030,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C39" t="s">
         <v>38</v>
@@ -3433,7 +5057,7 @@
         <v>0.8314</v>
       </c>
       <c r="M39" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N39">
         <v>0.8314</v>
@@ -3444,7 +5068,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C40" t="s">
         <v>38</v>
@@ -3471,7 +5095,7 @@
         <v>0.8202</v>
       </c>
       <c r="M40" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N40">
         <v>0.8202</v>
@@ -3482,7 +5106,7 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C41" t="s">
         <v>38</v>
@@ -3509,7 +5133,7 @@
         <v>0.6392</v>
       </c>
       <c r="M41" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N41">
         <v>0.764</v>
@@ -3520,7 +5144,7 @@
         <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C42" t="s">
         <v>38</v>
@@ -3558,7 +5182,7 @@
         <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C43" t="s">
         <v>38</v>
@@ -3585,7 +5209,7 @@
         <v>1</v>
       </c>
       <c r="M43" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N43">
         <v>1</v>
@@ -3596,7 +5220,7 @@
         <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C44" t="s">
         <v>38</v>
@@ -3623,7 +5247,7 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="M44" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N44">
         <v>0.1878</v>
@@ -3634,7 +5258,7 @@
         <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C45" t="s">
         <v>38</v>
@@ -3661,7 +5285,7 @@
         <v>0.008200000000000001</v>
       </c>
       <c r="M45" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N45">
         <v>0.024</v>
@@ -3672,7 +5296,7 @@
         <v>37</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C46" t="s">
         <v>38</v>
@@ -3699,7 +5323,7 @@
         <v>0.0086</v>
       </c>
       <c r="M46" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N46">
         <v>0.0188</v>
@@ -3710,7 +5334,7 @@
         <v>37</v>
       </c>
       <c r="B47" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C47" t="s">
         <v>38</v>
@@ -3737,7 +5361,7 @@
         <v>0.1548</v>
       </c>
       <c r="M47" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N47">
         <v>0.2654</v>
@@ -3748,7 +5372,7 @@
         <v>37</v>
       </c>
       <c r="B48" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C48" t="s">
         <v>38</v>
@@ -3786,7 +5410,7 @@
         <v>37</v>
       </c>
       <c r="B49" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C49" t="s">
         <v>38</v>
@@ -3813,7 +5437,7 @@
         <v>0.3018984444285246</v>
       </c>
       <c r="M49" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N49">
         <v>0.6037968888570493</v>
@@ -3824,7 +5448,7 @@
         <v>37</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C50" t="s">
         <v>39</v>
@@ -3851,7 +5475,7 @@
         <v>0.2944</v>
       </c>
       <c r="M50" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N50">
         <v>0.4768</v>
@@ -3862,7 +5486,7 @@
         <v>37</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C51" t="s">
         <v>39</v>
@@ -3889,7 +5513,7 @@
         <v>0.0186</v>
       </c>
       <c r="M51" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N51">
         <v>0.0348</v>
@@ -3900,7 +5524,7 @@
         <v>37</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C52" t="s">
         <v>39</v>
@@ -3927,7 +5551,7 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="M52" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N52">
         <v>0.0188</v>
@@ -3938,7 +5562,7 @@
         <v>37</v>
       </c>
       <c r="B53" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C53" t="s">
         <v>39</v>
@@ -3965,7 +5589,7 @@
         <v>0.3536</v>
       </c>
       <c r="M53" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N53">
         <v>0.4588</v>
@@ -3976,7 +5600,7 @@
         <v>37</v>
       </c>
       <c r="B54" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C54" t="s">
         <v>39</v>
@@ -4014,7 +5638,7 @@
         <v>37</v>
       </c>
       <c r="B55" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C55" t="s">
         <v>39</v>
@@ -4041,7 +5665,7 @@
         <v>0.3018984444285246</v>
       </c>
       <c r="M55" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N55">
         <v>0.6037968888570493</v>
@@ -4052,7 +5676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4062,49 +5686,49 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F1" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="G1" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="H1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="K1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="L1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="M1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="N1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="O1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="P1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -4112,16 +5736,16 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F2">
         <v>406</v>
@@ -4145,16 +5769,16 @@
         <v>42</v>
       </c>
       <c r="M2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -4162,16 +5786,16 @@
         <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F3">
         <v>207</v>
@@ -4195,16 +5819,16 @@
         <v>42</v>
       </c>
       <c r="M3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -4212,16 +5836,16 @@
         <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F4">
         <v>199</v>
@@ -4245,16 +5869,16 @@
         <v>42</v>
       </c>
       <c r="M4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O4" t="b">
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/examples/example_continuous_results.xlsx
+++ b/examples/example_continuous_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="142">
   <si>
     <t>Group</t>
   </si>
@@ -44,6 +44,12 @@
     <t>MPE Diff 95% CI high</t>
   </si>
   <si>
+    <t>MPE Diff 95% CI adj low</t>
+  </si>
+  <si>
+    <t>MPE Diff 95% CI adj high</t>
+  </si>
+  <si>
     <t>Boot (MPE) p</t>
   </si>
   <si>
@@ -59,6 +65,12 @@
     <t>MAE Diff 95% CI high</t>
   </si>
   <si>
+    <t>MAE Diff 95% CI adj low</t>
+  </si>
+  <si>
+    <t>MAE Diff 95% CI adj high</t>
+  </si>
+  <si>
     <t>Boot (MAE) p</t>
   </si>
   <si>
@@ -74,6 +86,12 @@
     <t>RMSE Diff 95% CI high</t>
   </si>
   <si>
+    <t>RMSE Diff 95% CI adj low</t>
+  </si>
+  <si>
+    <t>RMSE Diff 95% CI adj high</t>
+  </si>
+  <si>
     <t>Boot (RMSE) p</t>
   </si>
   <si>
@@ -89,6 +107,12 @@
     <t>MedAE Diff 95% CI high</t>
   </si>
   <si>
+    <t>MedAE Diff 95% CI adj low</t>
+  </si>
+  <si>
+    <t>MedAE Diff 95% CI adj high</t>
+  </si>
+  <si>
     <t>Boot (MedAE) p</t>
   </si>
   <si>
@@ -104,6 +128,12 @@
     <t>SD Diff 95% CI high</t>
   </si>
   <si>
+    <t>SD Diff 95% CI adj low</t>
+  </si>
+  <si>
+    <t>SD Diff 95% CI adj high</t>
+  </si>
+  <si>
     <t>Morgan-Pitman (SD) p</t>
   </si>
   <si>
@@ -119,6 +149,12 @@
     <t>McNemar Diff 95% CI high</t>
   </si>
   <si>
+    <t>McNemar Diff 95% CI adj low</t>
+  </si>
+  <si>
+    <t>McNemar Diff 95% CI adj high</t>
+  </si>
+  <si>
     <t>McNemar p</t>
   </si>
   <si>
@@ -179,9 +215,18 @@
     <t>FWER Correction</t>
   </si>
   <si>
+    <t>Adjusted p-values (p_adj)</t>
+  </si>
+  <si>
+    <t>Adjusted Confidence Intervals</t>
+  </si>
+  <si>
     <t>Fellow-Eye Correlation</t>
   </si>
   <si>
+    <t>Subgroups</t>
+  </si>
+  <si>
     <t>Patient as the unit (cluster bootstrap / cluster-robust tests)</t>
   </si>
   <si>
@@ -206,9 +251,18 @@
     <t>Romano-Wolf (bootstrap tests) / Hommel (other tests)</t>
   </si>
   <si>
+    <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Romano-Wolf step-down: Mean Error (MPE), MAE, RMSE, MedAE, SD; Hommel: Proportion Within Tolerance</t>
+  </si>
+  <si>
+    <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group. Romano-Wolf simultaneous (max-|t|): Mean Error (MPE), MAE, MedAE; Bonferroni (percentile bootstrap): RMSE, SD, Proportion Within Tolerance. MPE, MAE and MedAE: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). RMSE, SD and the proportion within tolerance: percentile interval of the same patient resamples at coverage 1 - 0.05/m (Bonferroni). These Bonferroni-type intervals need not agree with p_adj when p_adj comes from another statistic (Romano-Wolf, Hommel); use more resamples (e.g. 9,999) for their far tails</t>
+  </si>
+  <si>
     <t>ρΔ (rho_delta): intraclass correlation of the per-eye difference in loss between the two models; one_eye_factor: patients a one-eye study needs, relative to this analysis (design effect)</t>
   </si>
   <si>
+    <t>eye, nominal: one subgroup per level (L, R). Each subgroup is analyzed separately with the same models, tests and settings; p-values and intervals are adjusted for the model pairs within each group, not across groups</t>
+  </si>
+  <si>
     <t>group</t>
   </si>
   <si>
@@ -290,6 +344,18 @@
     <t>p_adj</t>
   </si>
   <si>
+    <t>p_adj_method</t>
+  </si>
+  <si>
+    <t>ci_adj_low</t>
+  </si>
+  <si>
+    <t>ci_adj_high</t>
+  </si>
+  <si>
+    <t>ci_adj_method</t>
+  </si>
+  <si>
     <t>bootstrap-t</t>
   </si>
   <si>
@@ -299,6 +365,21 @@
     <t>McNemar</t>
   </si>
   <si>
+    <t>Romano-Wolf step-down</t>
+  </si>
+  <si>
+    <t>Hommel</t>
+  </si>
+  <si>
+    <t>Romano-Wolf simultaneous (max-|t|)</t>
+  </si>
+  <si>
+    <t>Bonferroni (percentile bootstrap)</t>
+  </si>
+  <si>
+    <t>definition</t>
+  </si>
+  <si>
     <t>task</t>
   </si>
   <si>
@@ -336,6 +417,15 @@
   </si>
   <si>
     <t>fwer_method</t>
+  </si>
+  <si>
+    <t>All eyes: 406 eyes, 250 patients</t>
+  </si>
+  <si>
+    <t>eye = L: 207 eyes, 207 patients</t>
+  </si>
+  <si>
+    <t>eye = R: 199 eyes, 199 patients</t>
   </si>
   <si>
     <t>continuous</t>
@@ -685,24 +775,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AU10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="8" width="22.7109375" customWidth="1"/>
-    <col min="9" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="13" width="22.7109375" customWidth="1"/>
-    <col min="14" max="15" width="15.7109375" customWidth="1"/>
-    <col min="16" max="18" width="22.7109375" customWidth="1"/>
-    <col min="19" max="20" width="15.7109375" customWidth="1"/>
-    <col min="21" max="23" width="22.7109375" customWidth="1"/>
-    <col min="24" max="25" width="15.7109375" customWidth="1"/>
-    <col min="26" max="28" width="22.7109375" customWidth="1"/>
-    <col min="29" max="30" width="15.7109375" customWidth="1"/>
-    <col min="31" max="33" width="22.7109375" customWidth="1"/>
-    <col min="34" max="35" width="15.7109375" customWidth="1"/>
+    <col min="1" max="10" width="22.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" customWidth="1"/>
+    <col min="13" max="17" width="22.7109375" customWidth="1"/>
+    <col min="18" max="19" width="15.7109375" customWidth="1"/>
+    <col min="20" max="24" width="22.7109375" customWidth="1"/>
+    <col min="25" max="26" width="15.7109375" customWidth="1"/>
+    <col min="27" max="31" width="22.7109375" customWidth="1"/>
+    <col min="32" max="33" width="15.7109375" customWidth="1"/>
+    <col min="34" max="38" width="22.7109375" customWidth="1"/>
+    <col min="39" max="40" width="15.7109375" customWidth="1"/>
+    <col min="41" max="45" width="22.7109375" customWidth="1"/>
+    <col min="46" max="47" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:47">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -808,16 +898,52 @@
       <c r="AI1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:35">
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:47">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D2">
         <v>406</v>
@@ -835,96 +961,132 @@
         <v>0.03040411335473123</v>
       </c>
       <c r="I2">
+        <v>-0.05410272103966409</v>
+      </c>
+      <c r="J2">
+        <v>0.03893030724656065</v>
+      </c>
+      <c r="K2">
         <v>0.6926</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>0.7454</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <v>-0.01266009852216748</v>
       </c>
-      <c r="L2">
+      <c r="N2">
         <v>-0.04537308813124197</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>0.02084416313854757</v>
       </c>
-      <c r="N2">
+      <c r="P2">
+        <v>-0.05229618964656452</v>
+      </c>
+      <c r="Q2">
+        <v>0.02697599260222911</v>
+      </c>
+      <c r="R2">
         <v>0.461</v>
       </c>
-      <c r="O2">
+      <c r="S2">
         <v>0.461</v>
       </c>
-      <c r="P2">
+      <c r="T2">
         <v>-0.01568069402454331</v>
       </c>
-      <c r="Q2">
+      <c r="U2">
         <v>-0.05106318963604019</v>
       </c>
-      <c r="R2">
+      <c r="V2">
         <v>0.01787937336349208</v>
       </c>
-      <c r="S2">
+      <c r="W2">
+        <v>-0.05856576544801697</v>
+      </c>
+      <c r="X2">
+        <v>0.02781683152088908</v>
+      </c>
+      <c r="Y2">
         <v>0.3852</v>
       </c>
-      <c r="T2">
+      <c r="Z2">
         <v>0.3852</v>
       </c>
-      <c r="U2">
+      <c r="AA2">
         <v>-0.01000000000000012</v>
       </c>
-      <c r="V2">
+      <c r="AB2">
         <v>-0.07000000000000073</v>
       </c>
-      <c r="W2">
+      <c r="AC2">
         <v>0.04000000000000004</v>
       </c>
-      <c r="X2">
+      <c r="AD2">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="AE2">
+        <v>0.05999999999999983</v>
+      </c>
+      <c r="AF2">
         <v>0.6112</v>
       </c>
-      <c r="Y2">
+      <c r="AG2">
         <v>0.7282</v>
       </c>
-      <c r="Z2">
+      <c r="AH2">
         <v>-0.01535687255151641</v>
       </c>
-      <c r="AA2">
+      <c r="AI2">
         <v>-0.05064189418206685</v>
       </c>
-      <c r="AB2">
+      <c r="AJ2">
         <v>0.01876017330561063</v>
       </c>
-      <c r="AC2">
+      <c r="AK2">
+        <v>-0.05815433485882701</v>
+      </c>
+      <c r="AL2">
+        <v>0.02825025172545625</v>
+      </c>
+      <c r="AM2">
         <v>0.3894</v>
       </c>
-      <c r="AD2">
+      <c r="AN2">
         <v>0.3894</v>
       </c>
-      <c r="AE2">
+      <c r="AO2">
         <v>0.03448275862068961</v>
       </c>
-      <c r="AF2">
+      <c r="AP2">
         <v>-0.01805205348027686</v>
       </c>
-      <c r="AG2">
+      <c r="AQ2">
         <v>0.08780487804878048</v>
       </c>
-      <c r="AH2">
+      <c r="AR2">
+        <v>-0.03189014549308666</v>
+      </c>
+      <c r="AS2">
+        <v>0.09762516046213096</v>
+      </c>
+      <c r="AT2">
         <v>0.204560421762222</v>
       </c>
-      <c r="AI2">
+      <c r="AU2">
         <v>0.204560421762222</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:47">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D3">
         <v>406</v>
@@ -942,96 +1104,132 @@
         <v>0.02555545062902348</v>
       </c>
       <c r="I3">
+        <v>-0.08440726271056506</v>
+      </c>
+      <c r="J3">
+        <v>0.03465356812928424</v>
+      </c>
+      <c r="K3">
         <v>0.323</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>0.5734</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>-0.07147783251231526</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>-0.1094511309795232</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>-0.03377935695481725</v>
       </c>
-      <c r="N3">
+      <c r="P3">
+        <v>-0.1160939316204946</v>
+      </c>
+      <c r="Q3">
+        <v>-0.02686173340413656</v>
+      </c>
+      <c r="R3">
         <v>0.0004</v>
-      </c>
-      <c r="O3">
-        <v>0.0004</v>
-      </c>
-      <c r="P3">
-        <v>-0.08423565050872228</v>
-      </c>
-      <c r="Q3">
-        <v>-0.1255427629627514</v>
-      </c>
-      <c r="R3">
-        <v>-0.0419672383242247</v>
       </c>
       <c r="S3">
         <v>0.0004</v>
       </c>
       <c r="T3">
+        <v>-0.08423565050872228</v>
+      </c>
+      <c r="U3">
+        <v>-0.1255427629627514</v>
+      </c>
+      <c r="V3">
+        <v>-0.0419672383242247</v>
+      </c>
+      <c r="W3">
+        <v>-0.1343146850892964</v>
+      </c>
+      <c r="X3">
+        <v>-0.03239054644227161</v>
+      </c>
+      <c r="Y3">
+        <v>0.0004</v>
+      </c>
+      <c r="Z3">
         <v>0.0008</v>
       </c>
-      <c r="U3">
+      <c r="AA3">
         <v>-0.05999999999999994</v>
       </c>
-      <c r="V3">
+      <c r="AB3">
         <v>-0.1199999999999999</v>
       </c>
-      <c r="W3">
+      <c r="AC3">
         <v>-0.009999999999999839</v>
       </c>
-      <c r="X3">
+      <c r="AD3">
+        <v>-0.1280741611297381</v>
+      </c>
+      <c r="AE3">
+        <v>0.008074161129738217</v>
+      </c>
+      <c r="AF3">
         <v>0.028</v>
       </c>
-      <c r="Y3">
+      <c r="AG3">
         <v>0.09279999999999999</v>
       </c>
-      <c r="Z3">
+      <c r="AH3">
         <v>-0.08300106659587148</v>
       </c>
-      <c r="AA3">
+      <c r="AI3">
         <v>-0.1240127595235769</v>
       </c>
-      <c r="AB3">
+      <c r="AJ3">
         <v>-0.04070333062115</v>
       </c>
-      <c r="AC3">
+      <c r="AK3">
+        <v>-0.1324121069898527</v>
+      </c>
+      <c r="AL3">
+        <v>-0.03081160526701519</v>
+      </c>
+      <c r="AM3">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="AD3">
+      <c r="AN3">
         <v>0.0008</v>
       </c>
-      <c r="AE3">
+      <c r="AO3">
         <v>0.08128078817733986</v>
       </c>
-      <c r="AF3">
+      <c r="AP3">
         <v>0.02216476440614372</v>
       </c>
-      <c r="AG3">
+      <c r="AQ3">
         <v>0.1403530377668309</v>
       </c>
-      <c r="AH3">
+      <c r="AR3">
+        <v>0.009991271820448863</v>
+      </c>
+      <c r="AS3">
+        <v>0.152573275862069</v>
+      </c>
+      <c r="AT3">
         <v>0.006863871555196087</v>
       </c>
-      <c r="AI3">
+      <c r="AU3">
         <v>0.02059161466558826</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:47">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D4">
         <v>406</v>
@@ -1049,96 +1247,132 @@
         <v>0.03668306575040813</v>
       </c>
       <c r="I4">
+        <v>-0.08180644473769279</v>
+      </c>
+      <c r="J4">
+        <v>0.04722516394951541</v>
+      </c>
+      <c r="K4">
         <v>0.518</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>0.7454</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>-0.05881773399014778</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>-0.1025986784782056</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>-0.01794955791900316</v>
       </c>
-      <c r="N4">
+      <c r="P4">
+        <v>-0.1084139624854691</v>
+      </c>
+      <c r="Q4">
+        <v>-0.009221505494826733</v>
+      </c>
+      <c r="R4">
         <v>0.005</v>
       </c>
-      <c r="O4">
+      <c r="S4">
         <v>0.0104</v>
       </c>
-      <c r="P4">
+      <c r="T4">
         <v>-0.06855495648417897</v>
       </c>
-      <c r="Q4">
+      <c r="U4">
         <v>-0.1131287403553189</v>
       </c>
-      <c r="R4">
+      <c r="V4">
         <v>-0.02214090274061026</v>
       </c>
-      <c r="S4">
+      <c r="W4">
+        <v>-0.1237607966652773</v>
+      </c>
+      <c r="X4">
+        <v>-0.01197481543232409</v>
+      </c>
+      <c r="Y4">
         <v>0.0036</v>
       </c>
-      <c r="T4">
+      <c r="Z4">
         <v>0.0052</v>
       </c>
-      <c r="U4">
+      <c r="AA4">
         <v>-0.04999999999999982</v>
       </c>
-      <c r="V4">
+      <c r="AB4">
         <v>-0.1099999999999999</v>
       </c>
-      <c r="W4">
+      <c r="AC4">
         <v>0.01000000000000035</v>
       </c>
-      <c r="X4">
+      <c r="AD4">
+        <v>-0.1230166690346133</v>
+      </c>
+      <c r="AE4">
+        <v>0.02301666903461366</v>
+      </c>
+      <c r="AF4">
         <v>0.1748</v>
       </c>
-      <c r="Y4">
+      <c r="AG4">
         <v>0.2226</v>
       </c>
-      <c r="Z4">
+      <c r="AH4">
         <v>-0.06764419404435507</v>
       </c>
-      <c r="AA4">
+      <c r="AI4">
         <v>-0.1119735373189496</v>
       </c>
-      <c r="AB4">
+      <c r="AJ4">
         <v>-0.02111883542966709</v>
       </c>
-      <c r="AC4">
+      <c r="AK4">
+        <v>-0.1227389787054996</v>
+      </c>
+      <c r="AL4">
+        <v>-0.009991811914109265</v>
+      </c>
+      <c r="AM4">
         <v>0.005</v>
       </c>
-      <c r="AD4">
+      <c r="AN4">
         <v>0.008399999999999999</v>
       </c>
-      <c r="AE4">
+      <c r="AO4">
         <v>0.04679802955665024</v>
       </c>
-      <c r="AF4">
+      <c r="AP4">
         <v>-0.01452960812430945</v>
       </c>
-      <c r="AG4">
+      <c r="AQ4">
         <v>0.1075</v>
       </c>
-      <c r="AH4">
+      <c r="AR4">
+        <v>-0.02693148335989953</v>
+      </c>
+      <c r="AS4">
+        <v>0.118272411680621</v>
+      </c>
+      <c r="AT4">
         <v>0.1319988990199734</v>
       </c>
-      <c r="AI4">
+      <c r="AU4">
         <v>0.204560421762222</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:47">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D5">
         <v>207</v>
@@ -1156,96 +1390,132 @@
         <v>0.05950336880945854</v>
       </c>
       <c r="I5">
+        <v>-0.05103539816859672</v>
+      </c>
+      <c r="J5">
+        <v>0.06775037401400737</v>
+      </c>
+      <c r="K5">
         <v>0.7482</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>0.9228</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>-0.02004830917874395</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>-0.06341673548373197</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>0.02278842149249139</v>
       </c>
-      <c r="N5">
+      <c r="P5">
+        <v>-0.07233878000738253</v>
+      </c>
+      <c r="Q5">
+        <v>0.03224216164989475</v>
+      </c>
+      <c r="R5">
         <v>0.3648</v>
       </c>
-      <c r="O5">
+      <c r="S5">
         <v>0.3648</v>
       </c>
-      <c r="P5">
+      <c r="T5">
         <v>-0.03574780648719517</v>
       </c>
-      <c r="Q5">
+      <c r="U5">
         <v>-0.08117500431921684</v>
       </c>
-      <c r="R5">
+      <c r="V5">
         <v>0.01103192398107171</v>
       </c>
-      <c r="S5">
+      <c r="W5">
+        <v>-0.09123869203614131</v>
+      </c>
+      <c r="X5">
+        <v>0.0222793709494871</v>
+      </c>
+      <c r="Y5">
         <v>0.1386</v>
       </c>
-      <c r="T5">
+      <c r="Z5">
         <v>0.2192</v>
       </c>
-      <c r="U5">
+      <c r="AA5">
         <v>-0.01000000000000012</v>
       </c>
-      <c r="V5">
+      <c r="AB5">
         <v>-0.09999999999999987</v>
       </c>
-      <c r="W5">
+      <c r="AC5">
         <v>0.05999999999999994</v>
       </c>
-      <c r="X5">
+      <c r="AD5">
+        <v>-0.1038971985921919</v>
+      </c>
+      <c r="AE5">
+        <v>0.08389719859219168</v>
+      </c>
+      <c r="AF5">
         <v>0.6612</v>
       </c>
-      <c r="Y5">
+      <c r="AG5">
         <v>0.7706</v>
       </c>
-      <c r="Z5">
+      <c r="AH5">
         <v>-0.03601433464716908</v>
       </c>
-      <c r="AA5">
+      <c r="AI5">
         <v>-0.08128862160672953</v>
       </c>
-      <c r="AB5">
+      <c r="AJ5">
         <v>0.01090263065652809</v>
       </c>
-      <c r="AC5">
+      <c r="AK5">
+        <v>-0.09115161458112336</v>
+      </c>
+      <c r="AL5">
+        <v>0.02135292562963592</v>
+      </c>
+      <c r="AM5">
         <v>0.1346</v>
       </c>
-      <c r="AD5">
+      <c r="AN5">
         <v>0.2062</v>
       </c>
-      <c r="AE5">
+      <c r="AO5">
         <v>0.06763285024154586</v>
       </c>
-      <c r="AF5">
+      <c r="AP5">
         <v>-0.004830917874396135</v>
       </c>
-      <c r="AG5">
+      <c r="AQ5">
         <v>0.1400966183574879</v>
       </c>
-      <c r="AH5">
+      <c r="AR5">
+        <v>-0.01932367149758452</v>
+      </c>
+      <c r="AS5">
+        <v>0.1594202898550724</v>
+      </c>
+      <c r="AT5">
         <v>0.08782509563019504</v>
       </c>
-      <c r="AI5">
+      <c r="AU5">
         <v>0.1756501912603901</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:47">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D6">
         <v>207</v>
@@ -1263,96 +1533,132 @@
         <v>0.07238411204395538</v>
       </c>
       <c r="I6">
+        <v>-0.06168545131060543</v>
+      </c>
+      <c r="J6">
+        <v>0.08651636918500157</v>
+      </c>
+      <c r="K6">
         <v>0.6962</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>0.9156</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <v>-0.06797101449275361</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>-0.1150446795079015</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>-0.01980502496348764</v>
       </c>
-      <c r="N6">
+      <c r="P6">
+        <v>-0.1263846722789996</v>
+      </c>
+      <c r="Q6">
+        <v>-0.009557356706507911</v>
+      </c>
+      <c r="R6">
         <v>0.0066</v>
       </c>
-      <c r="O6">
+      <c r="S6">
         <v>0.0182</v>
       </c>
-      <c r="P6">
+      <c r="T6">
         <v>-0.08480322843731886</v>
       </c>
-      <c r="Q6">
+      <c r="U6">
         <v>-0.1392818727626998</v>
       </c>
-      <c r="R6">
+      <c r="V6">
         <v>-0.02765282063164901</v>
       </c>
-      <c r="S6">
+      <c r="W6">
+        <v>-0.1509793143671761</v>
+      </c>
+      <c r="X6">
+        <v>-0.01141466056599736</v>
+      </c>
+      <c r="Y6">
         <v>0.004</v>
       </c>
-      <c r="T6">
+      <c r="Z6">
         <v>0.0112</v>
       </c>
-      <c r="U6">
+      <c r="AA6">
         <v>-0.06000000000000005</v>
       </c>
-      <c r="V6">
+      <c r="AB6">
         <v>-0.15</v>
       </c>
-      <c r="W6">
+      <c r="AC6">
         <v>-1.110223024625157E-16</v>
       </c>
-      <c r="X6">
+      <c r="AD6">
+        <v>-0.1500000000000001</v>
+      </c>
+      <c r="AE6">
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="AF6">
         <v>0.044</v>
       </c>
-      <c r="Y6">
+      <c r="AG6">
         <v>0.3118</v>
       </c>
-      <c r="Z6">
+      <c r="AH6">
         <v>-0.08522215543724965</v>
       </c>
-      <c r="AA6">
+      <c r="AI6">
         <v>-0.1400943073214456</v>
       </c>
-      <c r="AB6">
+      <c r="AJ6">
         <v>-0.02918989008947918</v>
       </c>
-      <c r="AC6">
+      <c r="AK6">
+        <v>-0.1511909993124804</v>
+      </c>
+      <c r="AL6">
+        <v>-0.01232031333021981</v>
+      </c>
+      <c r="AM6">
         <v>0.006</v>
       </c>
-      <c r="AD6">
+      <c r="AN6">
         <v>0.0176</v>
       </c>
-      <c r="AE6">
+      <c r="AO6">
         <v>0.111111111111111</v>
       </c>
-      <c r="AF6">
+      <c r="AP6">
         <v>0.03381642512077294</v>
       </c>
-      <c r="AG6">
+      <c r="AQ6">
         <v>0.1835748792270532</v>
       </c>
-      <c r="AH6">
+      <c r="AR6">
+        <v>0.01932367149758452</v>
+      </c>
+      <c r="AS6">
+        <v>0.2028985507246377</v>
+      </c>
+      <c r="AT6">
         <v>0.006357215082587968</v>
       </c>
-      <c r="AI6">
+      <c r="AU6">
         <v>0.0190716452477639</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:47">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D7">
         <v>207</v>
@@ -1370,96 +1676,132 @@
         <v>0.07049753251267667</v>
       </c>
       <c r="I7">
+        <v>-0.07685225067811854</v>
+      </c>
+      <c r="J7">
+        <v>0.08496819270710404</v>
+      </c>
+      <c r="K7">
         <v>0.9026</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>0.9228</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>-0.04792270531400966</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>-0.1024447384258064</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>0.005401149152844641</v>
       </c>
-      <c r="N7">
+      <c r="P7">
+        <v>-0.111707487254363</v>
+      </c>
+      <c r="Q7">
+        <v>0.01586207662634324</v>
+      </c>
+      <c r="R7">
         <v>0.0788</v>
       </c>
-      <c r="O7">
+      <c r="S7">
         <v>0.1346</v>
       </c>
-      <c r="P7">
+      <c r="T7">
         <v>-0.04905542195012369</v>
       </c>
-      <c r="Q7">
+      <c r="U7">
         <v>-0.1111569370207811</v>
       </c>
-      <c r="R7">
+      <c r="V7">
         <v>0.01275237325302565</v>
       </c>
-      <c r="S7">
+      <c r="W7">
+        <v>-0.1238415295689909</v>
+      </c>
+      <c r="X7">
+        <v>0.02673239532361265</v>
+      </c>
+      <c r="Y7">
         <v>0.1238</v>
       </c>
-      <c r="T7">
+      <c r="Z7">
         <v>0.2192</v>
       </c>
-      <c r="U7">
+      <c r="AA7">
         <v>-0.04999999999999993</v>
       </c>
-      <c r="V7">
+      <c r="AB7">
         <v>-0.1400000000000001</v>
       </c>
-      <c r="W7">
+      <c r="AC7">
         <v>0.02999999999999992</v>
       </c>
-      <c r="X7">
+      <c r="AD7">
+        <v>-0.1519260792971539</v>
+      </c>
+      <c r="AE7">
+        <v>0.05192607929715401</v>
+      </c>
+      <c r="AF7">
         <v>0.224</v>
       </c>
-      <c r="Y7">
+      <c r="AG7">
         <v>0.4476</v>
       </c>
-      <c r="Z7">
+      <c r="AH7">
         <v>-0.04920782079008057</v>
       </c>
-      <c r="AA7">
+      <c r="AI7">
         <v>-0.1114327077564691</v>
       </c>
-      <c r="AB7">
+      <c r="AJ7">
         <v>0.01244135367620838</v>
       </c>
-      <c r="AC7">
+      <c r="AK7">
+        <v>-0.1228604273873636</v>
+      </c>
+      <c r="AL7">
+        <v>0.02669462629634863</v>
+      </c>
+      <c r="AM7">
         <v>0.1184</v>
       </c>
-      <c r="AD7">
+      <c r="AN7">
         <v>0.2062</v>
       </c>
-      <c r="AE7">
+      <c r="AO7">
         <v>0.04347826086956519</v>
       </c>
-      <c r="AF7">
+      <c r="AP7">
         <v>-0.03381642512077294</v>
       </c>
-      <c r="AG7">
+      <c r="AQ7">
         <v>0.1159420289855072</v>
       </c>
-      <c r="AH7">
+      <c r="AR7">
+        <v>-0.04830917874396135</v>
+      </c>
+      <c r="AS7">
+        <v>0.1352657004830918</v>
+      </c>
+      <c r="AT7">
         <v>0.3134999455835852</v>
       </c>
-      <c r="AI7">
+      <c r="AU7">
         <v>0.3134999455835852</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:47">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>199</v>
@@ -1477,96 +1819,132 @@
         <v>0.03473953972963441</v>
       </c>
       <c r="I8">
+        <v>-0.0908680477437257</v>
+      </c>
+      <c r="J8">
+        <v>0.0425263392010121</v>
+      </c>
+      <c r="K8">
         <v>0.3916</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>0.4768</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>-0.004974874371859284</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>-0.05070529366418342</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>0.04187065486244625</v>
       </c>
-      <c r="N8">
+      <c r="P8">
+        <v>-0.06040181445148433</v>
+      </c>
+      <c r="Q8">
+        <v>0.05045206570776576</v>
+      </c>
+      <c r="R8">
         <v>0.8314</v>
       </c>
-      <c r="O8">
+      <c r="S8">
         <v>0.8314</v>
       </c>
-      <c r="P8">
+      <c r="T8">
         <v>0.005705599957307794</v>
       </c>
-      <c r="Q8">
+      <c r="U8">
         <v>-0.0437486940349788</v>
       </c>
-      <c r="R8">
+      <c r="V8">
         <v>0.05394448983572651</v>
       </c>
-      <c r="S8">
+      <c r="W8">
+        <v>-0.05453718467014974</v>
+      </c>
+      <c r="X8">
+        <v>0.06313045014530488</v>
+      </c>
+      <c r="Y8">
         <v>0.8202</v>
       </c>
-      <c r="T8">
+      <c r="Z8">
         <v>0.8202</v>
       </c>
-      <c r="U8">
+      <c r="AA8">
         <v>-0.01000000000000012</v>
       </c>
-      <c r="V8">
+      <c r="AB8">
         <v>-0.08000000000000018</v>
       </c>
-      <c r="W8">
+      <c r="AC8">
         <v>0.05999999999999994</v>
       </c>
-      <c r="X8">
+      <c r="AD8">
+        <v>-0.09925482790573971</v>
+      </c>
+      <c r="AE8">
+        <v>0.07925482790573947</v>
+      </c>
+      <c r="AF8">
         <v>0.6392</v>
       </c>
-      <c r="Y8">
+      <c r="AG8">
         <v>0.764</v>
       </c>
-      <c r="Z8">
+      <c r="AH8">
         <v>0.00759652222489704</v>
       </c>
-      <c r="AA8">
+      <c r="AI8">
         <v>-0.04136267558648257</v>
       </c>
-      <c r="AB8">
+      <c r="AJ8">
         <v>0.05592181985989171</v>
       </c>
-      <c r="AC8">
+      <c r="AK8">
+        <v>-0.05188362266759145</v>
+      </c>
+      <c r="AL8">
+        <v>0.06498731161172748</v>
+      </c>
+      <c r="AM8">
         <v>0.761</v>
       </c>
-      <c r="AD8">
+      <c r="AN8">
         <v>0.761</v>
       </c>
-      <c r="AE8">
+      <c r="AO8">
         <v>0</v>
       </c>
-      <c r="AF8">
+      <c r="AP8">
         <v>-0.07537688442211055</v>
       </c>
-      <c r="AG8">
+      <c r="AQ8">
         <v>0.07537688442211055</v>
       </c>
-      <c r="AH8">
+      <c r="AR8">
+        <v>-0.09547738693467334</v>
+      </c>
+      <c r="AS8">
+        <v>0.09045226130653261</v>
+      </c>
+      <c r="AT8">
         <v>1</v>
       </c>
-      <c r="AI8">
+      <c r="AU8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:47">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D9">
         <v>199</v>
@@ -1584,96 +1962,132 @@
         <v>0.005948065860233304</v>
       </c>
       <c r="I9">
+        <v>-0.1488692935139442</v>
+      </c>
+      <c r="J9">
+        <v>0.02153261009685876</v>
+      </c>
+      <c r="K9">
         <v>0.08019999999999999</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>0.1878</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>-0.0751256281407035</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>-0.1310229499051968</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>-0.02007745571459697</v>
       </c>
-      <c r="N9">
+      <c r="P9">
+        <v>-0.1420685129346101</v>
+      </c>
+      <c r="Q9">
+        <v>-0.008182743346796903</v>
+      </c>
+      <c r="R9">
         <v>0.008200000000000001</v>
       </c>
-      <c r="O9">
+      <c r="S9">
         <v>0.024</v>
       </c>
-      <c r="P9">
+      <c r="T9">
         <v>-0.08365754688833371</v>
       </c>
-      <c r="Q9">
+      <c r="U9">
         <v>-0.1420902483200672</v>
       </c>
-      <c r="R9">
+      <c r="V9">
         <v>-0.02184629191013983</v>
       </c>
-      <c r="S9">
+      <c r="W9">
+        <v>-0.1557722033973963</v>
+      </c>
+      <c r="X9">
+        <v>-0.008380156597759411</v>
+      </c>
+      <c r="Y9">
         <v>0.0086</v>
       </c>
-      <c r="T9">
+      <c r="Z9">
         <v>0.0188</v>
       </c>
-      <c r="U9">
+      <c r="AA9">
         <v>-0.05000000000000016</v>
       </c>
-      <c r="V9">
+      <c r="AB9">
         <v>-0.1199999999999999</v>
       </c>
-      <c r="W9">
+      <c r="AC9">
         <v>0.02000000000000002</v>
       </c>
-      <c r="X9">
+      <c r="AD9">
+        <v>-0.1364378623663957</v>
+      </c>
+      <c r="AE9">
+        <v>0.03643786236639536</v>
+      </c>
+      <c r="AF9">
         <v>0.1548</v>
       </c>
-      <c r="Y9">
+      <c r="AG9">
         <v>0.2654</v>
       </c>
-      <c r="Z9">
+      <c r="AH9">
         <v>-0.07762958337910586</v>
       </c>
-      <c r="AA9">
+      <c r="AI9">
         <v>-0.1370381777191461</v>
       </c>
-      <c r="AB9">
+      <c r="AJ9">
         <v>-0.01531069818067748</v>
       </c>
-      <c r="AC9">
+      <c r="AK9">
+        <v>-0.149432629305434</v>
+      </c>
+      <c r="AL9">
+        <v>-0.001071822703622774</v>
+      </c>
+      <c r="AM9">
         <v>0.0224</v>
       </c>
-      <c r="AD9">
+      <c r="AN9">
         <v>0.0424</v>
       </c>
-      <c r="AE9">
+      <c r="AO9">
         <v>0.05025125628140703</v>
       </c>
-      <c r="AF9">
+      <c r="AP9">
         <v>-0.03517587939698492</v>
       </c>
-      <c r="AG9">
+      <c r="AQ9">
         <v>0.135678391959799</v>
       </c>
-      <c r="AH9">
+      <c r="AR9">
+        <v>-0.05527638190954776</v>
+      </c>
+      <c r="AS9">
+        <v>0.1457286432160805</v>
+      </c>
+      <c r="AT9">
         <v>0.3018984444285246</v>
       </c>
-      <c r="AI9">
+      <c r="AU9">
         <v>0.6037968888570493</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:47">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D10">
         <v>199</v>
@@ -1691,84 +2105,120 @@
         <v>0.03372151397468764</v>
       </c>
       <c r="I10">
+        <v>-0.1270242150164059</v>
+      </c>
+      <c r="J10">
+        <v>0.04802924014203403</v>
+      </c>
+      <c r="K10">
         <v>0.2944</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>0.4768</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>-0.07015075376884422</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>-0.1301497201187742</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>-0.01301543821783446</v>
       </c>
-      <c r="N10">
+      <c r="P10">
+        <v>-0.1390395629729493</v>
+      </c>
+      <c r="Q10">
+        <v>-0.001261944564739118</v>
+      </c>
+      <c r="R10">
         <v>0.0186</v>
       </c>
-      <c r="O10">
+      <c r="S10">
         <v>0.0348</v>
       </c>
-      <c r="P10">
+      <c r="T10">
         <v>-0.08936314684564151</v>
       </c>
-      <c r="Q10">
+      <c r="U10">
         <v>-0.1519342158815156</v>
       </c>
-      <c r="R10">
+      <c r="V10">
         <v>-0.02445697967964856</v>
       </c>
-      <c r="S10">
+      <c r="W10">
+        <v>-0.1647937957865656</v>
+      </c>
+      <c r="X10">
+        <v>-0.009124463780871214</v>
+      </c>
+      <c r="Y10">
         <v>0.008999999999999999</v>
       </c>
-      <c r="T10">
+      <c r="Z10">
         <v>0.0188</v>
       </c>
-      <c r="U10">
+      <c r="AA10">
         <v>-0.04000000000000004</v>
       </c>
-      <c r="V10">
+      <c r="AB10">
         <v>-0.1000000000000003</v>
       </c>
-      <c r="W10">
+      <c r="AC10">
         <v>0.0399999999999997</v>
       </c>
-      <c r="X10">
+      <c r="AD10">
+        <v>-0.13</v>
+      </c>
+      <c r="AE10">
+        <v>0.04999999999999993</v>
+      </c>
+      <c r="AF10">
         <v>0.3536</v>
       </c>
-      <c r="Y10">
+      <c r="AG10">
         <v>0.4588</v>
       </c>
-      <c r="Z10">
+      <c r="AH10">
         <v>-0.0852261056040029</v>
       </c>
-      <c r="AA10">
+      <c r="AI10">
         <v>-0.1485120228288059</v>
       </c>
-      <c r="AB10">
+      <c r="AJ10">
         <v>-0.01921195482153516</v>
       </c>
-      <c r="AC10">
+      <c r="AK10">
+        <v>-0.1609806360778065</v>
+      </c>
+      <c r="AL10">
+        <v>-0.003463348309243171</v>
+      </c>
+      <c r="AM10">
         <v>0.0134</v>
       </c>
-      <c r="AD10">
+      <c r="AN10">
         <v>0.0322</v>
       </c>
-      <c r="AE10">
+      <c r="AO10">
         <v>0.05025125628140703</v>
       </c>
-      <c r="AF10">
+      <c r="AP10">
         <v>-0.04020100502512563</v>
       </c>
-      <c r="AG10">
+      <c r="AQ10">
         <v>0.135678391959799</v>
       </c>
-      <c r="AH10">
+      <c r="AR10">
+        <v>-0.05527638190954776</v>
+      </c>
+      <c r="AS10">
+        <v>0.1507537688442211</v>
+      </c>
+      <c r="AT10">
         <v>0.3018984444285246</v>
       </c>
-      <c r="AI10">
+      <c r="AU10">
         <v>0.6037968888570493</v>
       </c>
     </row>
@@ -1779,7 +2229,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1788,98 +2238,122 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1897,42 +2371,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E1" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F1" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="G1" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="H1" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="I1" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D2">
         <v>0.02049261083743843</v>
@@ -1950,18 +2424,18 @@
         <v>250</v>
       </c>
       <c r="I2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D3">
         <v>0.02807881773399015</v>
@@ -1979,18 +2453,18 @@
         <v>250</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D4">
         <v>0.04536945812807881</v>
@@ -2008,18 +2482,18 @@
         <v>250</v>
       </c>
       <c r="I4" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D5">
         <v>0.4010837438423646</v>
@@ -2037,18 +2511,18 @@
         <v>250</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D6">
         <v>0.413743842364532</v>
@@ -2066,18 +2540,18 @@
         <v>250</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D7">
         <v>0.4725615763546798</v>
@@ -2095,18 +2569,18 @@
         <v>250</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D8">
         <v>0.503346436828533</v>
@@ -2124,18 +2598,18 @@
         <v>250</v>
       </c>
       <c r="I8" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D9">
         <v>0.5190271308530763</v>
@@ -2153,18 +2627,18 @@
         <v>250</v>
       </c>
       <c r="I9" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D10">
         <v>0.5875820873372553</v>
@@ -2182,18 +2656,18 @@
         <v>250</v>
       </c>
       <c r="I10" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D11">
         <v>0.34</v>
@@ -2211,18 +2685,18 @@
         <v>250</v>
       </c>
       <c r="I11" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D12">
         <v>0.3500000000000001</v>
@@ -2240,18 +2714,18 @@
         <v>250</v>
       </c>
       <c r="I12" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D13">
         <v>0.3999999999999999</v>
@@ -2269,18 +2743,18 @@
         <v>250</v>
       </c>
       <c r="I13" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D14">
         <v>0.5035496260262651</v>
@@ -2298,18 +2772,18 @@
         <v>250</v>
       </c>
       <c r="I14" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D15">
         <v>0.5189064985777815</v>
@@ -2327,18 +2801,18 @@
         <v>250</v>
       </c>
       <c r="I15" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D16">
         <v>0.5865506926221365</v>
@@ -2356,18 +2830,18 @@
         <v>250</v>
       </c>
       <c r="I16" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D17">
         <v>0.6921182266009852</v>
@@ -2385,18 +2859,18 @@
         <v>250</v>
       </c>
       <c r="I17" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D18">
         <v>0.6576354679802956</v>
@@ -2414,18 +2888,18 @@
         <v>250</v>
       </c>
       <c r="I18" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D19">
         <v>0.6108374384236454</v>
@@ -2443,18 +2917,18 @@
         <v>250</v>
       </c>
       <c r="I19" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D20">
         <v>0.01473429951690822</v>
@@ -2472,18 +2946,18 @@
         <v>207</v>
       </c>
       <c r="I20" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D21">
         <v>0.006376811594202901</v>
@@ -2501,18 +2975,18 @@
         <v>207</v>
       </c>
       <c r="I21" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D22">
         <v>0.002318840579710145</v>
@@ -2530,18 +3004,18 @@
         <v>207</v>
       </c>
       <c r="I22" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D23">
         <v>0.4014975845410628</v>
@@ -2559,18 +3033,18 @@
         <v>207</v>
       </c>
       <c r="I23" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D24">
         <v>0.4215458937198068</v>
@@ -2588,18 +3062,18 @@
         <v>207</v>
       </c>
       <c r="I24" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D25">
         <v>0.4694685990338164</v>
@@ -2617,18 +3091,18 @@
         <v>207</v>
       </c>
       <c r="I25" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D26">
         <v>0.4993498188103143</v>
@@ -2646,18 +3120,18 @@
         <v>207</v>
       </c>
       <c r="I26" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D27">
         <v>0.5350976252975095</v>
@@ -2675,18 +3149,18 @@
         <v>207</v>
       </c>
       <c r="I27" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D28">
         <v>0.5841530472476332</v>
@@ -2704,18 +3178,18 @@
         <v>207</v>
       </c>
       <c r="I28" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D29">
         <v>0.3599999999999999</v>
@@ -2733,18 +3207,18 @@
         <v>207</v>
       </c>
       <c r="I29" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D30">
         <v>0.37</v>
@@ -2762,18 +3236,18 @@
         <v>207</v>
       </c>
       <c r="I30" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D31">
         <v>0.4199999999999999</v>
@@ -2791,18 +3265,18 @@
         <v>207</v>
       </c>
       <c r="I31" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D32">
         <v>0.5003424089040717</v>
@@ -2820,18 +3294,18 @@
         <v>207</v>
       </c>
       <c r="I32" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D33">
         <v>0.5363567435512407</v>
@@ -2849,18 +3323,18 @@
         <v>207</v>
       </c>
       <c r="I33" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D34">
         <v>0.5855645643413213</v>
@@ -2878,18 +3352,18 @@
         <v>207</v>
       </c>
       <c r="I34" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D35">
         <v>0.714975845410628</v>
@@ -2907,18 +3381,18 @@
         <v>207</v>
       </c>
       <c r="I35" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D36">
         <v>0.6473429951690821</v>
@@ -2936,18 +3410,18 @@
         <v>207</v>
       </c>
       <c r="I36" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D37">
         <v>0.6038647342995169</v>
@@ -2965,18 +3439,18 @@
         <v>207</v>
       </c>
       <c r="I37" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D38">
         <v>0.02648241206030149</v>
@@ -2994,18 +3468,18 @@
         <v>199</v>
       </c>
       <c r="I38" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D39">
         <v>0.05065326633165827</v>
@@ -3023,18 +3497,18 @@
         <v>199</v>
       </c>
       <c r="I39" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D40">
         <v>0.09015075376884421</v>
@@ -3052,18 +3526,18 @@
         <v>199</v>
       </c>
       <c r="I40" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D41">
         <v>0.4006532663316583</v>
@@ -3081,18 +3555,18 @@
         <v>199</v>
       </c>
       <c r="I41" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D42">
         <v>0.4056281407035176</v>
@@ -3110,18 +3584,18 @@
         <v>199</v>
       </c>
       <c r="I42" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D43">
         <v>0.4757788944723618</v>
@@ -3139,18 +3613,18 @@
         <v>199</v>
       </c>
       <c r="I43" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D44">
         <v>0.5074703248991672</v>
@@ -3168,18 +3642,18 @@
         <v>199</v>
       </c>
       <c r="I44" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D45">
         <v>0.5017647249418594</v>
@@ -3197,18 +3671,18 @@
         <v>199</v>
       </c>
       <c r="I45" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D46">
         <v>0.5911278717875009</v>
@@ -3226,18 +3700,18 @@
         <v>199</v>
       </c>
       <c r="I46" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D47">
         <v>0.34</v>
@@ -3255,18 +3729,18 @@
         <v>199</v>
       </c>
       <c r="I47" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C48" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D48">
         <v>0.3500000000000001</v>
@@ -3284,18 +3758,18 @@
         <v>199</v>
       </c>
       <c r="I48" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D49">
         <v>0.3900000000000001</v>
@@ -3313,18 +3787,18 @@
         <v>199</v>
       </c>
       <c r="I49" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D50">
         <v>0.5080569923909963</v>
@@ -3342,18 +3816,18 @@
         <v>199</v>
       </c>
       <c r="I50" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C51" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D51">
         <v>0.5004604701660993</v>
@@ -3371,18 +3845,18 @@
         <v>199</v>
       </c>
       <c r="I51" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D52">
         <v>0.5856865757701022</v>
@@ -3400,18 +3874,18 @@
         <v>199</v>
       </c>
       <c r="I52" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C53" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D53">
         <v>0.6683417085427136</v>
@@ -3429,18 +3903,18 @@
         <v>199</v>
       </c>
       <c r="I53" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C54" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D54">
         <v>0.6683417085427136</v>
@@ -3458,18 +3932,18 @@
         <v>199</v>
       </c>
       <c r="I54" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C55" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D55">
         <v>0.6180904522613065</v>
@@ -3487,7 +3961,7 @@
         <v>199</v>
       </c>
       <c r="I55" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3497,68 +3971,85 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="14" width="18.7109375" customWidth="1"/>
+    <col min="1" max="12" width="18.7109375" customWidth="1"/>
+    <col min="13" max="13" width="36.7109375" customWidth="1"/>
+    <col min="14" max="14" width="18.7109375" customWidth="1"/>
+    <col min="15" max="15" width="36.7109375" customWidth="1"/>
+    <col min="16" max="17" width="18.7109375" customWidth="1"/>
+    <col min="18" max="18" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D1" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="E1" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F1" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="G1" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H1" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="I1" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="J1" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="K1" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L1" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="M1" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="N1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>107</v>
+      </c>
+      <c r="O1" t="s">
+        <v>108</v>
+      </c>
+      <c r="P1" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>110</v>
+      </c>
+      <c r="R1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E2">
         <v>0.02049261083743843</v>
@@ -3585,24 +4076,36 @@
         <v>1.530907631213612</v>
       </c>
       <c r="M2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="N2">
         <v>0.7454</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>115</v>
+      </c>
+      <c r="P2">
+        <v>-0.05410272103966409</v>
+      </c>
+      <c r="Q2">
+        <v>0.03893030724656065</v>
+      </c>
+      <c r="R2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E3">
         <v>0.4010837438423646</v>
@@ -3629,24 +4132,36 @@
         <v>1.455610834346575</v>
       </c>
       <c r="M3" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="N3">
         <v>0.461</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>115</v>
+      </c>
+      <c r="P3">
+        <v>-0.05229618964656452</v>
+      </c>
+      <c r="Q3">
+        <v>0.02697599260222911</v>
+      </c>
+      <c r="R3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E4">
         <v>0.503346436828533</v>
@@ -3673,24 +4188,36 @@
         <v>1.525496624127441</v>
       </c>
       <c r="M4" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="N4">
         <v>0.3852</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>115</v>
+      </c>
+      <c r="P4">
+        <v>-0.05856576544801697</v>
+      </c>
+      <c r="Q4">
+        <v>0.02781683152088908</v>
+      </c>
+      <c r="R4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E5">
         <v>0.34</v>
@@ -3711,24 +4238,36 @@
         <v>0.6112</v>
       </c>
       <c r="M5" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N5">
         <v>0.7282</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>115</v>
+      </c>
+      <c r="P5">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="Q5">
+        <v>0.05999999999999983</v>
+      </c>
+      <c r="R5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E6">
         <v>0.5035496260262651</v>
@@ -3749,24 +4288,36 @@
         <v>0.3894</v>
       </c>
       <c r="M6" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N6">
         <v>0.3894</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>115</v>
+      </c>
+      <c r="P6">
+        <v>-0.05815433485882701</v>
+      </c>
+      <c r="Q6">
+        <v>0.02825025172545625</v>
+      </c>
+      <c r="R6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E7">
         <v>0.6921182266009852</v>
@@ -3793,24 +4344,36 @@
         <v>1.575352047426485</v>
       </c>
       <c r="M7" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="N7">
         <v>0.204560421762222</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>116</v>
+      </c>
+      <c r="P7">
+        <v>-0.03189014549308666</v>
+      </c>
+      <c r="Q7">
+        <v>0.09762516046213096</v>
+      </c>
+      <c r="R7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E8">
         <v>0.02049261083743843</v>
@@ -3837,24 +4400,36 @@
         <v>1.496102394400772</v>
       </c>
       <c r="M8" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="N8">
         <v>0.5734</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>115</v>
+      </c>
+      <c r="P8">
+        <v>-0.08440726271056506</v>
+      </c>
+      <c r="Q8">
+        <v>0.03465356812928424</v>
+      </c>
+      <c r="R8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E9">
         <v>0.4010837438423646</v>
@@ -3881,24 +4456,36 @@
         <v>1.553586372596406</v>
       </c>
       <c r="M9" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="N9">
         <v>0.0004</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>115</v>
+      </c>
+      <c r="P9">
+        <v>-0.1160939316204946</v>
+      </c>
+      <c r="Q9">
+        <v>-0.02686173340413656</v>
+      </c>
+      <c r="R9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E10">
         <v>0.503346436828533</v>
@@ -3925,24 +4512,36 @@
         <v>1.581607874494274</v>
       </c>
       <c r="M10" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="N10">
         <v>0.0008</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>115</v>
+      </c>
+      <c r="P10">
+        <v>-0.1343146850892964</v>
+      </c>
+      <c r="Q10">
+        <v>-0.03239054644227161</v>
+      </c>
+      <c r="R10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E11">
         <v>0.34</v>
@@ -3963,24 +4562,36 @@
         <v>0.028</v>
       </c>
       <c r="M11" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N11">
         <v>0.09279999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>115</v>
+      </c>
+      <c r="P11">
+        <v>-0.1280741611297381</v>
+      </c>
+      <c r="Q11">
+        <v>0.008074161129738217</v>
+      </c>
+      <c r="R11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E12">
         <v>0.5035496260262651</v>
@@ -4001,24 +4612,36 @@
         <v>0.0005999999999999999</v>
       </c>
       <c r="M12" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N12">
         <v>0.0008</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>115</v>
+      </c>
+      <c r="P12">
+        <v>-0.1324121069898527</v>
+      </c>
+      <c r="Q12">
+        <v>-0.03081160526701519</v>
+      </c>
+      <c r="R12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E13">
         <v>0.6921182266009852</v>
@@ -4045,24 +4668,36 @@
         <v>1.535849843792607</v>
       </c>
       <c r="M13" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="N13">
         <v>0.02059161466558826</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>116</v>
+      </c>
+      <c r="P13">
+        <v>0.009991271820448863</v>
+      </c>
+      <c r="Q13">
+        <v>0.152573275862069</v>
+      </c>
+      <c r="R13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E14">
         <v>0.02807881773399015</v>
@@ -4089,24 +4724,36 @@
         <v>1.422466582636034</v>
       </c>
       <c r="M14" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="N14">
         <v>0.7454</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>115</v>
+      </c>
+      <c r="P14">
+        <v>-0.08180644473769279</v>
+      </c>
+      <c r="Q14">
+        <v>0.04722516394951541</v>
+      </c>
+      <c r="R14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E15">
         <v>0.413743842364532</v>
@@ -4133,24 +4780,36 @@
         <v>1.419611895158891</v>
       </c>
       <c r="M15" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="N15">
         <v>0.0104</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15">
+        <v>-0.1084139624854691</v>
+      </c>
+      <c r="Q15">
+        <v>-0.009221505494826733</v>
+      </c>
+      <c r="R15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E16">
         <v>0.5190271308530763</v>
@@ -4177,24 +4836,36 @@
         <v>1.504729680828269</v>
       </c>
       <c r="M16" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="N16">
         <v>0.0052</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16">
+        <v>-0.1237607966652773</v>
+      </c>
+      <c r="Q16">
+        <v>-0.01197481543232409</v>
+      </c>
+      <c r="R16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E17">
         <v>0.3500000000000001</v>
@@ -4215,24 +4886,36 @@
         <v>0.1748</v>
       </c>
       <c r="M17" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N17">
         <v>0.2226</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" t="s">
+        <v>115</v>
+      </c>
+      <c r="P17">
+        <v>-0.1230166690346133</v>
+      </c>
+      <c r="Q17">
+        <v>0.02301666903461366</v>
+      </c>
+      <c r="R17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E18">
         <v>0.5189064985777815</v>
@@ -4253,24 +4936,36 @@
         <v>0.005</v>
       </c>
       <c r="M18" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N18">
         <v>0.008399999999999999</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" t="s">
+        <v>115</v>
+      </c>
+      <c r="P18">
+        <v>-0.1227389787054996</v>
+      </c>
+      <c r="Q18">
+        <v>-0.009991811914109265</v>
+      </c>
+      <c r="R18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E19">
         <v>0.6576354679802956</v>
@@ -4297,24 +4992,36 @@
         <v>1.42473165658859</v>
       </c>
       <c r="M19" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="N19">
         <v>0.204560421762222</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19" t="s">
+        <v>116</v>
+      </c>
+      <c r="P19">
+        <v>-0.02693148335989953</v>
+      </c>
+      <c r="Q19">
+        <v>0.118272411680621</v>
+      </c>
+      <c r="R19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E20">
         <v>0.01473429951690822</v>
@@ -4335,24 +5042,36 @@
         <v>0.7482</v>
       </c>
       <c r="M20" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N20">
         <v>0.9228</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" t="s">
+        <v>115</v>
+      </c>
+      <c r="P20">
+        <v>-0.05103539816859672</v>
+      </c>
+      <c r="Q20">
+        <v>0.06775037401400737</v>
+      </c>
+      <c r="R20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E21">
         <v>0.4014975845410628</v>
@@ -4373,24 +5092,36 @@
         <v>0.3648</v>
       </c>
       <c r="M21" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N21">
         <v>0.3648</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21" t="s">
+        <v>115</v>
+      </c>
+      <c r="P21">
+        <v>-0.07233878000738253</v>
+      </c>
+      <c r="Q21">
+        <v>0.03224216164989475</v>
+      </c>
+      <c r="R21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E22">
         <v>0.4993498188103143</v>
@@ -4411,24 +5142,36 @@
         <v>0.1386</v>
       </c>
       <c r="M22" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N22">
         <v>0.2192</v>
       </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22" t="s">
+        <v>115</v>
+      </c>
+      <c r="P22">
+        <v>-0.09123869203614131</v>
+      </c>
+      <c r="Q22">
+        <v>0.0222793709494871</v>
+      </c>
+      <c r="R22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E23">
         <v>0.3599999999999999</v>
@@ -4449,24 +5192,36 @@
         <v>0.6612</v>
       </c>
       <c r="M23" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="N23">
         <v>0.7706</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23" t="s">
+        <v>115</v>
+      </c>
+      <c r="P23">
+        <v>-0.1038971985921919</v>
+      </c>
+      <c r="Q23">
+        <v>0.08389719859219168</v>
+      </c>
+      <c r="R23" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E24">
         <v>0.5003424089040717</v>
@@ -4487,24 +5242,36 @@
         <v>0.1346</v>
       </c>
       <c r="M24" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N24">
         <v>0.2062</v>
       </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24" t="s">
+        <v>115</v>
+      </c>
+      <c r="P24">
+        <v>-0.09115161458112336</v>
+      </c>
+      <c r="Q24">
+        <v>0.02135292562963592</v>
+      </c>
+      <c r="R24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E25">
         <v>0.714975845410628</v>
@@ -4525,24 +5292,36 @@
         <v>0.08782509563019504</v>
       </c>
       <c r="M25" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="N25">
         <v>0.1756501912603901</v>
       </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25" t="s">
+        <v>116</v>
+      </c>
+      <c r="P25">
+        <v>-0.01932367149758452</v>
+      </c>
+      <c r="Q25">
+        <v>0.1594202898550724</v>
+      </c>
+      <c r="R25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E26">
         <v>0.01473429951690822</v>
@@ -4563,24 +5342,36 @@
         <v>0.6962</v>
       </c>
       <c r="M26" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N26">
         <v>0.9156</v>
       </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26" t="s">
+        <v>115</v>
+      </c>
+      <c r="P26">
+        <v>-0.06168545131060543</v>
+      </c>
+      <c r="Q26">
+        <v>0.08651636918500157</v>
+      </c>
+      <c r="R26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E27">
         <v>0.4014975845410628</v>
@@ -4601,24 +5392,36 @@
         <v>0.0066</v>
       </c>
       <c r="M27" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N27">
         <v>0.0182</v>
       </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27" t="s">
+        <v>115</v>
+      </c>
+      <c r="P27">
+        <v>-0.1263846722789996</v>
+      </c>
+      <c r="Q27">
+        <v>-0.009557356706507911</v>
+      </c>
+      <c r="R27" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E28">
         <v>0.4993498188103143</v>
@@ -4639,24 +5442,36 @@
         <v>0.004</v>
       </c>
       <c r="M28" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N28">
         <v>0.0112</v>
       </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28" t="s">
+        <v>115</v>
+      </c>
+      <c r="P28">
+        <v>-0.1509793143671761</v>
+      </c>
+      <c r="Q28">
+        <v>-0.01141466056599736</v>
+      </c>
+      <c r="R28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E29">
         <v>0.3599999999999999</v>
@@ -4677,24 +5492,36 @@
         <v>0.044</v>
       </c>
       <c r="M29" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="N29">
         <v>0.3118</v>
       </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29" t="s">
+        <v>115</v>
+      </c>
+      <c r="P29">
+        <v>-0.1500000000000001</v>
+      </c>
+      <c r="Q29">
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="R29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E30">
         <v>0.5003424089040717</v>
@@ -4715,24 +5542,36 @@
         <v>0.006</v>
       </c>
       <c r="M30" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N30">
         <v>0.0176</v>
       </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="O30" t="s">
+        <v>115</v>
+      </c>
+      <c r="P30">
+        <v>-0.1511909993124804</v>
+      </c>
+      <c r="Q30">
+        <v>-0.01232031333021981</v>
+      </c>
+      <c r="R30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E31">
         <v>0.714975845410628</v>
@@ -4753,24 +5592,36 @@
         <v>0.006357215082587968</v>
       </c>
       <c r="M31" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="N31">
         <v>0.0190716452477639</v>
       </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="O31" t="s">
+        <v>116</v>
+      </c>
+      <c r="P31">
+        <v>0.01932367149758452</v>
+      </c>
+      <c r="Q31">
+        <v>0.2028985507246377</v>
+      </c>
+      <c r="R31" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E32">
         <v>0.006376811594202901</v>
@@ -4791,24 +5642,36 @@
         <v>0.9026</v>
       </c>
       <c r="M32" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N32">
         <v>0.9228</v>
       </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32" t="s">
+        <v>115</v>
+      </c>
+      <c r="P32">
+        <v>-0.07685225067811854</v>
+      </c>
+      <c r="Q32">
+        <v>0.08496819270710404</v>
+      </c>
+      <c r="R32" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E33">
         <v>0.4215458937198068</v>
@@ -4829,24 +5692,36 @@
         <v>0.0788</v>
       </c>
       <c r="M33" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N33">
         <v>0.1346</v>
       </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33" t="s">
+        <v>115</v>
+      </c>
+      <c r="P33">
+        <v>-0.111707487254363</v>
+      </c>
+      <c r="Q33">
+        <v>0.01586207662634324</v>
+      </c>
+      <c r="R33" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E34">
         <v>0.5350976252975095</v>
@@ -4867,24 +5742,36 @@
         <v>0.1238</v>
       </c>
       <c r="M34" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N34">
         <v>0.2192</v>
       </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="O34" t="s">
+        <v>115</v>
+      </c>
+      <c r="P34">
+        <v>-0.1238415295689909</v>
+      </c>
+      <c r="Q34">
+        <v>0.02673239532361265</v>
+      </c>
+      <c r="R34" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E35">
         <v>0.37</v>
@@ -4905,24 +5792,36 @@
         <v>0.224</v>
       </c>
       <c r="M35" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="N35">
         <v>0.4476</v>
       </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="O35" t="s">
+        <v>115</v>
+      </c>
+      <c r="P35">
+        <v>-0.1519260792971539</v>
+      </c>
+      <c r="Q35">
+        <v>0.05192607929715401</v>
+      </c>
+      <c r="R35" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D36" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E36">
         <v>0.5363567435512407</v>
@@ -4943,24 +5842,36 @@
         <v>0.1184</v>
       </c>
       <c r="M36" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N36">
         <v>0.2062</v>
       </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="O36" t="s">
+        <v>115</v>
+      </c>
+      <c r="P36">
+        <v>-0.1228604273873636</v>
+      </c>
+      <c r="Q36">
+        <v>0.02669462629634863</v>
+      </c>
+      <c r="R36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D37" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E37">
         <v>0.6473429951690821</v>
@@ -4981,24 +5892,36 @@
         <v>0.3134999455835852</v>
       </c>
       <c r="M37" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="N37">
         <v>0.3134999455835852</v>
       </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="O37" t="s">
+        <v>116</v>
+      </c>
+      <c r="P37">
+        <v>-0.04830917874396135</v>
+      </c>
+      <c r="Q37">
+        <v>0.1352657004830918</v>
+      </c>
+      <c r="R37" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D38" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E38">
         <v>0.02648241206030149</v>
@@ -5019,24 +5942,36 @@
         <v>0.3916</v>
       </c>
       <c r="M38" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N38">
         <v>0.4768</v>
       </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="O38" t="s">
+        <v>115</v>
+      </c>
+      <c r="P38">
+        <v>-0.0908680477437257</v>
+      </c>
+      <c r="Q38">
+        <v>0.0425263392010121</v>
+      </c>
+      <c r="R38" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C39" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D39" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E39">
         <v>0.4006532663316583</v>
@@ -5057,24 +5992,36 @@
         <v>0.8314</v>
       </c>
       <c r="M39" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N39">
         <v>0.8314</v>
       </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="O39" t="s">
+        <v>115</v>
+      </c>
+      <c r="P39">
+        <v>-0.06040181445148433</v>
+      </c>
+      <c r="Q39">
+        <v>0.05045206570776576</v>
+      </c>
+      <c r="R39" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C40" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D40" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E40">
         <v>0.5074703248991672</v>
@@ -5095,24 +6042,36 @@
         <v>0.8202</v>
       </c>
       <c r="M40" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N40">
         <v>0.8202</v>
       </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40" t="s">
+        <v>115</v>
+      </c>
+      <c r="P40">
+        <v>-0.05453718467014974</v>
+      </c>
+      <c r="Q40">
+        <v>0.06313045014530488</v>
+      </c>
+      <c r="R40" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E41">
         <v>0.34</v>
@@ -5133,24 +6092,36 @@
         <v>0.6392</v>
       </c>
       <c r="M41" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="N41">
         <v>0.764</v>
       </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41" t="s">
+        <v>115</v>
+      </c>
+      <c r="P41">
+        <v>-0.09925482790573971</v>
+      </c>
+      <c r="Q41">
+        <v>0.07925482790573947</v>
+      </c>
+      <c r="R41" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E42">
         <v>0.5080569923909963</v>
@@ -5171,24 +6142,36 @@
         <v>0.761</v>
       </c>
       <c r="M42" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N42">
         <v>0.761</v>
       </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="O42" t="s">
+        <v>115</v>
+      </c>
+      <c r="P42">
+        <v>-0.05188362266759145</v>
+      </c>
+      <c r="Q42">
+        <v>0.06498731161172748</v>
+      </c>
+      <c r="R42" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E43">
         <v>0.6683417085427136</v>
@@ -5209,24 +6192,36 @@
         <v>1</v>
       </c>
       <c r="M43" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="N43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="O43" t="s">
+        <v>116</v>
+      </c>
+      <c r="P43">
+        <v>-0.09547738693467334</v>
+      </c>
+      <c r="Q43">
+        <v>0.09045226130653261</v>
+      </c>
+      <c r="R43" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E44">
         <v>0.02648241206030149</v>
@@ -5247,24 +6242,36 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="M44" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N44">
         <v>0.1878</v>
       </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="O44" t="s">
+        <v>115</v>
+      </c>
+      <c r="P44">
+        <v>-0.1488692935139442</v>
+      </c>
+      <c r="Q44">
+        <v>0.02153261009685876</v>
+      </c>
+      <c r="R44" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C45" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E45">
         <v>0.4006532663316583</v>
@@ -5285,24 +6292,36 @@
         <v>0.008200000000000001</v>
       </c>
       <c r="M45" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N45">
         <v>0.024</v>
       </c>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="O45" t="s">
+        <v>115</v>
+      </c>
+      <c r="P45">
+        <v>-0.1420685129346101</v>
+      </c>
+      <c r="Q45">
+        <v>-0.008182743346796903</v>
+      </c>
+      <c r="R45" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C46" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E46">
         <v>0.5074703248991672</v>
@@ -5323,24 +6342,36 @@
         <v>0.0086</v>
       </c>
       <c r="M46" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N46">
         <v>0.0188</v>
       </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46" t="s">
+        <v>115</v>
+      </c>
+      <c r="P46">
+        <v>-0.1557722033973963</v>
+      </c>
+      <c r="Q46">
+        <v>-0.008380156597759411</v>
+      </c>
+      <c r="R46" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E47">
         <v>0.34</v>
@@ -5361,24 +6392,36 @@
         <v>0.1548</v>
       </c>
       <c r="M47" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="N47">
         <v>0.2654</v>
       </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47" t="s">
+        <v>115</v>
+      </c>
+      <c r="P47">
+        <v>-0.1364378623663957</v>
+      </c>
+      <c r="Q47">
+        <v>0.03643786236639536</v>
+      </c>
+      <c r="R47" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C48" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E48">
         <v>0.5080569923909963</v>
@@ -5399,24 +6442,36 @@
         <v>0.0224</v>
       </c>
       <c r="M48" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N48">
         <v>0.0424</v>
       </c>
-    </row>
-    <row r="49" spans="1:14">
+      <c r="O48" t="s">
+        <v>115</v>
+      </c>
+      <c r="P48">
+        <v>-0.149432629305434</v>
+      </c>
+      <c r="Q48">
+        <v>-0.001071822703622774</v>
+      </c>
+      <c r="R48" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C49" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D49" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E49">
         <v>0.6683417085427136</v>
@@ -5437,24 +6492,36 @@
         <v>0.3018984444285246</v>
       </c>
       <c r="M49" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="N49">
         <v>0.6037968888570493</v>
       </c>
-    </row>
-    <row r="50" spans="1:14">
+      <c r="O49" t="s">
+        <v>116</v>
+      </c>
+      <c r="P49">
+        <v>-0.05527638190954776</v>
+      </c>
+      <c r="Q49">
+        <v>0.1457286432160805</v>
+      </c>
+      <c r="R49" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C50" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D50" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E50">
         <v>0.05065326633165827</v>
@@ -5475,24 +6542,36 @@
         <v>0.2944</v>
       </c>
       <c r="M50" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N50">
         <v>0.4768</v>
       </c>
-    </row>
-    <row r="51" spans="1:14">
+      <c r="O50" t="s">
+        <v>115</v>
+      </c>
+      <c r="P50">
+        <v>-0.1270242150164059</v>
+      </c>
+      <c r="Q50">
+        <v>0.04802924014203403</v>
+      </c>
+      <c r="R50" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C51" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D51" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E51">
         <v>0.4056281407035176</v>
@@ -5513,24 +6592,36 @@
         <v>0.0186</v>
       </c>
       <c r="M51" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N51">
         <v>0.0348</v>
       </c>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="O51" t="s">
+        <v>115</v>
+      </c>
+      <c r="P51">
+        <v>-0.1390395629729493</v>
+      </c>
+      <c r="Q51">
+        <v>-0.001261944564739118</v>
+      </c>
+      <c r="R51" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C52" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D52" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E52">
         <v>0.5017647249418594</v>
@@ -5551,24 +6642,36 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="M52" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N52">
         <v>0.0188</v>
       </c>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="O52" t="s">
+        <v>115</v>
+      </c>
+      <c r="P52">
+        <v>-0.1647937957865656</v>
+      </c>
+      <c r="Q52">
+        <v>-0.009124463780871214</v>
+      </c>
+      <c r="R52" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C53" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D53" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E53">
         <v>0.3500000000000001</v>
@@ -5589,24 +6692,36 @@
         <v>0.3536</v>
       </c>
       <c r="M53" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="N53">
         <v>0.4588</v>
       </c>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="O53" t="s">
+        <v>115</v>
+      </c>
+      <c r="P53">
+        <v>-0.13</v>
+      </c>
+      <c r="Q53">
+        <v>0.04999999999999993</v>
+      </c>
+      <c r="R53" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C54" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D54" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E54">
         <v>0.5004604701660993</v>
@@ -5627,24 +6742,36 @@
         <v>0.0134</v>
       </c>
       <c r="M54" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N54">
         <v>0.0322</v>
       </c>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="O54" t="s">
+        <v>115</v>
+      </c>
+      <c r="P54">
+        <v>-0.1609806360778065</v>
+      </c>
+      <c r="Q54">
+        <v>-0.003463348309243171</v>
+      </c>
+      <c r="R54" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C55" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D55" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E55">
         <v>0.6683417085427136</v>
@@ -5665,10 +6792,22 @@
         <v>0.3018984444285246</v>
       </c>
       <c r="M55" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="N55">
         <v>0.6037968888570493</v>
+      </c>
+      <c r="O55" t="s">
+        <v>116</v>
+      </c>
+      <c r="P55">
+        <v>-0.05527638190954776</v>
+      </c>
+      <c r="Q55">
+        <v>0.1507537688442211</v>
+      </c>
+      <c r="R55" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -5678,207 +6817,224 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="60.7109375" customWidth="1"/>
+    <col min="3" max="17" width="16.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="C1" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="D1" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="E1" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="G1" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="H1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I1" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="J1" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="K1" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="L1" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="M1" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="N1" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="O1" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="P1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
+        <v>131</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2">
+        <v>138</v>
+      </c>
+      <c r="F2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2">
         <v>406</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>250</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>156</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.624</v>
       </c>
-      <c r="J2" t="b">
+      <c r="K2" t="b">
         <v>1</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>4999</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>42</v>
       </c>
-      <c r="M2" t="s">
-        <v>109</v>
-      </c>
       <c r="N2" t="s">
-        <v>110</v>
-      </c>
-      <c r="O2" t="b">
+        <v>139</v>
+      </c>
+      <c r="O2" t="s">
+        <v>140</v>
+      </c>
+      <c r="P2" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F3">
-        <v>207</v>
+        <v>138</v>
+      </c>
+      <c r="F3" t="s">
+        <v>123</v>
       </c>
       <c r="G3">
         <v>207</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3" t="b">
+      <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3">
         <v>4999</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>42</v>
       </c>
-      <c r="M3" t="s">
-        <v>109</v>
-      </c>
       <c r="N3" t="s">
-        <v>110</v>
-      </c>
-      <c r="O3" t="b">
+        <v>139</v>
+      </c>
+      <c r="O3" t="s">
+        <v>140</v>
+      </c>
+      <c r="P3" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F4">
-        <v>199</v>
+        <v>138</v>
+      </c>
+      <c r="F4" t="s">
+        <v>123</v>
       </c>
       <c r="G4">
         <v>199</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4" t="b">
+      <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>4999</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>42</v>
       </c>
-      <c r="M4" t="s">
-        <v>109</v>
-      </c>
       <c r="N4" t="s">
-        <v>110</v>
-      </c>
-      <c r="O4" t="b">
+        <v>139</v>
+      </c>
+      <c r="O4" t="s">
+        <v>140</v>
+      </c>
+      <c r="P4" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="s">
-        <v>111</v>
+      <c r="Q4" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/examples/example_continuous_results.xlsx
+++ b/examples/example_continuous_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="145">
   <si>
     <t>Group</t>
   </si>
@@ -191,22 +191,22 @@
     <t>Weighting of Eyes (mean-loss metrics)</t>
   </si>
   <si>
-    <t>Mean Error (MPE) Test</t>
-  </si>
-  <si>
-    <t>MAE Test</t>
-  </si>
-  <si>
-    <t>RMSE Test</t>
-  </si>
-  <si>
-    <t>MedAE Test</t>
-  </si>
-  <si>
-    <t>SD Test</t>
-  </si>
-  <si>
-    <t>Proportion Within Tolerance Test</t>
+    <t>Mean error Test</t>
+  </si>
+  <si>
+    <t>Mean absolute error Test</t>
+  </si>
+  <si>
+    <t>Root mean squared error Test</t>
+  </si>
+  <si>
+    <t>Median absolute error Test</t>
+  </si>
+  <si>
+    <t>SD of the error Test</t>
+  </si>
+  <si>
+    <t>Proportion within tolerance Test</t>
   </si>
   <si>
     <t>Tolerance (proportion within)</t>
@@ -227,6 +227,9 @@
     <t>Subgroups</t>
   </si>
   <si>
+    <t>Subgroup adjustment</t>
+  </si>
+  <si>
     <t>Patient as the unit (cluster bootstrap / cluster-robust tests)</t>
   </si>
   <si>
@@ -251,21 +254,27 @@
     <t>Romano-Wolf (bootstrap tests) / Hommel (other tests)</t>
   </si>
   <si>
-    <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Romano-Wolf step-down: Mean Error (MPE), MAE, RMSE, MedAE, SD; Hommel: Proportion Within Tolerance</t>
-  </si>
-  <si>
-    <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group. Romano-Wolf simultaneous (max-|t|): Mean Error (MPE), MAE, MedAE; Bonferroni (percentile bootstrap): RMSE, SD, Proportion Within Tolerance. MPE, MAE and MedAE: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). RMSE, SD and the proportion within tolerance: percentile interval of the same patient resamples at coverage 1 - 0.05/m (Bonferroni). These Bonferroni-type intervals need not agree with p_adj when p_adj comes from another statistic (Romano-Wolf, Hommel); use more resamples (e.g. 9,999) for their far tails</t>
+    <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Romano-Wolf step-down: Mean error, Mean absolute error, Root mean squared error, Median absolute error, SD of the error; Hommel: Proportion within tolerance</t>
+  </si>
+  <si>
+    <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group. Romano-Wolf simultaneous (max-|t|): Mean error, Mean absolute error, Median absolute error; Bonferroni (percentile bootstrap): Root mean squared error, SD of the error, Proportion within tolerance. MPE, MAE and MedAE: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). RMSE, SD and the proportion within tolerance: percentile interval of the same patient resamples at coverage 1 - 0.05/m (Bonferroni). These Bonferroni-type intervals need not agree with p_adj when p_adj comes from another statistic (Romano-Wolf, Hommel); use more resamples (e.g. 9,999) for their far tails</t>
   </si>
   <si>
     <t>ρΔ (rho_delta): intraclass correlation of the per-eye difference in loss between the two models; one_eye_factor: patients a one-eye study needs, relative to this analysis (design effect)</t>
   </si>
   <si>
-    <t>eye, nominal: one subgroup per level (L, R). Each subgroup is analyzed separately with the same models, tests and settings; p-values and intervals are adjusted for the model pairs within each group, not across groups</t>
+    <t>eye, nominal: one subgroup per level (L, R). Each subgroup is analyzed separately with the same models, tests and settings</t>
+  </si>
+  <si>
+    <t>Subgroup results are exploratory: p-values and intervals are adjusted for the model pairs within each group, not across groups</t>
   </si>
   <si>
     <t>group</t>
   </si>
   <si>
+    <t>grouping</t>
+  </si>
+  <si>
     <t>model</t>
   </si>
   <si>
@@ -290,6 +299,9 @@
     <t>method</t>
   </si>
   <si>
+    <t>eye</t>
+  </si>
+  <si>
     <t>bias</t>
   </si>
   <si>
@@ -435,9 +447,6 @@
   </si>
   <si>
     <t>patient_id</t>
-  </si>
-  <si>
-    <t>eye</t>
   </si>
   <si>
     <t>patient</t>
@@ -2229,7 +2238,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -2249,7 +2258,7 @@
         <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2257,7 +2266,7 @@
         <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2265,7 +2274,7 @@
         <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2273,7 +2282,7 @@
         <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2281,7 +2290,7 @@
         <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2289,7 +2298,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2297,7 +2306,7 @@
         <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2305,7 +2314,7 @@
         <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2313,7 +2322,7 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2321,7 +2330,7 @@
         <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2329,7 +2338,7 @@
         <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2337,7 +2346,7 @@
         <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2345,7 +2354,7 @@
         <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2353,7 +2362,15 @@
         <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2363,1605 +2380,1770 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="9" width="18.7109375" customWidth="1"/>
+    <col min="1" max="10" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>91</v>
+      </c>
+      <c r="J1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>47</v>
       </c>
       <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
         <v>50</v>
       </c>
-      <c r="C2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2">
         <v>0.02049261083743843</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>-0.03627408686752381</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0.07817344322344313</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>406</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>250</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3">
+        <v>0.02807881773399015</v>
+      </c>
+      <c r="F3">
+        <v>-0.03130163576219235</v>
+      </c>
+      <c r="G3">
+        <v>0.08814663182346116</v>
+      </c>
+      <c r="H3">
+        <v>406</v>
+      </c>
+      <c r="I3">
+        <v>250</v>
+      </c>
+      <c r="J3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4">
+        <v>0.04536945812807881</v>
+      </c>
+      <c r="F4">
+        <v>-0.0227918672839506</v>
+      </c>
+      <c r="G4">
+        <v>0.1117210615626027</v>
+      </c>
+      <c r="H4">
+        <v>406</v>
+      </c>
+      <c r="I4">
+        <v>250</v>
+      </c>
+      <c r="J4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5">
+        <v>0.4010837438423646</v>
+      </c>
+      <c r="F5">
+        <v>0.3695515125104408</v>
+      </c>
+      <c r="G5">
+        <v>0.4314988474459895</v>
+      </c>
+      <c r="H5">
+        <v>406</v>
+      </c>
+      <c r="I5">
+        <v>250</v>
+      </c>
+      <c r="J5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6">
+        <v>0.413743842364532</v>
+      </c>
+      <c r="F6">
+        <v>0.3824580685289189</v>
+      </c>
+      <c r="G6">
+        <v>0.4454042263674867</v>
+      </c>
+      <c r="H6">
+        <v>406</v>
+      </c>
+      <c r="I6">
+        <v>250</v>
+      </c>
+      <c r="J6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7">
+        <v>0.4725615763546798</v>
+      </c>
+      <c r="F7">
+        <v>0.4363228203517588</v>
+      </c>
+      <c r="G7">
+        <v>0.5081824833702879</v>
+      </c>
+      <c r="H7">
+        <v>406</v>
+      </c>
+      <c r="I7">
+        <v>250</v>
+      </c>
+      <c r="J7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E8">
+        <v>0.503346436828533</v>
+      </c>
+      <c r="F8">
+        <v>0.467341335102832</v>
+      </c>
+      <c r="G8">
+        <v>0.5381596977405826</v>
+      </c>
+      <c r="H8">
+        <v>406</v>
+      </c>
+      <c r="I8">
+        <v>250</v>
+      </c>
+      <c r="J8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
         <v>51</v>
       </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3">
-        <v>0.02807881773399015</v>
-      </c>
-      <c r="E3">
-        <v>-0.03130163576219235</v>
-      </c>
-      <c r="F3">
-        <v>0.08814663182346116</v>
-      </c>
-      <c r="G3">
+      <c r="D9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9">
+        <v>0.5190271308530763</v>
+      </c>
+      <c r="F9">
+        <v>0.4829163917076886</v>
+      </c>
+      <c r="G9">
+        <v>0.5537674085132629</v>
+      </c>
+      <c r="H9">
         <v>406</v>
       </c>
-      <c r="H3">
+      <c r="I9">
         <v>250</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="E10">
+        <v>0.5875820873372553</v>
+      </c>
+      <c r="F10">
+        <v>0.5463605798821267</v>
+      </c>
+      <c r="G10">
+        <v>0.6266470149182912</v>
+      </c>
+      <c r="H10">
+        <v>406</v>
+      </c>
+      <c r="I10">
+        <v>250</v>
+      </c>
+      <c r="J10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11">
+        <v>0.34</v>
+      </c>
+      <c r="F11">
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="G11">
+        <v>0.38</v>
+      </c>
+      <c r="H11">
+        <v>406</v>
+      </c>
+      <c r="I11">
+        <v>250</v>
+      </c>
+      <c r="J11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12">
+        <v>0.3500000000000001</v>
+      </c>
+      <c r="F12">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="G12">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="H12">
+        <v>406</v>
+      </c>
+      <c r="I12">
+        <v>250</v>
+      </c>
+      <c r="J12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
         <v>52</v>
       </c>
-      <c r="C4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4">
-        <v>0.04536945812807881</v>
-      </c>
-      <c r="E4">
-        <v>-0.0227918672839506</v>
-      </c>
-      <c r="F4">
-        <v>0.1117210615626027</v>
-      </c>
-      <c r="G4">
+      <c r="D13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="F13">
+        <v>0.36</v>
+      </c>
+      <c r="G13">
+        <v>0.45</v>
+      </c>
+      <c r="H13">
         <v>406</v>
       </c>
-      <c r="H4">
+      <c r="I13">
         <v>250</v>
       </c>
-      <c r="I4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="J13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
         <v>50</v>
       </c>
-      <c r="C5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5">
-        <v>0.4010837438423646</v>
-      </c>
-      <c r="E5">
-        <v>0.3695515125104408</v>
-      </c>
-      <c r="F5">
-        <v>0.4314988474459895</v>
-      </c>
-      <c r="G5">
+      <c r="D14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14">
+        <v>0.5035496260262651</v>
+      </c>
+      <c r="F14">
+        <v>0.4670729663895484</v>
+      </c>
+      <c r="G14">
+        <v>0.5373554039329193</v>
+      </c>
+      <c r="H14">
         <v>406</v>
       </c>
-      <c r="H5">
+      <c r="I14">
         <v>250</v>
       </c>
-      <c r="I5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="J14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
         <v>51</v>
       </c>
-      <c r="C6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6">
-        <v>0.413743842364532</v>
-      </c>
-      <c r="E6">
-        <v>0.3824580685289189</v>
-      </c>
-      <c r="F6">
-        <v>0.4454042263674867</v>
-      </c>
-      <c r="G6">
+      <c r="D15" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15">
+        <v>0.5189064985777815</v>
+      </c>
+      <c r="F15">
+        <v>0.481268604979075</v>
+      </c>
+      <c r="G15">
+        <v>0.5530250723007292</v>
+      </c>
+      <c r="H15">
         <v>406</v>
       </c>
-      <c r="H6">
+      <c r="I15">
         <v>250</v>
       </c>
-      <c r="I6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="J15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
         <v>52</v>
       </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7">
-        <v>0.4725615763546798</v>
-      </c>
-      <c r="E7">
-        <v>0.4363228203517588</v>
-      </c>
-      <c r="F7">
-        <v>0.5081824833702879</v>
-      </c>
-      <c r="G7">
+      <c r="D16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16">
+        <v>0.5865506926221365</v>
+      </c>
+      <c r="F16">
+        <v>0.5442726547777093</v>
+      </c>
+      <c r="G16">
+        <v>0.624844231822534</v>
+      </c>
+      <c r="H16">
         <v>406</v>
       </c>
-      <c r="H7">
+      <c r="I16">
         <v>250</v>
       </c>
-      <c r="I7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="J16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
         <v>50</v>
       </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8">
-        <v>0.503346436828533</v>
-      </c>
-      <c r="E8">
-        <v>0.467341335102832</v>
-      </c>
-      <c r="F8">
-        <v>0.5381596977405826</v>
-      </c>
-      <c r="G8">
+      <c r="D17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17">
+        <v>0.6921182266009852</v>
+      </c>
+      <c r="F17">
+        <v>0.6451574224491374</v>
+      </c>
+      <c r="G17">
+        <v>0.739135938359934</v>
+      </c>
+      <c r="H17">
         <v>406</v>
       </c>
-      <c r="H8">
+      <c r="I17">
         <v>250</v>
       </c>
-      <c r="I8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="J17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
         <v>51</v>
       </c>
-      <c r="C9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9">
-        <v>0.5190271308530763</v>
-      </c>
-      <c r="E9">
-        <v>0.4829163917076886</v>
-      </c>
-      <c r="F9">
-        <v>0.5537674085132629</v>
-      </c>
-      <c r="G9">
+      <c r="D18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18">
+        <v>0.6576354679802956</v>
+      </c>
+      <c r="F18">
+        <v>0.6104218362282878</v>
+      </c>
+      <c r="G18">
+        <v>0.7064676616915423</v>
+      </c>
+      <c r="H18">
         <v>406</v>
       </c>
-      <c r="H9">
+      <c r="I18">
         <v>250</v>
       </c>
-      <c r="I9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="J18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
         <v>52</v>
       </c>
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10">
-        <v>0.5875820873372553</v>
-      </c>
-      <c r="E10">
-        <v>0.5463605798821267</v>
-      </c>
-      <c r="F10">
-        <v>0.6266470149182912</v>
-      </c>
-      <c r="G10">
+      <c r="D19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19">
+        <v>0.6108374384236454</v>
+      </c>
+      <c r="F19">
+        <v>0.5601965601965602</v>
+      </c>
+      <c r="G19">
+        <v>0.6616933849272157</v>
+      </c>
+      <c r="H19">
         <v>406</v>
       </c>
-      <c r="H10">
+      <c r="I19">
         <v>250</v>
       </c>
-      <c r="I10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11">
-        <v>0.34</v>
-      </c>
-      <c r="E11">
-        <v>0.2999999999999998</v>
-      </c>
-      <c r="F11">
-        <v>0.38</v>
-      </c>
-      <c r="G11">
-        <v>406</v>
-      </c>
-      <c r="H11">
-        <v>250</v>
-      </c>
-      <c r="I11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12">
-        <v>0.3500000000000001</v>
-      </c>
-      <c r="E12">
-        <v>0.3100000000000001</v>
-      </c>
-      <c r="F12">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="G12">
-        <v>406</v>
-      </c>
-      <c r="H12">
-        <v>250</v>
-      </c>
-      <c r="I12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="E13">
-        <v>0.36</v>
-      </c>
-      <c r="F13">
-        <v>0.45</v>
-      </c>
-      <c r="G13">
-        <v>406</v>
-      </c>
-      <c r="H13">
-        <v>250</v>
-      </c>
-      <c r="I13" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14">
-        <v>0.5035496260262651</v>
-      </c>
-      <c r="E14">
-        <v>0.4670729663895484</v>
-      </c>
-      <c r="F14">
-        <v>0.5373554039329193</v>
-      </c>
-      <c r="G14">
-        <v>406</v>
-      </c>
-      <c r="H14">
-        <v>250</v>
-      </c>
-      <c r="I14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15">
-        <v>0.5189064985777815</v>
-      </c>
-      <c r="E15">
-        <v>0.481268604979075</v>
-      </c>
-      <c r="F15">
-        <v>0.5530250723007292</v>
-      </c>
-      <c r="G15">
-        <v>406</v>
-      </c>
-      <c r="H15">
-        <v>250</v>
-      </c>
-      <c r="I15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16">
-        <v>0.5865506926221365</v>
-      </c>
-      <c r="E16">
-        <v>0.5442726547777093</v>
-      </c>
-      <c r="F16">
-        <v>0.624844231822534</v>
-      </c>
-      <c r="G16">
-        <v>406</v>
-      </c>
-      <c r="H16">
-        <v>250</v>
-      </c>
-      <c r="I16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" t="s">
-        <v>95</v>
-      </c>
-      <c r="D17">
-        <v>0.6921182266009852</v>
-      </c>
-      <c r="E17">
-        <v>0.6451574224491374</v>
-      </c>
-      <c r="F17">
-        <v>0.739135938359934</v>
-      </c>
-      <c r="G17">
-        <v>406</v>
-      </c>
-      <c r="H17">
-        <v>250</v>
-      </c>
-      <c r="I17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18">
-        <v>0.6576354679802956</v>
-      </c>
-      <c r="E18">
-        <v>0.6104218362282878</v>
-      </c>
-      <c r="F18">
-        <v>0.7064676616915423</v>
-      </c>
-      <c r="G18">
-        <v>406</v>
-      </c>
-      <c r="H18">
-        <v>250</v>
-      </c>
-      <c r="I18" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19">
-        <v>0.6108374384236454</v>
-      </c>
-      <c r="E19">
-        <v>0.5601965601965602</v>
-      </c>
-      <c r="F19">
-        <v>0.6616933849272157</v>
-      </c>
-      <c r="G19">
-        <v>406</v>
-      </c>
-      <c r="H19">
-        <v>250</v>
-      </c>
-      <c r="I19" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="J19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>48</v>
       </c>
       <c r="B20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s">
         <v>50</v>
       </c>
-      <c r="C20" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20">
+      <c r="D20" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20">
         <v>0.01473429951690822</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>-0.05386956521739131</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.08382367149758455</v>
-      </c>
-      <c r="G20">
-        <v>207</v>
       </c>
       <c r="H20">
         <v>207</v>
       </c>
-      <c r="I20" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="I20">
+        <v>207</v>
+      </c>
+      <c r="J20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>48</v>
       </c>
       <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
         <v>51</v>
       </c>
-      <c r="C21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21">
+      <c r="D21" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21">
         <v>0.006376811594202901</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>-0.06710386473429948</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.07851690821256047</v>
-      </c>
-      <c r="G21">
-        <v>207</v>
       </c>
       <c r="H21">
         <v>207</v>
       </c>
-      <c r="I21" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="I21">
+        <v>207</v>
+      </c>
+      <c r="J21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>48</v>
       </c>
       <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
         <v>52</v>
       </c>
-      <c r="C22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22">
+      <c r="D22" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22">
         <v>0.002318840579710145</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>-0.07716183574879226</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.08183816425120778</v>
-      </c>
-      <c r="G22">
-        <v>207</v>
       </c>
       <c r="H22">
         <v>207</v>
       </c>
-      <c r="I22" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="I22">
+        <v>207</v>
+      </c>
+      <c r="J22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>48</v>
       </c>
       <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
         <v>50</v>
       </c>
-      <c r="C23" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23">
+      <c r="D23" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23">
         <v>0.4014975845410628</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.3609106280193235</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.4427584541062801</v>
-      </c>
-      <c r="G23">
-        <v>207</v>
       </c>
       <c r="H23">
         <v>207</v>
       </c>
-      <c r="I23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="I23">
+        <v>207</v>
+      </c>
+      <c r="J23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>48</v>
       </c>
       <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
         <v>51</v>
       </c>
-      <c r="C24" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24">
+      <c r="D24" t="s">
+        <v>95</v>
+      </c>
+      <c r="E24">
         <v>0.4215458937198068</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>0.3783091787439615</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>0.4659565217391309</v>
-      </c>
-      <c r="G24">
-        <v>207</v>
       </c>
       <c r="H24">
         <v>207</v>
       </c>
-      <c r="I24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="I24">
+        <v>207</v>
+      </c>
+      <c r="J24" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>48</v>
       </c>
       <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" t="s">
         <v>52</v>
       </c>
-      <c r="C25" t="s">
-        <v>91</v>
-      </c>
-      <c r="D25">
+      <c r="D25" t="s">
+        <v>95</v>
+      </c>
+      <c r="E25">
         <v>0.4694685990338164</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>0.4212487922705314</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>0.5170048309178744</v>
-      </c>
-      <c r="G25">
-        <v>207</v>
       </c>
       <c r="H25">
         <v>207</v>
       </c>
-      <c r="I25" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="I25">
+        <v>207</v>
+      </c>
+      <c r="J25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>48</v>
       </c>
       <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" t="s">
         <v>50</v>
       </c>
-      <c r="C26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D26">
+      <c r="D26" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26">
         <v>0.4993498188103143</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>0.4489748654168933</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>0.5487215267707212</v>
-      </c>
-      <c r="G26">
-        <v>207</v>
       </c>
       <c r="H26">
         <v>207</v>
       </c>
-      <c r="I26" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="I26">
+        <v>207</v>
+      </c>
+      <c r="J26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>48</v>
       </c>
       <c r="B27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" t="s">
         <v>51</v>
       </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27">
+      <c r="D27" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27">
         <v>0.5350976252975095</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>0.4824960764236936</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>0.5865781583925679</v>
-      </c>
-      <c r="G27">
-        <v>207</v>
       </c>
       <c r="H27">
         <v>207</v>
       </c>
-      <c r="I27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="I27">
+        <v>207</v>
+      </c>
+      <c r="J27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>48</v>
       </c>
       <c r="B28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" t="s">
         <v>52</v>
       </c>
-      <c r="C28" t="s">
-        <v>92</v>
-      </c>
-      <c r="D28">
+      <c r="D28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28">
         <v>0.5841530472476332</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>0.5291510823472348</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>0.6371627741675031</v>
-      </c>
-      <c r="G28">
-        <v>207</v>
       </c>
       <c r="H28">
         <v>207</v>
       </c>
-      <c r="I28" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="I28">
+        <v>207</v>
+      </c>
+      <c r="J28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="B29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" t="s">
         <v>50</v>
       </c>
-      <c r="C29" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29">
+      <c r="D29" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29">
         <v>0.3599999999999999</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>0.29</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>0.3999999999999999</v>
-      </c>
-      <c r="G29">
-        <v>207</v>
       </c>
       <c r="H29">
         <v>207</v>
       </c>
-      <c r="I29" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="I29">
+        <v>207</v>
+      </c>
+      <c r="J29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>48</v>
       </c>
       <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" t="s">
         <v>51</v>
       </c>
-      <c r="C30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30">
+      <c r="D30" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30">
         <v>0.37</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>0.3</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>0.4300000000000002</v>
-      </c>
-      <c r="G30">
-        <v>207</v>
       </c>
       <c r="H30">
         <v>207</v>
       </c>
-      <c r="I30" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="I30">
+        <v>207</v>
+      </c>
+      <c r="J30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>48</v>
       </c>
       <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
         <v>52</v>
       </c>
-      <c r="C31" t="s">
-        <v>93</v>
-      </c>
-      <c r="D31">
+      <c r="D31" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31">
         <v>0.4199999999999999</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>0.3599999999999994</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>0.48</v>
-      </c>
-      <c r="G31">
-        <v>207</v>
       </c>
       <c r="H31">
         <v>207</v>
       </c>
-      <c r="I31" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="I31">
+        <v>207</v>
+      </c>
+      <c r="J31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>48</v>
       </c>
       <c r="B32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" t="s">
         <v>50</v>
       </c>
-      <c r="C32" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32">
+      <c r="D32" t="s">
+        <v>98</v>
+      </c>
+      <c r="E32">
         <v>0.5003424089040717</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>0.4484747263872393</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>0.5472560680830526</v>
-      </c>
-      <c r="G32">
-        <v>207</v>
       </c>
       <c r="H32">
         <v>207</v>
       </c>
-      <c r="I32" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+      <c r="I32">
+        <v>207</v>
+      </c>
+      <c r="J32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>48</v>
       </c>
       <c r="B33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" t="s">
         <v>51</v>
       </c>
-      <c r="C33" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33">
+      <c r="D33" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33">
         <v>0.5363567435512407</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>0.4821727389220226</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>0.5863463364422008</v>
-      </c>
-      <c r="G33">
-        <v>207</v>
       </c>
       <c r="H33">
         <v>207</v>
       </c>
-      <c r="I33" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+      <c r="I33">
+        <v>207</v>
+      </c>
+      <c r="J33" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>48</v>
       </c>
       <c r="B34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" t="s">
         <v>52</v>
       </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34">
+      <c r="D34" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34">
         <v>0.5855645643413213</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>0.529478721324974</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>0.6374656501091623</v>
-      </c>
-      <c r="G34">
-        <v>207</v>
       </c>
       <c r="H34">
         <v>207</v>
       </c>
-      <c r="I34" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+      <c r="I34">
+        <v>207</v>
+      </c>
+      <c r="J34" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>48</v>
       </c>
       <c r="B35" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" t="s">
         <v>50</v>
       </c>
-      <c r="C35" t="s">
-        <v>95</v>
-      </c>
-      <c r="D35">
+      <c r="D35" t="s">
+        <v>99</v>
+      </c>
+      <c r="E35">
         <v>0.714975845410628</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>0.6521739130434783</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>0.7777777777777778</v>
-      </c>
-      <c r="G35">
-        <v>207</v>
       </c>
       <c r="H35">
         <v>207</v>
       </c>
-      <c r="I35" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+      <c r="I35">
+        <v>207</v>
+      </c>
+      <c r="J35" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>48</v>
       </c>
       <c r="B36" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" t="s">
         <v>51</v>
       </c>
-      <c r="C36" t="s">
-        <v>95</v>
-      </c>
-      <c r="D36">
+      <c r="D36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36">
         <v>0.6473429951690821</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>0.5797101449275363</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>0.7101449275362319</v>
-      </c>
-      <c r="G36">
-        <v>207</v>
       </c>
       <c r="H36">
         <v>207</v>
       </c>
-      <c r="I36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="I36">
+        <v>207</v>
+      </c>
+      <c r="J36" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>48</v>
       </c>
       <c r="B37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" t="s">
         <v>52</v>
       </c>
-      <c r="C37" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37">
+      <c r="D37" t="s">
+        <v>99</v>
+      </c>
+      <c r="E37">
         <v>0.6038647342995169</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>0.5362318840579711</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>0.6714975845410628</v>
-      </c>
-      <c r="G37">
-        <v>207</v>
       </c>
       <c r="H37">
         <v>207</v>
       </c>
-      <c r="I37" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="I37">
+        <v>207</v>
+      </c>
+      <c r="J37" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>49</v>
       </c>
       <c r="B38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" t="s">
         <v>50</v>
       </c>
-      <c r="C38" t="s">
-        <v>90</v>
-      </c>
-      <c r="D38">
+      <c r="D38" t="s">
+        <v>94</v>
+      </c>
+      <c r="E38">
         <v>0.02648241206030149</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>-0.04417587939698493</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>0.09693718592964826</v>
-      </c>
-      <c r="G38">
-        <v>199</v>
       </c>
       <c r="H38">
         <v>199</v>
       </c>
-      <c r="I38" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+      <c r="I38">
+        <v>199</v>
+      </c>
+      <c r="J38" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>49</v>
       </c>
       <c r="B39" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" t="s">
         <v>51</v>
       </c>
-      <c r="C39" t="s">
-        <v>90</v>
-      </c>
-      <c r="D39">
+      <c r="D39" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39">
         <v>0.05065326633165827</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>-0.01932160804020097</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>0.1202537688442211</v>
-      </c>
-      <c r="G39">
-        <v>199</v>
       </c>
       <c r="H39">
         <v>199</v>
       </c>
-      <c r="I39" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+      <c r="I39">
+        <v>199</v>
+      </c>
+      <c r="J39" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>49</v>
       </c>
       <c r="B40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" t="s">
         <v>52</v>
       </c>
-      <c r="C40" t="s">
-        <v>90</v>
-      </c>
-      <c r="D40">
+      <c r="D40" t="s">
+        <v>94</v>
+      </c>
+      <c r="E40">
         <v>0.09015075376884421</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>0.005876884422110537</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>0.1709070351758794</v>
-      </c>
-      <c r="G40">
-        <v>199</v>
       </c>
       <c r="H40">
         <v>199</v>
       </c>
-      <c r="I40" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+      <c r="I40">
+        <v>199</v>
+      </c>
+      <c r="J40" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>49</v>
       </c>
       <c r="B41" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" t="s">
         <v>50</v>
       </c>
-      <c r="C41" t="s">
-        <v>91</v>
-      </c>
-      <c r="D41">
+      <c r="D41" t="s">
+        <v>95</v>
+      </c>
+      <c r="E41">
         <v>0.4006532663316583</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>0.3574874371859297</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>0.4432688442211056</v>
-      </c>
-      <c r="G41">
-        <v>199</v>
       </c>
       <c r="H41">
         <v>199</v>
       </c>
-      <c r="I41" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+      <c r="I41">
+        <v>199</v>
+      </c>
+      <c r="J41" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>49</v>
       </c>
       <c r="B42" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" t="s">
         <v>51</v>
       </c>
-      <c r="C42" t="s">
-        <v>91</v>
-      </c>
-      <c r="D42">
+      <c r="D42" t="s">
+        <v>95</v>
+      </c>
+      <c r="E42">
         <v>0.4056281407035176</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>0.3649698492462313</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>0.4472889447236182</v>
-      </c>
-      <c r="G42">
-        <v>199</v>
       </c>
       <c r="H42">
         <v>199</v>
       </c>
-      <c r="I42" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
+      <c r="I42">
+        <v>199</v>
+      </c>
+      <c r="J42" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
         <v>49</v>
       </c>
       <c r="B43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" t="s">
         <v>52</v>
       </c>
-      <c r="C43" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43">
+      <c r="D43" t="s">
+        <v>95</v>
+      </c>
+      <c r="E43">
         <v>0.4757788944723618</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>0.4288944723618093</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>0.5252286432160804</v>
-      </c>
-      <c r="G43">
-        <v>199</v>
       </c>
       <c r="H43">
         <v>199</v>
       </c>
-      <c r="I43" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+      <c r="I43">
+        <v>199</v>
+      </c>
+      <c r="J43" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="B44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" t="s">
         <v>50</v>
       </c>
-      <c r="C44" t="s">
-        <v>92</v>
-      </c>
-      <c r="D44">
+      <c r="D44" t="s">
+        <v>96</v>
+      </c>
+      <c r="E44">
         <v>0.5074703248991672</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>0.4568519922236322</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>0.5557394457416932</v>
-      </c>
-      <c r="G44">
-        <v>199</v>
       </c>
       <c r="H44">
         <v>199</v>
       </c>
-      <c r="I44" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+      <c r="I44">
+        <v>199</v>
+      </c>
+      <c r="J44" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
         <v>49</v>
       </c>
       <c r="B45" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" t="s">
         <v>51</v>
       </c>
-      <c r="C45" t="s">
-        <v>92</v>
-      </c>
-      <c r="D45">
+      <c r="D45" t="s">
+        <v>96</v>
+      </c>
+      <c r="E45">
         <v>0.5017647249418594</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>0.4565332790587962</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>0.5461399953055275</v>
-      </c>
-      <c r="G45">
-        <v>199</v>
       </c>
       <c r="H45">
         <v>199</v>
       </c>
-      <c r="I45" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+      <c r="I45">
+        <v>199</v>
+      </c>
+      <c r="J45" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" t="s">
         <v>52</v>
       </c>
-      <c r="C46" t="s">
-        <v>92</v>
-      </c>
-      <c r="D46">
+      <c r="D46" t="s">
+        <v>96</v>
+      </c>
+      <c r="E46">
         <v>0.5911278717875009</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>0.5363117100554832</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>0.6456197404269474</v>
-      </c>
-      <c r="G46">
-        <v>199</v>
       </c>
       <c r="H46">
         <v>199</v>
       </c>
-      <c r="I46" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+      <c r="I46">
+        <v>199</v>
+      </c>
+      <c r="J46" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
         <v>49</v>
       </c>
       <c r="B47" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" t="s">
         <v>50</v>
       </c>
-      <c r="C47" t="s">
-        <v>93</v>
-      </c>
-      <c r="D47">
+      <c r="D47" t="s">
+        <v>97</v>
+      </c>
+      <c r="E47">
         <v>0.34</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>0.29</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>0.4099999999999999</v>
-      </c>
-      <c r="G47">
-        <v>199</v>
       </c>
       <c r="H47">
         <v>199</v>
       </c>
-      <c r="I47" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+      <c r="I47">
+        <v>199</v>
+      </c>
+      <c r="J47" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
         <v>49</v>
       </c>
       <c r="B48" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" t="s">
         <v>51</v>
       </c>
-      <c r="C48" t="s">
-        <v>93</v>
-      </c>
-      <c r="D48">
+      <c r="D48" t="s">
+        <v>97</v>
+      </c>
+      <c r="E48">
         <v>0.3500000000000001</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>0.3099999999999998</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>0.4</v>
-      </c>
-      <c r="G48">
-        <v>199</v>
       </c>
       <c r="H48">
         <v>199</v>
       </c>
-      <c r="I48" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+      <c r="I48">
+        <v>199</v>
+      </c>
+      <c r="J48" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>49</v>
       </c>
       <c r="B49" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" t="s">
         <v>52</v>
       </c>
-      <c r="C49" t="s">
-        <v>93</v>
-      </c>
-      <c r="D49">
+      <c r="D49" t="s">
+        <v>97</v>
+      </c>
+      <c r="E49">
         <v>0.3900000000000001</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>0.34</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>0.4400000000000001</v>
-      </c>
-      <c r="G49">
-        <v>199</v>
       </c>
       <c r="H49">
         <v>199</v>
       </c>
-      <c r="I49" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+      <c r="I49">
+        <v>199</v>
+      </c>
+      <c r="J49" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" t="s">
         <v>50</v>
       </c>
-      <c r="C50" t="s">
-        <v>94</v>
-      </c>
-      <c r="D50">
+      <c r="D50" t="s">
+        <v>98</v>
+      </c>
+      <c r="E50">
         <v>0.5080569923909963</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>0.4565598267050878</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>0.5549796484849452</v>
-      </c>
-      <c r="G50">
-        <v>199</v>
       </c>
       <c r="H50">
         <v>199</v>
       </c>
-      <c r="I50" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+      <c r="I50">
+        <v>199</v>
+      </c>
+      <c r="J50" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>49</v>
       </c>
       <c r="B51" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" t="s">
         <v>51</v>
       </c>
-      <c r="C51" t="s">
-        <v>94</v>
-      </c>
-      <c r="D51">
+      <c r="D51" t="s">
+        <v>98</v>
+      </c>
+      <c r="E51">
         <v>0.5004604701660993</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>0.4533062480035989</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>0.5438143015862841</v>
-      </c>
-      <c r="G51">
-        <v>199</v>
       </c>
       <c r="H51">
         <v>199</v>
       </c>
-      <c r="I51" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+      <c r="I51">
+        <v>199</v>
+      </c>
+      <c r="J51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>49</v>
       </c>
       <c r="B52" t="s">
+        <v>93</v>
+      </c>
+      <c r="C52" t="s">
         <v>52</v>
       </c>
-      <c r="C52" t="s">
-        <v>94</v>
-      </c>
-      <c r="D52">
+      <c r="D52" t="s">
+        <v>98</v>
+      </c>
+      <c r="E52">
         <v>0.5856865757701022</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>0.528603758787536</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>0.6404274271255828</v>
-      </c>
-      <c r="G52">
-        <v>199</v>
       </c>
       <c r="H52">
         <v>199</v>
       </c>
-      <c r="I52" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+      <c r="I52">
+        <v>199</v>
+      </c>
+      <c r="J52" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
         <v>49</v>
       </c>
       <c r="B53" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" t="s">
         <v>50</v>
       </c>
-      <c r="C53" t="s">
-        <v>95</v>
-      </c>
-      <c r="D53">
+      <c r="D53" t="s">
+        <v>99</v>
+      </c>
+      <c r="E53">
         <v>0.6683417085427136</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>0.6030150753768844</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>0.7336683417085427</v>
-      </c>
-      <c r="G53">
-        <v>199</v>
       </c>
       <c r="H53">
         <v>199</v>
       </c>
-      <c r="I53" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+      <c r="I53">
+        <v>199</v>
+      </c>
+      <c r="J53" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>49</v>
       </c>
       <c r="B54" t="s">
+        <v>93</v>
+      </c>
+      <c r="C54" t="s">
         <v>51</v>
       </c>
-      <c r="C54" t="s">
-        <v>95</v>
-      </c>
-      <c r="D54">
+      <c r="D54" t="s">
+        <v>99</v>
+      </c>
+      <c r="E54">
         <v>0.6683417085427136</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>0.5979899497487438</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>0.7336683417085427</v>
-      </c>
-      <c r="G54">
-        <v>199</v>
       </c>
       <c r="H54">
         <v>199</v>
       </c>
-      <c r="I54" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
+      <c r="I54">
+        <v>199</v>
+      </c>
+      <c r="J54" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
         <v>49</v>
       </c>
       <c r="B55" t="s">
+        <v>93</v>
+      </c>
+      <c r="C55" t="s">
         <v>52</v>
       </c>
-      <c r="C55" t="s">
-        <v>95</v>
-      </c>
-      <c r="D55">
+      <c r="D55" t="s">
+        <v>99</v>
+      </c>
+      <c r="E55">
         <v>0.6180904522613065</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>0.5477386934673367</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>0.6834170854271356</v>
-      </c>
-      <c r="G55">
-        <v>199</v>
       </c>
       <c r="H55">
         <v>199</v>
       </c>
-      <c r="I55" t="s">
-        <v>97</v>
+      <c r="I55">
+        <v>199</v>
+      </c>
+      <c r="J55" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3971,1196 +4153,1262 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R55"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="12" width="18.7109375" customWidth="1"/>
-    <col min="13" max="13" width="36.7109375" customWidth="1"/>
-    <col min="14" max="14" width="18.7109375" customWidth="1"/>
-    <col min="15" max="15" width="36.7109375" customWidth="1"/>
-    <col min="16" max="17" width="18.7109375" customWidth="1"/>
-    <col min="18" max="18" width="36.7109375" customWidth="1"/>
+    <col min="1" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="36.7109375" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="36.7109375" customWidth="1"/>
+    <col min="17" max="18" width="18.7109375" customWidth="1"/>
+    <col min="19" max="19" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" t="s">
+        <v>89</v>
+      </c>
+      <c r="K1" t="s">
+        <v>107</v>
+      </c>
+      <c r="L1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M1" t="s">
+        <v>109</v>
+      </c>
+      <c r="N1" t="s">
+        <v>110</v>
+      </c>
+      <c r="O1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P1" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>113</v>
+      </c>
+      <c r="R1" t="s">
+        <v>114</v>
+      </c>
+      <c r="S1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2">
+        <v>0.02049261083743843</v>
+      </c>
+      <c r="G2">
+        <v>0.02807881773399015</v>
+      </c>
+      <c r="H2">
+        <v>-0.00758620689655172</v>
+      </c>
+      <c r="I2">
+        <v>-0.04493901095487549</v>
+      </c>
+      <c r="J2">
+        <v>0.03040411335473123</v>
+      </c>
+      <c r="K2">
+        <v>0.6926</v>
+      </c>
+      <c r="L2">
+        <v>0.07912915589624739</v>
+      </c>
+      <c r="M2">
+        <v>1.530907631213612</v>
+      </c>
+      <c r="N2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2">
+        <v>0.7454</v>
+      </c>
+      <c r="P2" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q2">
+        <v>-0.05410272103966409</v>
+      </c>
+      <c r="R2">
+        <v>0.03893030724656065</v>
+      </c>
+      <c r="S2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3">
+        <v>0.4010837438423646</v>
+      </c>
+      <c r="G3">
+        <v>0.413743842364532</v>
+      </c>
+      <c r="H3">
+        <v>-0.01266009852216748</v>
+      </c>
+      <c r="I3">
+        <v>-0.04537308813124197</v>
+      </c>
+      <c r="J3">
+        <v>0.02084416313854757</v>
+      </c>
+      <c r="K3">
+        <v>0.461</v>
+      </c>
+      <c r="L3">
+        <v>0.1505359768729158</v>
+      </c>
+      <c r="M3">
+        <v>1.455610834346575</v>
+      </c>
+      <c r="N3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O3">
+        <v>0.461</v>
+      </c>
+      <c r="P3" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q3">
+        <v>-0.05229618964656452</v>
+      </c>
+      <c r="R3">
+        <v>0.02697599260222911</v>
+      </c>
+      <c r="S3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4">
+        <v>0.503346436828533</v>
+      </c>
+      <c r="G4">
+        <v>0.5190271308530763</v>
+      </c>
+      <c r="H4">
+        <v>-0.01568069402454331</v>
+      </c>
+      <c r="I4">
+        <v>-0.05106318963604019</v>
+      </c>
+      <c r="J4">
+        <v>0.01787937336349208</v>
+      </c>
+      <c r="K4">
+        <v>0.3852</v>
+      </c>
+      <c r="L4">
+        <v>0.0840255382977116</v>
+      </c>
+      <c r="M4">
+        <v>1.525496624127441</v>
+      </c>
+      <c r="N4" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4">
+        <v>0.3852</v>
+      </c>
+      <c r="P4" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q4">
+        <v>-0.05856576544801697</v>
+      </c>
+      <c r="R4">
+        <v>0.02781683152088908</v>
+      </c>
+      <c r="S4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5">
+        <v>0.34</v>
+      </c>
+      <c r="G5">
+        <v>0.3500000000000001</v>
+      </c>
+      <c r="H5">
+        <v>-0.01000000000000012</v>
+      </c>
+      <c r="I5">
+        <v>-0.07000000000000073</v>
+      </c>
+      <c r="J5">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="K5">
+        <v>0.6112</v>
+      </c>
+      <c r="N5" t="s">
+        <v>73</v>
+      </c>
+      <c r="O5">
+        <v>0.7282</v>
+      </c>
+      <c r="P5" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q5">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="R5">
+        <v>0.05999999999999983</v>
+      </c>
+      <c r="S5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
         <v>98</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6">
+        <v>0.5035496260262651</v>
+      </c>
+      <c r="G6">
+        <v>0.5189064985777815</v>
+      </c>
+      <c r="H6">
+        <v>-0.01535687255151641</v>
+      </c>
+      <c r="I6">
+        <v>-0.05064189418206685</v>
+      </c>
+      <c r="J6">
+        <v>0.01876017330561063</v>
+      </c>
+      <c r="K6">
+        <v>0.3894</v>
+      </c>
+      <c r="N6" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6">
+        <v>0.3894</v>
+      </c>
+      <c r="P6" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q6">
+        <v>-0.05815433485882701</v>
+      </c>
+      <c r="R6">
+        <v>0.02825025172545625</v>
+      </c>
+      <c r="S6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
         <v>99</v>
       </c>
-      <c r="E1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J1" t="s">
-        <v>103</v>
-      </c>
-      <c r="K1" t="s">
-        <v>104</v>
-      </c>
-      <c r="L1" t="s">
-        <v>105</v>
-      </c>
-      <c r="M1" t="s">
-        <v>106</v>
-      </c>
-      <c r="N1" t="s">
-        <v>107</v>
-      </c>
-      <c r="O1" t="s">
-        <v>108</v>
-      </c>
-      <c r="P1" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>110</v>
-      </c>
-      <c r="R1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D7" t="s">
         <v>50</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E7" t="s">
         <v>51</v>
       </c>
-      <c r="E2">
+      <c r="F7">
+        <v>0.6921182266009852</v>
+      </c>
+      <c r="G7">
+        <v>0.6576354679802956</v>
+      </c>
+      <c r="H7">
+        <v>0.03448275862068961</v>
+      </c>
+      <c r="I7">
+        <v>-0.01805205348027686</v>
+      </c>
+      <c r="J7">
+        <v>0.08780487804878048</v>
+      </c>
+      <c r="K7">
+        <v>0.204560421762222</v>
+      </c>
+      <c r="L7">
+        <v>0.04018448296617311</v>
+      </c>
+      <c r="M7">
+        <v>1.575352047426485</v>
+      </c>
+      <c r="N7" t="s">
+        <v>75</v>
+      </c>
+      <c r="O7">
+        <v>0.204560421762222</v>
+      </c>
+      <c r="P7" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q7">
+        <v>-0.03189014549308666</v>
+      </c>
+      <c r="R7">
+        <v>0.09762516046213096</v>
+      </c>
+      <c r="S7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8">
         <v>0.02049261083743843</v>
       </c>
-      <c r="F2">
+      <c r="G8">
+        <v>0.04536945812807881</v>
+      </c>
+      <c r="H8">
+        <v>-0.02487684729064039</v>
+      </c>
+      <c r="I8">
+        <v>-0.07516438999171429</v>
+      </c>
+      <c r="J8">
+        <v>0.02555545062902348</v>
+      </c>
+      <c r="K8">
+        <v>0.323</v>
+      </c>
+      <c r="L8">
+        <v>0.1112429598342346</v>
+      </c>
+      <c r="M8">
+        <v>1.496102394400772</v>
+      </c>
+      <c r="N8" t="s">
+        <v>72</v>
+      </c>
+      <c r="O8">
+        <v>0.5734</v>
+      </c>
+      <c r="P8" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q8">
+        <v>-0.08440726271056506</v>
+      </c>
+      <c r="R8">
+        <v>0.03465356812928424</v>
+      </c>
+      <c r="S8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9">
+        <v>0.4010837438423646</v>
+      </c>
+      <c r="G9">
+        <v>0.4725615763546798</v>
+      </c>
+      <c r="H9">
+        <v>-0.07147783251231526</v>
+      </c>
+      <c r="I9">
+        <v>-0.1094511309795232</v>
+      </c>
+      <c r="J9">
+        <v>-0.03377935695481725</v>
+      </c>
+      <c r="K9">
+        <v>0.0004</v>
+      </c>
+      <c r="L9">
+        <v>0.0589783684526196</v>
+      </c>
+      <c r="M9">
+        <v>1.553586372596406</v>
+      </c>
+      <c r="N9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O9">
+        <v>0.0004</v>
+      </c>
+      <c r="P9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q9">
+        <v>-0.1160939316204946</v>
+      </c>
+      <c r="R9">
+        <v>-0.02686173340413656</v>
+      </c>
+      <c r="S9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10">
+        <v>0.503346436828533</v>
+      </c>
+      <c r="G10">
+        <v>0.5875820873372553</v>
+      </c>
+      <c r="H10">
+        <v>-0.08423565050872228</v>
+      </c>
+      <c r="I10">
+        <v>-0.1255427629627514</v>
+      </c>
+      <c r="J10">
+        <v>-0.0419672383242247</v>
+      </c>
+      <c r="K10">
+        <v>0.0004</v>
+      </c>
+      <c r="L10">
+        <v>0.03487850112907194</v>
+      </c>
+      <c r="M10">
+        <v>1.581607874494274</v>
+      </c>
+      <c r="N10" t="s">
+        <v>72</v>
+      </c>
+      <c r="O10">
+        <v>0.0008</v>
+      </c>
+      <c r="P10" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q10">
+        <v>-0.1343146850892964</v>
+      </c>
+      <c r="R10">
+        <v>-0.03239054644227161</v>
+      </c>
+      <c r="S10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11">
+        <v>0.34</v>
+      </c>
+      <c r="G11">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="H11">
+        <v>-0.05999999999999994</v>
+      </c>
+      <c r="I11">
+        <v>-0.1199999999999999</v>
+      </c>
+      <c r="J11">
+        <v>-0.009999999999999839</v>
+      </c>
+      <c r="K11">
+        <v>0.028</v>
+      </c>
+      <c r="N11" t="s">
+        <v>73</v>
+      </c>
+      <c r="O11">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="P11" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q11">
+        <v>-0.1280741611297381</v>
+      </c>
+      <c r="R11">
+        <v>0.008074161129738217</v>
+      </c>
+      <c r="S11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12">
+        <v>0.5035496260262651</v>
+      </c>
+      <c r="G12">
+        <v>0.5865506926221365</v>
+      </c>
+      <c r="H12">
+        <v>-0.08300106659587148</v>
+      </c>
+      <c r="I12">
+        <v>-0.1240127595235769</v>
+      </c>
+      <c r="J12">
+        <v>-0.04070333062115</v>
+      </c>
+      <c r="K12">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="N12" t="s">
+        <v>74</v>
+      </c>
+      <c r="O12">
+        <v>0.0008</v>
+      </c>
+      <c r="P12" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q12">
+        <v>-0.1324121069898527</v>
+      </c>
+      <c r="R12">
+        <v>-0.03081160526701519</v>
+      </c>
+      <c r="S12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13">
+        <v>0.6921182266009852</v>
+      </c>
+      <c r="G13">
+        <v>0.6108374384236454</v>
+      </c>
+      <c r="H13">
+        <v>0.08128078817733986</v>
+      </c>
+      <c r="I13">
+        <v>0.02216476440614372</v>
+      </c>
+      <c r="J13">
+        <v>0.1403530377668309</v>
+      </c>
+      <c r="K13">
+        <v>0.006863871555196087</v>
+      </c>
+      <c r="L13">
+        <v>0.074687129444328</v>
+      </c>
+      <c r="M13">
+        <v>1.535849843792607</v>
+      </c>
+      <c r="N13" t="s">
+        <v>75</v>
+      </c>
+      <c r="O13">
+        <v>0.02059161466558826</v>
+      </c>
+      <c r="P13" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q13">
+        <v>0.009991271820448863</v>
+      </c>
+      <c r="R13">
+        <v>0.152573275862069</v>
+      </c>
+      <c r="S13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14">
         <v>0.02807881773399015</v>
       </c>
-      <c r="G2">
-        <v>-0.00758620689655172</v>
-      </c>
-      <c r="H2">
-        <v>-0.04493901095487549</v>
-      </c>
-      <c r="I2">
-        <v>0.03040411335473123</v>
-      </c>
-      <c r="J2">
-        <v>0.6926</v>
-      </c>
-      <c r="K2">
-        <v>0.07912915589624739</v>
-      </c>
-      <c r="L2">
-        <v>1.530907631213612</v>
-      </c>
-      <c r="M2" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2">
+      <c r="G14">
+        <v>0.04536945812807881</v>
+      </c>
+      <c r="H14">
+        <v>-0.01729064039408867</v>
+      </c>
+      <c r="I14">
+        <v>-0.07150679591982625</v>
+      </c>
+      <c r="J14">
+        <v>0.03668306575040813</v>
+      </c>
+      <c r="K14">
+        <v>0.518</v>
+      </c>
+      <c r="L14">
+        <v>0.1843641333656313</v>
+      </c>
+      <c r="M14">
+        <v>1.422466582636034</v>
+      </c>
+      <c r="N14" t="s">
+        <v>72</v>
+      </c>
+      <c r="O14">
         <v>0.7454</v>
       </c>
-      <c r="O2" t="s">
-        <v>115</v>
-      </c>
-      <c r="P2">
-        <v>-0.05410272103966409</v>
-      </c>
-      <c r="Q2">
-        <v>0.03893030724656065</v>
-      </c>
-      <c r="R2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="P14" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q14">
+        <v>-0.08180644473769279</v>
+      </c>
+      <c r="R14">
+        <v>0.04722516394951541</v>
+      </c>
+      <c r="S14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
         <v>51</v>
       </c>
-      <c r="E3">
-        <v>0.4010837438423646</v>
-      </c>
-      <c r="F3">
+      <c r="E15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15">
         <v>0.413743842364532</v>
       </c>
-      <c r="G3">
-        <v>-0.01266009852216748</v>
-      </c>
-      <c r="H3">
-        <v>-0.04537308813124197</v>
-      </c>
-      <c r="I3">
-        <v>0.02084416313854757</v>
-      </c>
-      <c r="J3">
-        <v>0.461</v>
-      </c>
-      <c r="K3">
-        <v>0.1505359768729158</v>
-      </c>
-      <c r="L3">
-        <v>1.455610834346575</v>
-      </c>
-      <c r="M3" t="s">
-        <v>71</v>
-      </c>
-      <c r="N3">
-        <v>0.461</v>
-      </c>
-      <c r="O3" t="s">
-        <v>115</v>
-      </c>
-      <c r="P3">
-        <v>-0.05229618964656452</v>
-      </c>
-      <c r="Q3">
-        <v>0.02697599260222911</v>
-      </c>
-      <c r="R3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="G15">
+        <v>0.4725615763546798</v>
+      </c>
+      <c r="H15">
+        <v>-0.05881773399014778</v>
+      </c>
+      <c r="I15">
+        <v>-0.1025986784782056</v>
+      </c>
+      <c r="J15">
+        <v>-0.01794955791900316</v>
+      </c>
+      <c r="K15">
+        <v>0.005</v>
+      </c>
+      <c r="L15">
+        <v>0.187351608726497</v>
+      </c>
+      <c r="M15">
+        <v>1.419611895158891</v>
+      </c>
+      <c r="N15" t="s">
+        <v>72</v>
+      </c>
+      <c r="O15">
+        <v>0.0104</v>
+      </c>
+      <c r="P15" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q15">
+        <v>-0.1084139624854691</v>
+      </c>
+      <c r="R15">
+        <v>-0.009221505494826733</v>
+      </c>
+      <c r="S15" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
         <v>51</v>
       </c>
-      <c r="E4">
-        <v>0.503346436828533</v>
-      </c>
-      <c r="F4">
+      <c r="E16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16">
         <v>0.5190271308530763</v>
       </c>
-      <c r="G4">
-        <v>-0.01568069402454331</v>
-      </c>
-      <c r="H4">
-        <v>-0.05106318963604019</v>
-      </c>
-      <c r="I4">
-        <v>0.01787937336349208</v>
-      </c>
-      <c r="J4">
-        <v>0.3852</v>
-      </c>
-      <c r="K4">
-        <v>0.0840255382977116</v>
-      </c>
-      <c r="L4">
-        <v>1.525496624127441</v>
-      </c>
-      <c r="M4" t="s">
-        <v>71</v>
-      </c>
-      <c r="N4">
-        <v>0.3852</v>
-      </c>
-      <c r="O4" t="s">
-        <v>115</v>
-      </c>
-      <c r="P4">
-        <v>-0.05856576544801697</v>
-      </c>
-      <c r="Q4">
-        <v>0.02781683152088908</v>
-      </c>
-      <c r="R4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="G16">
+        <v>0.5875820873372553</v>
+      </c>
+      <c r="H16">
+        <v>-0.06855495648417897</v>
+      </c>
+      <c r="I16">
+        <v>-0.1131287403553189</v>
+      </c>
+      <c r="J16">
+        <v>-0.02214090274061026</v>
+      </c>
+      <c r="K16">
+        <v>0.0036</v>
+      </c>
+      <c r="L16">
+        <v>0.1031443239050249</v>
+      </c>
+      <c r="M16">
+        <v>1.504729680828269</v>
+      </c>
+      <c r="N16" t="s">
+        <v>72</v>
+      </c>
+      <c r="O16">
+        <v>0.0052</v>
+      </c>
+      <c r="P16" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q16">
+        <v>-0.1237607966652773</v>
+      </c>
+      <c r="R16">
+        <v>-0.01197481543232409</v>
+      </c>
+      <c r="S16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
         <v>51</v>
       </c>
-      <c r="E5">
-        <v>0.34</v>
-      </c>
-      <c r="F5">
+      <c r="E17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17">
         <v>0.3500000000000001</v>
       </c>
-      <c r="G5">
-        <v>-0.01000000000000012</v>
-      </c>
-      <c r="H5">
-        <v>-0.07000000000000073</v>
-      </c>
-      <c r="I5">
-        <v>0.04000000000000004</v>
-      </c>
-      <c r="J5">
-        <v>0.6112</v>
-      </c>
-      <c r="M5" t="s">
-        <v>72</v>
-      </c>
-      <c r="N5">
-        <v>0.7282</v>
-      </c>
-      <c r="O5" t="s">
-        <v>115</v>
-      </c>
-      <c r="P5">
-        <v>-0.08000000000000007</v>
-      </c>
-      <c r="Q5">
-        <v>0.05999999999999983</v>
-      </c>
-      <c r="R5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="G17">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="H17">
+        <v>-0.04999999999999982</v>
+      </c>
+      <c r="I17">
+        <v>-0.1099999999999999</v>
+      </c>
+      <c r="J17">
+        <v>0.01000000000000035</v>
+      </c>
+      <c r="K17">
+        <v>0.1748</v>
+      </c>
+      <c r="N17" t="s">
+        <v>73</v>
+      </c>
+      <c r="O17">
+        <v>0.2226</v>
+      </c>
+      <c r="P17" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q17">
+        <v>-0.1230166690346133</v>
+      </c>
+      <c r="R17">
+        <v>0.02301666903461366</v>
+      </c>
+      <c r="S17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
         <v>51</v>
       </c>
-      <c r="E6">
-        <v>0.5035496260262651</v>
-      </c>
-      <c r="F6">
+      <c r="E18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18">
         <v>0.5189064985777815</v>
       </c>
-      <c r="G6">
-        <v>-0.01535687255151641</v>
-      </c>
-      <c r="H6">
-        <v>-0.05064189418206685</v>
-      </c>
-      <c r="I6">
-        <v>0.01876017330561063</v>
-      </c>
-      <c r="J6">
-        <v>0.3894</v>
-      </c>
-      <c r="M6" t="s">
-        <v>73</v>
-      </c>
-      <c r="N6">
-        <v>0.3894</v>
-      </c>
-      <c r="O6" t="s">
-        <v>115</v>
-      </c>
-      <c r="P6">
-        <v>-0.05815433485882701</v>
-      </c>
-      <c r="Q6">
-        <v>0.02825025172545625</v>
-      </c>
-      <c r="R6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="G18">
+        <v>0.5865506926221365</v>
+      </c>
+      <c r="H18">
+        <v>-0.06764419404435507</v>
+      </c>
+      <c r="I18">
+        <v>-0.1119735373189496</v>
+      </c>
+      <c r="J18">
+        <v>-0.02111883542966709</v>
+      </c>
+      <c r="K18">
+        <v>0.005</v>
+      </c>
+      <c r="N18" t="s">
+        <v>74</v>
+      </c>
+      <c r="O18">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="P18" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q18">
+        <v>-0.1227389787054996</v>
+      </c>
+      <c r="R18">
+        <v>-0.009991811914109265</v>
+      </c>
+      <c r="S18" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" t="s">
         <v>51</v>
       </c>
-      <c r="E7">
-        <v>0.6921182266009852</v>
-      </c>
-      <c r="F7">
+      <c r="E19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19">
         <v>0.6576354679802956</v>
       </c>
-      <c r="G7">
-        <v>0.03448275862068961</v>
-      </c>
-      <c r="H7">
-        <v>-0.01805205348027686</v>
-      </c>
-      <c r="I7">
-        <v>0.08780487804878048</v>
-      </c>
-      <c r="J7">
+      <c r="G19">
+        <v>0.6108374384236454</v>
+      </c>
+      <c r="H19">
+        <v>0.04679802955665024</v>
+      </c>
+      <c r="I19">
+        <v>-0.01452960812430945</v>
+      </c>
+      <c r="J19">
+        <v>0.1075</v>
+      </c>
+      <c r="K19">
+        <v>0.1319988990199734</v>
+      </c>
+      <c r="L19">
+        <v>0.1820022159757861</v>
+      </c>
+      <c r="M19">
+        <v>1.42473165658859</v>
+      </c>
+      <c r="N19" t="s">
+        <v>75</v>
+      </c>
+      <c r="O19">
         <v>0.204560421762222</v>
       </c>
-      <c r="K7">
-        <v>0.04018448296617311</v>
-      </c>
-      <c r="L7">
-        <v>1.575352047426485</v>
-      </c>
-      <c r="M7" t="s">
-        <v>74</v>
-      </c>
-      <c r="N7">
-        <v>0.204560421762222</v>
-      </c>
-      <c r="O7" t="s">
-        <v>116</v>
-      </c>
-      <c r="P7">
-        <v>-0.03189014549308666</v>
-      </c>
-      <c r="Q7">
-        <v>0.09762516046213096</v>
-      </c>
-      <c r="R7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8">
-        <v>0.02049261083743843</v>
-      </c>
-      <c r="F8">
-        <v>0.04536945812807881</v>
-      </c>
-      <c r="G8">
-        <v>-0.02487684729064039</v>
-      </c>
-      <c r="H8">
-        <v>-0.07516438999171429</v>
-      </c>
-      <c r="I8">
-        <v>0.02555545062902348</v>
-      </c>
-      <c r="J8">
-        <v>0.323</v>
-      </c>
-      <c r="K8">
-        <v>0.1112429598342346</v>
-      </c>
-      <c r="L8">
-        <v>1.496102394400772</v>
-      </c>
-      <c r="M8" t="s">
-        <v>71</v>
-      </c>
-      <c r="N8">
-        <v>0.5734</v>
-      </c>
-      <c r="O8" t="s">
-        <v>115</v>
-      </c>
-      <c r="P8">
-        <v>-0.08440726271056506</v>
-      </c>
-      <c r="Q8">
-        <v>0.03465356812928424</v>
-      </c>
-      <c r="R8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9">
-        <v>0.4010837438423646</v>
-      </c>
-      <c r="F9">
-        <v>0.4725615763546798</v>
-      </c>
-      <c r="G9">
-        <v>-0.07147783251231526</v>
-      </c>
-      <c r="H9">
-        <v>-0.1094511309795232</v>
-      </c>
-      <c r="I9">
-        <v>-0.03377935695481725</v>
-      </c>
-      <c r="J9">
-        <v>0.0004</v>
-      </c>
-      <c r="K9">
-        <v>0.0589783684526196</v>
-      </c>
-      <c r="L9">
-        <v>1.553586372596406</v>
-      </c>
-      <c r="M9" t="s">
-        <v>71</v>
-      </c>
-      <c r="N9">
-        <v>0.0004</v>
-      </c>
-      <c r="O9" t="s">
-        <v>115</v>
-      </c>
-      <c r="P9">
-        <v>-0.1160939316204946</v>
-      </c>
-      <c r="Q9">
-        <v>-0.02686173340413656</v>
-      </c>
-      <c r="R9" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10">
-        <v>0.503346436828533</v>
-      </c>
-      <c r="F10">
-        <v>0.5875820873372553</v>
-      </c>
-      <c r="G10">
-        <v>-0.08423565050872228</v>
-      </c>
-      <c r="H10">
-        <v>-0.1255427629627514</v>
-      </c>
-      <c r="I10">
-        <v>-0.0419672383242247</v>
-      </c>
-      <c r="J10">
-        <v>0.0004</v>
-      </c>
-      <c r="K10">
-        <v>0.03487850112907194</v>
-      </c>
-      <c r="L10">
-        <v>1.581607874494274</v>
-      </c>
-      <c r="M10" t="s">
-        <v>71</v>
-      </c>
-      <c r="N10">
-        <v>0.0008</v>
-      </c>
-      <c r="O10" t="s">
-        <v>115</v>
-      </c>
-      <c r="P10">
-        <v>-0.1343146850892964</v>
-      </c>
-      <c r="Q10">
-        <v>-0.03239054644227161</v>
-      </c>
-      <c r="R10" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11">
-        <v>0.34</v>
-      </c>
-      <c r="F11">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="G11">
-        <v>-0.05999999999999994</v>
-      </c>
-      <c r="H11">
-        <v>-0.1199999999999999</v>
-      </c>
-      <c r="I11">
-        <v>-0.009999999999999839</v>
-      </c>
-      <c r="J11">
-        <v>0.028</v>
-      </c>
-      <c r="M11" t="s">
-        <v>72</v>
-      </c>
-      <c r="N11">
-        <v>0.09279999999999999</v>
-      </c>
-      <c r="O11" t="s">
-        <v>115</v>
-      </c>
-      <c r="P11">
-        <v>-0.1280741611297381</v>
-      </c>
-      <c r="Q11">
-        <v>0.008074161129738217</v>
-      </c>
-      <c r="R11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12">
-        <v>0.5035496260262651</v>
-      </c>
-      <c r="F12">
-        <v>0.5865506926221365</v>
-      </c>
-      <c r="G12">
-        <v>-0.08300106659587148</v>
-      </c>
-      <c r="H12">
-        <v>-0.1240127595235769</v>
-      </c>
-      <c r="I12">
-        <v>-0.04070333062115</v>
-      </c>
-      <c r="J12">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="M12" t="s">
-        <v>73</v>
-      </c>
-      <c r="N12">
-        <v>0.0008</v>
-      </c>
-      <c r="O12" t="s">
-        <v>115</v>
-      </c>
-      <c r="P12">
-        <v>-0.1324121069898527</v>
-      </c>
-      <c r="Q12">
-        <v>-0.03081160526701519</v>
-      </c>
-      <c r="R12" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13">
-        <v>0.6921182266009852</v>
-      </c>
-      <c r="F13">
-        <v>0.6108374384236454</v>
-      </c>
-      <c r="G13">
-        <v>0.08128078817733986</v>
-      </c>
-      <c r="H13">
-        <v>0.02216476440614372</v>
-      </c>
-      <c r="I13">
-        <v>0.1403530377668309</v>
-      </c>
-      <c r="J13">
-        <v>0.006863871555196087</v>
-      </c>
-      <c r="K13">
-        <v>0.074687129444328</v>
-      </c>
-      <c r="L13">
-        <v>1.535849843792607</v>
-      </c>
-      <c r="M13" t="s">
-        <v>74</v>
-      </c>
-      <c r="N13">
-        <v>0.02059161466558826</v>
-      </c>
-      <c r="O13" t="s">
-        <v>116</v>
-      </c>
-      <c r="P13">
-        <v>0.009991271820448863</v>
-      </c>
-      <c r="Q13">
-        <v>0.152573275862069</v>
-      </c>
-      <c r="R13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14">
-        <v>0.02807881773399015</v>
-      </c>
-      <c r="F14">
-        <v>0.04536945812807881</v>
-      </c>
-      <c r="G14">
-        <v>-0.01729064039408867</v>
-      </c>
-      <c r="H14">
-        <v>-0.07150679591982625</v>
-      </c>
-      <c r="I14">
-        <v>0.03668306575040813</v>
-      </c>
-      <c r="J14">
-        <v>0.518</v>
-      </c>
-      <c r="K14">
-        <v>0.1843641333656313</v>
-      </c>
-      <c r="L14">
-        <v>1.422466582636034</v>
-      </c>
-      <c r="M14" t="s">
-        <v>71</v>
-      </c>
-      <c r="N14">
-        <v>0.7454</v>
-      </c>
-      <c r="O14" t="s">
-        <v>115</v>
-      </c>
-      <c r="P14">
-        <v>-0.08180644473769279</v>
-      </c>
-      <c r="Q14">
-        <v>0.04722516394951541</v>
-      </c>
-      <c r="R14" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15">
-        <v>0.413743842364532</v>
-      </c>
-      <c r="F15">
-        <v>0.4725615763546798</v>
-      </c>
-      <c r="G15">
-        <v>-0.05881773399014778</v>
-      </c>
-      <c r="H15">
-        <v>-0.1025986784782056</v>
-      </c>
-      <c r="I15">
-        <v>-0.01794955791900316</v>
-      </c>
-      <c r="J15">
-        <v>0.005</v>
-      </c>
-      <c r="K15">
-        <v>0.187351608726497</v>
-      </c>
-      <c r="L15">
-        <v>1.419611895158891</v>
-      </c>
-      <c r="M15" t="s">
-        <v>71</v>
-      </c>
-      <c r="N15">
-        <v>0.0104</v>
-      </c>
-      <c r="O15" t="s">
-        <v>115</v>
-      </c>
-      <c r="P15">
-        <v>-0.1084139624854691</v>
-      </c>
-      <c r="Q15">
-        <v>-0.009221505494826733</v>
-      </c>
-      <c r="R15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16">
-        <v>0.5190271308530763</v>
-      </c>
-      <c r="F16">
-        <v>0.5875820873372553</v>
-      </c>
-      <c r="G16">
-        <v>-0.06855495648417897</v>
-      </c>
-      <c r="H16">
-        <v>-0.1131287403553189</v>
-      </c>
-      <c r="I16">
-        <v>-0.02214090274061026</v>
-      </c>
-      <c r="J16">
-        <v>0.0036</v>
-      </c>
-      <c r="K16">
-        <v>0.1031443239050249</v>
-      </c>
-      <c r="L16">
-        <v>1.504729680828269</v>
-      </c>
-      <c r="M16" t="s">
-        <v>71</v>
-      </c>
-      <c r="N16">
-        <v>0.0052</v>
-      </c>
-      <c r="O16" t="s">
-        <v>115</v>
-      </c>
-      <c r="P16">
-        <v>-0.1237607966652773</v>
-      </c>
-      <c r="Q16">
-        <v>-0.01197481543232409</v>
-      </c>
-      <c r="R16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17">
-        <v>0.3500000000000001</v>
-      </c>
-      <c r="F17">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="G17">
-        <v>-0.04999999999999982</v>
-      </c>
-      <c r="H17">
-        <v>-0.1099999999999999</v>
-      </c>
-      <c r="I17">
-        <v>0.01000000000000035</v>
-      </c>
-      <c r="J17">
-        <v>0.1748</v>
-      </c>
-      <c r="M17" t="s">
-        <v>72</v>
-      </c>
-      <c r="N17">
-        <v>0.2226</v>
-      </c>
-      <c r="O17" t="s">
-        <v>115</v>
-      </c>
-      <c r="P17">
-        <v>-0.1230166690346133</v>
-      </c>
-      <c r="Q17">
-        <v>0.02301666903461366</v>
-      </c>
-      <c r="R17" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18">
-        <v>0.5189064985777815</v>
-      </c>
-      <c r="F18">
-        <v>0.5865506926221365</v>
-      </c>
-      <c r="G18">
-        <v>-0.06764419404435507</v>
-      </c>
-      <c r="H18">
-        <v>-0.1119735373189496</v>
-      </c>
-      <c r="I18">
-        <v>-0.02111883542966709</v>
-      </c>
-      <c r="J18">
-        <v>0.005</v>
-      </c>
-      <c r="M18" t="s">
-        <v>73</v>
-      </c>
-      <c r="N18">
-        <v>0.008399999999999999</v>
-      </c>
-      <c r="O18" t="s">
-        <v>115</v>
-      </c>
-      <c r="P18">
-        <v>-0.1227389787054996</v>
-      </c>
-      <c r="Q18">
-        <v>-0.009991811914109265</v>
-      </c>
-      <c r="R18" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19">
-        <v>0.6576354679802956</v>
-      </c>
-      <c r="F19">
-        <v>0.6108374384236454</v>
-      </c>
-      <c r="G19">
-        <v>0.04679802955665024</v>
-      </c>
-      <c r="H19">
-        <v>-0.01452960812430945</v>
-      </c>
-      <c r="I19">
-        <v>0.1075</v>
-      </c>
-      <c r="J19">
-        <v>0.1319988990199734</v>
-      </c>
-      <c r="K19">
-        <v>0.1820022159757861</v>
-      </c>
-      <c r="L19">
-        <v>1.42473165658859</v>
-      </c>
-      <c r="M19" t="s">
-        <v>74</v>
-      </c>
-      <c r="N19">
-        <v>0.204560421762222</v>
-      </c>
-      <c r="O19" t="s">
-        <v>116</v>
-      </c>
-      <c r="P19">
+      <c r="P19" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q19">
         <v>-0.02693148335989953</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>0.118272411680621</v>
       </c>
-      <c r="R19" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
+      <c r="S19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" t="s">
         <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" t="s">
         <v>50</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>51</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.01473429951690822</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.006376811594202901</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0.008357487922705319</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>-0.03937699896679999</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>0.05950336880945854</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.7482</v>
       </c>
-      <c r="M20" t="s">
-        <v>112</v>
-      </c>
-      <c r="N20">
+      <c r="N20" t="s">
+        <v>116</v>
+      </c>
+      <c r="O20">
         <v>0.9228</v>
       </c>
-      <c r="O20" t="s">
-        <v>115</v>
-      </c>
-      <c r="P20">
+      <c r="P20" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q20">
         <v>-0.05103539816859672</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>0.06775037401400737</v>
       </c>
-      <c r="R20" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
+      <c r="S20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" t="s">
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" t="s">
         <v>50</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>51</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.4014975845410628</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.4215458937198068</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>-0.02004830917874395</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>-0.06341673548373197</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.02278842149249139</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>0.3648</v>
       </c>
-      <c r="M21" t="s">
-        <v>112</v>
-      </c>
-      <c r="N21">
+      <c r="N21" t="s">
+        <v>116</v>
+      </c>
+      <c r="O21">
         <v>0.3648</v>
       </c>
-      <c r="O21" t="s">
-        <v>115</v>
-      </c>
-      <c r="P21">
+      <c r="P21" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q21">
         <v>-0.07233878000738253</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>0.03224216164989475</v>
       </c>
-      <c r="R21" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
+      <c r="S21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" t="s">
         <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" t="s">
         <v>50</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>51</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.4993498188103143</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.5350976252975095</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>-0.03574780648719517</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>-0.08117500431921684</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>0.01103192398107171</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>0.1386</v>
       </c>
-      <c r="M22" t="s">
-        <v>112</v>
-      </c>
-      <c r="N22">
+      <c r="N22" t="s">
+        <v>116</v>
+      </c>
+      <c r="O22">
         <v>0.2192</v>
       </c>
-      <c r="O22" t="s">
-        <v>115</v>
-      </c>
-      <c r="P22">
+      <c r="P22" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q22">
         <v>-0.09123869203614131</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>0.0222793709494871</v>
       </c>
-      <c r="R22" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
+      <c r="S22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -5168,299 +5416,317 @@
         <v>93</v>
       </c>
       <c r="C23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" t="s">
         <v>50</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>51</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.3599999999999999</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.37</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>-0.01000000000000012</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>-0.09999999999999987</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>0.05999999999999994</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>0.6612</v>
       </c>
-      <c r="M23" t="s">
-        <v>113</v>
-      </c>
-      <c r="N23">
+      <c r="N23" t="s">
+        <v>117</v>
+      </c>
+      <c r="O23">
         <v>0.7706</v>
       </c>
-      <c r="O23" t="s">
-        <v>115</v>
-      </c>
-      <c r="P23">
+      <c r="P23" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q23">
         <v>-0.1038971985921919</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>0.08389719859219168</v>
       </c>
-      <c r="R23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
+      <c r="S23" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" t="s">
         <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" t="s">
         <v>50</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>51</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>0.5003424089040717</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>0.5363567435512407</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>-0.03601433464716908</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>-0.08128862160672953</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>0.01090263065652809</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>0.1346</v>
       </c>
-      <c r="M24" t="s">
-        <v>73</v>
-      </c>
-      <c r="N24">
+      <c r="N24" t="s">
+        <v>74</v>
+      </c>
+      <c r="O24">
         <v>0.2062</v>
       </c>
-      <c r="O24" t="s">
-        <v>115</v>
-      </c>
-      <c r="P24">
+      <c r="P24" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q24">
         <v>-0.09115161458112336</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>0.02135292562963592</v>
       </c>
-      <c r="R24" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
+      <c r="S24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" t="s">
         <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" t="s">
         <v>50</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>51</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>0.714975845410628</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>0.6473429951690821</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>0.06763285024154586</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>-0.004830917874396135</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>0.1400966183574879</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>0.08782509563019504</v>
       </c>
-      <c r="M25" t="s">
-        <v>114</v>
-      </c>
-      <c r="N25">
+      <c r="N25" t="s">
+        <v>118</v>
+      </c>
+      <c r="O25">
         <v>0.1756501912603901</v>
       </c>
-      <c r="O25" t="s">
-        <v>116</v>
-      </c>
-      <c r="P25">
+      <c r="P25" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q25">
         <v>-0.01932367149758452</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>0.1594202898550724</v>
       </c>
-      <c r="R25" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
+      <c r="S25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" t="s">
         <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" t="s">
         <v>50</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>52</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>0.01473429951690822</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>0.002318840579710145</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>0.01241545893719808</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>-0.05180369647565036</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>0.07238411204395538</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>0.6962</v>
       </c>
-      <c r="M26" t="s">
-        <v>112</v>
-      </c>
-      <c r="N26">
+      <c r="N26" t="s">
+        <v>116</v>
+      </c>
+      <c r="O26">
         <v>0.9156</v>
       </c>
-      <c r="O26" t="s">
-        <v>115</v>
-      </c>
-      <c r="P26">
+      <c r="P26" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q26">
         <v>-0.06168545131060543</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>0.08651636918500157</v>
       </c>
-      <c r="R26" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
+      <c r="S26" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" t="s">
         <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" t="s">
         <v>50</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>52</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>0.4014975845410628</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>0.4694685990338164</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>-0.06797101449275361</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>-0.1150446795079015</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>-0.01980502496348764</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>0.0066</v>
       </c>
-      <c r="M27" t="s">
-        <v>112</v>
-      </c>
-      <c r="N27">
+      <c r="N27" t="s">
+        <v>116</v>
+      </c>
+      <c r="O27">
         <v>0.0182</v>
       </c>
-      <c r="O27" t="s">
-        <v>115</v>
-      </c>
-      <c r="P27">
+      <c r="P27" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q27">
         <v>-0.1263846722789996</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>-0.009557356706507911</v>
       </c>
-      <c r="R27" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
+      <c r="S27" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" t="s">
         <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" t="s">
         <v>50</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>52</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>0.4993498188103143</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>0.5841530472476332</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>-0.08480322843731886</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>-0.1392818727626998</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>-0.02765282063164901</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>0.004</v>
       </c>
-      <c r="M28" t="s">
-        <v>112</v>
-      </c>
-      <c r="N28">
+      <c r="N28" t="s">
+        <v>116</v>
+      </c>
+      <c r="O28">
         <v>0.0112</v>
       </c>
-      <c r="O28" t="s">
-        <v>115</v>
-      </c>
-      <c r="P28">
+      <c r="P28" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q28">
         <v>-0.1509793143671761</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>-0.01141466056599736</v>
       </c>
-      <c r="R28" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18">
+      <c r="S28" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -5468,299 +5734,317 @@
         <v>93</v>
       </c>
       <c r="C29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" t="s">
         <v>50</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>52</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>0.3599999999999999</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>0.4199999999999999</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>-0.06000000000000005</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>-0.15</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>-1.110223024625157E-16</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>0.044</v>
       </c>
-      <c r="M29" t="s">
-        <v>113</v>
-      </c>
-      <c r="N29">
+      <c r="N29" t="s">
+        <v>117</v>
+      </c>
+      <c r="O29">
         <v>0.3118</v>
       </c>
-      <c r="O29" t="s">
-        <v>115</v>
-      </c>
-      <c r="P29">
+      <c r="P29" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q29">
         <v>-0.1500000000000001</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>0.03000000000000003</v>
       </c>
-      <c r="R29" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18">
+      <c r="S29" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" t="s">
         <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" t="s">
         <v>50</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>52</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>0.5003424089040717</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>0.5855645643413213</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>-0.08522215543724965</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>-0.1400943073214456</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>-0.02918989008947918</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>0.006</v>
       </c>
-      <c r="M30" t="s">
-        <v>73</v>
-      </c>
-      <c r="N30">
+      <c r="N30" t="s">
+        <v>74</v>
+      </c>
+      <c r="O30">
         <v>0.0176</v>
       </c>
-      <c r="O30" t="s">
-        <v>115</v>
-      </c>
-      <c r="P30">
+      <c r="P30" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q30">
         <v>-0.1511909993124804</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>-0.01232031333021981</v>
       </c>
-      <c r="R30" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18">
+      <c r="S30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" t="s">
         <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" t="s">
         <v>50</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>52</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>0.714975845410628</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>0.6038647342995169</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>0.111111111111111</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>0.03381642512077294</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>0.1835748792270532</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>0.006357215082587968</v>
       </c>
-      <c r="M31" t="s">
-        <v>114</v>
-      </c>
-      <c r="N31">
+      <c r="N31" t="s">
+        <v>118</v>
+      </c>
+      <c r="O31">
         <v>0.0190716452477639</v>
       </c>
-      <c r="O31" t="s">
-        <v>116</v>
-      </c>
-      <c r="P31">
+      <c r="P31" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q31">
         <v>0.01932367149758452</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>0.2028985507246377</v>
       </c>
-      <c r="R31" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18">
+      <c r="S31" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
         <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" t="s">
         <v>51</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>52</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>0.006376811594202901</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>0.002318840579710145</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>0.004057971014492756</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>-0.06646966441868675</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>0.07049753251267667</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>0.9026</v>
       </c>
-      <c r="M32" t="s">
-        <v>112</v>
-      </c>
-      <c r="N32">
+      <c r="N32" t="s">
+        <v>116</v>
+      </c>
+      <c r="O32">
         <v>0.9228</v>
       </c>
-      <c r="O32" t="s">
-        <v>115</v>
-      </c>
-      <c r="P32">
+      <c r="P32" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q32">
         <v>-0.07685225067811854</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>0.08496819270710404</v>
       </c>
-      <c r="R32" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18">
+      <c r="S32" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" t="s">
         <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
+        <v>95</v>
+      </c>
+      <c r="D33" t="s">
         <v>51</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>52</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>0.4215458937198068</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>0.4694685990338164</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>-0.04792270531400966</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>-0.1024447384258064</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>0.005401149152844641</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>0.0788</v>
       </c>
-      <c r="M33" t="s">
-        <v>112</v>
-      </c>
-      <c r="N33">
+      <c r="N33" t="s">
+        <v>116</v>
+      </c>
+      <c r="O33">
         <v>0.1346</v>
       </c>
-      <c r="O33" t="s">
-        <v>115</v>
-      </c>
-      <c r="P33">
+      <c r="P33" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q33">
         <v>-0.111707487254363</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>0.01586207662634324</v>
       </c>
-      <c r="R33" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18">
+      <c r="S33" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34" t="s">
         <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" t="s">
         <v>51</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>52</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>0.5350976252975095</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>0.5841530472476332</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>-0.04905542195012369</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>-0.1111569370207811</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>0.01275237325302565</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>0.1238</v>
       </c>
-      <c r="M34" t="s">
-        <v>112</v>
-      </c>
-      <c r="N34">
+      <c r="N34" t="s">
+        <v>116</v>
+      </c>
+      <c r="O34">
         <v>0.2192</v>
       </c>
-      <c r="O34" t="s">
-        <v>115</v>
-      </c>
-      <c r="P34">
+      <c r="P34" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q34">
         <v>-0.1238415295689909</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>0.02673239532361265</v>
       </c>
-      <c r="R34" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18">
+      <c r="S34" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -5768,299 +6052,317 @@
         <v>93</v>
       </c>
       <c r="C35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" t="s">
         <v>51</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>52</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>0.37</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>0.4199999999999999</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>-0.04999999999999993</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>-0.1400000000000001</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>0.02999999999999992</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>0.224</v>
       </c>
-      <c r="M35" t="s">
-        <v>113</v>
-      </c>
-      <c r="N35">
+      <c r="N35" t="s">
+        <v>117</v>
+      </c>
+      <c r="O35">
         <v>0.4476</v>
       </c>
-      <c r="O35" t="s">
-        <v>115</v>
-      </c>
-      <c r="P35">
+      <c r="P35" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q35">
         <v>-0.1519260792971539</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>0.05192607929715401</v>
       </c>
-      <c r="R35" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18">
+      <c r="S35" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
       <c r="A36" t="s">
         <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36" t="s">
         <v>51</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>52</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>0.5363567435512407</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>0.5855645643413213</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>-0.04920782079008057</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>-0.1114327077564691</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>0.01244135367620838</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>0.1184</v>
       </c>
-      <c r="M36" t="s">
-        <v>73</v>
-      </c>
-      <c r="N36">
+      <c r="N36" t="s">
+        <v>74</v>
+      </c>
+      <c r="O36">
         <v>0.2062</v>
       </c>
-      <c r="O36" t="s">
-        <v>115</v>
-      </c>
-      <c r="P36">
+      <c r="P36" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q36">
         <v>-0.1228604273873636</v>
       </c>
-      <c r="Q36">
+      <c r="R36">
         <v>0.02669462629634863</v>
       </c>
-      <c r="R36" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18">
+      <c r="S36" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
       <c r="A37" t="s">
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" t="s">
         <v>51</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>52</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>0.6473429951690821</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>0.6038647342995169</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>0.04347826086956519</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>-0.03381642512077294</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>0.1159420289855072</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>0.3134999455835852</v>
       </c>
-      <c r="M37" t="s">
-        <v>114</v>
-      </c>
-      <c r="N37">
+      <c r="N37" t="s">
+        <v>118</v>
+      </c>
+      <c r="O37">
         <v>0.3134999455835852</v>
       </c>
-      <c r="O37" t="s">
-        <v>116</v>
-      </c>
-      <c r="P37">
+      <c r="P37" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q37">
         <v>-0.04830917874396135</v>
       </c>
-      <c r="Q37">
+      <c r="R37">
         <v>0.1352657004830918</v>
       </c>
-      <c r="R37" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18">
+      <c r="S37" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
       <c r="A38" t="s">
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C38" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" t="s">
         <v>50</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>51</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>0.02648241206030149</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>0.05065326633165827</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>-0.02417085427135678</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>-0.07938859663334021</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>0.03473953972963441</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>0.3916</v>
       </c>
-      <c r="M38" t="s">
-        <v>112</v>
-      </c>
-      <c r="N38">
+      <c r="N38" t="s">
+        <v>116</v>
+      </c>
+      <c r="O38">
         <v>0.4768</v>
       </c>
-      <c r="O38" t="s">
-        <v>115</v>
-      </c>
-      <c r="P38">
+      <c r="P38" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q38">
         <v>-0.0908680477437257</v>
       </c>
-      <c r="Q38">
+      <c r="R38">
         <v>0.0425263392010121</v>
       </c>
-      <c r="R38" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18">
+      <c r="S38" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
       <c r="A39" t="s">
         <v>49</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D39" t="s">
         <v>50</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>51</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>0.4006532663316583</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>0.4056281407035176</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>-0.004974874371859284</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>-0.05070529366418342</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>0.04187065486244625</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>0.8314</v>
       </c>
-      <c r="M39" t="s">
-        <v>112</v>
-      </c>
-      <c r="N39">
+      <c r="N39" t="s">
+        <v>116</v>
+      </c>
+      <c r="O39">
         <v>0.8314</v>
       </c>
-      <c r="O39" t="s">
-        <v>115</v>
-      </c>
-      <c r="P39">
+      <c r="P39" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q39">
         <v>-0.06040181445148433</v>
       </c>
-      <c r="Q39">
+      <c r="R39">
         <v>0.05045206570776576</v>
       </c>
-      <c r="R39" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18">
+      <c r="S39" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19">
       <c r="A40" t="s">
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" t="s">
         <v>50</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>51</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>0.5074703248991672</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>0.5017647249418594</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>0.005705599957307794</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>-0.0437486940349788</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>0.05394448983572651</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>0.8202</v>
       </c>
-      <c r="M40" t="s">
-        <v>112</v>
-      </c>
-      <c r="N40">
+      <c r="N40" t="s">
+        <v>116</v>
+      </c>
+      <c r="O40">
         <v>0.8202</v>
       </c>
-      <c r="O40" t="s">
-        <v>115</v>
-      </c>
-      <c r="P40">
+      <c r="P40" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q40">
         <v>-0.05453718467014974</v>
       </c>
-      <c r="Q40">
+      <c r="R40">
         <v>0.06313045014530488</v>
       </c>
-      <c r="R40" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18">
+      <c r="S40" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -6068,299 +6370,317 @@
         <v>93</v>
       </c>
       <c r="C41" t="s">
+        <v>97</v>
+      </c>
+      <c r="D41" t="s">
         <v>50</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>51</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>0.34</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>0.3500000000000001</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>-0.01000000000000012</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>-0.08000000000000018</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>0.05999999999999994</v>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>0.6392</v>
       </c>
-      <c r="M41" t="s">
-        <v>113</v>
-      </c>
-      <c r="N41">
+      <c r="N41" t="s">
+        <v>117</v>
+      </c>
+      <c r="O41">
         <v>0.764</v>
       </c>
-      <c r="O41" t="s">
-        <v>115</v>
-      </c>
-      <c r="P41">
+      <c r="P41" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q41">
         <v>-0.09925482790573971</v>
       </c>
-      <c r="Q41">
+      <c r="R41">
         <v>0.07925482790573947</v>
       </c>
-      <c r="R41" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18">
+      <c r="S41" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19">
       <c r="A42" t="s">
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C42" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" t="s">
         <v>50</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>51</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>0.5080569923909963</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>0.5004604701660993</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>0.00759652222489704</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>-0.04136267558648257</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>0.05592181985989171</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>0.761</v>
       </c>
-      <c r="M42" t="s">
-        <v>73</v>
-      </c>
-      <c r="N42">
+      <c r="N42" t="s">
+        <v>74</v>
+      </c>
+      <c r="O42">
         <v>0.761</v>
       </c>
-      <c r="O42" t="s">
-        <v>115</v>
-      </c>
-      <c r="P42">
+      <c r="P42" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q42">
         <v>-0.05188362266759145</v>
       </c>
-      <c r="Q42">
+      <c r="R42">
         <v>0.06498731161172748</v>
       </c>
-      <c r="R42" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18">
+      <c r="S42" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19">
       <c r="A43" t="s">
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D43" t="s">
         <v>50</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>51</v>
-      </c>
-      <c r="E43">
-        <v>0.6683417085427136</v>
       </c>
       <c r="F43">
         <v>0.6683417085427136</v>
       </c>
       <c r="G43">
+        <v>0.6683417085427136</v>
+      </c>
+      <c r="H43">
         <v>0</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>-0.07537688442211055</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>0.07537688442211055</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>1</v>
       </c>
-      <c r="M43" t="s">
-        <v>114</v>
-      </c>
-      <c r="N43">
+      <c r="N43" t="s">
+        <v>118</v>
+      </c>
+      <c r="O43">
         <v>1</v>
       </c>
-      <c r="O43" t="s">
-        <v>116</v>
-      </c>
-      <c r="P43">
+      <c r="P43" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q43">
         <v>-0.09547738693467334</v>
       </c>
-      <c r="Q43">
+      <c r="R43">
         <v>0.09045226130653261</v>
       </c>
-      <c r="R43" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18">
+      <c r="S43" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C44" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" t="s">
         <v>50</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>52</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>0.02648241206030149</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>0.09015075376884421</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>-0.06366834170854271</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>-0.134711306615152</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>0.005948065860233304</v>
       </c>
-      <c r="J44">
+      <c r="K44">
         <v>0.08019999999999999</v>
       </c>
-      <c r="M44" t="s">
-        <v>112</v>
-      </c>
-      <c r="N44">
+      <c r="N44" t="s">
+        <v>116</v>
+      </c>
+      <c r="O44">
         <v>0.1878</v>
       </c>
-      <c r="O44" t="s">
-        <v>115</v>
-      </c>
-      <c r="P44">
+      <c r="P44" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q44">
         <v>-0.1488692935139442</v>
       </c>
-      <c r="Q44">
+      <c r="R44">
         <v>0.02153261009685876</v>
       </c>
-      <c r="R44" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18">
+      <c r="S44" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19">
       <c r="A45" t="s">
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C45" t="s">
+        <v>95</v>
+      </c>
+      <c r="D45" t="s">
         <v>50</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>52</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>0.4006532663316583</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>0.4757788944723618</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>-0.0751256281407035</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <v>-0.1310229499051968</v>
       </c>
-      <c r="I45">
+      <c r="J45">
         <v>-0.02007745571459697</v>
       </c>
-      <c r="J45">
+      <c r="K45">
         <v>0.008200000000000001</v>
       </c>
-      <c r="M45" t="s">
-        <v>112</v>
-      </c>
-      <c r="N45">
+      <c r="N45" t="s">
+        <v>116</v>
+      </c>
+      <c r="O45">
         <v>0.024</v>
       </c>
-      <c r="O45" t="s">
-        <v>115</v>
-      </c>
-      <c r="P45">
+      <c r="P45" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q45">
         <v>-0.1420685129346101</v>
       </c>
-      <c r="Q45">
+      <c r="R45">
         <v>-0.008182743346796903</v>
       </c>
-      <c r="R45" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18">
+      <c r="S45" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D46" t="s">
         <v>50</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>52</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>0.5074703248991672</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>0.5911278717875009</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>-0.08365754688833371</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>-0.1420902483200672</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>-0.02184629191013983</v>
       </c>
-      <c r="J46">
+      <c r="K46">
         <v>0.0086</v>
       </c>
-      <c r="M46" t="s">
-        <v>112</v>
-      </c>
-      <c r="N46">
+      <c r="N46" t="s">
+        <v>116</v>
+      </c>
+      <c r="O46">
         <v>0.0188</v>
       </c>
-      <c r="O46" t="s">
-        <v>115</v>
-      </c>
-      <c r="P46">
+      <c r="P46" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q46">
         <v>-0.1557722033973963</v>
       </c>
-      <c r="Q46">
+      <c r="R46">
         <v>-0.008380156597759411</v>
       </c>
-      <c r="R46" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18">
+      <c r="S46" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -6368,299 +6688,317 @@
         <v>93</v>
       </c>
       <c r="C47" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" t="s">
         <v>50</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>52</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>0.34</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>0.3900000000000001</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>-0.05000000000000016</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>-0.1199999999999999</v>
       </c>
-      <c r="I47">
+      <c r="J47">
         <v>0.02000000000000002</v>
       </c>
-      <c r="J47">
+      <c r="K47">
         <v>0.1548</v>
       </c>
-      <c r="M47" t="s">
-        <v>113</v>
-      </c>
-      <c r="N47">
+      <c r="N47" t="s">
+        <v>117</v>
+      </c>
+      <c r="O47">
         <v>0.2654</v>
       </c>
-      <c r="O47" t="s">
-        <v>115</v>
-      </c>
-      <c r="P47">
+      <c r="P47" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q47">
         <v>-0.1364378623663957</v>
       </c>
-      <c r="Q47">
+      <c r="R47">
         <v>0.03643786236639536</v>
       </c>
-      <c r="R47" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18">
+      <c r="S47" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
       <c r="A48" t="s">
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C48" t="s">
+        <v>98</v>
+      </c>
+      <c r="D48" t="s">
         <v>50</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>52</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>0.5080569923909963</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>0.5856865757701022</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>-0.07762958337910586</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>-0.1370381777191461</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>-0.01531069818067748</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>0.0224</v>
       </c>
-      <c r="M48" t="s">
-        <v>73</v>
-      </c>
-      <c r="N48">
+      <c r="N48" t="s">
+        <v>74</v>
+      </c>
+      <c r="O48">
         <v>0.0424</v>
       </c>
-      <c r="O48" t="s">
-        <v>115</v>
-      </c>
-      <c r="P48">
+      <c r="P48" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q48">
         <v>-0.149432629305434</v>
       </c>
-      <c r="Q48">
+      <c r="R48">
         <v>-0.001071822703622774</v>
       </c>
-      <c r="R48" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18">
+      <c r="S48" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49" t="s">
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s">
+        <v>99</v>
+      </c>
+      <c r="D49" t="s">
         <v>50</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>52</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>0.6683417085427136</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>0.6180904522613065</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>0.05025125628140703</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <v>-0.03517587939698492</v>
       </c>
-      <c r="I49">
+      <c r="J49">
         <v>0.135678391959799</v>
       </c>
-      <c r="J49">
+      <c r="K49">
         <v>0.3018984444285246</v>
       </c>
-      <c r="M49" t="s">
-        <v>114</v>
-      </c>
-      <c r="N49">
+      <c r="N49" t="s">
+        <v>118</v>
+      </c>
+      <c r="O49">
         <v>0.6037968888570493</v>
       </c>
-      <c r="O49" t="s">
-        <v>116</v>
-      </c>
-      <c r="P49">
+      <c r="P49" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q49">
         <v>-0.05527638190954776</v>
       </c>
-      <c r="Q49">
+      <c r="R49">
         <v>0.1457286432160805</v>
       </c>
-      <c r="R49" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18">
+      <c r="S49" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19">
       <c r="A50" t="s">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C50" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" t="s">
         <v>51</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>52</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>0.05065326633165827</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>0.09015075376884421</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>-0.03949748743718594</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>-0.114302675420823</v>
       </c>
-      <c r="I50">
+      <c r="J50">
         <v>0.03372151397468764</v>
       </c>
-      <c r="J50">
+      <c r="K50">
         <v>0.2944</v>
       </c>
-      <c r="M50" t="s">
-        <v>112</v>
-      </c>
-      <c r="N50">
+      <c r="N50" t="s">
+        <v>116</v>
+      </c>
+      <c r="O50">
         <v>0.4768</v>
       </c>
-      <c r="O50" t="s">
-        <v>115</v>
-      </c>
-      <c r="P50">
+      <c r="P50" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q50">
         <v>-0.1270242150164059</v>
       </c>
-      <c r="Q50">
+      <c r="R50">
         <v>0.04802924014203403</v>
       </c>
-      <c r="R50" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18">
+      <c r="S50" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19">
       <c r="A51" t="s">
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C51" t="s">
+        <v>95</v>
+      </c>
+      <c r="D51" t="s">
         <v>51</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>52</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>0.4056281407035176</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>0.4757788944723618</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>-0.07015075376884422</v>
       </c>
-      <c r="H51">
+      <c r="I51">
         <v>-0.1301497201187742</v>
       </c>
-      <c r="I51">
+      <c r="J51">
         <v>-0.01301543821783446</v>
       </c>
-      <c r="J51">
+      <c r="K51">
         <v>0.0186</v>
       </c>
-      <c r="M51" t="s">
-        <v>112</v>
-      </c>
-      <c r="N51">
+      <c r="N51" t="s">
+        <v>116</v>
+      </c>
+      <c r="O51">
         <v>0.0348</v>
       </c>
-      <c r="O51" t="s">
-        <v>115</v>
-      </c>
-      <c r="P51">
+      <c r="P51" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q51">
         <v>-0.1390395629729493</v>
       </c>
-      <c r="Q51">
+      <c r="R51">
         <v>-0.001261944564739118</v>
       </c>
-      <c r="R51" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18">
+      <c r="S51" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19">
       <c r="A52" t="s">
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C52" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52" t="s">
         <v>51</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>52</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>0.5017647249418594</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>0.5911278717875009</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>-0.08936314684564151</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>-0.1519342158815156</v>
       </c>
-      <c r="I52">
+      <c r="J52">
         <v>-0.02445697967964856</v>
       </c>
-      <c r="J52">
+      <c r="K52">
         <v>0.008999999999999999</v>
       </c>
-      <c r="M52" t="s">
-        <v>112</v>
-      </c>
-      <c r="N52">
+      <c r="N52" t="s">
+        <v>116</v>
+      </c>
+      <c r="O52">
         <v>0.0188</v>
       </c>
-      <c r="O52" t="s">
-        <v>115</v>
-      </c>
-      <c r="P52">
+      <c r="P52" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q52">
         <v>-0.1647937957865656</v>
       </c>
-      <c r="Q52">
+      <c r="R52">
         <v>-0.009124463780871214</v>
       </c>
-      <c r="R52" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18">
+      <c r="S52" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19">
       <c r="A53" t="s">
         <v>49</v>
       </c>
@@ -6668,146 +7006,155 @@
         <v>93</v>
       </c>
       <c r="C53" t="s">
+        <v>97</v>
+      </c>
+      <c r="D53" t="s">
         <v>51</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>52</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>0.3500000000000001</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>0.3900000000000001</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>-0.04000000000000004</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>-0.1000000000000003</v>
       </c>
-      <c r="I53">
+      <c r="J53">
         <v>0.0399999999999997</v>
       </c>
-      <c r="J53">
+      <c r="K53">
         <v>0.3536</v>
       </c>
-      <c r="M53" t="s">
-        <v>113</v>
-      </c>
-      <c r="N53">
+      <c r="N53" t="s">
+        <v>117</v>
+      </c>
+      <c r="O53">
         <v>0.4588</v>
       </c>
-      <c r="O53" t="s">
-        <v>115</v>
-      </c>
-      <c r="P53">
+      <c r="P53" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q53">
         <v>-0.13</v>
       </c>
-      <c r="Q53">
+      <c r="R53">
         <v>0.04999999999999993</v>
       </c>
-      <c r="R53" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18">
+      <c r="S53" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19">
       <c r="A54" t="s">
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C54" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" t="s">
         <v>51</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>52</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>0.5004604701660993</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>0.5856865757701022</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>-0.0852261056040029</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>-0.1485120228288059</v>
       </c>
-      <c r="I54">
+      <c r="J54">
         <v>-0.01921195482153516</v>
       </c>
-      <c r="J54">
+      <c r="K54">
         <v>0.0134</v>
       </c>
-      <c r="M54" t="s">
-        <v>73</v>
-      </c>
-      <c r="N54">
+      <c r="N54" t="s">
+        <v>74</v>
+      </c>
+      <c r="O54">
         <v>0.0322</v>
       </c>
-      <c r="O54" t="s">
-        <v>115</v>
-      </c>
-      <c r="P54">
+      <c r="P54" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q54">
         <v>-0.1609806360778065</v>
       </c>
-      <c r="Q54">
+      <c r="R54">
         <v>-0.003463348309243171</v>
       </c>
-      <c r="R54" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18">
+      <c r="S54" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19">
       <c r="A55" t="s">
         <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C55" t="s">
+        <v>99</v>
+      </c>
+      <c r="D55" t="s">
         <v>51</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>52</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>0.6683417085427136</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>0.6180904522613065</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>0.05025125628140703</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>-0.04020100502512563</v>
       </c>
-      <c r="I55">
+      <c r="J55">
         <v>0.135678391959799</v>
       </c>
-      <c r="J55">
+      <c r="K55">
         <v>0.3018984444285246</v>
       </c>
-      <c r="M55" t="s">
-        <v>114</v>
-      </c>
-      <c r="N55">
+      <c r="N55" t="s">
+        <v>118</v>
+      </c>
+      <c r="O55">
         <v>0.6037968888570493</v>
       </c>
-      <c r="O55" t="s">
-        <v>116</v>
-      </c>
-      <c r="P55">
+      <c r="P55" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q55">
         <v>-0.05527638190954776</v>
       </c>
-      <c r="Q55">
+      <c r="R55">
         <v>0.1507537688442211</v>
       </c>
-      <c r="R55" t="s">
-        <v>118</v>
+      <c r="S55" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -6817,224 +7164,237 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="60.7109375" customWidth="1"/>
-    <col min="3" max="17" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="60.7109375" customWidth="1"/>
+    <col min="4" max="18" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="C1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G1" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="H1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I1" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="J1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L1" t="s">
+        <v>130</v>
+      </c>
+      <c r="M1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P1" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>135</v>
+      </c>
+      <c r="R1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G2" t="s">
         <v>127</v>
       </c>
-      <c r="M1" t="s">
-        <v>128</v>
-      </c>
-      <c r="N1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O1" t="s">
-        <v>130</v>
-      </c>
-      <c r="P1" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G2">
+      <c r="H2">
         <v>406</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>250</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>156</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.624</v>
       </c>
-      <c r="K2" t="b">
+      <c r="L2" t="b">
         <v>1</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>4999</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>42</v>
       </c>
-      <c r="N2" t="s">
-        <v>139</v>
-      </c>
       <c r="O2" t="s">
-        <v>140</v>
-      </c>
-      <c r="P2" t="b">
+        <v>93</v>
+      </c>
+      <c r="P2" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q2" t="b">
         <v>0</v>
       </c>
-      <c r="Q2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
         <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G3">
-        <v>207</v>
+        <v>142</v>
+      </c>
+      <c r="G3" t="s">
+        <v>127</v>
       </c>
       <c r="H3">
         <v>207</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3" t="b">
+      <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3">
         <v>4999</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>42</v>
       </c>
-      <c r="N3" t="s">
-        <v>139</v>
-      </c>
       <c r="O3" t="s">
-        <v>140</v>
-      </c>
-      <c r="P3" t="b">
+        <v>93</v>
+      </c>
+      <c r="P3" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q3" t="b">
         <v>0</v>
       </c>
-      <c r="Q3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G4">
-        <v>199</v>
+        <v>142</v>
+      </c>
+      <c r="G4" t="s">
+        <v>127</v>
       </c>
       <c r="H4">
         <v>199</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4" t="b">
+      <c r="K4">
         <v>0</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>4999</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>42</v>
       </c>
-      <c r="N4" t="s">
-        <v>139</v>
-      </c>
       <c r="O4" t="s">
-        <v>140</v>
-      </c>
-      <c r="P4" t="b">
+        <v>93</v>
+      </c>
+      <c r="P4" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q4" t="b">
         <v>0</v>
       </c>
-      <c r="Q4" t="s">
-        <v>141</v>
+      <c r="R4" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/examples/example_continuous_results.xlsx
+++ b/examples/example_continuous_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="140">
   <si>
     <t>Group</t>
   </si>
@@ -86,12 +86,6 @@
     <t>RMSE Diff 95% CI high</t>
   </si>
   <si>
-    <t>RMSE Diff 95% CI adj low</t>
-  </si>
-  <si>
-    <t>RMSE Diff 95% CI adj high</t>
-  </si>
-  <si>
     <t>Boot (RMSE) p</t>
   </si>
   <si>
@@ -128,12 +122,6 @@
     <t>SD Diff 95% CI high</t>
   </si>
   <si>
-    <t>SD Diff 95% CI adj low</t>
-  </si>
-  <si>
-    <t>SD Diff 95% CI adj high</t>
-  </si>
-  <si>
     <t>Morgan-Pitman (SD) p</t>
   </si>
   <si>
@@ -149,12 +137,6 @@
     <t>McNemar Diff 95% CI high</t>
   </si>
   <si>
-    <t>McNemar Diff 95% CI adj low</t>
-  </si>
-  <si>
-    <t>McNemar Diff 95% CI adj high</t>
-  </si>
-  <si>
     <t>McNemar p</t>
   </si>
   <si>
@@ -191,22 +173,22 @@
     <t>Weighting of Eyes (mean-loss metrics)</t>
   </si>
   <si>
-    <t>Mean error Test</t>
-  </si>
-  <si>
-    <t>Mean absolute error Test</t>
-  </si>
-  <si>
-    <t>Root mean squared error Test</t>
-  </si>
-  <si>
-    <t>Median absolute error Test</t>
-  </si>
-  <si>
-    <t>SD of the error Test</t>
-  </si>
-  <si>
-    <t>Proportion within tolerance Test</t>
+    <t>Mean Error (MPE) Test</t>
+  </si>
+  <si>
+    <t>MAE Test</t>
+  </si>
+  <si>
+    <t>RMSE Test</t>
+  </si>
+  <si>
+    <t>MedAE Test</t>
+  </si>
+  <si>
+    <t>SD Test</t>
+  </si>
+  <si>
+    <t>Proportion Within Tolerance Test</t>
   </si>
   <si>
     <t>Tolerance (proportion within)</t>
@@ -254,10 +236,10 @@
     <t>Romano-Wolf (bootstrap tests) / Hommel (other tests)</t>
   </si>
   <si>
-    <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Romano-Wolf step-down: Mean error, Mean absolute error, Root mean squared error, Median absolute error, SD of the error; Hommel: Proportion within tolerance</t>
-  </si>
-  <si>
-    <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group. Romano-Wolf simultaneous (max-|t|): Mean error, Mean absolute error, Median absolute error; Bonferroni (percentile bootstrap): Root mean squared error, SD of the error, Proportion within tolerance. MPE, MAE and MedAE: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). RMSE, SD and the proportion within tolerance: percentile interval of the same patient resamples at coverage 1 - 0.05/m (Bonferroni). These Bonferroni-type intervals need not agree with p_adj when p_adj comes from another statistic (Romano-Wolf, Hommel); use more resamples (e.g. 9,999) for their far tails</t>
+    <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Romano-Wolf step-down: Mean Error (MPE), MAE, RMSE, MedAE, SD; Hommel: Proportion Within Tolerance</t>
+  </si>
+  <si>
+    <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group, for the MPE, MAE and MedAE only: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). The RMSE, SD and the proportion within tolerance have no adjusted interval: their adjusted p-values (Romano-Wolf from a different statistic, or Hommel) have no matching interval, so their CIs are unadjusted. fwer_method='bonferroni' gives Bonferroni p-values with matching intervals for every metric</t>
   </si>
   <si>
     <t>ρΔ (rho_delta): intraclass correlation of the per-eye difference in loss between the two models; one_eye_factor: patients a one-eye study needs, relative to this analysis (design effect)</t>
@@ -386,7 +368,10 @@
     <t>Romano-Wolf simultaneous (max-|t|)</t>
   </si>
   <si>
-    <t>Bonferroni (percentile bootstrap)</t>
+    <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
+  </si>
+  <si>
+    <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
   </si>
   <si>
     <t>definition</t>
@@ -784,24 +769,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="12" width="15.7109375" customWidth="1"/>
     <col min="13" max="17" width="22.7109375" customWidth="1"/>
     <col min="18" max="19" width="15.7109375" customWidth="1"/>
-    <col min="20" max="24" width="22.7109375" customWidth="1"/>
-    <col min="25" max="26" width="15.7109375" customWidth="1"/>
-    <col min="27" max="31" width="22.7109375" customWidth="1"/>
-    <col min="32" max="33" width="15.7109375" customWidth="1"/>
-    <col min="34" max="38" width="22.7109375" customWidth="1"/>
-    <col min="39" max="40" width="15.7109375" customWidth="1"/>
-    <col min="41" max="45" width="22.7109375" customWidth="1"/>
-    <col min="46" max="47" width="15.7109375" customWidth="1"/>
+    <col min="20" max="22" width="22.7109375" customWidth="1"/>
+    <col min="23" max="24" width="15.7109375" customWidth="1"/>
+    <col min="25" max="29" width="22.7109375" customWidth="1"/>
+    <col min="30" max="31" width="15.7109375" customWidth="1"/>
+    <col min="32" max="34" width="22.7109375" customWidth="1"/>
+    <col min="35" max="36" width="15.7109375" customWidth="1"/>
+    <col min="37" max="39" width="22.7109375" customWidth="1"/>
+    <col min="40" max="41" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -925,34 +910,16 @@
       <c r="AO1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" t="s">
+    </row>
+    <row r="2" spans="1:41">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="C2" t="s">
         <v>45</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:47">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
       </c>
       <c r="D2">
         <v>406</v>
@@ -1012,90 +979,72 @@
         <v>0.01787937336349208</v>
       </c>
       <c r="W2">
-        <v>-0.05856576544801697</v>
+        <v>0.3852</v>
       </c>
       <c r="X2">
-        <v>0.02781683152088908</v>
+        <v>0.3852</v>
       </c>
       <c r="Y2">
-        <v>0.3852</v>
+        <v>-0.01000000000000012</v>
       </c>
       <c r="Z2">
-        <v>0.3852</v>
+        <v>-0.07000000000000073</v>
       </c>
       <c r="AA2">
-        <v>-0.01000000000000012</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="AB2">
-        <v>-0.07000000000000073</v>
+        <v>-0.08000000000000007</v>
       </c>
       <c r="AC2">
-        <v>0.04000000000000004</v>
+        <v>0.05999999999999983</v>
       </c>
       <c r="AD2">
-        <v>-0.08000000000000007</v>
+        <v>0.6112</v>
       </c>
       <c r="AE2">
-        <v>0.05999999999999983</v>
+        <v>0.7282</v>
       </c>
       <c r="AF2">
-        <v>0.6112</v>
+        <v>-0.01535687255151641</v>
       </c>
       <c r="AG2">
-        <v>0.7282</v>
+        <v>-0.05064189418206685</v>
       </c>
       <c r="AH2">
-        <v>-0.01535687255151641</v>
+        <v>0.01876017330561063</v>
       </c>
       <c r="AI2">
-        <v>-0.05064189418206685</v>
+        <v>0.3894</v>
       </c>
       <c r="AJ2">
-        <v>0.01876017330561063</v>
+        <v>0.3894</v>
       </c>
       <c r="AK2">
-        <v>-0.05815433485882701</v>
+        <v>0.03448275862068961</v>
       </c>
       <c r="AL2">
-        <v>0.02825025172545625</v>
+        <v>-0.01805205348027686</v>
       </c>
       <c r="AM2">
-        <v>0.3894</v>
+        <v>0.08780487804878048</v>
       </c>
       <c r="AN2">
-        <v>0.3894</v>
+        <v>0.204560421762222</v>
       </c>
       <c r="AO2">
-        <v>0.03448275862068961</v>
-      </c>
-      <c r="AP2">
-        <v>-0.01805205348027686</v>
-      </c>
-      <c r="AQ2">
-        <v>0.08780487804878048</v>
-      </c>
-      <c r="AR2">
-        <v>-0.03189014549308666</v>
-      </c>
-      <c r="AS2">
-        <v>0.09762516046213096</v>
-      </c>
-      <c r="AT2">
         <v>0.204560421762222</v>
       </c>
-      <c r="AU2">
-        <v>0.204560421762222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:47">
+    </row>
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D3">
         <v>406</v>
@@ -1155,90 +1104,72 @@
         <v>-0.0419672383242247</v>
       </c>
       <c r="W3">
-        <v>-0.1343146850892964</v>
+        <v>0.0004</v>
       </c>
       <c r="X3">
-        <v>-0.03239054644227161</v>
+        <v>0.0008</v>
       </c>
       <c r="Y3">
-        <v>0.0004</v>
+        <v>-0.05999999999999994</v>
       </c>
       <c r="Z3">
+        <v>-0.1199999999999999</v>
+      </c>
+      <c r="AA3">
+        <v>-0.009999999999999839</v>
+      </c>
+      <c r="AB3">
+        <v>-0.1280741611297381</v>
+      </c>
+      <c r="AC3">
+        <v>0.008074161129738217</v>
+      </c>
+      <c r="AD3">
+        <v>0.028</v>
+      </c>
+      <c r="AE3">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="AF3">
+        <v>-0.08300106659587148</v>
+      </c>
+      <c r="AG3">
+        <v>-0.1240127595235769</v>
+      </c>
+      <c r="AH3">
+        <v>-0.04070333062115</v>
+      </c>
+      <c r="AI3">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="AJ3">
         <v>0.0008</v>
       </c>
-      <c r="AA3">
-        <v>-0.05999999999999994</v>
-      </c>
-      <c r="AB3">
-        <v>-0.1199999999999999</v>
-      </c>
-      <c r="AC3">
-        <v>-0.009999999999999839</v>
-      </c>
-      <c r="AD3">
-        <v>-0.1280741611297381</v>
-      </c>
-      <c r="AE3">
-        <v>0.008074161129738217</v>
-      </c>
-      <c r="AF3">
-        <v>0.028</v>
-      </c>
-      <c r="AG3">
-        <v>0.09279999999999999</v>
-      </c>
-      <c r="AH3">
-        <v>-0.08300106659587148</v>
-      </c>
-      <c r="AI3">
-        <v>-0.1240127595235769</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.04070333062115</v>
-      </c>
       <c r="AK3">
-        <v>-0.1324121069898527</v>
+        <v>0.08128078817733986</v>
       </c>
       <c r="AL3">
-        <v>-0.03081160526701519</v>
+        <v>0.02216476440614372</v>
       </c>
       <c r="AM3">
-        <v>0.0005999999999999999</v>
+        <v>0.1403530377668309</v>
       </c>
       <c r="AN3">
-        <v>0.0008</v>
+        <v>0.006863871555196087</v>
       </c>
       <c r="AO3">
-        <v>0.08128078817733986</v>
-      </c>
-      <c r="AP3">
-        <v>0.02216476440614372</v>
-      </c>
-      <c r="AQ3">
-        <v>0.1403530377668309</v>
-      </c>
-      <c r="AR3">
-        <v>0.009991271820448863</v>
-      </c>
-      <c r="AS3">
-        <v>0.152573275862069</v>
-      </c>
-      <c r="AT3">
-        <v>0.006863871555196087</v>
-      </c>
-      <c r="AU3">
         <v>0.02059161466558826</v>
       </c>
     </row>
-    <row r="4" spans="1:47">
+    <row r="4" spans="1:41">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D4">
         <v>406</v>
@@ -1298,90 +1229,72 @@
         <v>-0.02214090274061026</v>
       </c>
       <c r="W4">
-        <v>-0.1237607966652773</v>
+        <v>0.0036</v>
       </c>
       <c r="X4">
-        <v>-0.01197481543232409</v>
+        <v>0.0052</v>
       </c>
       <c r="Y4">
-        <v>0.0036</v>
+        <v>-0.04999999999999982</v>
       </c>
       <c r="Z4">
-        <v>0.0052</v>
+        <v>-0.1099999999999999</v>
       </c>
       <c r="AA4">
-        <v>-0.04999999999999982</v>
+        <v>0.01000000000000035</v>
       </c>
       <c r="AB4">
-        <v>-0.1099999999999999</v>
+        <v>-0.1230166690346133</v>
       </c>
       <c r="AC4">
-        <v>0.01000000000000035</v>
+        <v>0.02301666903461366</v>
       </c>
       <c r="AD4">
-        <v>-0.1230166690346133</v>
+        <v>0.1748</v>
       </c>
       <c r="AE4">
-        <v>0.02301666903461366</v>
+        <v>0.2226</v>
       </c>
       <c r="AF4">
-        <v>0.1748</v>
+        <v>-0.06764419404435507</v>
       </c>
       <c r="AG4">
-        <v>0.2226</v>
+        <v>-0.1119735373189496</v>
       </c>
       <c r="AH4">
-        <v>-0.06764419404435507</v>
+        <v>-0.02111883542966709</v>
       </c>
       <c r="AI4">
-        <v>-0.1119735373189496</v>
+        <v>0.005</v>
       </c>
       <c r="AJ4">
-        <v>-0.02111883542966709</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="AK4">
-        <v>-0.1227389787054996</v>
+        <v>0.04679802955665024</v>
       </c>
       <c r="AL4">
-        <v>-0.009991811914109265</v>
+        <v>-0.01452960812430945</v>
       </c>
       <c r="AM4">
-        <v>0.005</v>
+        <v>0.1075</v>
       </c>
       <c r="AN4">
-        <v>0.008399999999999999</v>
+        <v>0.1319988990199734</v>
       </c>
       <c r="AO4">
-        <v>0.04679802955665024</v>
-      </c>
-      <c r="AP4">
-        <v>-0.01452960812430945</v>
-      </c>
-      <c r="AQ4">
-        <v>0.1075</v>
-      </c>
-      <c r="AR4">
-        <v>-0.02693148335989953</v>
-      </c>
-      <c r="AS4">
-        <v>0.118272411680621</v>
-      </c>
-      <c r="AT4">
-        <v>0.1319988990199734</v>
-      </c>
-      <c r="AU4">
         <v>0.204560421762222</v>
       </c>
     </row>
-    <row r="5" spans="1:47">
+    <row r="5" spans="1:41">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D5">
         <v>207</v>
@@ -1441,90 +1354,72 @@
         <v>0.01103192398107171</v>
       </c>
       <c r="W5">
-        <v>-0.09123869203614131</v>
+        <v>0.1386</v>
       </c>
       <c r="X5">
-        <v>0.0222793709494871</v>
+        <v>0.2192</v>
       </c>
       <c r="Y5">
-        <v>0.1386</v>
+        <v>-0.01000000000000012</v>
       </c>
       <c r="Z5">
-        <v>0.2192</v>
+        <v>-0.09999999999999987</v>
       </c>
       <c r="AA5">
-        <v>-0.01000000000000012</v>
+        <v>0.05999999999999994</v>
       </c>
       <c r="AB5">
-        <v>-0.09999999999999987</v>
+        <v>-0.1038971985921919</v>
       </c>
       <c r="AC5">
-        <v>0.05999999999999994</v>
+        <v>0.08389719859219168</v>
       </c>
       <c r="AD5">
-        <v>-0.1038971985921919</v>
+        <v>0.6612</v>
       </c>
       <c r="AE5">
-        <v>0.08389719859219168</v>
+        <v>0.7706</v>
       </c>
       <c r="AF5">
-        <v>0.6612</v>
+        <v>-0.03601433464716908</v>
       </c>
       <c r="AG5">
-        <v>0.7706</v>
+        <v>-0.08128862160672953</v>
       </c>
       <c r="AH5">
-        <v>-0.03601433464716908</v>
+        <v>0.01090263065652809</v>
       </c>
       <c r="AI5">
-        <v>-0.08128862160672953</v>
+        <v>0.1346</v>
       </c>
       <c r="AJ5">
-        <v>0.01090263065652809</v>
+        <v>0.2062</v>
       </c>
       <c r="AK5">
-        <v>-0.09115161458112336</v>
+        <v>0.06763285024154586</v>
       </c>
       <c r="AL5">
-        <v>0.02135292562963592</v>
+        <v>-0.004830917874396135</v>
       </c>
       <c r="AM5">
-        <v>0.1346</v>
+        <v>0.1400966183574879</v>
       </c>
       <c r="AN5">
-        <v>0.2062</v>
+        <v>0.08782509563019504</v>
       </c>
       <c r="AO5">
-        <v>0.06763285024154586</v>
-      </c>
-      <c r="AP5">
-        <v>-0.004830917874396135</v>
-      </c>
-      <c r="AQ5">
-        <v>0.1400966183574879</v>
-      </c>
-      <c r="AR5">
-        <v>-0.01932367149758452</v>
-      </c>
-      <c r="AS5">
-        <v>0.1594202898550724</v>
-      </c>
-      <c r="AT5">
-        <v>0.08782509563019504</v>
-      </c>
-      <c r="AU5">
         <v>0.1756501912603901</v>
       </c>
     </row>
-    <row r="6" spans="1:47">
+    <row r="6" spans="1:41">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D6">
         <v>207</v>
@@ -1584,90 +1479,72 @@
         <v>-0.02765282063164901</v>
       </c>
       <c r="W6">
-        <v>-0.1509793143671761</v>
+        <v>0.004</v>
       </c>
       <c r="X6">
-        <v>-0.01141466056599736</v>
+        <v>0.0112</v>
       </c>
       <c r="Y6">
-        <v>0.004</v>
+        <v>-0.06000000000000005</v>
       </c>
       <c r="Z6">
-        <v>0.0112</v>
+        <v>-0.15</v>
       </c>
       <c r="AA6">
-        <v>-0.06000000000000005</v>
+        <v>-1.110223024625157E-16</v>
       </c>
       <c r="AB6">
-        <v>-0.15</v>
+        <v>-0.1500000000000001</v>
       </c>
       <c r="AC6">
-        <v>-1.110223024625157E-16</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="AD6">
-        <v>-0.1500000000000001</v>
+        <v>0.044</v>
       </c>
       <c r="AE6">
-        <v>0.03000000000000003</v>
+        <v>0.3118</v>
       </c>
       <c r="AF6">
-        <v>0.044</v>
+        <v>-0.08522215543724965</v>
       </c>
       <c r="AG6">
-        <v>0.3118</v>
+        <v>-0.1400943073214456</v>
       </c>
       <c r="AH6">
-        <v>-0.08522215543724965</v>
+        <v>-0.02918989008947918</v>
       </c>
       <c r="AI6">
-        <v>-0.1400943073214456</v>
+        <v>0.006</v>
       </c>
       <c r="AJ6">
-        <v>-0.02918989008947918</v>
+        <v>0.0176</v>
       </c>
       <c r="AK6">
-        <v>-0.1511909993124804</v>
+        <v>0.111111111111111</v>
       </c>
       <c r="AL6">
-        <v>-0.01232031333021981</v>
+        <v>0.03381642512077294</v>
       </c>
       <c r="AM6">
-        <v>0.006</v>
+        <v>0.1835748792270532</v>
       </c>
       <c r="AN6">
-        <v>0.0176</v>
+        <v>0.006357215082587968</v>
       </c>
       <c r="AO6">
-        <v>0.111111111111111</v>
-      </c>
-      <c r="AP6">
-        <v>0.03381642512077294</v>
-      </c>
-      <c r="AQ6">
-        <v>0.1835748792270532</v>
-      </c>
-      <c r="AR6">
-        <v>0.01932367149758452</v>
-      </c>
-      <c r="AS6">
-        <v>0.2028985507246377</v>
-      </c>
-      <c r="AT6">
-        <v>0.006357215082587968</v>
-      </c>
-      <c r="AU6">
         <v>0.0190716452477639</v>
       </c>
     </row>
-    <row r="7" spans="1:47">
+    <row r="7" spans="1:41">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D7">
         <v>207</v>
@@ -1727,90 +1604,72 @@
         <v>0.01275237325302565</v>
       </c>
       <c r="W7">
-        <v>-0.1238415295689909</v>
+        <v>0.1238</v>
       </c>
       <c r="X7">
-        <v>0.02673239532361265</v>
+        <v>0.2192</v>
       </c>
       <c r="Y7">
-        <v>0.1238</v>
+        <v>-0.04999999999999993</v>
       </c>
       <c r="Z7">
-        <v>0.2192</v>
+        <v>-0.1400000000000001</v>
       </c>
       <c r="AA7">
-        <v>-0.04999999999999993</v>
+        <v>0.02999999999999992</v>
       </c>
       <c r="AB7">
-        <v>-0.1400000000000001</v>
+        <v>-0.1519260792971539</v>
       </c>
       <c r="AC7">
-        <v>0.02999999999999992</v>
+        <v>0.05192607929715401</v>
       </c>
       <c r="AD7">
-        <v>-0.1519260792971539</v>
+        <v>0.224</v>
       </c>
       <c r="AE7">
-        <v>0.05192607929715401</v>
+        <v>0.4476</v>
       </c>
       <c r="AF7">
-        <v>0.224</v>
+        <v>-0.04920782079008057</v>
       </c>
       <c r="AG7">
-        <v>0.4476</v>
+        <v>-0.1114327077564691</v>
       </c>
       <c r="AH7">
-        <v>-0.04920782079008057</v>
+        <v>0.01244135367620838</v>
       </c>
       <c r="AI7">
-        <v>-0.1114327077564691</v>
+        <v>0.1184</v>
       </c>
       <c r="AJ7">
-        <v>0.01244135367620838</v>
+        <v>0.2062</v>
       </c>
       <c r="AK7">
-        <v>-0.1228604273873636</v>
+        <v>0.04347826086956519</v>
       </c>
       <c r="AL7">
-        <v>0.02669462629634863</v>
+        <v>-0.03381642512077294</v>
       </c>
       <c r="AM7">
-        <v>0.1184</v>
+        <v>0.1159420289855072</v>
       </c>
       <c r="AN7">
-        <v>0.2062</v>
+        <v>0.3134999455835852</v>
       </c>
       <c r="AO7">
-        <v>0.04347826086956519</v>
-      </c>
-      <c r="AP7">
-        <v>-0.03381642512077294</v>
-      </c>
-      <c r="AQ7">
-        <v>0.1159420289855072</v>
-      </c>
-      <c r="AR7">
-        <v>-0.04830917874396135</v>
-      </c>
-      <c r="AS7">
-        <v>0.1352657004830918</v>
-      </c>
-      <c r="AT7">
         <v>0.3134999455835852</v>
       </c>
-      <c r="AU7">
-        <v>0.3134999455835852</v>
-      </c>
-    </row>
-    <row r="8" spans="1:47">
+    </row>
+    <row r="8" spans="1:41">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D8">
         <v>199</v>
@@ -1870,90 +1729,72 @@
         <v>0.05394448983572651</v>
       </c>
       <c r="W8">
-        <v>-0.05453718467014974</v>
+        <v>0.8202</v>
       </c>
       <c r="X8">
-        <v>0.06313045014530488</v>
+        <v>0.8202</v>
       </c>
       <c r="Y8">
-        <v>0.8202</v>
+        <v>-0.01000000000000012</v>
       </c>
       <c r="Z8">
-        <v>0.8202</v>
+        <v>-0.08000000000000018</v>
       </c>
       <c r="AA8">
-        <v>-0.01000000000000012</v>
+        <v>0.05999999999999994</v>
       </c>
       <c r="AB8">
-        <v>-0.08000000000000018</v>
+        <v>-0.09925482790573971</v>
       </c>
       <c r="AC8">
-        <v>0.05999999999999994</v>
+        <v>0.07925482790573947</v>
       </c>
       <c r="AD8">
-        <v>-0.09925482790573971</v>
+        <v>0.6392</v>
       </c>
       <c r="AE8">
-        <v>0.07925482790573947</v>
+        <v>0.764</v>
       </c>
       <c r="AF8">
-        <v>0.6392</v>
+        <v>0.00759652222489704</v>
       </c>
       <c r="AG8">
-        <v>0.764</v>
+        <v>-0.04136267558648257</v>
       </c>
       <c r="AH8">
-        <v>0.00759652222489704</v>
+        <v>0.05592181985989171</v>
       </c>
       <c r="AI8">
-        <v>-0.04136267558648257</v>
+        <v>0.761</v>
       </c>
       <c r="AJ8">
-        <v>0.05592181985989171</v>
+        <v>0.761</v>
       </c>
       <c r="AK8">
-        <v>-0.05188362266759145</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>0.06498731161172748</v>
+        <v>-0.07537688442211055</v>
       </c>
       <c r="AM8">
-        <v>0.761</v>
+        <v>0.07537688442211055</v>
       </c>
       <c r="AN8">
-        <v>0.761</v>
+        <v>1</v>
       </c>
       <c r="AO8">
-        <v>0</v>
-      </c>
-      <c r="AP8">
-        <v>-0.07537688442211055</v>
-      </c>
-      <c r="AQ8">
-        <v>0.07537688442211055</v>
-      </c>
-      <c r="AR8">
-        <v>-0.09547738693467334</v>
-      </c>
-      <c r="AS8">
-        <v>0.09045226130653261</v>
-      </c>
-      <c r="AT8">
         <v>1</v>
       </c>
-      <c r="AU8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:47">
+    </row>
+    <row r="9" spans="1:41">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D9">
         <v>199</v>
@@ -2013,90 +1854,72 @@
         <v>-0.02184629191013983</v>
       </c>
       <c r="W9">
-        <v>-0.1557722033973963</v>
+        <v>0.0086</v>
       </c>
       <c r="X9">
-        <v>-0.008380156597759411</v>
+        <v>0.0188</v>
       </c>
       <c r="Y9">
-        <v>0.0086</v>
+        <v>-0.05000000000000016</v>
       </c>
       <c r="Z9">
-        <v>0.0188</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="AA9">
-        <v>-0.05000000000000016</v>
+        <v>0.02000000000000002</v>
       </c>
       <c r="AB9">
-        <v>-0.1199999999999999</v>
+        <v>-0.1364378623663957</v>
       </c>
       <c r="AC9">
-        <v>0.02000000000000002</v>
+        <v>0.03643786236639536</v>
       </c>
       <c r="AD9">
-        <v>-0.1364378623663957</v>
+        <v>0.1548</v>
       </c>
       <c r="AE9">
-        <v>0.03643786236639536</v>
+        <v>0.2654</v>
       </c>
       <c r="AF9">
-        <v>0.1548</v>
+        <v>-0.07762958337910586</v>
       </c>
       <c r="AG9">
-        <v>0.2654</v>
+        <v>-0.1370381777191461</v>
       </c>
       <c r="AH9">
-        <v>-0.07762958337910586</v>
+        <v>-0.01531069818067748</v>
       </c>
       <c r="AI9">
-        <v>-0.1370381777191461</v>
+        <v>0.0224</v>
       </c>
       <c r="AJ9">
-        <v>-0.01531069818067748</v>
+        <v>0.0424</v>
       </c>
       <c r="AK9">
-        <v>-0.149432629305434</v>
+        <v>0.05025125628140703</v>
       </c>
       <c r="AL9">
-        <v>-0.001071822703622774</v>
+        <v>-0.03517587939698492</v>
       </c>
       <c r="AM9">
-        <v>0.0224</v>
+        <v>0.135678391959799</v>
       </c>
       <c r="AN9">
-        <v>0.0424</v>
+        <v>0.3018984444285246</v>
       </c>
       <c r="AO9">
-        <v>0.05025125628140703</v>
-      </c>
-      <c r="AP9">
-        <v>-0.03517587939698492</v>
-      </c>
-      <c r="AQ9">
-        <v>0.135678391959799</v>
-      </c>
-      <c r="AR9">
-        <v>-0.05527638190954776</v>
-      </c>
-      <c r="AS9">
-        <v>0.1457286432160805</v>
-      </c>
-      <c r="AT9">
-        <v>0.3018984444285246</v>
-      </c>
-      <c r="AU9">
         <v>0.6037968888570493</v>
       </c>
     </row>
-    <row r="10" spans="1:47">
+    <row r="10" spans="1:41">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D10">
         <v>199</v>
@@ -2156,78 +1979,60 @@
         <v>-0.02445697967964856</v>
       </c>
       <c r="W10">
-        <v>-0.1647937957865656</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="X10">
-        <v>-0.009124463780871214</v>
+        <v>0.0188</v>
       </c>
       <c r="Y10">
-        <v>0.008999999999999999</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="Z10">
-        <v>0.0188</v>
+        <v>-0.1000000000000003</v>
       </c>
       <c r="AA10">
-        <v>-0.04000000000000004</v>
+        <v>0.0399999999999997</v>
       </c>
       <c r="AB10">
-        <v>-0.1000000000000003</v>
+        <v>-0.13</v>
       </c>
       <c r="AC10">
-        <v>0.0399999999999997</v>
+        <v>0.04999999999999993</v>
       </c>
       <c r="AD10">
-        <v>-0.13</v>
+        <v>0.3536</v>
       </c>
       <c r="AE10">
-        <v>0.04999999999999993</v>
+        <v>0.4588</v>
       </c>
       <c r="AF10">
-        <v>0.3536</v>
+        <v>-0.0852261056040029</v>
       </c>
       <c r="AG10">
-        <v>0.4588</v>
+        <v>-0.1485120228288059</v>
       </c>
       <c r="AH10">
-        <v>-0.0852261056040029</v>
+        <v>-0.01921195482153516</v>
       </c>
       <c r="AI10">
-        <v>-0.1485120228288059</v>
+        <v>0.0134</v>
       </c>
       <c r="AJ10">
-        <v>-0.01921195482153516</v>
+        <v>0.0322</v>
       </c>
       <c r="AK10">
-        <v>-0.1609806360778065</v>
+        <v>0.05025125628140703</v>
       </c>
       <c r="AL10">
-        <v>-0.003463348309243171</v>
+        <v>-0.04020100502512563</v>
       </c>
       <c r="AM10">
-        <v>0.0134</v>
+        <v>0.135678391959799</v>
       </c>
       <c r="AN10">
-        <v>0.0322</v>
+        <v>0.3018984444285246</v>
       </c>
       <c r="AO10">
-        <v>0.05025125628140703</v>
-      </c>
-      <c r="AP10">
-        <v>-0.04020100502512563</v>
-      </c>
-      <c r="AQ10">
-        <v>0.135678391959799</v>
-      </c>
-      <c r="AR10">
-        <v>-0.05527638190954776</v>
-      </c>
-      <c r="AS10">
-        <v>0.1507537688442211</v>
-      </c>
-      <c r="AT10">
-        <v>0.3018984444285246</v>
-      </c>
-      <c r="AU10">
         <v>0.6037968888570493</v>
       </c>
     </row>
@@ -2247,130 +2052,130 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2388,48 +2193,48 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" t="s">
         <v>83</v>
       </c>
-      <c r="B1" t="s">
+      <c r="H1" t="s">
         <v>84</v>
       </c>
-      <c r="C1" t="s">
+      <c r="I1" t="s">
         <v>85</v>
       </c>
-      <c r="D1" t="s">
+      <c r="J1" t="s">
         <v>86</v>
-      </c>
-      <c r="E1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E2">
         <v>0.02049261083743843</v>
@@ -2447,21 +2252,21 @@
         <v>250</v>
       </c>
       <c r="J2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E3">
         <v>0.02807881773399015</v>
@@ -2479,21 +2284,21 @@
         <v>250</v>
       </c>
       <c r="J3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E4">
         <v>0.04536945812807881</v>
@@ -2511,21 +2316,21 @@
         <v>250</v>
       </c>
       <c r="J4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E5">
         <v>0.4010837438423646</v>
@@ -2543,21 +2348,21 @@
         <v>250</v>
       </c>
       <c r="J5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E6">
         <v>0.413743842364532</v>
@@ -2575,21 +2380,21 @@
         <v>250</v>
       </c>
       <c r="J6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E7">
         <v>0.4725615763546798</v>
@@ -2607,21 +2412,21 @@
         <v>250</v>
       </c>
       <c r="J7" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E8">
         <v>0.503346436828533</v>
@@ -2639,21 +2444,21 @@
         <v>250</v>
       </c>
       <c r="J8" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E9">
         <v>0.5190271308530763</v>
@@ -2671,21 +2476,21 @@
         <v>250</v>
       </c>
       <c r="J9" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E10">
         <v>0.5875820873372553</v>
@@ -2703,21 +2508,21 @@
         <v>250</v>
       </c>
       <c r="J10" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E11">
         <v>0.34</v>
@@ -2735,21 +2540,21 @@
         <v>250</v>
       </c>
       <c r="J11" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E12">
         <v>0.3500000000000001</v>
@@ -2767,21 +2572,21 @@
         <v>250</v>
       </c>
       <c r="J12" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E13">
         <v>0.3999999999999999</v>
@@ -2799,21 +2604,21 @@
         <v>250</v>
       </c>
       <c r="J13" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E14">
         <v>0.5035496260262651</v>
@@ -2831,21 +2636,21 @@
         <v>250</v>
       </c>
       <c r="J14" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E15">
         <v>0.5189064985777815</v>
@@ -2863,21 +2668,21 @@
         <v>250</v>
       </c>
       <c r="J15" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E16">
         <v>0.5865506926221365</v>
@@ -2895,21 +2700,21 @@
         <v>250</v>
       </c>
       <c r="J16" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E17">
         <v>0.6921182266009852</v>
@@ -2927,21 +2732,21 @@
         <v>250</v>
       </c>
       <c r="J17" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E18">
         <v>0.6576354679802956</v>
@@ -2959,21 +2764,21 @@
         <v>250</v>
       </c>
       <c r="J18" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E19">
         <v>0.6108374384236454</v>
@@ -2991,21 +2796,21 @@
         <v>250</v>
       </c>
       <c r="J19" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E20">
         <v>0.01473429951690822</v>
@@ -3023,21 +2828,21 @@
         <v>207</v>
       </c>
       <c r="J20" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E21">
         <v>0.006376811594202901</v>
@@ -3055,21 +2860,21 @@
         <v>207</v>
       </c>
       <c r="J21" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E22">
         <v>0.002318840579710145</v>
@@ -3087,21 +2892,21 @@
         <v>207</v>
       </c>
       <c r="J22" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E23">
         <v>0.4014975845410628</v>
@@ -3119,21 +2924,21 @@
         <v>207</v>
       </c>
       <c r="J23" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E24">
         <v>0.4215458937198068</v>
@@ -3151,21 +2956,21 @@
         <v>207</v>
       </c>
       <c r="J24" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E25">
         <v>0.4694685990338164</v>
@@ -3183,21 +2988,21 @@
         <v>207</v>
       </c>
       <c r="J25" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E26">
         <v>0.4993498188103143</v>
@@ -3215,21 +3020,21 @@
         <v>207</v>
       </c>
       <c r="J26" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E27">
         <v>0.5350976252975095</v>
@@ -3247,21 +3052,21 @@
         <v>207</v>
       </c>
       <c r="J27" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E28">
         <v>0.5841530472476332</v>
@@ -3279,21 +3084,21 @@
         <v>207</v>
       </c>
       <c r="J28" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E29">
         <v>0.3599999999999999</v>
@@ -3311,21 +3116,21 @@
         <v>207</v>
       </c>
       <c r="J29" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E30">
         <v>0.37</v>
@@ -3343,21 +3148,21 @@
         <v>207</v>
       </c>
       <c r="J30" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E31">
         <v>0.4199999999999999</v>
@@ -3375,21 +3180,21 @@
         <v>207</v>
       </c>
       <c r="J31" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E32">
         <v>0.5003424089040717</v>
@@ -3407,21 +3212,21 @@
         <v>207</v>
       </c>
       <c r="J32" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E33">
         <v>0.5363567435512407</v>
@@ -3439,21 +3244,21 @@
         <v>207</v>
       </c>
       <c r="J33" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D34" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E34">
         <v>0.5855645643413213</v>
@@ -3471,21 +3276,21 @@
         <v>207</v>
       </c>
       <c r="J34" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" t="s">
         <v>93</v>
-      </c>
-      <c r="C35" t="s">
-        <v>50</v>
-      </c>
-      <c r="D35" t="s">
-        <v>99</v>
       </c>
       <c r="E35">
         <v>0.714975845410628</v>
@@ -3503,21 +3308,21 @@
         <v>207</v>
       </c>
       <c r="J35" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B36" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" t="s">
         <v>93</v>
-      </c>
-      <c r="C36" t="s">
-        <v>51</v>
-      </c>
-      <c r="D36" t="s">
-        <v>99</v>
       </c>
       <c r="E36">
         <v>0.6473429951690821</v>
@@ -3535,21 +3340,21 @@
         <v>207</v>
       </c>
       <c r="J36" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" t="s">
         <v>93</v>
-      </c>
-      <c r="C37" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" t="s">
-        <v>99</v>
       </c>
       <c r="E37">
         <v>0.6038647342995169</v>
@@ -3567,21 +3372,21 @@
         <v>207</v>
       </c>
       <c r="J37" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E38">
         <v>0.02648241206030149</v>
@@ -3599,21 +3404,21 @@
         <v>199</v>
       </c>
       <c r="J38" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C39" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E39">
         <v>0.05065326633165827</v>
@@ -3631,21 +3436,21 @@
         <v>199</v>
       </c>
       <c r="J39" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D40" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E40">
         <v>0.09015075376884421</v>
@@ -3663,21 +3468,21 @@
         <v>199</v>
       </c>
       <c r="J40" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E41">
         <v>0.4006532663316583</v>
@@ -3695,21 +3500,21 @@
         <v>199</v>
       </c>
       <c r="J41" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C42" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E42">
         <v>0.4056281407035176</v>
@@ -3727,21 +3532,21 @@
         <v>199</v>
       </c>
       <c r="J42" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C43" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D43" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E43">
         <v>0.4757788944723618</v>
@@ -3759,21 +3564,21 @@
         <v>199</v>
       </c>
       <c r="J43" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E44">
         <v>0.5074703248991672</v>
@@ -3791,21 +3596,21 @@
         <v>199</v>
       </c>
       <c r="J44" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D45" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E45">
         <v>0.5017647249418594</v>
@@ -3823,21 +3628,21 @@
         <v>199</v>
       </c>
       <c r="J45" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C46" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D46" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E46">
         <v>0.5911278717875009</v>
@@ -3855,21 +3660,21 @@
         <v>199</v>
       </c>
       <c r="J46" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D47" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E47">
         <v>0.34</v>
@@ -3887,21 +3692,21 @@
         <v>199</v>
       </c>
       <c r="J47" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C48" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D48" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E48">
         <v>0.3500000000000001</v>
@@ -3919,21 +3724,21 @@
         <v>199</v>
       </c>
       <c r="J48" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B49" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C49" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D49" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E49">
         <v>0.3900000000000001</v>
@@ -3951,21 +3756,21 @@
         <v>199</v>
       </c>
       <c r="J49" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B50" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E50">
         <v>0.5080569923909963</v>
@@ -3983,21 +3788,21 @@
         <v>199</v>
       </c>
       <c r="J50" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D51" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E51">
         <v>0.5004604701660993</v>
@@ -4015,21 +3820,21 @@
         <v>199</v>
       </c>
       <c r="J51" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D52" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E52">
         <v>0.5856865757701022</v>
@@ -4047,21 +3852,21 @@
         <v>199</v>
       </c>
       <c r="J52" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B53" t="s">
+        <v>87</v>
+      </c>
+      <c r="C53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D53" t="s">
         <v>93</v>
-      </c>
-      <c r="C53" t="s">
-        <v>50</v>
-      </c>
-      <c r="D53" t="s">
-        <v>99</v>
       </c>
       <c r="E53">
         <v>0.6683417085427136</v>
@@ -4079,21 +3884,21 @@
         <v>199</v>
       </c>
       <c r="J53" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B54" t="s">
+        <v>87</v>
+      </c>
+      <c r="C54" t="s">
+        <v>45</v>
+      </c>
+      <c r="D54" t="s">
         <v>93</v>
-      </c>
-      <c r="C54" t="s">
-        <v>51</v>
-      </c>
-      <c r="D54" t="s">
-        <v>99</v>
       </c>
       <c r="E54">
         <v>0.6683417085427136</v>
@@ -4111,21 +3916,21 @@
         <v>199</v>
       </c>
       <c r="J54" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B55" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" t="s">
+        <v>46</v>
+      </c>
+      <c r="D55" t="s">
         <v>93</v>
-      </c>
-      <c r="C55" t="s">
-        <v>52</v>
-      </c>
-      <c r="D55" t="s">
-        <v>99</v>
       </c>
       <c r="E55">
         <v>0.6180904522613065</v>
@@ -4143,7 +3948,7 @@
         <v>199</v>
       </c>
       <c r="J55" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -4166,78 +3971,78 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1" t="s">
         <v>83</v>
       </c>
-      <c r="B1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="K1" t="s">
+        <v>101</v>
+      </c>
+      <c r="L1" t="s">
         <v>102</v>
       </c>
-      <c r="E1" t="s">
+      <c r="M1" t="s">
         <v>103</v>
       </c>
-      <c r="F1" t="s">
+      <c r="N1" t="s">
         <v>104</v>
       </c>
-      <c r="G1" t="s">
+      <c r="O1" t="s">
         <v>105</v>
       </c>
-      <c r="H1" t="s">
+      <c r="P1" t="s">
         <v>106</v>
       </c>
-      <c r="I1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="Q1" t="s">
         <v>107</v>
       </c>
-      <c r="L1" t="s">
+      <c r="R1" t="s">
         <v>108</v>
       </c>
-      <c r="M1" t="s">
+      <c r="S1" t="s">
         <v>109</v>
-      </c>
-      <c r="N1" t="s">
-        <v>110</v>
-      </c>
-      <c r="O1" t="s">
-        <v>111</v>
-      </c>
-      <c r="P1" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>113</v>
-      </c>
-      <c r="R1" t="s">
-        <v>114</v>
-      </c>
-      <c r="S1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F2">
         <v>0.02049261083743843</v>
@@ -4264,13 +4069,13 @@
         <v>1.530907631213612</v>
       </c>
       <c r="N2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="O2">
         <v>0.7454</v>
       </c>
       <c r="P2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q2">
         <v>-0.05410272103966409</v>
@@ -4279,24 +4084,24 @@
         <v>0.03893030724656065</v>
       </c>
       <c r="S2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F3">
         <v>0.4010837438423646</v>
@@ -4323,13 +4128,13 @@
         <v>1.455610834346575</v>
       </c>
       <c r="N3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="O3">
         <v>0.461</v>
       </c>
       <c r="P3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q3">
         <v>-0.05229618964656452</v>
@@ -4338,24 +4143,24 @@
         <v>0.02697599260222911</v>
       </c>
       <c r="S3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F4">
         <v>0.503346436828533</v>
@@ -4382,39 +4187,33 @@
         <v>1.525496624127441</v>
       </c>
       <c r="N4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="O4">
         <v>0.3852</v>
       </c>
       <c r="P4" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q4">
-        <v>-0.05856576544801697</v>
-      </c>
-      <c r="R4">
-        <v>0.02781683152088908</v>
+        <v>113</v>
       </c>
       <c r="S4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F5">
         <v>0.34</v>
@@ -4435,13 +4234,13 @@
         <v>0.6112</v>
       </c>
       <c r="N5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O5">
         <v>0.7282</v>
       </c>
       <c r="P5" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q5">
         <v>-0.08000000000000007</v>
@@ -4450,24 +4249,24 @@
         <v>0.05999999999999983</v>
       </c>
       <c r="S5" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F6">
         <v>0.5035496260262651</v>
@@ -4488,39 +4287,33 @@
         <v>0.3894</v>
       </c>
       <c r="N6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O6">
         <v>0.3894</v>
       </c>
       <c r="P6" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q6">
-        <v>-0.05815433485882701</v>
-      </c>
-      <c r="R6">
-        <v>0.02825025172545625</v>
+        <v>113</v>
       </c>
       <c r="S6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F7">
         <v>0.6921182266009852</v>
@@ -4547,39 +4340,33 @@
         <v>1.575352047426485</v>
       </c>
       <c r="N7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O7">
         <v>0.204560421762222</v>
       </c>
       <c r="P7" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q7">
-        <v>-0.03189014549308666</v>
-      </c>
-      <c r="R7">
-        <v>0.09762516046213096</v>
+        <v>114</v>
       </c>
       <c r="S7" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F8">
         <v>0.02049261083743843</v>
@@ -4606,13 +4393,13 @@
         <v>1.496102394400772</v>
       </c>
       <c r="N8" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="O8">
         <v>0.5734</v>
       </c>
       <c r="P8" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q8">
         <v>-0.08440726271056506</v>
@@ -4621,24 +4408,24 @@
         <v>0.03465356812928424</v>
       </c>
       <c r="S8" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F9">
         <v>0.4010837438423646</v>
@@ -4665,13 +4452,13 @@
         <v>1.553586372596406</v>
       </c>
       <c r="N9" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="O9">
         <v>0.0004</v>
       </c>
       <c r="P9" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q9">
         <v>-0.1160939316204946</v>
@@ -4680,24 +4467,24 @@
         <v>-0.02686173340413656</v>
       </c>
       <c r="S9" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F10">
         <v>0.503346436828533</v>
@@ -4724,39 +4511,33 @@
         <v>1.581607874494274</v>
       </c>
       <c r="N10" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="O10">
         <v>0.0008</v>
       </c>
       <c r="P10" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q10">
-        <v>-0.1343146850892964</v>
-      </c>
-      <c r="R10">
-        <v>-0.03239054644227161</v>
+        <v>113</v>
       </c>
       <c r="S10" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F11">
         <v>0.34</v>
@@ -4777,13 +4558,13 @@
         <v>0.028</v>
       </c>
       <c r="N11" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O11">
         <v>0.09279999999999999</v>
       </c>
       <c r="P11" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q11">
         <v>-0.1280741611297381</v>
@@ -4792,24 +4573,24 @@
         <v>0.008074161129738217</v>
       </c>
       <c r="S11" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F12">
         <v>0.5035496260262651</v>
@@ -4830,39 +4611,33 @@
         <v>0.0005999999999999999</v>
       </c>
       <c r="N12" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O12">
         <v>0.0008</v>
       </c>
       <c r="P12" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q12">
-        <v>-0.1324121069898527</v>
-      </c>
-      <c r="R12">
-        <v>-0.03081160526701519</v>
+        <v>113</v>
       </c>
       <c r="S12" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F13">
         <v>0.6921182266009852</v>
@@ -4889,39 +4664,33 @@
         <v>1.535849843792607</v>
       </c>
       <c r="N13" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O13">
         <v>0.02059161466558826</v>
       </c>
       <c r="P13" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q13">
-        <v>0.009991271820448863</v>
-      </c>
-      <c r="R13">
-        <v>0.152573275862069</v>
+        <v>114</v>
       </c>
       <c r="S13" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F14">
         <v>0.02807881773399015</v>
@@ -4948,13 +4717,13 @@
         <v>1.422466582636034</v>
       </c>
       <c r="N14" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="O14">
         <v>0.7454</v>
       </c>
       <c r="P14" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q14">
         <v>-0.08180644473769279</v>
@@ -4963,24 +4732,24 @@
         <v>0.04722516394951541</v>
       </c>
       <c r="S14" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F15">
         <v>0.413743842364532</v>
@@ -5007,13 +4776,13 @@
         <v>1.419611895158891</v>
       </c>
       <c r="N15" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="O15">
         <v>0.0104</v>
       </c>
       <c r="P15" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q15">
         <v>-0.1084139624854691</v>
@@ -5022,24 +4791,24 @@
         <v>-0.009221505494826733</v>
       </c>
       <c r="S15" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F16">
         <v>0.5190271308530763</v>
@@ -5066,39 +4835,33 @@
         <v>1.504729680828269</v>
       </c>
       <c r="N16" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="O16">
         <v>0.0052</v>
       </c>
       <c r="P16" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q16">
-        <v>-0.1237607966652773</v>
-      </c>
-      <c r="R16">
-        <v>-0.01197481543232409</v>
+        <v>113</v>
       </c>
       <c r="S16" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F17">
         <v>0.3500000000000001</v>
@@ -5119,13 +4882,13 @@
         <v>0.1748</v>
       </c>
       <c r="N17" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="O17">
         <v>0.2226</v>
       </c>
       <c r="P17" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q17">
         <v>-0.1230166690346133</v>
@@ -5134,24 +4897,24 @@
         <v>0.02301666903461366</v>
       </c>
       <c r="S17" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F18">
         <v>0.5189064985777815</v>
@@ -5172,39 +4935,33 @@
         <v>0.005</v>
       </c>
       <c r="N18" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O18">
         <v>0.008399999999999999</v>
       </c>
       <c r="P18" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q18">
-        <v>-0.1227389787054996</v>
-      </c>
-      <c r="R18">
-        <v>-0.009991811914109265</v>
+        <v>113</v>
       </c>
       <c r="S18" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E19" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F19">
         <v>0.6576354679802956</v>
@@ -5231,39 +4988,33 @@
         <v>1.42473165658859</v>
       </c>
       <c r="N19" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="O19">
         <v>0.204560421762222</v>
       </c>
       <c r="P19" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q19">
-        <v>-0.02693148335989953</v>
-      </c>
-      <c r="R19">
-        <v>0.118272411680621</v>
+        <v>114</v>
       </c>
       <c r="S19" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F20">
         <v>0.01473429951690822</v>
@@ -5284,13 +5035,13 @@
         <v>0.7482</v>
       </c>
       <c r="N20" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O20">
         <v>0.9228</v>
       </c>
       <c r="P20" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q20">
         <v>-0.05103539816859672</v>
@@ -5299,24 +5050,24 @@
         <v>0.06775037401400737</v>
       </c>
       <c r="S20" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:19">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F21">
         <v>0.4014975845410628</v>
@@ -5337,13 +5088,13 @@
         <v>0.3648</v>
       </c>
       <c r="N21" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O21">
         <v>0.3648</v>
       </c>
       <c r="P21" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q21">
         <v>-0.07233878000738253</v>
@@ -5352,24 +5103,24 @@
         <v>0.03224216164989475</v>
       </c>
       <c r="S21" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:19">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F22">
         <v>0.4993498188103143</v>
@@ -5390,39 +5141,33 @@
         <v>0.1386</v>
       </c>
       <c r="N22" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O22">
         <v>0.2192</v>
       </c>
       <c r="P22" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q22">
-        <v>-0.09123869203614131</v>
-      </c>
-      <c r="R22">
-        <v>0.0222793709494871</v>
+        <v>113</v>
       </c>
       <c r="S22" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:19">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F23">
         <v>0.3599999999999999</v>
@@ -5443,13 +5188,13 @@
         <v>0.6612</v>
       </c>
       <c r="N23" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="O23">
         <v>0.7706</v>
       </c>
       <c r="P23" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q23">
         <v>-0.1038971985921919</v>
@@ -5458,24 +5203,24 @@
         <v>0.08389719859219168</v>
       </c>
       <c r="S23" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F24">
         <v>0.5003424089040717</v>
@@ -5496,39 +5241,33 @@
         <v>0.1346</v>
       </c>
       <c r="N24" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O24">
         <v>0.2062</v>
       </c>
       <c r="P24" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q24">
-        <v>-0.09115161458112336</v>
-      </c>
-      <c r="R24">
-        <v>0.02135292562963592</v>
+        <v>113</v>
       </c>
       <c r="S24" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s">
         <v>93</v>
       </c>
-      <c r="C25" t="s">
-        <v>99</v>
-      </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F25">
         <v>0.714975845410628</v>
@@ -5549,39 +5288,33 @@
         <v>0.08782509563019504</v>
       </c>
       <c r="N25" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="O25">
         <v>0.1756501912603901</v>
       </c>
       <c r="P25" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q25">
-        <v>-0.01932367149758452</v>
-      </c>
-      <c r="R25">
-        <v>0.1594202898550724</v>
+        <v>114</v>
       </c>
       <c r="S25" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F26">
         <v>0.01473429951690822</v>
@@ -5602,13 +5335,13 @@
         <v>0.6962</v>
       </c>
       <c r="N26" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O26">
         <v>0.9156</v>
       </c>
       <c r="P26" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q26">
         <v>-0.06168545131060543</v>
@@ -5617,24 +5350,24 @@
         <v>0.08651636918500157</v>
       </c>
       <c r="S26" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:19">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F27">
         <v>0.4014975845410628</v>
@@ -5655,13 +5388,13 @@
         <v>0.0066</v>
       </c>
       <c r="N27" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O27">
         <v>0.0182</v>
       </c>
       <c r="P27" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q27">
         <v>-0.1263846722789996</v>
@@ -5670,24 +5403,24 @@
         <v>-0.009557356706507911</v>
       </c>
       <c r="S27" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:19">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F28">
         <v>0.4993498188103143</v>
@@ -5708,39 +5441,33 @@
         <v>0.004</v>
       </c>
       <c r="N28" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O28">
         <v>0.0112</v>
       </c>
       <c r="P28" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q28">
-        <v>-0.1509793143671761</v>
-      </c>
-      <c r="R28">
-        <v>-0.01141466056599736</v>
+        <v>113</v>
       </c>
       <c r="S28" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F29">
         <v>0.3599999999999999</v>
@@ -5761,13 +5488,13 @@
         <v>0.044</v>
       </c>
       <c r="N29" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="O29">
         <v>0.3118</v>
       </c>
       <c r="P29" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q29">
         <v>-0.1500000000000001</v>
@@ -5776,24 +5503,24 @@
         <v>0.03000000000000003</v>
       </c>
       <c r="S29" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:19">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F30">
         <v>0.5003424089040717</v>
@@ -5814,39 +5541,33 @@
         <v>0.006</v>
       </c>
       <c r="N30" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O30">
         <v>0.0176</v>
       </c>
       <c r="P30" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q30">
-        <v>-0.1511909993124804</v>
-      </c>
-      <c r="R30">
-        <v>-0.01232031333021981</v>
+        <v>113</v>
       </c>
       <c r="S30" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:19">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" t="s">
         <v>93</v>
       </c>
-      <c r="C31" t="s">
-        <v>99</v>
-      </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F31">
         <v>0.714975845410628</v>
@@ -5867,39 +5588,33 @@
         <v>0.006357215082587968</v>
       </c>
       <c r="N31" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="O31">
         <v>0.0190716452477639</v>
       </c>
       <c r="P31" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q31">
-        <v>0.01932367149758452</v>
-      </c>
-      <c r="R31">
-        <v>0.2028985507246377</v>
+        <v>114</v>
       </c>
       <c r="S31" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:19">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E32" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F32">
         <v>0.006376811594202901</v>
@@ -5920,13 +5635,13 @@
         <v>0.9026</v>
       </c>
       <c r="N32" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O32">
         <v>0.9228</v>
       </c>
       <c r="P32" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q32">
         <v>-0.07685225067811854</v>
@@ -5935,24 +5650,24 @@
         <v>0.08496819270710404</v>
       </c>
       <c r="S32" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:19">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E33" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F33">
         <v>0.4215458937198068</v>
@@ -5973,13 +5688,13 @@
         <v>0.0788</v>
       </c>
       <c r="N33" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O33">
         <v>0.1346</v>
       </c>
       <c r="P33" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q33">
         <v>-0.111707487254363</v>
@@ -5988,24 +5703,24 @@
         <v>0.01586207662634324</v>
       </c>
       <c r="S33" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:19">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E34" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F34">
         <v>0.5350976252975095</v>
@@ -6026,39 +5741,33 @@
         <v>0.1238</v>
       </c>
       <c r="N34" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O34">
         <v>0.2192</v>
       </c>
       <c r="P34" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q34">
-        <v>-0.1238415295689909</v>
-      </c>
-      <c r="R34">
-        <v>0.02673239532361265</v>
+        <v>113</v>
       </c>
       <c r="S34" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:19">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F35">
         <v>0.37</v>
@@ -6079,13 +5788,13 @@
         <v>0.224</v>
       </c>
       <c r="N35" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="O35">
         <v>0.4476</v>
       </c>
       <c r="P35" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q35">
         <v>-0.1519260792971539</v>
@@ -6094,24 +5803,24 @@
         <v>0.05192607929715401</v>
       </c>
       <c r="S35" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:19">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D36" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E36" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F36">
         <v>0.5363567435512407</v>
@@ -6132,39 +5841,33 @@
         <v>0.1184</v>
       </c>
       <c r="N36" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O36">
         <v>0.2062</v>
       </c>
       <c r="P36" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q36">
-        <v>-0.1228604273873636</v>
-      </c>
-      <c r="R36">
-        <v>0.02669462629634863</v>
+        <v>113</v>
       </c>
       <c r="S36" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:19">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" t="s">
         <v>93</v>
       </c>
-      <c r="C37" t="s">
-        <v>99</v>
-      </c>
       <c r="D37" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E37" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F37">
         <v>0.6473429951690821</v>
@@ -6185,39 +5888,33 @@
         <v>0.3134999455835852</v>
       </c>
       <c r="N37" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="O37">
         <v>0.3134999455835852</v>
       </c>
       <c r="P37" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q37">
-        <v>-0.04830917874396135</v>
-      </c>
-      <c r="R37">
-        <v>0.1352657004830918</v>
+        <v>114</v>
       </c>
       <c r="S37" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:19">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F38">
         <v>0.02648241206030149</v>
@@ -6238,13 +5935,13 @@
         <v>0.3916</v>
       </c>
       <c r="N38" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O38">
         <v>0.4768</v>
       </c>
       <c r="P38" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q38">
         <v>-0.0908680477437257</v>
@@ -6253,24 +5950,24 @@
         <v>0.0425263392010121</v>
       </c>
       <c r="S38" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:19">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D39" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E39" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F39">
         <v>0.4006532663316583</v>
@@ -6291,13 +5988,13 @@
         <v>0.8314</v>
       </c>
       <c r="N39" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O39">
         <v>0.8314</v>
       </c>
       <c r="P39" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q39">
         <v>-0.06040181445148433</v>
@@ -6306,24 +6003,24 @@
         <v>0.05045206570776576</v>
       </c>
       <c r="S39" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:19">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E40" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F40">
         <v>0.5074703248991672</v>
@@ -6344,39 +6041,33 @@
         <v>0.8202</v>
       </c>
       <c r="N40" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O40">
         <v>0.8202</v>
       </c>
       <c r="P40" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q40">
-        <v>-0.05453718467014974</v>
-      </c>
-      <c r="R40">
-        <v>0.06313045014530488</v>
+        <v>113</v>
       </c>
       <c r="S40" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:19">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E41" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F41">
         <v>0.34</v>
@@ -6397,13 +6088,13 @@
         <v>0.6392</v>
       </c>
       <c r="N41" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="O41">
         <v>0.764</v>
       </c>
       <c r="P41" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q41">
         <v>-0.09925482790573971</v>
@@ -6412,24 +6103,24 @@
         <v>0.07925482790573947</v>
       </c>
       <c r="S41" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:19">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E42" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F42">
         <v>0.5080569923909963</v>
@@ -6450,39 +6141,33 @@
         <v>0.761</v>
       </c>
       <c r="N42" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O42">
         <v>0.761</v>
       </c>
       <c r="P42" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q42">
-        <v>-0.05188362266759145</v>
-      </c>
-      <c r="R42">
-        <v>0.06498731161172748</v>
+        <v>113</v>
       </c>
       <c r="S42" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:19">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" t="s">
         <v>93</v>
       </c>
-      <c r="C43" t="s">
-        <v>99</v>
-      </c>
       <c r="D43" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E43" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F43">
         <v>0.6683417085427136</v>
@@ -6503,39 +6188,33 @@
         <v>1</v>
       </c>
       <c r="N43" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q43">
-        <v>-0.09547738693467334</v>
-      </c>
-      <c r="R43">
-        <v>0.09045226130653261</v>
+        <v>114</v>
       </c>
       <c r="S43" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E44" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F44">
         <v>0.02648241206030149</v>
@@ -6556,13 +6235,13 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="N44" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O44">
         <v>0.1878</v>
       </c>
       <c r="P44" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q44">
         <v>-0.1488692935139442</v>
@@ -6571,24 +6250,24 @@
         <v>0.02153261009685876</v>
       </c>
       <c r="S44" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:19">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E45" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F45">
         <v>0.4006532663316583</v>
@@ -6609,13 +6288,13 @@
         <v>0.008200000000000001</v>
       </c>
       <c r="N45" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O45">
         <v>0.024</v>
       </c>
       <c r="P45" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q45">
         <v>-0.1420685129346101</v>
@@ -6624,24 +6303,24 @@
         <v>-0.008182743346796903</v>
       </c>
       <c r="S45" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:19">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C46" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D46" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E46" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F46">
         <v>0.5074703248991672</v>
@@ -6662,39 +6341,33 @@
         <v>0.0086</v>
       </c>
       <c r="N46" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O46">
         <v>0.0188</v>
       </c>
       <c r="P46" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q46">
-        <v>-0.1557722033973963</v>
-      </c>
-      <c r="R46">
-        <v>-0.008380156597759411</v>
+        <v>113</v>
       </c>
       <c r="S46" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:19">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C47" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D47" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E47" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F47">
         <v>0.34</v>
@@ -6715,13 +6388,13 @@
         <v>0.1548</v>
       </c>
       <c r="N47" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="O47">
         <v>0.2654</v>
       </c>
       <c r="P47" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q47">
         <v>-0.1364378623663957</v>
@@ -6730,24 +6403,24 @@
         <v>0.03643786236639536</v>
       </c>
       <c r="S47" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:19">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C48" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D48" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E48" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F48">
         <v>0.5080569923909963</v>
@@ -6768,39 +6441,33 @@
         <v>0.0224</v>
       </c>
       <c r="N48" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O48">
         <v>0.0424</v>
       </c>
       <c r="P48" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q48">
-        <v>-0.149432629305434</v>
-      </c>
-      <c r="R48">
-        <v>-0.001071822703622774</v>
+        <v>113</v>
       </c>
       <c r="S48" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:19">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B49" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" t="s">
         <v>93</v>
       </c>
-      <c r="C49" t="s">
-        <v>99</v>
-      </c>
       <c r="D49" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E49" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F49">
         <v>0.6683417085427136</v>
@@ -6821,39 +6488,33 @@
         <v>0.3018984444285246</v>
       </c>
       <c r="N49" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="O49">
         <v>0.6037968888570493</v>
       </c>
       <c r="P49" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q49">
-        <v>-0.05527638190954776</v>
-      </c>
-      <c r="R49">
-        <v>0.1457286432160805</v>
+        <v>114</v>
       </c>
       <c r="S49" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:19">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B50" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C50" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E50" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F50">
         <v>0.05065326633165827</v>
@@ -6874,13 +6535,13 @@
         <v>0.2944</v>
       </c>
       <c r="N50" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O50">
         <v>0.4768</v>
       </c>
       <c r="P50" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q50">
         <v>-0.1270242150164059</v>
@@ -6889,24 +6550,24 @@
         <v>0.04802924014203403</v>
       </c>
       <c r="S50" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:19">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D51" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E51" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F51">
         <v>0.4056281407035176</v>
@@ -6927,13 +6588,13 @@
         <v>0.0186</v>
       </c>
       <c r="N51" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O51">
         <v>0.0348</v>
       </c>
       <c r="P51" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q51">
         <v>-0.1390395629729493</v>
@@ -6942,24 +6603,24 @@
         <v>-0.001261944564739118</v>
       </c>
       <c r="S51" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:19">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D52" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E52" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F52">
         <v>0.5017647249418594</v>
@@ -6980,39 +6641,33 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="N52" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="O52">
         <v>0.0188</v>
       </c>
       <c r="P52" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q52">
-        <v>-0.1647937957865656</v>
-      </c>
-      <c r="R52">
-        <v>-0.009124463780871214</v>
+        <v>113</v>
       </c>
       <c r="S52" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:19">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C53" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D53" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E53" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F53">
         <v>0.3500000000000001</v>
@@ -7033,13 +6688,13 @@
         <v>0.3536</v>
       </c>
       <c r="N53" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="O53">
         <v>0.4588</v>
       </c>
       <c r="P53" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Q53">
         <v>-0.13</v>
@@ -7048,24 +6703,24 @@
         <v>0.04999999999999993</v>
       </c>
       <c r="S53" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:19">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C54" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D54" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E54" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F54">
         <v>0.5004604701660993</v>
@@ -7086,39 +6741,33 @@
         <v>0.0134</v>
       </c>
       <c r="N54" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="O54">
         <v>0.0322</v>
       </c>
       <c r="P54" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q54">
-        <v>-0.1609806360778065</v>
-      </c>
-      <c r="R54">
-        <v>-0.003463348309243171</v>
+        <v>113</v>
       </c>
       <c r="S54" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:19">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B55" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" t="s">
         <v>93</v>
       </c>
-      <c r="C55" t="s">
-        <v>99</v>
-      </c>
       <c r="D55" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E55" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F55">
         <v>0.6683417085427136</v>
@@ -7139,22 +6788,16 @@
         <v>0.3018984444285246</v>
       </c>
       <c r="N55" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="O55">
         <v>0.6037968888570493</v>
       </c>
       <c r="P55" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q55">
-        <v>-0.05527638190954776</v>
-      </c>
-      <c r="R55">
-        <v>0.1507537688442211</v>
+        <v>114</v>
       </c>
       <c r="S55" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -7178,78 +6821,78 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H1" t="s">
         <v>84</v>
       </c>
-      <c r="C1" t="s">
+      <c r="I1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1" t="s">
         <v>123</v>
       </c>
-      <c r="D1" t="s">
+      <c r="K1" t="s">
         <v>124</v>
       </c>
-      <c r="E1" t="s">
+      <c r="L1" t="s">
         <v>125</v>
       </c>
-      <c r="F1" t="s">
+      <c r="M1" t="s">
         <v>126</v>
       </c>
-      <c r="G1" t="s">
+      <c r="N1" t="s">
         <v>127</v>
       </c>
-      <c r="H1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
         <v>128</v>
       </c>
-      <c r="K1" t="s">
+      <c r="P1" t="s">
         <v>129</v>
       </c>
-      <c r="L1" t="s">
+      <c r="Q1" t="s">
         <v>130</v>
       </c>
-      <c r="M1" t="s">
+      <c r="R1" t="s">
         <v>131</v>
-      </c>
-      <c r="N1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O1" t="s">
-        <v>133</v>
-      </c>
-      <c r="P1" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>135</v>
-      </c>
-      <c r="R1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" t="s">
         <v>137</v>
       </c>
-      <c r="D2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" t="s">
-        <v>142</v>
-      </c>
       <c r="G2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H2">
         <v>406</v>
@@ -7273,39 +6916,39 @@
         <v>42</v>
       </c>
       <c r="O2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="P2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H3">
         <v>207</v>
@@ -7329,39 +6972,39 @@
         <v>42</v>
       </c>
       <c r="O3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H4">
         <v>199</v>
@@ -7385,16 +7028,16 @@
         <v>42</v>
       </c>
       <c r="O4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="P4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/examples/example_continuous_results.xlsx
+++ b/examples/example_continuous_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="139">
   <si>
     <t>Group</t>
   </si>
@@ -146,10 +146,13 @@
     <t>All</t>
   </si>
   <si>
-    <t>eye = L</t>
-  </si>
-  <si>
-    <t>eye = R</t>
+    <t>axial_length &lt;22</t>
+  </si>
+  <si>
+    <t>axial_length 22 to &lt;24.5</t>
+  </si>
+  <si>
+    <t>axial_length &gt;=24.5</t>
   </si>
   <si>
     <t>model_A</t>
@@ -245,7 +248,7 @@
     <t>ρΔ (rho_delta): intraclass correlation of the per-eye difference in loss between the two models; one_eye_factor: patients a one-eye study needs, relative to this analysis (design effect)</t>
   </si>
   <si>
-    <t>eye, nominal: one subgroup per level (L, R). Each subgroup is analyzed separately with the same models, tests and settings</t>
+    <t>axial_length, continuous, cut points 22, 24.5: &lt;22, 22 to &lt;24.5, &gt;=24.5 (each interval includes its lower cut point). Each subgroup is analyzed separately with the same models, tests and settings</t>
   </si>
   <si>
     <t>Subgroup results are exploratory: p-values and intervals are adjusted for the model pairs within each group, not across groups</t>
@@ -281,157 +284,151 @@
     <t>method</t>
   </si>
   <si>
+    <t>axial_length</t>
+  </si>
+  <si>
+    <t>bias</t>
+  </si>
+  <si>
+    <t>mae</t>
+  </si>
+  <si>
+    <t>rmse</t>
+  </si>
+  <si>
+    <t>medae</t>
+  </si>
+  <si>
+    <t>sd</t>
+  </si>
+  <si>
+    <t>within</t>
+  </si>
+  <si>
+    <t>patient bootstrap, percentile</t>
+  </si>
+  <si>
+    <t>model_a</t>
+  </si>
+  <si>
+    <t>model_b</t>
+  </si>
+  <si>
+    <t>est_a</t>
+  </si>
+  <si>
+    <t>est_b</t>
+  </si>
+  <si>
+    <t>diff</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>rho_delta</t>
+  </si>
+  <si>
+    <t>one_eye_factor</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>p_adj</t>
+  </si>
+  <si>
+    <t>p_adj_method</t>
+  </si>
+  <si>
+    <t>ci_adj_low</t>
+  </si>
+  <si>
+    <t>ci_adj_high</t>
+  </si>
+  <si>
+    <t>ci_adj_method</t>
+  </si>
+  <si>
+    <t>Romano-Wolf step-down</t>
+  </si>
+  <si>
+    <t>Hommel</t>
+  </si>
+  <si>
+    <t>Romano-Wolf simultaneous (max-|t|)</t>
+  </si>
+  <si>
+    <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
+  </si>
+  <si>
+    <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
+  </si>
+  <si>
+    <t>definition</t>
+  </si>
+  <si>
+    <t>task</t>
+  </si>
+  <si>
+    <t>models</t>
+  </si>
+  <si>
+    <t>patient_column</t>
+  </si>
+  <si>
+    <t>truth</t>
+  </si>
+  <si>
+    <t>n_bilateral</t>
+  </si>
+  <si>
+    <t>bilateral_fraction</t>
+  </si>
+  <si>
+    <t>clustered</t>
+  </si>
+  <si>
+    <t>bootstrap_iterations</t>
+  </si>
+  <si>
+    <t>seed</t>
+  </si>
+  <si>
+    <t>weighting</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>one_eye</t>
+  </si>
+  <si>
+    <t>fwer_method</t>
+  </si>
+  <si>
+    <t>All eyes: 406 eyes, 250 patients</t>
+  </si>
+  <si>
+    <t>axial_length &lt;22: 69 eyes, 44 patients</t>
+  </si>
+  <si>
+    <t>axial_length 22 to &lt;24.5: 238 eyes, 154 patients</t>
+  </si>
+  <si>
+    <t>axial_length &gt;=24.5: 99 eyes, 64 patients</t>
+  </si>
+  <si>
+    <t>continuous</t>
+  </si>
+  <si>
+    <t>['model_A', 'model_B', 'model_C']</t>
+  </si>
+  <si>
+    <t>patient_id</t>
+  </si>
+  <si>
     <t>eye</t>
-  </si>
-  <si>
-    <t>bias</t>
-  </si>
-  <si>
-    <t>mae</t>
-  </si>
-  <si>
-    <t>rmse</t>
-  </si>
-  <si>
-    <t>medae</t>
-  </si>
-  <si>
-    <t>sd</t>
-  </si>
-  <si>
-    <t>within</t>
-  </si>
-  <si>
-    <t>patient bootstrap, percentile</t>
-  </si>
-  <si>
-    <t>bootstrap, percentile</t>
-  </si>
-  <si>
-    <t>model_a</t>
-  </si>
-  <si>
-    <t>model_b</t>
-  </si>
-  <si>
-    <t>est_a</t>
-  </si>
-  <si>
-    <t>est_b</t>
-  </si>
-  <si>
-    <t>diff</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>rho_delta</t>
-  </si>
-  <si>
-    <t>one_eye_factor</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>p_adj</t>
-  </si>
-  <si>
-    <t>p_adj_method</t>
-  </si>
-  <si>
-    <t>ci_adj_low</t>
-  </si>
-  <si>
-    <t>ci_adj_high</t>
-  </si>
-  <si>
-    <t>ci_adj_method</t>
-  </si>
-  <si>
-    <t>bootstrap-t</t>
-  </si>
-  <si>
-    <t>percentile bootstrap</t>
-  </si>
-  <si>
-    <t>McNemar</t>
-  </si>
-  <si>
-    <t>Romano-Wolf step-down</t>
-  </si>
-  <si>
-    <t>Hommel</t>
-  </si>
-  <si>
-    <t>Romano-Wolf simultaneous (max-|t|)</t>
-  </si>
-  <si>
-    <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
-  </si>
-  <si>
-    <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
-  </si>
-  <si>
-    <t>definition</t>
-  </si>
-  <si>
-    <t>task</t>
-  </si>
-  <si>
-    <t>models</t>
-  </si>
-  <si>
-    <t>patient_column</t>
-  </si>
-  <si>
-    <t>truth</t>
-  </si>
-  <si>
-    <t>n_bilateral</t>
-  </si>
-  <si>
-    <t>bilateral_fraction</t>
-  </si>
-  <si>
-    <t>clustered</t>
-  </si>
-  <si>
-    <t>bootstrap_iterations</t>
-  </si>
-  <si>
-    <t>seed</t>
-  </si>
-  <si>
-    <t>weighting</t>
-  </si>
-  <si>
-    <t>unit</t>
-  </si>
-  <si>
-    <t>one_eye</t>
-  </si>
-  <si>
-    <t>fwer_method</t>
-  </si>
-  <si>
-    <t>All eyes: 406 eyes, 250 patients</t>
-  </si>
-  <si>
-    <t>eye = L: 207 eyes, 207 patients</t>
-  </si>
-  <si>
-    <t>eye = R: 199 eyes, 199 patients</t>
-  </si>
-  <si>
-    <t>continuous</t>
-  </si>
-  <si>
-    <t>['model_A', 'model_B', 'model_C']</t>
-  </si>
-  <si>
-    <t>patient_id</t>
   </si>
   <si>
     <t>patient</t>
@@ -769,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="10" width="22.7109375" customWidth="1"/>
@@ -916,10 +913,10 @@
         <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2">
         <v>406</v>
@@ -928,19 +925,19 @@
         <v>250</v>
       </c>
       <c r="F2">
-        <v>-0.00758620689655172</v>
+        <v>-0.007586206896551734</v>
       </c>
       <c r="G2">
-        <v>-0.04493901095487549</v>
+        <v>-0.04493901095487556</v>
       </c>
       <c r="H2">
-        <v>0.03040411335473123</v>
+        <v>0.03040411335473117</v>
       </c>
       <c r="I2">
-        <v>-0.05410272103966409</v>
+        <v>-0.05410272103966406</v>
       </c>
       <c r="J2">
-        <v>0.03893030724656065</v>
+        <v>0.03893030724656057</v>
       </c>
       <c r="K2">
         <v>0.6926</v>
@@ -952,16 +949,16 @@
         <v>-0.01266009852216748</v>
       </c>
       <c r="N2">
-        <v>-0.04537308813124197</v>
+        <v>-0.04537308813124185</v>
       </c>
       <c r="O2">
-        <v>0.02084416313854757</v>
+        <v>0.0208441631385477</v>
       </c>
       <c r="P2">
-        <v>-0.05229618964656452</v>
+        <v>-0.05229618964656447</v>
       </c>
       <c r="Q2">
-        <v>0.02697599260222911</v>
+        <v>0.02697599260222917</v>
       </c>
       <c r="R2">
         <v>0.461</v>
@@ -973,10 +970,10 @@
         <v>-0.01568069402454331</v>
       </c>
       <c r="U2">
-        <v>-0.05106318963604019</v>
+        <v>-0.05106318963604003</v>
       </c>
       <c r="V2">
-        <v>0.01787937336349208</v>
+        <v>0.01787937336349218</v>
       </c>
       <c r="W2">
         <v>0.3852</v>
@@ -985,34 +982,34 @@
         <v>0.3852</v>
       </c>
       <c r="Y2">
-        <v>-0.01000000000000012</v>
+        <v>-0.009999999999999953</v>
       </c>
       <c r="Z2">
-        <v>-0.07000000000000073</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AA2">
-        <v>0.04000000000000004</v>
+        <v>0.03999999999999998</v>
       </c>
       <c r="AB2">
-        <v>-0.08000000000000007</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="AC2">
-        <v>0.05999999999999983</v>
+        <v>0.06000000000000011</v>
       </c>
       <c r="AD2">
-        <v>0.6112</v>
+        <v>0.6968</v>
       </c>
       <c r="AE2">
-        <v>0.7282</v>
+        <v>0.844</v>
       </c>
       <c r="AF2">
         <v>-0.01535687255151641</v>
       </c>
       <c r="AG2">
-        <v>-0.05064189418206685</v>
+        <v>-0.05064189418206674</v>
       </c>
       <c r="AH2">
-        <v>0.01876017330561063</v>
+        <v>0.01876017330561083</v>
       </c>
       <c r="AI2">
         <v>0.3894</v>
@@ -1041,10 +1038,10 @@
         <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3">
         <v>406</v>
@@ -1056,16 +1053,16 @@
         <v>-0.02487684729064039</v>
       </c>
       <c r="G3">
-        <v>-0.07516438999171429</v>
+        <v>-0.07516438999171443</v>
       </c>
       <c r="H3">
-        <v>0.02555545062902348</v>
+        <v>0.02555545062902334</v>
       </c>
       <c r="I3">
-        <v>-0.08440726271056506</v>
+        <v>-0.08440726271056505</v>
       </c>
       <c r="J3">
-        <v>0.03465356812928424</v>
+        <v>0.03465356812928412</v>
       </c>
       <c r="K3">
         <v>0.323</v>
@@ -1077,16 +1074,16 @@
         <v>-0.07147783251231526</v>
       </c>
       <c r="N3">
-        <v>-0.1094511309795232</v>
+        <v>-0.1094511309795231</v>
       </c>
       <c r="O3">
-        <v>-0.03377935695481725</v>
+        <v>-0.03377935695481713</v>
       </c>
       <c r="P3">
         <v>-0.1160939316204946</v>
       </c>
       <c r="Q3">
-        <v>-0.02686173340413656</v>
+        <v>-0.02686173340413649</v>
       </c>
       <c r="R3">
         <v>0.0004</v>
@@ -1098,7 +1095,7 @@
         <v>-0.08423565050872228</v>
       </c>
       <c r="U3">
-        <v>-0.1255427629627514</v>
+        <v>-0.1255427629627515</v>
       </c>
       <c r="V3">
         <v>-0.0419672383242247</v>
@@ -1110,34 +1107,34 @@
         <v>0.0008</v>
       </c>
       <c r="Y3">
-        <v>-0.05999999999999994</v>
+        <v>-0.06</v>
       </c>
       <c r="Z3">
-        <v>-0.1199999999999999</v>
+        <v>-0.12</v>
       </c>
       <c r="AA3">
-        <v>-0.009999999999999839</v>
+        <v>-0.009999999999999953</v>
       </c>
       <c r="AB3">
-        <v>-0.1280741611297381</v>
+        <v>-0.1280741611297382</v>
       </c>
       <c r="AC3">
-        <v>0.008074161129738217</v>
+        <v>0.008074161129738258</v>
       </c>
       <c r="AD3">
-        <v>0.028</v>
+        <v>0.0392</v>
       </c>
       <c r="AE3">
-        <v>0.09279999999999999</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="AF3">
         <v>-0.08300106659587148</v>
       </c>
       <c r="AG3">
-        <v>-0.1240127595235769</v>
+        <v>-0.124012759523577</v>
       </c>
       <c r="AH3">
-        <v>-0.04070333062115</v>
+        <v>-0.04070333062114999</v>
       </c>
       <c r="AI3">
         <v>0.0005999999999999999</v>
@@ -1146,19 +1143,19 @@
         <v>0.0008</v>
       </c>
       <c r="AK3">
-        <v>0.08128078817733986</v>
+        <v>0.0788177339901478</v>
       </c>
       <c r="AL3">
-        <v>0.02216476440614372</v>
+        <v>0.01979710286299567</v>
       </c>
       <c r="AM3">
-        <v>0.1403530377668309</v>
+        <v>0.1380185633575464</v>
       </c>
       <c r="AN3">
-        <v>0.006863871555196087</v>
+        <v>0.009022063055144957</v>
       </c>
       <c r="AO3">
-        <v>0.02059161466558826</v>
+        <v>0.02706618916543487</v>
       </c>
     </row>
     <row r="4" spans="1:41">
@@ -1166,10 +1163,10 @@
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4">
         <v>406</v>
@@ -1178,19 +1175,19 @@
         <v>250</v>
       </c>
       <c r="F4">
-        <v>-0.01729064039408867</v>
+        <v>-0.01729064039408866</v>
       </c>
       <c r="G4">
-        <v>-0.07150679591982625</v>
+        <v>-0.07150679591982637</v>
       </c>
       <c r="H4">
-        <v>0.03668306575040813</v>
+        <v>0.03668306575040802</v>
       </c>
       <c r="I4">
-        <v>-0.08180644473769279</v>
+        <v>-0.08180644473769276</v>
       </c>
       <c r="J4">
-        <v>0.04722516394951541</v>
+        <v>0.0472251639495153</v>
       </c>
       <c r="K4">
         <v>0.518</v>
@@ -1205,7 +1202,7 @@
         <v>-0.1025986784782056</v>
       </c>
       <c r="O4">
-        <v>-0.01794955791900316</v>
+        <v>-0.01794955791900317</v>
       </c>
       <c r="P4">
         <v>-0.1084139624854691</v>
@@ -1223,7 +1220,7 @@
         <v>-0.06855495648417897</v>
       </c>
       <c r="U4">
-        <v>-0.1131287403553189</v>
+        <v>-0.1131287403553188</v>
       </c>
       <c r="V4">
         <v>-0.02214090274061026</v>
@@ -1235,25 +1232,25 @@
         <v>0.0052</v>
       </c>
       <c r="Y4">
-        <v>-0.04999999999999982</v>
+        <v>-0.05000000000000004</v>
       </c>
       <c r="Z4">
-        <v>-0.1099999999999999</v>
+        <v>-0.11</v>
       </c>
       <c r="AA4">
-        <v>0.01000000000000035</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="AB4">
-        <v>-0.1230166690346133</v>
+        <v>-0.1230166690346137</v>
       </c>
       <c r="AC4">
-        <v>0.02301666903461366</v>
+        <v>0.02301666903461358</v>
       </c>
       <c r="AD4">
-        <v>0.1748</v>
+        <v>0.2012</v>
       </c>
       <c r="AE4">
-        <v>0.2226</v>
+        <v>0.2164</v>
       </c>
       <c r="AF4">
         <v>-0.06764419404435507</v>
@@ -1262,7 +1259,7 @@
         <v>-0.1119735373189496</v>
       </c>
       <c r="AH4">
-        <v>-0.02111883542966709</v>
+        <v>-0.0211188354296671</v>
       </c>
       <c r="AI4">
         <v>0.005</v>
@@ -1271,16 +1268,16 @@
         <v>0.008399999999999999</v>
       </c>
       <c r="AK4">
-        <v>0.04679802955665024</v>
+        <v>0.04433497536945818</v>
       </c>
       <c r="AL4">
-        <v>-0.01452960812430945</v>
+        <v>-0.01686950701356149</v>
       </c>
       <c r="AM4">
-        <v>0.1075</v>
+        <v>0.1050067237163814</v>
       </c>
       <c r="AN4">
-        <v>0.1319988990199734</v>
+        <v>0.1549785601955193</v>
       </c>
       <c r="AO4">
         <v>0.204560421762222</v>
@@ -1291,124 +1288,124 @@
         <v>42</v>
       </c>
       <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5">
+        <v>69</v>
+      </c>
+      <c r="E5">
         <v>44</v>
       </c>
-      <c r="C5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5">
-        <v>207</v>
-      </c>
-      <c r="E5">
-        <v>207</v>
-      </c>
       <c r="F5">
-        <v>0.008357487922705319</v>
+        <v>-0.007681159420289864</v>
       </c>
       <c r="G5">
-        <v>-0.03937699896679999</v>
+        <v>-0.08681275054350658</v>
       </c>
       <c r="H5">
-        <v>0.05950336880945854</v>
+        <v>0.09128877870612474</v>
       </c>
       <c r="I5">
-        <v>-0.05103539816859672</v>
+        <v>-0.1141871619631026</v>
       </c>
       <c r="J5">
-        <v>0.06775037401400737</v>
+        <v>0.09882484312252289</v>
       </c>
       <c r="K5">
-        <v>0.7482</v>
+        <v>0.8618</v>
       </c>
       <c r="L5">
+        <v>0.8618</v>
+      </c>
+      <c r="M5">
+        <v>-0.009130434782608721</v>
+      </c>
+      <c r="N5">
+        <v>-0.09398305560858214</v>
+      </c>
+      <c r="O5">
+        <v>0.07321618921121935</v>
+      </c>
+      <c r="P5">
+        <v>-0.1101837620501105</v>
+      </c>
+      <c r="Q5">
+        <v>0.0919228924848931</v>
+      </c>
+      <c r="R5">
+        <v>0.8304</v>
+      </c>
+      <c r="S5">
+        <v>0.8304</v>
+      </c>
+      <c r="T5">
+        <v>-0.01731512257839207</v>
+      </c>
+      <c r="U5">
+        <v>-0.1164926751154171</v>
+      </c>
+      <c r="V5">
+        <v>0.08380091829685227</v>
+      </c>
+      <c r="W5">
+        <v>0.7464</v>
+      </c>
+      <c r="X5">
         <v>0.9228</v>
       </c>
-      <c r="M5">
-        <v>-0.02004830917874395</v>
-      </c>
-      <c r="N5">
-        <v>-0.06341673548373197</v>
-      </c>
-      <c r="O5">
-        <v>0.02278842149249139</v>
-      </c>
-      <c r="P5">
-        <v>-0.07233878000738253</v>
-      </c>
-      <c r="Q5">
-        <v>0.03224216164989475</v>
-      </c>
-      <c r="R5">
-        <v>0.3648</v>
-      </c>
-      <c r="S5">
-        <v>0.3648</v>
-      </c>
-      <c r="T5">
-        <v>-0.03574780648719517</v>
-      </c>
-      <c r="U5">
-        <v>-0.08117500431921684</v>
-      </c>
-      <c r="V5">
-        <v>0.01103192398107171</v>
-      </c>
-      <c r="W5">
-        <v>0.1386</v>
-      </c>
-      <c r="X5">
-        <v>0.2192</v>
-      </c>
       <c r="Y5">
-        <v>-0.01000000000000012</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="Z5">
-        <v>-0.09999999999999987</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="AA5">
-        <v>0.05999999999999994</v>
+        <v>0.09500000000000003</v>
       </c>
       <c r="AB5">
-        <v>-0.1038971985921919</v>
+        <v>-0.09734129388236519</v>
       </c>
       <c r="AC5">
-        <v>0.08389719859219168</v>
+        <v>0.1173412938823652</v>
       </c>
       <c r="AD5">
-        <v>0.6612</v>
+        <v>0.8336</v>
       </c>
       <c r="AE5">
-        <v>0.7706</v>
+        <v>0.8766</v>
       </c>
       <c r="AF5">
-        <v>-0.03601433464716908</v>
+        <v>-0.01723977231617346</v>
       </c>
       <c r="AG5">
-        <v>-0.08128862160672953</v>
+        <v>-0.117765501818481</v>
       </c>
       <c r="AH5">
-        <v>0.01090263065652809</v>
+        <v>0.08218194600946505</v>
       </c>
       <c r="AI5">
-        <v>0.1346</v>
+        <v>0.751</v>
       </c>
       <c r="AJ5">
-        <v>0.2062</v>
+        <v>0.9198</v>
       </c>
       <c r="AK5">
-        <v>0.06763285024154586</v>
+        <v>-0.0434782608695653</v>
       </c>
       <c r="AL5">
-        <v>-0.004830917874396135</v>
+        <v>-0.1486789027833803</v>
       </c>
       <c r="AM5">
-        <v>0.1400966183574879</v>
+        <v>0.05714285714285714</v>
       </c>
       <c r="AN5">
-        <v>0.08782509563019504</v>
+        <v>0.4104456923623511</v>
       </c>
       <c r="AO5">
-        <v>0.1756501912603901</v>
+        <v>0.8208913847247021</v>
       </c>
     </row>
     <row r="6" spans="1:41">
@@ -1416,124 +1413,124 @@
         <v>42</v>
       </c>
       <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6">
+        <v>69</v>
+      </c>
+      <c r="E6">
         <v>44</v>
       </c>
-      <c r="C6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6">
-        <v>207</v>
-      </c>
-      <c r="E6">
-        <v>207</v>
-      </c>
       <c r="F6">
-        <v>0.01241545893719808</v>
+        <v>-0.05260869565217391</v>
       </c>
       <c r="G6">
-        <v>-0.05180369647565036</v>
+        <v>-0.1879810138775782</v>
       </c>
       <c r="H6">
-        <v>0.07238411204395538</v>
+        <v>0.05830076237802242</v>
       </c>
       <c r="I6">
-        <v>-0.06168545131060543</v>
+        <v>-0.2000900155857261</v>
       </c>
       <c r="J6">
-        <v>0.08651636918500157</v>
+        <v>0.09487262428137828</v>
       </c>
       <c r="K6">
-        <v>0.6962</v>
+        <v>0.3848</v>
       </c>
       <c r="L6">
-        <v>0.9156</v>
+        <v>0.6546</v>
       </c>
       <c r="M6">
-        <v>-0.06797101449275361</v>
+        <v>-0.0369565217391305</v>
       </c>
       <c r="N6">
-        <v>-0.1150446795079015</v>
+        <v>-0.1201436004796208</v>
       </c>
       <c r="O6">
-        <v>-0.01980502496348764</v>
+        <v>0.05199748898995496</v>
       </c>
       <c r="P6">
-        <v>-0.1263846722789996</v>
+        <v>-0.1410315331593855</v>
       </c>
       <c r="Q6">
-        <v>-0.009557356706507911</v>
+        <v>0.06711848968112478</v>
       </c>
       <c r="R6">
-        <v>0.0066</v>
+        <v>0.39</v>
       </c>
       <c r="S6">
-        <v>0.0182</v>
+        <v>0.6682</v>
       </c>
       <c r="T6">
-        <v>-0.08480322843731886</v>
+        <v>-0.03434705324452769</v>
       </c>
       <c r="U6">
-        <v>-0.1392818727626998</v>
+        <v>-0.1272371763235338</v>
       </c>
       <c r="V6">
-        <v>-0.02765282063164901</v>
+        <v>0.06288154246470519</v>
       </c>
       <c r="W6">
-        <v>0.004</v>
+        <v>0.5024</v>
       </c>
       <c r="X6">
-        <v>0.0112</v>
+        <v>0.7744</v>
       </c>
       <c r="Y6">
-        <v>-0.06000000000000005</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="Z6">
-        <v>-0.15</v>
+        <v>-0.145</v>
       </c>
       <c r="AA6">
-        <v>-1.110223024625157E-16</v>
+        <v>0.06999999999999995</v>
       </c>
       <c r="AB6">
-        <v>-0.1500000000000001</v>
+        <v>-0.1700413668805986</v>
       </c>
       <c r="AC6">
-        <v>0.03000000000000003</v>
+        <v>0.09004136688059849</v>
       </c>
       <c r="AD6">
-        <v>0.044</v>
+        <v>0.5732</v>
       </c>
       <c r="AE6">
-        <v>0.3118</v>
+        <v>0.7028</v>
       </c>
       <c r="AF6">
-        <v>-0.08522215543724965</v>
+        <v>-0.03108205860070312</v>
       </c>
       <c r="AG6">
-        <v>-0.1400943073214456</v>
+        <v>-0.1262655503625984</v>
       </c>
       <c r="AH6">
-        <v>-0.02918989008947918</v>
+        <v>0.06957054598927924</v>
       </c>
       <c r="AI6">
-        <v>0.006</v>
+        <v>0.5556</v>
       </c>
       <c r="AJ6">
-        <v>0.0176</v>
+        <v>0.8274</v>
       </c>
       <c r="AK6">
-        <v>0.111111111111111</v>
+        <v>0.01449275362318836</v>
       </c>
       <c r="AL6">
-        <v>0.03381642512077294</v>
+        <v>-0.1475963668586618</v>
       </c>
       <c r="AM6">
-        <v>0.1835748792270532</v>
+        <v>0.1803392531876139</v>
       </c>
       <c r="AN6">
-        <v>0.006357215082587968</v>
+        <v>0.8633641527524397</v>
       </c>
       <c r="AO6">
-        <v>0.0190716452477639</v>
+        <v>0.8633641527524397</v>
       </c>
     </row>
     <row r="7" spans="1:41">
@@ -1541,124 +1538,124 @@
         <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="E7">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="F7">
-        <v>0.004057971014492756</v>
+        <v>-0.04492753623188404</v>
       </c>
       <c r="G7">
-        <v>-0.06646966441868675</v>
+        <v>-0.1754659154641391</v>
       </c>
       <c r="H7">
-        <v>0.07049753251267667</v>
+        <v>0.08188536834779539</v>
       </c>
       <c r="I7">
-        <v>-0.07685225067811854</v>
+        <v>-0.2027351339597176</v>
       </c>
       <c r="J7">
-        <v>0.08496819270710404</v>
+        <v>0.1128800614959495</v>
       </c>
       <c r="K7">
-        <v>0.9026</v>
+        <v>0.4786</v>
       </c>
       <c r="L7">
+        <v>0.7151999999999999</v>
+      </c>
+      <c r="M7">
+        <v>-0.02782608695652178</v>
+      </c>
+      <c r="N7">
+        <v>-0.1214282966917444</v>
+      </c>
+      <c r="O7">
+        <v>0.07867450219518883</v>
+      </c>
+      <c r="P7">
+        <v>-0.1503432645023226</v>
+      </c>
+      <c r="Q7">
+        <v>0.09469109058927928</v>
+      </c>
+      <c r="R7">
+        <v>0.5806</v>
+      </c>
+      <c r="S7">
+        <v>0.7912</v>
+      </c>
+      <c r="T7">
+        <v>-0.01703193066613562</v>
+      </c>
+      <c r="U7">
+        <v>-0.1356648710020678</v>
+      </c>
+      <c r="V7">
+        <v>0.100814865669678</v>
+      </c>
+      <c r="W7">
+        <v>0.8066</v>
+      </c>
+      <c r="X7">
         <v>0.9228</v>
       </c>
-      <c r="M7">
-        <v>-0.04792270531400966</v>
-      </c>
-      <c r="N7">
-        <v>-0.1024447384258064</v>
-      </c>
-      <c r="O7">
-        <v>0.005401149152844641</v>
-      </c>
-      <c r="P7">
-        <v>-0.111707487254363</v>
-      </c>
-      <c r="Q7">
-        <v>0.01586207662634324</v>
-      </c>
-      <c r="R7">
-        <v>0.0788</v>
-      </c>
-      <c r="S7">
-        <v>0.1346</v>
-      </c>
-      <c r="T7">
-        <v>-0.04905542195012369</v>
-      </c>
-      <c r="U7">
-        <v>-0.1111569370207811</v>
-      </c>
-      <c r="V7">
-        <v>0.01275237325302565</v>
-      </c>
-      <c r="W7">
-        <v>0.1238</v>
-      </c>
-      <c r="X7">
-        <v>0.2192</v>
-      </c>
       <c r="Y7">
-        <v>-0.04999999999999993</v>
+        <v>-0.05000000000000004</v>
       </c>
       <c r="Z7">
-        <v>-0.1400000000000001</v>
+        <v>-0.17</v>
       </c>
       <c r="AA7">
-        <v>0.02999999999999992</v>
+        <v>0.06</v>
       </c>
       <c r="AB7">
-        <v>-0.1519260792971539</v>
+        <v>-0.1850000000000001</v>
       </c>
       <c r="AC7">
-        <v>0.05192607929715401</v>
+        <v>0.08500000000000002</v>
       </c>
       <c r="AD7">
-        <v>0.224</v>
+        <v>0.4592</v>
       </c>
       <c r="AE7">
-        <v>0.4476</v>
+        <v>0.6756</v>
       </c>
       <c r="AF7">
-        <v>-0.04920782079008057</v>
+        <v>-0.01384228628452966</v>
       </c>
       <c r="AG7">
-        <v>-0.1114327077564691</v>
+        <v>-0.1354366941567308</v>
       </c>
       <c r="AH7">
-        <v>0.01244135367620838</v>
+        <v>0.1085662294439589</v>
       </c>
       <c r="AI7">
-        <v>0.1184</v>
+        <v>0.8346</v>
       </c>
       <c r="AJ7">
-        <v>0.2062</v>
+        <v>0.9198</v>
       </c>
       <c r="AK7">
-        <v>0.04347826086956519</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="AL7">
-        <v>-0.03381642512077294</v>
+        <v>-0.07142857142857142</v>
       </c>
       <c r="AM7">
-        <v>0.1159420289855072</v>
+        <v>0.1940298507462687</v>
       </c>
       <c r="AN7">
-        <v>0.3134999455835852</v>
+        <v>0.3988546137823287</v>
       </c>
       <c r="AO7">
-        <v>0.3134999455835852</v>
+        <v>0.7977092275646573</v>
       </c>
     </row>
     <row r="8" spans="1:41">
@@ -1666,124 +1663,124 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="E8">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="F8">
-        <v>-0.02417085427135678</v>
+        <v>-0.002815126050420166</v>
       </c>
       <c r="G8">
-        <v>-0.07938859663334021</v>
+        <v>-0.05748818465674033</v>
       </c>
       <c r="H8">
-        <v>0.03473953972963441</v>
+        <v>0.05012159164749841</v>
       </c>
       <c r="I8">
-        <v>-0.0908680477437257</v>
+        <v>-0.06625616770219352</v>
       </c>
       <c r="J8">
-        <v>0.0425263392010121</v>
+        <v>0.06062591560135315</v>
       </c>
       <c r="K8">
-        <v>0.3916</v>
+        <v>0.9176</v>
       </c>
       <c r="L8">
-        <v>0.4768</v>
+        <v>0.982</v>
       </c>
       <c r="M8">
-        <v>-0.004974874371859284</v>
+        <v>-0.01357142857142862</v>
       </c>
       <c r="N8">
-        <v>-0.05070529366418342</v>
+        <v>-0.06071090006005311</v>
       </c>
       <c r="O8">
-        <v>0.04187065486244625</v>
+        <v>0.03126504210044222</v>
       </c>
       <c r="P8">
-        <v>-0.06040181445148433</v>
+        <v>-0.06891405825293671</v>
       </c>
       <c r="Q8">
-        <v>0.05045206570776576</v>
+        <v>0.04177120111008013</v>
       </c>
       <c r="R8">
-        <v>0.8314</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="S8">
-        <v>0.8314</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="T8">
-        <v>0.005705599957307794</v>
+        <v>-0.01519916403466753</v>
       </c>
       <c r="U8">
-        <v>-0.0437486940349788</v>
+        <v>-0.05959981574711692</v>
       </c>
       <c r="V8">
-        <v>0.05394448983572651</v>
+        <v>0.02961214099715429</v>
       </c>
       <c r="W8">
-        <v>0.8202</v>
+        <v>0.503</v>
       </c>
       <c r="X8">
-        <v>0.8202</v>
+        <v>0.503</v>
       </c>
       <c r="Y8">
-        <v>-0.01000000000000012</v>
+        <v>-0.04500000000000004</v>
       </c>
       <c r="Z8">
-        <v>-0.08000000000000018</v>
+        <v>-0.105</v>
       </c>
       <c r="AA8">
-        <v>0.05999999999999994</v>
+        <v>0.03999999999999998</v>
       </c>
       <c r="AB8">
-        <v>-0.09925482790573971</v>
+        <v>-0.131897207526139</v>
       </c>
       <c r="AC8">
-        <v>0.07925482790573947</v>
+        <v>0.04189720752613892</v>
       </c>
       <c r="AD8">
-        <v>0.6392</v>
+        <v>0.3164</v>
       </c>
       <c r="AE8">
-        <v>0.764</v>
+        <v>0.3292</v>
       </c>
       <c r="AF8">
-        <v>0.00759652222489704</v>
+        <v>-0.01513592838370859</v>
       </c>
       <c r="AG8">
-        <v>-0.04136267558648257</v>
+        <v>-0.05940962551562724</v>
       </c>
       <c r="AH8">
-        <v>0.05592181985989171</v>
+        <v>0.02955483342924571</v>
       </c>
       <c r="AI8">
-        <v>0.761</v>
+        <v>0.5008</v>
       </c>
       <c r="AJ8">
-        <v>0.761</v>
+        <v>0.5008</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>0.06302521008403361</v>
       </c>
       <c r="AL8">
-        <v>-0.07537688442211055</v>
+        <v>-0.008298755186721992</v>
       </c>
       <c r="AM8">
-        <v>0.07537688442211055</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="AN8">
-        <v>1</v>
+        <v>0.0785432549942764</v>
       </c>
       <c r="AO8">
-        <v>1</v>
+        <v>0.1570865099885528</v>
       </c>
     </row>
     <row r="9" spans="1:41">
@@ -1791,124 +1788,124 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="E9">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="F9">
-        <v>-0.06366834170854271</v>
+        <v>0.005630252100840326</v>
       </c>
       <c r="G9">
-        <v>-0.134711306615152</v>
+        <v>-0.06081467861304428</v>
       </c>
       <c r="H9">
-        <v>0.005948065860233304</v>
+        <v>0.07283379687072547</v>
       </c>
       <c r="I9">
-        <v>-0.1488692935139442</v>
+        <v>-0.0744154556769744</v>
       </c>
       <c r="J9">
-        <v>0.02153261009685876</v>
+        <v>0.08567595987865505</v>
       </c>
       <c r="K9">
-        <v>0.08019999999999999</v>
+        <v>0.862</v>
       </c>
       <c r="L9">
-        <v>0.1878</v>
+        <v>0.982</v>
       </c>
       <c r="M9">
-        <v>-0.0751256281407035</v>
+        <v>-0.08436974789915969</v>
       </c>
       <c r="N9">
-        <v>-0.1310229499051968</v>
+        <v>-0.1398838651624345</v>
       </c>
       <c r="O9">
-        <v>-0.02007745571459697</v>
+        <v>-0.0295327372730704</v>
       </c>
       <c r="P9">
-        <v>-0.1420685129346101</v>
+        <v>-0.1507495494343032</v>
       </c>
       <c r="Q9">
-        <v>-0.008182743346796903</v>
+        <v>-0.01798994636401634</v>
       </c>
       <c r="R9">
-        <v>0.008200000000000001</v>
+        <v>0.0034</v>
       </c>
       <c r="S9">
-        <v>0.024</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="T9">
-        <v>-0.08365754688833371</v>
+        <v>-0.1001473032693878</v>
       </c>
       <c r="U9">
-        <v>-0.1420902483200672</v>
+        <v>-0.1606451278002748</v>
       </c>
       <c r="V9">
-        <v>-0.02184629191013983</v>
+        <v>-0.03734422411782519</v>
       </c>
       <c r="W9">
-        <v>0.0086</v>
+        <v>0.0032</v>
       </c>
       <c r="X9">
-        <v>0.0188</v>
+        <v>0.0058</v>
       </c>
       <c r="Y9">
-        <v>-0.05000000000000016</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="Z9">
-        <v>-0.1199999999999999</v>
+        <v>-0.16</v>
       </c>
       <c r="AA9">
-        <v>0.02000000000000002</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>-0.1364378623663957</v>
+        <v>-0.1748543278868911</v>
       </c>
       <c r="AC9">
-        <v>0.03643786236639536</v>
+        <v>0.01485432788689105</v>
       </c>
       <c r="AD9">
-        <v>0.1548</v>
+        <v>0.0716</v>
       </c>
       <c r="AE9">
-        <v>0.2654</v>
+        <v>0.125</v>
       </c>
       <c r="AF9">
-        <v>-0.07762958337910586</v>
+        <v>-0.1005471804430421</v>
       </c>
       <c r="AG9">
-        <v>-0.1370381777191461</v>
+        <v>-0.1598467389143226</v>
       </c>
       <c r="AH9">
-        <v>-0.01531069818067748</v>
+        <v>-0.03791708938899847</v>
       </c>
       <c r="AI9">
-        <v>0.0224</v>
+        <v>0.0042</v>
       </c>
       <c r="AJ9">
-        <v>0.0424</v>
+        <v>0.0114</v>
       </c>
       <c r="AK9">
-        <v>0.05025125628140703</v>
+        <v>0.1008403361344539</v>
       </c>
       <c r="AL9">
-        <v>-0.03517587939698492</v>
+        <v>0.02574557059535602</v>
       </c>
       <c r="AM9">
-        <v>0.135678391959799</v>
+        <v>0.1769547325102881</v>
       </c>
       <c r="AN9">
-        <v>0.3018984444285246</v>
+        <v>0.01051393361055575</v>
       </c>
       <c r="AO9">
-        <v>0.6037968888570493</v>
+        <v>0.03154180083166726</v>
       </c>
     </row>
     <row r="10" spans="1:41">
@@ -1916,124 +1913,499 @@
         <v>43</v>
       </c>
       <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10">
+        <v>238</v>
+      </c>
+      <c r="E10">
+        <v>154</v>
+      </c>
+      <c r="F10">
+        <v>0.008445378151260492</v>
+      </c>
+      <c r="G10">
+        <v>-0.06093731332680365</v>
+      </c>
+      <c r="H10">
+        <v>0.07706069689774481</v>
+      </c>
+      <c r="I10">
+        <v>-0.07491254037785042</v>
+      </c>
+      <c r="J10">
+        <v>0.09180329668037143</v>
+      </c>
+      <c r="K10">
+        <v>0.8086</v>
+      </c>
+      <c r="L10">
+        <v>0.9704</v>
+      </c>
+      <c r="M10">
+        <v>-0.07079831932773106</v>
+      </c>
+      <c r="N10">
+        <v>-0.1273640479129107</v>
+      </c>
+      <c r="O10">
+        <v>-0.0154243638359112</v>
+      </c>
+      <c r="P10">
+        <v>-0.1394101766616208</v>
+      </c>
+      <c r="Q10">
+        <v>-0.002186461993842218</v>
+      </c>
+      <c r="R10">
+        <v>0.0158</v>
+      </c>
+      <c r="S10">
+        <v>0.0308</v>
+      </c>
+      <c r="T10">
+        <v>-0.08494813923472028</v>
+      </c>
+      <c r="U10">
+        <v>-0.1446335592384758</v>
+      </c>
+      <c r="V10">
+        <v>-0.02545425540213038</v>
+      </c>
+      <c r="W10">
+        <v>0.0092</v>
+      </c>
+      <c r="X10">
+        <v>0.0178</v>
+      </c>
+      <c r="Y10">
+        <v>-0.03499999999999998</v>
+      </c>
+      <c r="Z10">
+        <v>-0.13</v>
+      </c>
+      <c r="AA10">
+        <v>0.04999999999999999</v>
+      </c>
+      <c r="AB10">
+        <v>-0.145</v>
+      </c>
+      <c r="AC10">
+        <v>0.07500000000000001</v>
+      </c>
+      <c r="AD10">
+        <v>0.454</v>
+      </c>
+      <c r="AE10">
+        <v>0.4868</v>
+      </c>
+      <c r="AF10">
+        <v>-0.08541125205933353</v>
+      </c>
+      <c r="AG10">
+        <v>-0.1444532979412127</v>
+      </c>
+      <c r="AH10">
+        <v>-0.0259623222200178</v>
+      </c>
+      <c r="AI10">
+        <v>0.0078</v>
+      </c>
+      <c r="AJ10">
+        <v>0.0204</v>
+      </c>
+      <c r="AK10">
+        <v>0.03781512605042026</v>
+      </c>
+      <c r="AL10">
+        <v>-0.04166666666666666</v>
+      </c>
+      <c r="AM10">
+        <v>0.1174456345342423</v>
+      </c>
+      <c r="AN10">
+        <v>0.3611297063274773</v>
+      </c>
+      <c r="AO10">
+        <v>0.3611297063274773</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
         <v>45</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>46</v>
       </c>
-      <c r="D10">
-        <v>199</v>
-      </c>
-      <c r="E10">
-        <v>199</v>
-      </c>
-      <c r="F10">
-        <v>-0.03949748743718594</v>
-      </c>
-      <c r="G10">
-        <v>-0.114302675420823</v>
-      </c>
-      <c r="H10">
-        <v>0.03372151397468764</v>
-      </c>
-      <c r="I10">
-        <v>-0.1270242150164059</v>
-      </c>
-      <c r="J10">
-        <v>0.04802924014203403</v>
-      </c>
-      <c r="K10">
-        <v>0.2944</v>
-      </c>
-      <c r="L10">
-        <v>0.4768</v>
-      </c>
-      <c r="M10">
-        <v>-0.07015075376884422</v>
-      </c>
-      <c r="N10">
-        <v>-0.1301497201187742</v>
-      </c>
-      <c r="O10">
-        <v>-0.01301543821783446</v>
-      </c>
-      <c r="P10">
-        <v>-0.1390395629729493</v>
-      </c>
-      <c r="Q10">
-        <v>-0.001261944564739118</v>
-      </c>
-      <c r="R10">
-        <v>0.0186</v>
-      </c>
-      <c r="S10">
-        <v>0.0348</v>
-      </c>
-      <c r="T10">
-        <v>-0.08936314684564151</v>
-      </c>
-      <c r="U10">
-        <v>-0.1519342158815156</v>
-      </c>
-      <c r="V10">
-        <v>-0.02445697967964856</v>
-      </c>
-      <c r="W10">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="X10">
-        <v>0.0188</v>
-      </c>
-      <c r="Y10">
-        <v>-0.04000000000000004</v>
-      </c>
-      <c r="Z10">
-        <v>-0.1000000000000003</v>
-      </c>
-      <c r="AA10">
-        <v>0.0399999999999997</v>
-      </c>
-      <c r="AB10">
-        <v>-0.13</v>
-      </c>
-      <c r="AC10">
-        <v>0.04999999999999993</v>
-      </c>
-      <c r="AD10">
-        <v>0.3536</v>
-      </c>
-      <c r="AE10">
-        <v>0.4588</v>
-      </c>
-      <c r="AF10">
-        <v>-0.0852261056040029</v>
-      </c>
-      <c r="AG10">
-        <v>-0.1485120228288059</v>
-      </c>
-      <c r="AH10">
-        <v>-0.01921195482153516</v>
-      </c>
-      <c r="AI10">
-        <v>0.0134</v>
-      </c>
-      <c r="AJ10">
-        <v>0.0322</v>
-      </c>
-      <c r="AK10">
-        <v>0.05025125628140703</v>
-      </c>
-      <c r="AL10">
-        <v>-0.04020100502512563</v>
-      </c>
-      <c r="AM10">
-        <v>0.135678391959799</v>
-      </c>
-      <c r="AN10">
-        <v>0.3018984444285246</v>
-      </c>
-      <c r="AO10">
-        <v>0.6037968888570493</v>
+      <c r="D11">
+        <v>99</v>
+      </c>
+      <c r="E11">
+        <v>64</v>
+      </c>
+      <c r="F11">
+        <v>-0.01898989898989898</v>
+      </c>
+      <c r="G11">
+        <v>-0.08862496046271545</v>
+      </c>
+      <c r="H11">
+        <v>0.05388728593976482</v>
+      </c>
+      <c r="I11">
+        <v>-0.1041717788624654</v>
+      </c>
+      <c r="J11">
+        <v>0.06619198088266737</v>
+      </c>
+      <c r="K11">
+        <v>0.6018</v>
+      </c>
+      <c r="L11">
+        <v>0.6018</v>
+      </c>
+      <c r="M11">
+        <v>-0.01292929292929296</v>
+      </c>
+      <c r="N11">
+        <v>-0.07435904196308235</v>
+      </c>
+      <c r="O11">
+        <v>0.055124609713654</v>
+      </c>
+      <c r="P11">
+        <v>-0.09169388423036738</v>
+      </c>
+      <c r="Q11">
+        <v>0.06583529837178102</v>
+      </c>
+      <c r="R11">
+        <v>0.6848</v>
+      </c>
+      <c r="S11">
+        <v>0.6848</v>
+      </c>
+      <c r="T11">
+        <v>-0.01569946509810405</v>
+      </c>
+      <c r="U11">
+        <v>-0.08072115640039265</v>
+      </c>
+      <c r="V11">
+        <v>0.05111977716054127</v>
+      </c>
+      <c r="W11">
+        <v>0.6614</v>
+      </c>
+      <c r="X11">
+        <v>0.6614</v>
+      </c>
+      <c r="Y11">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="Z11">
+        <v>-0.11</v>
+      </c>
+      <c r="AA11">
+        <v>0.11</v>
+      </c>
+      <c r="AB11">
+        <v>-0.114656049457789</v>
+      </c>
+      <c r="AC11">
+        <v>0.134656049457789</v>
+      </c>
+      <c r="AD11">
+        <v>0.9892</v>
+      </c>
+      <c r="AE11">
+        <v>0.9892</v>
+      </c>
+      <c r="AF11">
+        <v>-0.01425285713497848</v>
+      </c>
+      <c r="AG11">
+        <v>-0.08059016955817802</v>
+      </c>
+      <c r="AH11">
+        <v>0.05341654811530116</v>
+      </c>
+      <c r="AI11">
+        <v>0.6748</v>
+      </c>
+      <c r="AJ11">
+        <v>0.6748</v>
+      </c>
+      <c r="AK11">
+        <v>0.02020202020202011</v>
+      </c>
+      <c r="AL11">
+        <v>-0.09900990099009901</v>
+      </c>
+      <c r="AM11">
+        <v>0.1320754716981132</v>
+      </c>
+      <c r="AN11">
+        <v>0.7329150910757301</v>
+      </c>
+      <c r="AO11">
+        <v>0.7329150910757301</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12">
+        <v>99</v>
+      </c>
+      <c r="E12">
+        <v>64</v>
+      </c>
+      <c r="F12">
+        <v>-0.07888888888888887</v>
+      </c>
+      <c r="G12">
+        <v>-0.1770903863284953</v>
+      </c>
+      <c r="H12">
+        <v>0.01515153893145468</v>
+      </c>
+      <c r="I12">
+        <v>-0.1930728623380932</v>
+      </c>
+      <c r="J12">
+        <v>0.03529508456031522</v>
+      </c>
+      <c r="K12">
+        <v>0.1058</v>
+      </c>
+      <c r="L12">
+        <v>0.2266</v>
+      </c>
+      <c r="M12">
+        <v>-0.06454545454545457</v>
+      </c>
+      <c r="N12">
+        <v>-0.1304029636920622</v>
+      </c>
+      <c r="O12">
+        <v>-0.005277721363423381</v>
+      </c>
+      <c r="P12">
+        <v>-0.1428151845382822</v>
+      </c>
+      <c r="Q12">
+        <v>0.01372427544737288</v>
+      </c>
+      <c r="R12">
+        <v>0.045</v>
+      </c>
+      <c r="S12">
+        <v>0.119</v>
+      </c>
+      <c r="T12">
+        <v>-0.08183291328324471</v>
+      </c>
+      <c r="U12">
+        <v>-0.1462367376518515</v>
+      </c>
+      <c r="V12">
+        <v>-0.01656233111272169</v>
+      </c>
+      <c r="W12">
+        <v>0.0324</v>
+      </c>
+      <c r="X12">
+        <v>0.0764</v>
+      </c>
+      <c r="Y12">
+        <v>-0.03999999999999998</v>
+      </c>
+      <c r="Z12">
+        <v>-0.12</v>
+      </c>
+      <c r="AA12">
+        <v>0.04999999999999999</v>
+      </c>
+      <c r="AB12">
+        <v>-0.14</v>
+      </c>
+      <c r="AC12">
+        <v>0.06000000000000004</v>
+      </c>
+      <c r="AD12">
+        <v>0.6532</v>
+      </c>
+      <c r="AE12">
+        <v>0.7156</v>
+      </c>
+      <c r="AF12">
+        <v>-0.07274264322691626</v>
+      </c>
+      <c r="AG12">
+        <v>-0.1326539191798262</v>
+      </c>
+      <c r="AH12">
+        <v>-0.01153379621125429</v>
+      </c>
+      <c r="AI12">
+        <v>0.029</v>
+      </c>
+      <c r="AJ12">
+        <v>0.0992</v>
+      </c>
+      <c r="AK12">
+        <v>0.07070707070707061</v>
+      </c>
+      <c r="AL12">
+        <v>-0.0396039603960396</v>
+      </c>
+      <c r="AM12">
+        <v>0.1747572815533981</v>
+      </c>
+      <c r="AN12">
+        <v>0.2080477461314518</v>
+      </c>
+      <c r="AO12">
+        <v>0.6241432383943554</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13">
+        <v>99</v>
+      </c>
+      <c r="E13">
+        <v>64</v>
+      </c>
+      <c r="F13">
+        <v>-0.05989898989898989</v>
+      </c>
+      <c r="G13">
+        <v>-0.1734529329899067</v>
+      </c>
+      <c r="H13">
+        <v>0.04550799786446531</v>
+      </c>
+      <c r="I13">
+        <v>-0.1906136501021066</v>
+      </c>
+      <c r="J13">
+        <v>0.07081567030412667</v>
+      </c>
+      <c r="K13">
+        <v>0.2758</v>
+      </c>
+      <c r="L13">
+        <v>0.4524</v>
+      </c>
+      <c r="M13">
+        <v>-0.05161616161616162</v>
+      </c>
+      <c r="N13">
+        <v>-0.1467751922665724</v>
+      </c>
+      <c r="O13">
+        <v>0.02086892772980065</v>
+      </c>
+      <c r="P13">
+        <v>-0.1526720041364751</v>
+      </c>
+      <c r="Q13">
+        <v>0.04943968090415207</v>
+      </c>
+      <c r="R13">
+        <v>0.224</v>
+      </c>
+      <c r="S13">
+        <v>0.3428</v>
+      </c>
+      <c r="T13">
+        <v>-0.06613344818514066</v>
+      </c>
+      <c r="U13">
+        <v>-0.1528966205025178</v>
+      </c>
+      <c r="V13">
+        <v>0.01365989588905082</v>
+      </c>
+      <c r="W13">
+        <v>0.1566</v>
+      </c>
+      <c r="X13">
+        <v>0.2464</v>
+      </c>
+      <c r="Y13">
+        <v>-0.04999999999999999</v>
+      </c>
+      <c r="Z13">
+        <v>-0.16</v>
+      </c>
+      <c r="AA13">
+        <v>0.08500000000000002</v>
+      </c>
+      <c r="AB13">
+        <v>-0.1935531761552672</v>
+      </c>
+      <c r="AC13">
+        <v>0.09355317615526718</v>
+      </c>
+      <c r="AD13">
+        <v>0.6528</v>
+      </c>
+      <c r="AE13">
+        <v>0.7156</v>
+      </c>
+      <c r="AF13">
+        <v>-0.05848978609193778</v>
+      </c>
+      <c r="AG13">
+        <v>-0.1360691728962422</v>
+      </c>
+      <c r="AH13">
+        <v>0.01505136763452953</v>
+      </c>
+      <c r="AI13">
+        <v>0.148</v>
+      </c>
+      <c r="AJ13">
+        <v>0.2186</v>
+      </c>
+      <c r="AK13">
+        <v>0.0505050505050505</v>
+      </c>
+      <c r="AL13">
+        <v>-0.0721930646672914</v>
+      </c>
+      <c r="AM13">
+        <v>0.1739552553820179</v>
+      </c>
+      <c r="AN13">
+        <v>0.4273643299212784</v>
+      </c>
+      <c r="AO13">
+        <v>0.7329150910757301</v>
       </c>
     </row>
   </sheetData>
@@ -2052,130 +2424,130 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2185,7 +2557,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="10" width="18.7109375" customWidth="1"/>
@@ -2193,34 +2565,34 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2231,19 +2603,19 @@
         <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E2">
-        <v>0.02049261083743843</v>
+        <v>0.02049261083743842</v>
       </c>
       <c r="F2">
         <v>-0.03627408686752381</v>
       </c>
       <c r="G2">
-        <v>0.07817344322344313</v>
+        <v>0.07817344322344316</v>
       </c>
       <c r="H2">
         <v>406</v>
@@ -2252,7 +2624,7 @@
         <v>250</v>
       </c>
       <c r="J2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2263,10 +2635,10 @@
         <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E3">
         <v>0.02807881773399015</v>
@@ -2275,7 +2647,7 @@
         <v>-0.03130163576219235</v>
       </c>
       <c r="G3">
-        <v>0.08814663182346116</v>
+        <v>0.08814663182346119</v>
       </c>
       <c r="H3">
         <v>406</v>
@@ -2284,7 +2656,7 @@
         <v>250</v>
       </c>
       <c r="J3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2295,16 +2667,16 @@
         <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E4">
         <v>0.04536945812807881</v>
       </c>
       <c r="F4">
-        <v>-0.0227918672839506</v>
+        <v>-0.02279186728395061</v>
       </c>
       <c r="G4">
         <v>0.1117210615626027</v>
@@ -2316,7 +2688,7 @@
         <v>250</v>
       </c>
       <c r="J4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2327,10 +2699,10 @@
         <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E5">
         <v>0.4010837438423646</v>
@@ -2348,7 +2720,7 @@
         <v>250</v>
       </c>
       <c r="J5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2359,16 +2731,16 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E6">
         <v>0.413743842364532</v>
       </c>
       <c r="F6">
-        <v>0.3824580685289189</v>
+        <v>0.382458068528919</v>
       </c>
       <c r="G6">
         <v>0.4454042263674867</v>
@@ -2380,7 +2752,7 @@
         <v>250</v>
       </c>
       <c r="J6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2391,10 +2763,10 @@
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E7">
         <v>0.4725615763546798</v>
@@ -2412,7 +2784,7 @@
         <v>250</v>
       </c>
       <c r="J7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -2423,19 +2795,19 @@
         <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E8">
         <v>0.503346436828533</v>
       </c>
       <c r="F8">
-        <v>0.467341335102832</v>
+        <v>0.4673413351028322</v>
       </c>
       <c r="G8">
-        <v>0.5381596977405826</v>
+        <v>0.5381596977405827</v>
       </c>
       <c r="H8">
         <v>406</v>
@@ -2444,7 +2816,7 @@
         <v>250</v>
       </c>
       <c r="J8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -2455,10 +2827,10 @@
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E9">
         <v>0.5190271308530763</v>
@@ -2476,7 +2848,7 @@
         <v>250</v>
       </c>
       <c r="J9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2487,19 +2859,19 @@
         <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E10">
         <v>0.5875820873372553</v>
       </c>
       <c r="F10">
-        <v>0.5463605798821267</v>
+        <v>0.5463605798821268</v>
       </c>
       <c r="G10">
-        <v>0.6266470149182912</v>
+        <v>0.6266470149182913</v>
       </c>
       <c r="H10">
         <v>406</v>
@@ -2508,7 +2880,7 @@
         <v>250</v>
       </c>
       <c r="J10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2519,16 +2891,16 @@
         <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E11">
         <v>0.34</v>
       </c>
       <c r="F11">
-        <v>0.2999999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="G11">
         <v>0.38</v>
@@ -2540,7 +2912,7 @@
         <v>250</v>
       </c>
       <c r="J11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2551,19 +2923,19 @@
         <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E12">
-        <v>0.3500000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="F12">
-        <v>0.3100000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="G12">
-        <v>0.3999999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="H12">
         <v>406</v>
@@ -2572,7 +2944,7 @@
         <v>250</v>
       </c>
       <c r="J12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -2583,13 +2955,13 @@
         <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E13">
-        <v>0.3999999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="F13">
         <v>0.36</v>
@@ -2604,7 +2976,7 @@
         <v>250</v>
       </c>
       <c r="J13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -2615,16 +2987,16 @@
         <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E14">
         <v>0.5035496260262651</v>
       </c>
       <c r="F14">
-        <v>0.4670729663895484</v>
+        <v>0.4670729663895485</v>
       </c>
       <c r="G14">
         <v>0.5373554039329193</v>
@@ -2636,7 +3008,7 @@
         <v>250</v>
       </c>
       <c r="J14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2647,16 +3019,16 @@
         <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E15">
         <v>0.5189064985777815</v>
       </c>
       <c r="F15">
-        <v>0.481268604979075</v>
+        <v>0.4812686049790749</v>
       </c>
       <c r="G15">
         <v>0.5530250723007292</v>
@@ -2668,7 +3040,7 @@
         <v>250</v>
       </c>
       <c r="J15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2679,16 +3051,16 @@
         <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E16">
         <v>0.5865506926221365</v>
       </c>
       <c r="F16">
-        <v>0.5442726547777093</v>
+        <v>0.5442726547777094</v>
       </c>
       <c r="G16">
         <v>0.624844231822534</v>
@@ -2700,7 +3072,7 @@
         <v>250</v>
       </c>
       <c r="J16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -2711,10 +3083,10 @@
         <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E17">
         <v>0.6921182266009852</v>
@@ -2732,7 +3104,7 @@
         <v>250</v>
       </c>
       <c r="J17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2743,10 +3115,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E18">
         <v>0.6576354679802956</v>
@@ -2764,7 +3136,7 @@
         <v>250</v>
       </c>
       <c r="J18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -2775,19 +3147,19 @@
         <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E19">
-        <v>0.6108374384236454</v>
+        <v>0.6133004926108374</v>
       </c>
       <c r="F19">
-        <v>0.5601965601965602</v>
+        <v>0.5623261083560855</v>
       </c>
       <c r="G19">
-        <v>0.6616933849272157</v>
+        <v>0.6649370426527788</v>
       </c>
       <c r="H19">
         <v>406</v>
@@ -2796,7 +3168,7 @@
         <v>250</v>
       </c>
       <c r="J19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -2804,28 +3176,28 @@
         <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20">
+        <v>0.01043478260869565</v>
+      </c>
+      <c r="F20">
+        <v>-0.1405866818558409</v>
+      </c>
+      <c r="G20">
+        <v>0.1541802941812676</v>
+      </c>
+      <c r="H20">
+        <v>69</v>
+      </c>
+      <c r="I20">
         <v>44</v>
-      </c>
-      <c r="D20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20">
-        <v>0.01473429951690822</v>
-      </c>
-      <c r="F20">
-        <v>-0.05386956521739131</v>
-      </c>
-      <c r="G20">
-        <v>0.08382367149758455</v>
-      </c>
-      <c r="H20">
-        <v>207</v>
-      </c>
-      <c r="I20">
-        <v>207</v>
       </c>
       <c r="J20" t="s">
         <v>95</v>
@@ -2836,28 +3208,28 @@
         <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E21">
-        <v>0.006376811594202901</v>
+        <v>0.01811594202898551</v>
       </c>
       <c r="F21">
-        <v>-0.06710386473429948</v>
+        <v>-0.1240307692307692</v>
       </c>
       <c r="G21">
-        <v>0.07851690821256047</v>
+        <v>0.1600074626865672</v>
       </c>
       <c r="H21">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="I21">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="J21" t="s">
         <v>95</v>
@@ -2868,28 +3240,28 @@
         <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E22">
-        <v>0.002318840579710145</v>
+        <v>0.06304347826086956</v>
       </c>
       <c r="F22">
-        <v>-0.07716183574879226</v>
+        <v>-0.08418067556952083</v>
       </c>
       <c r="G22">
-        <v>0.08183816425120778</v>
+        <v>0.20672519160952</v>
       </c>
       <c r="H22">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="I22">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="J22" t="s">
         <v>95</v>
@@ -2900,28 +3272,28 @@
         <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23">
+        <v>0.4165217391304348</v>
+      </c>
+      <c r="F23">
+        <v>0.3406073426573427</v>
+      </c>
+      <c r="G23">
+        <v>0.4958143892339545</v>
+      </c>
+      <c r="H23">
+        <v>69</v>
+      </c>
+      <c r="I23">
         <v>44</v>
-      </c>
-      <c r="D23" t="s">
-        <v>89</v>
-      </c>
-      <c r="E23">
-        <v>0.4014975845410628</v>
-      </c>
-      <c r="F23">
-        <v>0.3609106280193235</v>
-      </c>
-      <c r="G23">
-        <v>0.4427584541062801</v>
-      </c>
-      <c r="H23">
-        <v>207</v>
-      </c>
-      <c r="I23">
-        <v>207</v>
       </c>
       <c r="J23" t="s">
         <v>95</v>
@@ -2932,28 +3304,28 @@
         <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E24">
-        <v>0.4215458937198068</v>
+        <v>0.4256521739130435</v>
       </c>
       <c r="F24">
-        <v>0.3783091787439615</v>
+        <v>0.3438439869989167</v>
       </c>
       <c r="G24">
-        <v>0.4659565217391309</v>
+        <v>0.5062345755693584</v>
       </c>
       <c r="H24">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="I24">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="J24" t="s">
         <v>95</v>
@@ -2964,28 +3336,28 @@
         <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E25">
-        <v>0.4694685990338164</v>
+        <v>0.4534782608695653</v>
       </c>
       <c r="F25">
-        <v>0.4212487922705314</v>
+        <v>0.3886563130294475</v>
       </c>
       <c r="G25">
-        <v>0.5170048309178744</v>
+        <v>0.5249209799861974</v>
       </c>
       <c r="H25">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="I25">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="J25" t="s">
         <v>95</v>
@@ -2996,28 +3368,28 @@
         <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26">
+        <v>0.5201170436838566</v>
+      </c>
+      <c r="F26">
+        <v>0.4284678805213774</v>
+      </c>
+      <c r="G26">
+        <v>0.6072271720564225</v>
+      </c>
+      <c r="H26">
+        <v>69</v>
+      </c>
+      <c r="I26">
         <v>44</v>
-      </c>
-      <c r="D26" t="s">
-        <v>90</v>
-      </c>
-      <c r="E26">
-        <v>0.4993498188103143</v>
-      </c>
-      <c r="F26">
-        <v>0.4489748654168933</v>
-      </c>
-      <c r="G26">
-        <v>0.5487215267707212</v>
-      </c>
-      <c r="H26">
-        <v>207</v>
-      </c>
-      <c r="I26">
-        <v>207</v>
       </c>
       <c r="J26" t="s">
         <v>95</v>
@@ -3028,28 +3400,28 @@
         <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E27">
-        <v>0.5350976252975095</v>
+        <v>0.5374321662622487</v>
       </c>
       <c r="F27">
-        <v>0.4824960764236936</v>
+        <v>0.4330597529790759</v>
       </c>
       <c r="G27">
-        <v>0.5865781583925679</v>
+        <v>0.6319503432093759</v>
       </c>
       <c r="H27">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="I27">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="J27" t="s">
         <v>95</v>
@@ -3060,28 +3432,28 @@
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E28">
-        <v>0.5841530472476332</v>
+        <v>0.5544640969283843</v>
       </c>
       <c r="F28">
-        <v>0.5291510823472348</v>
+        <v>0.4730864484316748</v>
       </c>
       <c r="G28">
-        <v>0.6371627741675031</v>
+        <v>0.6373175941800167</v>
       </c>
       <c r="H28">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="I28">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="J28" t="s">
         <v>95</v>
@@ -3092,28 +3464,28 @@
         <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29">
+        <v>0.36</v>
+      </c>
+      <c r="F29">
+        <v>0.3</v>
+      </c>
+      <c r="G29">
+        <v>0.45</v>
+      </c>
+      <c r="H29">
+        <v>69</v>
+      </c>
+      <c r="I29">
         <v>44</v>
-      </c>
-      <c r="D29" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29">
-        <v>0.3599999999999999</v>
-      </c>
-      <c r="F29">
-        <v>0.29</v>
-      </c>
-      <c r="G29">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="H29">
-        <v>207</v>
-      </c>
-      <c r="I29">
-        <v>207</v>
       </c>
       <c r="J29" t="s">
         <v>95</v>
@@ -3124,28 +3496,28 @@
         <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E30">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="F30">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="G30">
-        <v>0.4300000000000002</v>
+        <v>0.46</v>
       </c>
       <c r="H30">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="I30">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="J30" t="s">
         <v>95</v>
@@ -3156,28 +3528,28 @@
         <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E31">
-        <v>0.4199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="F31">
-        <v>0.3599999999999994</v>
+        <v>0.31</v>
       </c>
       <c r="G31">
         <v>0.48</v>
       </c>
       <c r="H31">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="I31">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="J31" t="s">
         <v>95</v>
@@ -3188,28 +3560,28 @@
         <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32">
+        <v>0.5238220251826913</v>
+      </c>
+      <c r="F32">
+        <v>0.425397438980178</v>
+      </c>
+      <c r="G32">
+        <v>0.605553217988143</v>
+      </c>
+      <c r="H32">
+        <v>69</v>
+      </c>
+      <c r="I32">
         <v>44</v>
-      </c>
-      <c r="D32" t="s">
-        <v>92</v>
-      </c>
-      <c r="E32">
-        <v>0.5003424089040717</v>
-      </c>
-      <c r="F32">
-        <v>0.4484747263872393</v>
-      </c>
-      <c r="G32">
-        <v>0.5472560680830526</v>
-      </c>
-      <c r="H32">
-        <v>207</v>
-      </c>
-      <c r="I32">
-        <v>207</v>
       </c>
       <c r="J32" t="s">
         <v>95</v>
@@ -3220,28 +3592,28 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E33">
-        <v>0.5363567435512407</v>
+        <v>0.5410617974988647</v>
       </c>
       <c r="F33">
-        <v>0.4821727389220226</v>
+        <v>0.4317391992536254</v>
       </c>
       <c r="G33">
-        <v>0.5863463364422008</v>
+        <v>0.6309148172084375</v>
       </c>
       <c r="H33">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="I33">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="J33" t="s">
         <v>95</v>
@@ -3252,28 +3624,28 @@
         <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E34">
-        <v>0.5855645643413213</v>
+        <v>0.5549040837833944</v>
       </c>
       <c r="F34">
-        <v>0.529478721324974</v>
+        <v>0.4665901674614412</v>
       </c>
       <c r="G34">
-        <v>0.6374656501091623</v>
+        <v>0.6374200101169525</v>
       </c>
       <c r="H34">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="I34">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="J34" t="s">
         <v>95</v>
@@ -3284,28 +3656,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F35">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="G35">
+        <v>0.7910447761194029</v>
+      </c>
+      <c r="H35">
+        <v>69</v>
+      </c>
+      <c r="I35">
         <v>44</v>
-      </c>
-      <c r="D35" t="s">
-        <v>93</v>
-      </c>
-      <c r="E35">
-        <v>0.714975845410628</v>
-      </c>
-      <c r="F35">
-        <v>0.6521739130434783</v>
-      </c>
-      <c r="G35">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="H35">
-        <v>207</v>
-      </c>
-      <c r="I35">
-        <v>207</v>
       </c>
       <c r="J35" t="s">
         <v>95</v>
@@ -3316,28 +3688,28 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E36">
-        <v>0.6473429951690821</v>
+        <v>0.7101449275362319</v>
       </c>
       <c r="F36">
-        <v>0.5797101449275363</v>
+        <v>0.5966456287985042</v>
       </c>
       <c r="G36">
-        <v>0.7101449275362319</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="H36">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="I36">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="J36" t="s">
         <v>95</v>
@@ -3348,28 +3720,28 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E37">
-        <v>0.6038647342995169</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="F37">
-        <v>0.5362318840579711</v>
+        <v>0.5373134328358209</v>
       </c>
       <c r="G37">
-        <v>0.6714975845410628</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="H37">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="I37">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="J37" t="s">
         <v>95</v>
@@ -3380,28 +3752,28 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D38" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E38">
-        <v>0.02648241206030149</v>
+        <v>0.01693277310924369</v>
       </c>
       <c r="F38">
-        <v>-0.04417587939698493</v>
+        <v>-0.05493833289554333</v>
       </c>
       <c r="G38">
-        <v>0.09693718592964826</v>
+        <v>0.0878347802546582</v>
       </c>
       <c r="H38">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I38">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J38" t="s">
         <v>95</v>
@@ -3412,28 +3784,28 @@
         <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E39">
-        <v>0.05065326633165827</v>
+        <v>0.01974789915966386</v>
       </c>
       <c r="F39">
-        <v>-0.01932160804020097</v>
+        <v>-0.05385132514544282</v>
       </c>
       <c r="G39">
-        <v>0.1202537688442211</v>
+        <v>0.09216067119220821</v>
       </c>
       <c r="H39">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I39">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J39" t="s">
         <v>95</v>
@@ -3444,28 +3816,28 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E40">
-        <v>0.09015075376884421</v>
+        <v>0.01130252100840337</v>
       </c>
       <c r="F40">
-        <v>0.005876884422110537</v>
+        <v>-0.07513349699945444</v>
       </c>
       <c r="G40">
-        <v>0.1709070351758794</v>
+        <v>0.09668995796523235</v>
       </c>
       <c r="H40">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I40">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J40" t="s">
         <v>95</v>
@@ -3476,28 +3848,28 @@
         <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E41">
-        <v>0.4006532663316583</v>
+        <v>0.3740756302521008</v>
       </c>
       <c r="F41">
-        <v>0.3574874371859297</v>
+        <v>0.3347098884618991</v>
       </c>
       <c r="G41">
-        <v>0.4432688442211056</v>
+        <v>0.4146456049655938</v>
       </c>
       <c r="H41">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I41">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J41" t="s">
         <v>95</v>
@@ -3508,28 +3880,28 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E42">
-        <v>0.4056281407035176</v>
+        <v>0.3876470588235295</v>
       </c>
       <c r="F42">
-        <v>0.3649698492462313</v>
+        <v>0.3476754384342164</v>
       </c>
       <c r="G42">
-        <v>0.4472889447236182</v>
+        <v>0.4285869397759103</v>
       </c>
       <c r="H42">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I42">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J42" t="s">
         <v>95</v>
@@ -3540,28 +3912,28 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C43" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E43">
-        <v>0.4757788944723618</v>
+        <v>0.4584453781512605</v>
       </c>
       <c r="F43">
-        <v>0.4288944723618093</v>
+        <v>0.4111537670148784</v>
       </c>
       <c r="G43">
-        <v>0.5252286432160804</v>
+        <v>0.5100834219858156</v>
       </c>
       <c r="H43">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I43">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J43" t="s">
         <v>95</v>
@@ -3572,28 +3944,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E44">
-        <v>0.5074703248991672</v>
+        <v>0.4805271090386144</v>
       </c>
       <c r="F44">
-        <v>0.4568519922236322</v>
+        <v>0.4319239833622951</v>
       </c>
       <c r="G44">
-        <v>0.5557394457416932</v>
+        <v>0.5290570429882944</v>
       </c>
       <c r="H44">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I44">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J44" t="s">
         <v>95</v>
@@ -3604,28 +3976,28 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E45">
-        <v>0.5017647249418594</v>
+        <v>0.4957262730732819</v>
       </c>
       <c r="F45">
-        <v>0.4565332790587962</v>
+        <v>0.4490506933811403</v>
       </c>
       <c r="G45">
-        <v>0.5461399953055275</v>
+        <v>0.5432667880392282</v>
       </c>
       <c r="H45">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I45">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J45" t="s">
         <v>95</v>
@@ -3636,28 +4008,28 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E46">
-        <v>0.5911278717875009</v>
+        <v>0.5806744123080022</v>
       </c>
       <c r="F46">
-        <v>0.5363117100554832</v>
+        <v>0.5258431036973865</v>
       </c>
       <c r="G46">
-        <v>0.6456197404269474</v>
+        <v>0.6349583666787159</v>
       </c>
       <c r="H46">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I46">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J46" t="s">
         <v>95</v>
@@ -3668,28 +4040,28 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D47" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E47">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="F47">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="G47">
-        <v>0.4099999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="H47">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I47">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J47" t="s">
         <v>95</v>
@@ -3700,28 +4072,28 @@
         <v>43</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D48" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E48">
-        <v>0.3500000000000001</v>
+        <v>0.335</v>
       </c>
       <c r="F48">
-        <v>0.3099999999999998</v>
+        <v>0.27</v>
       </c>
       <c r="G48">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H48">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I48">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J48" t="s">
         <v>95</v>
@@ -3732,28 +4104,28 @@
         <v>43</v>
       </c>
       <c r="B49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D49" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E49">
-        <v>0.3900000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="F49">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="G49">
-        <v>0.4400000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="H49">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I49">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J49" t="s">
         <v>95</v>
@@ -3764,28 +4136,28 @@
         <v>43</v>
       </c>
       <c r="B50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E50">
-        <v>0.5080569923909963</v>
+        <v>0.4812407527715649</v>
       </c>
       <c r="F50">
-        <v>0.4565598267050878</v>
+        <v>0.4319931836210766</v>
       </c>
       <c r="G50">
-        <v>0.5549796484849452</v>
+        <v>0.5277549495812133</v>
       </c>
       <c r="H50">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I50">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J50" t="s">
         <v>95</v>
@@ -3796,28 +4168,28 @@
         <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E51">
-        <v>0.5004604701660993</v>
+        <v>0.4963766811552734</v>
       </c>
       <c r="F51">
-        <v>0.4533062480035989</v>
+        <v>0.4481946743754427</v>
       </c>
       <c r="G51">
-        <v>0.5438143015862841</v>
+        <v>0.5425005845529751</v>
       </c>
       <c r="H51">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I51">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J51" t="s">
         <v>95</v>
@@ -3828,28 +4200,28 @@
         <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C52" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D52" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E52">
-        <v>0.5856865757701022</v>
+        <v>0.581787933214607</v>
       </c>
       <c r="F52">
-        <v>0.528603758787536</v>
+        <v>0.5249154479852544</v>
       </c>
       <c r="G52">
-        <v>0.6404274271255828</v>
+        <v>0.6342739322681901</v>
       </c>
       <c r="H52">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I52">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J52" t="s">
         <v>95</v>
@@ -3860,28 +4232,28 @@
         <v>43</v>
       </c>
       <c r="B53" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D53" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E53">
-        <v>0.6683417085427136</v>
+        <v>0.7394957983193278</v>
       </c>
       <c r="F53">
-        <v>0.6030150753768844</v>
+        <v>0.680672268907563</v>
       </c>
       <c r="G53">
-        <v>0.7336683417085427</v>
+        <v>0.7949842238836683</v>
       </c>
       <c r="H53">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I53">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J53" t="s">
         <v>95</v>
@@ -3892,28 +4264,28 @@
         <v>43</v>
       </c>
       <c r="B54" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D54" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E54">
-        <v>0.6683417085427136</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="F54">
-        <v>0.5979899497487438</v>
+        <v>0.6147030229657349</v>
       </c>
       <c r="G54">
-        <v>0.7336683417085427</v>
+        <v>0.7364016736401674</v>
       </c>
       <c r="H54">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I54">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J54" t="s">
         <v>95</v>
@@ -3924,30 +4296,606 @@
         <v>43</v>
       </c>
       <c r="B55" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C55" t="s">
+        <v>47</v>
+      </c>
+      <c r="D55" t="s">
+        <v>94</v>
+      </c>
+      <c r="E55">
+        <v>0.6386554621848739</v>
+      </c>
+      <c r="F55">
+        <v>0.5665236051502146</v>
+      </c>
+      <c r="G55">
+        <v>0.7024793388429752</v>
+      </c>
+      <c r="H55">
+        <v>238</v>
+      </c>
+      <c r="I55">
+        <v>154</v>
+      </c>
+      <c r="J55" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" t="s">
+        <v>88</v>
+      </c>
+      <c r="C56" t="s">
+        <v>45</v>
+      </c>
+      <c r="D56" t="s">
+        <v>89</v>
+      </c>
+      <c r="E56">
+        <v>0.03606060606060607</v>
+      </c>
+      <c r="F56">
+        <v>-0.08726458333333333</v>
+      </c>
+      <c r="G56">
+        <v>0.158636274509804</v>
+      </c>
+      <c r="H56">
+        <v>99</v>
+      </c>
+      <c r="I56">
+        <v>64</v>
+      </c>
+      <c r="J56" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>44</v>
+      </c>
+      <c r="B57" t="s">
+        <v>88</v>
+      </c>
+      <c r="C57" t="s">
         <v>46</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D57" t="s">
+        <v>89</v>
+      </c>
+      <c r="E57">
+        <v>0.05505050505050505</v>
+      </c>
+      <c r="F57">
+        <v>-0.07600303030303028</v>
+      </c>
+      <c r="G57">
+        <v>0.1818428361035136</v>
+      </c>
+      <c r="H57">
+        <v>99</v>
+      </c>
+      <c r="I57">
+        <v>64</v>
+      </c>
+      <c r="J57" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" t="s">
+        <v>88</v>
+      </c>
+      <c r="C58" t="s">
+        <v>47</v>
+      </c>
+      <c r="D58" t="s">
+        <v>89</v>
+      </c>
+      <c r="E58">
+        <v>0.1149494949494949</v>
+      </c>
+      <c r="F58">
+        <v>-0.02216176470588235</v>
+      </c>
+      <c r="G58">
+        <v>0.249908653846154</v>
+      </c>
+      <c r="H58">
+        <v>99</v>
+      </c>
+      <c r="I58">
+        <v>64</v>
+      </c>
+      <c r="J58" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" t="s">
+        <v>45</v>
+      </c>
+      <c r="D59" t="s">
+        <v>90</v>
+      </c>
+      <c r="E59">
+        <v>0.4552525252525252</v>
+      </c>
+      <c r="F59">
+        <v>0.3999027669902913</v>
+      </c>
+      <c r="G59">
+        <v>0.5174239953713444</v>
+      </c>
+      <c r="H59">
+        <v>99</v>
+      </c>
+      <c r="I59">
+        <v>64</v>
+      </c>
+      <c r="J59" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" t="s">
+        <v>88</v>
+      </c>
+      <c r="C60" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" t="s">
+        <v>90</v>
+      </c>
+      <c r="E60">
+        <v>0.4681818181818182</v>
+      </c>
+      <c r="F60">
+        <v>0.40969840430645</v>
+      </c>
+      <c r="G60">
+        <v>0.5268939379787034</v>
+      </c>
+      <c r="H60">
+        <v>99</v>
+      </c>
+      <c r="I60">
+        <v>64</v>
+      </c>
+      <c r="J60" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" t="s">
+        <v>47</v>
+      </c>
+      <c r="D61" t="s">
+        <v>90</v>
+      </c>
+      <c r="E61">
+        <v>0.5197979797979798</v>
+      </c>
+      <c r="F61">
+        <v>0.449176170212766</v>
+      </c>
+      <c r="G61">
+        <v>0.5939079702970298</v>
+      </c>
+      <c r="H61">
+        <v>99</v>
+      </c>
+      <c r="I61">
+        <v>64</v>
+      </c>
+      <c r="J61" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" t="s">
+        <v>88</v>
+      </c>
+      <c r="C62" t="s">
+        <v>45</v>
+      </c>
+      <c r="D62" t="s">
+        <v>91</v>
+      </c>
+      <c r="E62">
+        <v>0.543478322353971</v>
+      </c>
+      <c r="F62">
+        <v>0.4817497049522778</v>
+      </c>
+      <c r="G62">
+        <v>0.6083533319636707</v>
+      </c>
+      <c r="H62">
+        <v>99</v>
+      </c>
+      <c r="I62">
+        <v>64</v>
+      </c>
+      <c r="J62" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63" t="s">
+        <v>46</v>
+      </c>
+      <c r="D63" t="s">
+        <v>91</v>
+      </c>
+      <c r="E63">
+        <v>0.559177787452075</v>
+      </c>
+      <c r="F63">
+        <v>0.4971917299145414</v>
+      </c>
+      <c r="G63">
+        <v>0.6172601740831101</v>
+      </c>
+      <c r="H63">
+        <v>99</v>
+      </c>
+      <c r="I63">
+        <v>64</v>
+      </c>
+      <c r="J63" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" t="s">
+        <v>88</v>
+      </c>
+      <c r="C64" t="s">
+        <v>47</v>
+      </c>
+      <c r="D64" t="s">
+        <v>91</v>
+      </c>
+      <c r="E64">
+        <v>0.6253112356372157</v>
+      </c>
+      <c r="F64">
+        <v>0.5432590730716428</v>
+      </c>
+      <c r="G64">
+        <v>0.7045706765071336</v>
+      </c>
+      <c r="H64">
+        <v>99</v>
+      </c>
+      <c r="I64">
+        <v>64</v>
+      </c>
+      <c r="J64" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" t="s">
+        <v>44</v>
+      </c>
+      <c r="B65" t="s">
+        <v>88</v>
+      </c>
+      <c r="C65" t="s">
+        <v>45</v>
+      </c>
+      <c r="D65" t="s">
+        <v>92</v>
+      </c>
+      <c r="E65">
+        <v>0.45</v>
+      </c>
+      <c r="F65">
+        <v>0.36</v>
+      </c>
+      <c r="G65">
+        <v>0.49</v>
+      </c>
+      <c r="H65">
+        <v>99</v>
+      </c>
+      <c r="I65">
+        <v>64</v>
+      </c>
+      <c r="J65" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" t="s">
+        <v>44</v>
+      </c>
+      <c r="B66" t="s">
+        <v>88</v>
+      </c>
+      <c r="C66" t="s">
+        <v>46</v>
+      </c>
+      <c r="D66" t="s">
+        <v>92</v>
+      </c>
+      <c r="E66">
+        <v>0.44</v>
+      </c>
+      <c r="F66">
+        <v>0.33</v>
+      </c>
+      <c r="G66">
+        <v>0.54</v>
+      </c>
+      <c r="H66">
+        <v>99</v>
+      </c>
+      <c r="I66">
+        <v>64</v>
+      </c>
+      <c r="J66" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" t="s">
+        <v>47</v>
+      </c>
+      <c r="D67" t="s">
+        <v>92</v>
+      </c>
+      <c r="E67">
+        <v>0.49</v>
+      </c>
+      <c r="F67">
+        <v>0.39</v>
+      </c>
+      <c r="G67">
+        <v>0.53</v>
+      </c>
+      <c r="H67">
+        <v>99</v>
+      </c>
+      <c r="I67">
+        <v>64</v>
+      </c>
+      <c r="J67" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" t="s">
+        <v>88</v>
+      </c>
+      <c r="C68" t="s">
+        <v>45</v>
+      </c>
+      <c r="D68" t="s">
         <v>93</v>
       </c>
-      <c r="E55">
-        <v>0.6180904522613065</v>
-      </c>
-      <c r="F55">
-        <v>0.5477386934673367</v>
-      </c>
-      <c r="G55">
-        <v>0.6834170854271356</v>
-      </c>
-      <c r="H55">
-        <v>199</v>
-      </c>
-      <c r="I55">
-        <v>199</v>
-      </c>
-      <c r="J55" t="s">
+      <c r="E68">
+        <v>0.5450403807953941</v>
+      </c>
+      <c r="F68">
+        <v>0.4784080911106443</v>
+      </c>
+      <c r="G68">
+        <v>0.6054111907182181</v>
+      </c>
+      <c r="H68">
+        <v>99</v>
+      </c>
+      <c r="I68">
+        <v>64</v>
+      </c>
+      <c r="J68" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" t="s">
+        <v>44</v>
+      </c>
+      <c r="B69" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" t="s">
+        <v>46</v>
+      </c>
+      <c r="D69" t="s">
+        <v>93</v>
+      </c>
+      <c r="E69">
+        <v>0.5592932379303726</v>
+      </c>
+      <c r="F69">
+        <v>0.4907488224673515</v>
+      </c>
+      <c r="G69">
+        <v>0.6162487836377396</v>
+      </c>
+      <c r="H69">
+        <v>99</v>
+      </c>
+      <c r="I69">
+        <v>64</v>
+      </c>
+      <c r="J69" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" t="s">
+        <v>47</v>
+      </c>
+      <c r="D70" t="s">
+        <v>93</v>
+      </c>
+      <c r="E70">
+        <v>0.6177830240223103</v>
+      </c>
+      <c r="F70">
+        <v>0.5390617375857683</v>
+      </c>
+      <c r="G70">
+        <v>0.6882910415358988</v>
+      </c>
+      <c r="H70">
+        <v>99</v>
+      </c>
+      <c r="I70">
+        <v>64</v>
+      </c>
+      <c r="J70" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" t="s">
+        <v>88</v>
+      </c>
+      <c r="C71" t="s">
+        <v>45</v>
+      </c>
+      <c r="D71" t="s">
+        <v>94</v>
+      </c>
+      <c r="E71">
+        <v>0.5959595959595959</v>
+      </c>
+      <c r="F71">
+        <v>0.5</v>
+      </c>
+      <c r="G71">
+        <v>0.684802737520129</v>
+      </c>
+      <c r="H71">
+        <v>99</v>
+      </c>
+      <c r="I71">
+        <v>64</v>
+      </c>
+      <c r="J71" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C72" t="s">
+        <v>46</v>
+      </c>
+      <c r="D72" t="s">
+        <v>94</v>
+      </c>
+      <c r="E72">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="F72">
+        <v>0.4838347227256253</v>
+      </c>
+      <c r="G72">
+        <v>0.67</v>
+      </c>
+      <c r="H72">
+        <v>99</v>
+      </c>
+      <c r="I72">
+        <v>64</v>
+      </c>
+      <c r="J72" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" t="s">
+        <v>44</v>
+      </c>
+      <c r="B73" t="s">
+        <v>88</v>
+      </c>
+      <c r="C73" t="s">
+        <v>47</v>
+      </c>
+      <c r="D73" t="s">
+        <v>94</v>
+      </c>
+      <c r="E73">
+        <v>0.5252525252525253</v>
+      </c>
+      <c r="F73">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="G73">
+        <v>0.6263220439691031</v>
+      </c>
+      <c r="H73">
+        <v>99</v>
+      </c>
+      <c r="I73">
+        <v>64</v>
+      </c>
+      <c r="J73" t="s">
         <v>95</v>
       </c>
     </row>
@@ -3958,7 +4906,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S55"/>
+  <dimension ref="A1:S73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="13" width="18.7109375" customWidth="1"/>
@@ -3971,13 +4919,13 @@
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D1" t="s">
         <v>96</v>
@@ -3995,10 +4943,10 @@
         <v>100</v>
       </c>
       <c r="I1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K1" t="s">
         <v>101</v>
@@ -4036,28 +4984,28 @@
         <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F2">
-        <v>0.02049261083743843</v>
+        <v>0.02049261083743842</v>
       </c>
       <c r="G2">
         <v>0.02807881773399015</v>
       </c>
       <c r="H2">
-        <v>-0.00758620689655172</v>
+        <v>-0.007586206896551734</v>
       </c>
       <c r="I2">
-        <v>-0.04493901095487549</v>
+        <v>-0.04493901095487556</v>
       </c>
       <c r="J2">
-        <v>0.03040411335473123</v>
+        <v>0.03040411335473117</v>
       </c>
       <c r="K2">
         <v>0.6926</v>
@@ -4069,22 +5017,22 @@
         <v>1.530907631213612</v>
       </c>
       <c r="N2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O2">
         <v>0.7454</v>
       </c>
       <c r="P2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q2">
-        <v>-0.05410272103966409</v>
+        <v>-0.05410272103966406</v>
       </c>
       <c r="R2">
-        <v>0.03893030724656065</v>
+        <v>0.03893030724656057</v>
       </c>
       <c r="S2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -4095,13 +5043,13 @@
         <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3">
         <v>0.4010837438423646</v>
@@ -4113,37 +5061,37 @@
         <v>-0.01266009852216748</v>
       </c>
       <c r="I3">
-        <v>-0.04537308813124197</v>
+        <v>-0.04537308813124185</v>
       </c>
       <c r="J3">
-        <v>0.02084416313854757</v>
+        <v>0.0208441631385477</v>
       </c>
       <c r="K3">
         <v>0.461</v>
       </c>
       <c r="L3">
-        <v>0.1505359768729158</v>
+        <v>0.1505359768729156</v>
       </c>
       <c r="M3">
         <v>1.455610834346575</v>
       </c>
       <c r="N3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O3">
         <v>0.461</v>
       </c>
       <c r="P3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q3">
-        <v>-0.05229618964656452</v>
+        <v>-0.05229618964656447</v>
       </c>
       <c r="R3">
-        <v>0.02697599260222911</v>
+        <v>0.02697599260222917</v>
       </c>
       <c r="S3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -4154,13 +5102,13 @@
         <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F4">
         <v>0.503346436828533</v>
@@ -4172,31 +5120,31 @@
         <v>-0.01568069402454331</v>
       </c>
       <c r="I4">
-        <v>-0.05106318963604019</v>
+        <v>-0.05106318963604003</v>
       </c>
       <c r="J4">
-        <v>0.01787937336349208</v>
+        <v>0.01787937336349218</v>
       </c>
       <c r="K4">
         <v>0.3852</v>
       </c>
       <c r="L4">
-        <v>0.0840255382977116</v>
+        <v>0.08402553829771155</v>
       </c>
       <c r="M4">
         <v>1.525496624127441</v>
       </c>
       <c r="N4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O4">
         <v>0.3852</v>
       </c>
       <c r="P4" t="s">
+        <v>110</v>
+      </c>
+      <c r="S4" t="s">
         <v>113</v>
-      </c>
-      <c r="S4" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -4207,49 +5155,49 @@
         <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5">
         <v>0.34</v>
       </c>
       <c r="G5">
-        <v>0.3500000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="H5">
-        <v>-0.01000000000000012</v>
+        <v>-0.009999999999999953</v>
       </c>
       <c r="I5">
-        <v>-0.07000000000000073</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J5">
-        <v>0.04000000000000004</v>
+        <v>0.03999999999999998</v>
       </c>
       <c r="K5">
-        <v>0.6112</v>
+        <v>0.6968</v>
       </c>
       <c r="N5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O5">
-        <v>0.7282</v>
+        <v>0.844</v>
       </c>
       <c r="P5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q5">
-        <v>-0.08000000000000007</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="R5">
-        <v>0.05999999999999983</v>
+        <v>0.06000000000000011</v>
       </c>
       <c r="S5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -4260,13 +5208,13 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6">
         <v>0.5035496260262651</v>
@@ -4278,25 +5226,25 @@
         <v>-0.01535687255151641</v>
       </c>
       <c r="I6">
-        <v>-0.05064189418206685</v>
+        <v>-0.05064189418206674</v>
       </c>
       <c r="J6">
-        <v>0.01876017330561063</v>
+        <v>0.01876017330561083</v>
       </c>
       <c r="K6">
         <v>0.3894</v>
       </c>
       <c r="N6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O6">
         <v>0.3894</v>
       </c>
       <c r="P6" t="s">
+        <v>110</v>
+      </c>
+      <c r="S6" t="s">
         <v>113</v>
-      </c>
-      <c r="S6" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4307,13 +5255,13 @@
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7">
         <v>0.6921182266009852</v>
@@ -4340,16 +5288,16 @@
         <v>1.575352047426485</v>
       </c>
       <c r="N7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O7">
         <v>0.204560421762222</v>
       </c>
       <c r="P7" t="s">
+        <v>111</v>
+      </c>
+      <c r="S7" t="s">
         <v>114</v>
-      </c>
-      <c r="S7" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4360,16 +5308,16 @@
         <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F8">
-        <v>0.02049261083743843</v>
+        <v>0.02049261083743842</v>
       </c>
       <c r="G8">
         <v>0.04536945812807881</v>
@@ -4378,10 +5326,10 @@
         <v>-0.02487684729064039</v>
       </c>
       <c r="I8">
-        <v>-0.07516438999171429</v>
+        <v>-0.07516438999171443</v>
       </c>
       <c r="J8">
-        <v>0.02555545062902348</v>
+        <v>0.02555545062902334</v>
       </c>
       <c r="K8">
         <v>0.323</v>
@@ -4393,22 +5341,22 @@
         <v>1.496102394400772</v>
       </c>
       <c r="N8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O8">
         <v>0.5734</v>
       </c>
       <c r="P8" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q8">
-        <v>-0.08440726271056506</v>
+        <v>-0.08440726271056505</v>
       </c>
       <c r="R8">
-        <v>0.03465356812928424</v>
+        <v>0.03465356812928412</v>
       </c>
       <c r="S8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4419,13 +5367,13 @@
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F9">
         <v>0.4010837438423646</v>
@@ -4437,37 +5385,37 @@
         <v>-0.07147783251231526</v>
       </c>
       <c r="I9">
-        <v>-0.1094511309795232</v>
+        <v>-0.1094511309795231</v>
       </c>
       <c r="J9">
-        <v>-0.03377935695481725</v>
+        <v>-0.03377935695481713</v>
       </c>
       <c r="K9">
         <v>0.0004</v>
       </c>
       <c r="L9">
-        <v>0.0589783684526196</v>
+        <v>0.05897836845261967</v>
       </c>
       <c r="M9">
         <v>1.553586372596406</v>
       </c>
       <c r="N9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O9">
         <v>0.0004</v>
       </c>
       <c r="P9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q9">
         <v>-0.1160939316204946</v>
       </c>
       <c r="R9">
-        <v>-0.02686173340413656</v>
+        <v>-0.02686173340413649</v>
       </c>
       <c r="S9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4478,13 +5426,13 @@
         <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F10">
         <v>0.503346436828533</v>
@@ -4496,7 +5444,7 @@
         <v>-0.08423565050872228</v>
       </c>
       <c r="I10">
-        <v>-0.1255427629627514</v>
+        <v>-0.1255427629627515</v>
       </c>
       <c r="J10">
         <v>-0.0419672383242247</v>
@@ -4505,22 +5453,22 @@
         <v>0.0004</v>
       </c>
       <c r="L10">
-        <v>0.03487850112907194</v>
+        <v>0.03487850112907201</v>
       </c>
       <c r="M10">
         <v>1.581607874494274</v>
       </c>
       <c r="N10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O10">
         <v>0.0008</v>
       </c>
       <c r="P10" t="s">
+        <v>110</v>
+      </c>
+      <c r="S10" t="s">
         <v>113</v>
-      </c>
-      <c r="S10" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4531,49 +5479,49 @@
         <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F11">
         <v>0.34</v>
       </c>
       <c r="G11">
-        <v>0.3999999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="H11">
-        <v>-0.05999999999999994</v>
+        <v>-0.06</v>
       </c>
       <c r="I11">
-        <v>-0.1199999999999999</v>
+        <v>-0.12</v>
       </c>
       <c r="J11">
-        <v>-0.009999999999999839</v>
+        <v>-0.009999999999999953</v>
       </c>
       <c r="K11">
-        <v>0.028</v>
+        <v>0.0392</v>
       </c>
       <c r="N11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O11">
-        <v>0.09279999999999999</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="P11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q11">
-        <v>-0.1280741611297381</v>
+        <v>-0.1280741611297382</v>
       </c>
       <c r="R11">
-        <v>0.008074161129738217</v>
+        <v>0.008074161129738258</v>
       </c>
       <c r="S11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4584,13 +5532,13 @@
         <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F12">
         <v>0.5035496260262651</v>
@@ -4602,25 +5550,25 @@
         <v>-0.08300106659587148</v>
       </c>
       <c r="I12">
-        <v>-0.1240127595235769</v>
+        <v>-0.124012759523577</v>
       </c>
       <c r="J12">
-        <v>-0.04070333062115</v>
+        <v>-0.04070333062114999</v>
       </c>
       <c r="K12">
         <v>0.0005999999999999999</v>
       </c>
       <c r="N12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O12">
         <v>0.0008</v>
       </c>
       <c r="P12" t="s">
+        <v>110</v>
+      </c>
+      <c r="S12" t="s">
         <v>113</v>
-      </c>
-      <c r="S12" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4631,49 +5579,49 @@
         <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F13">
         <v>0.6921182266009852</v>
       </c>
       <c r="G13">
-        <v>0.6108374384236454</v>
+        <v>0.6133004926108374</v>
       </c>
       <c r="H13">
-        <v>0.08128078817733986</v>
+        <v>0.0788177339901478</v>
       </c>
       <c r="I13">
-        <v>0.02216476440614372</v>
+        <v>0.01979710286299567</v>
       </c>
       <c r="J13">
-        <v>0.1403530377668309</v>
+        <v>0.1380185633575464</v>
       </c>
       <c r="K13">
-        <v>0.006863871555196087</v>
+        <v>0.009022063055144957</v>
       </c>
       <c r="L13">
-        <v>0.074687129444328</v>
+        <v>0.09523875150218851</v>
       </c>
       <c r="M13">
-        <v>1.535849843792607</v>
+        <v>1.513247813472457</v>
       </c>
       <c r="N13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O13">
-        <v>0.02059161466558826</v>
+        <v>0.02706618916543487</v>
       </c>
       <c r="P13" t="s">
+        <v>111</v>
+      </c>
+      <c r="S13" t="s">
         <v>114</v>
-      </c>
-      <c r="S13" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4684,13 +5632,13 @@
         <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F14">
         <v>0.02807881773399015</v>
@@ -4699,40 +5647,40 @@
         <v>0.04536945812807881</v>
       </c>
       <c r="H14">
-        <v>-0.01729064039408867</v>
+        <v>-0.01729064039408866</v>
       </c>
       <c r="I14">
-        <v>-0.07150679591982625</v>
+        <v>-0.07150679591982637</v>
       </c>
       <c r="J14">
-        <v>0.03668306575040813</v>
+        <v>0.03668306575040802</v>
       </c>
       <c r="K14">
         <v>0.518</v>
       </c>
       <c r="L14">
-        <v>0.1843641333656313</v>
+        <v>0.1843641333656314</v>
       </c>
       <c r="M14">
         <v>1.422466582636034</v>
       </c>
       <c r="N14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O14">
         <v>0.7454</v>
       </c>
       <c r="P14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q14">
-        <v>-0.08180644473769279</v>
+        <v>-0.08180644473769276</v>
       </c>
       <c r="R14">
-        <v>0.04722516394951541</v>
+        <v>0.0472251639495153</v>
       </c>
       <c r="S14" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4743,13 +5691,13 @@
         <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F15">
         <v>0.413743842364532</v>
@@ -4764,7 +5712,7 @@
         <v>-0.1025986784782056</v>
       </c>
       <c r="J15">
-        <v>-0.01794955791900316</v>
+        <v>-0.01794955791900317</v>
       </c>
       <c r="K15">
         <v>0.005</v>
@@ -4776,13 +5724,13 @@
         <v>1.419611895158891</v>
       </c>
       <c r="N15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O15">
         <v>0.0104</v>
       </c>
       <c r="P15" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q15">
         <v>-0.1084139624854691</v>
@@ -4791,7 +5739,7 @@
         <v>-0.009221505494826733</v>
       </c>
       <c r="S15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4802,13 +5750,13 @@
         <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F16">
         <v>0.5190271308530763</v>
@@ -4820,7 +5768,7 @@
         <v>-0.06855495648417897</v>
       </c>
       <c r="I16">
-        <v>-0.1131287403553189</v>
+        <v>-0.1131287403553188</v>
       </c>
       <c r="J16">
         <v>-0.02214090274061026</v>
@@ -4829,22 +5777,22 @@
         <v>0.0036</v>
       </c>
       <c r="L16">
-        <v>0.1031443239050249</v>
+        <v>0.103144323905025</v>
       </c>
       <c r="M16">
         <v>1.504729680828269</v>
       </c>
       <c r="N16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O16">
         <v>0.0052</v>
       </c>
       <c r="P16" t="s">
+        <v>110</v>
+      </c>
+      <c r="S16" t="s">
         <v>113</v>
-      </c>
-      <c r="S16" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4855,49 +5803,49 @@
         <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17">
-        <v>0.3500000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="G17">
-        <v>0.3999999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="H17">
-        <v>-0.04999999999999982</v>
+        <v>-0.05000000000000004</v>
       </c>
       <c r="I17">
-        <v>-0.1099999999999999</v>
+        <v>-0.11</v>
       </c>
       <c r="J17">
-        <v>0.01000000000000035</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="K17">
-        <v>0.1748</v>
+        <v>0.2012</v>
       </c>
       <c r="N17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O17">
-        <v>0.2226</v>
+        <v>0.2164</v>
       </c>
       <c r="P17" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q17">
-        <v>-0.1230166690346133</v>
+        <v>-0.1230166690346137</v>
       </c>
       <c r="R17">
-        <v>0.02301666903461366</v>
+        <v>0.02301666903461358</v>
       </c>
       <c r="S17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4908,13 +5856,13 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F18">
         <v>0.5189064985777815</v>
@@ -4929,22 +5877,22 @@
         <v>-0.1119735373189496</v>
       </c>
       <c r="J18">
-        <v>-0.02111883542966709</v>
+        <v>-0.0211188354296671</v>
       </c>
       <c r="K18">
         <v>0.005</v>
       </c>
       <c r="N18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O18">
         <v>0.008399999999999999</v>
       </c>
       <c r="P18" t="s">
+        <v>110</v>
+      </c>
+      <c r="S18" t="s">
         <v>113</v>
-      </c>
-      <c r="S18" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4955,49 +5903,49 @@
         <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F19">
         <v>0.6576354679802956</v>
       </c>
       <c r="G19">
-        <v>0.6108374384236454</v>
+        <v>0.6133004926108374</v>
       </c>
       <c r="H19">
-        <v>0.04679802955665024</v>
+        <v>0.04433497536945818</v>
       </c>
       <c r="I19">
-        <v>-0.01452960812430945</v>
+        <v>-0.01686950701356149</v>
       </c>
       <c r="J19">
-        <v>0.1075</v>
+        <v>0.1050067237163814</v>
       </c>
       <c r="K19">
-        <v>0.1319988990199734</v>
+        <v>0.1549785601955193</v>
       </c>
       <c r="L19">
-        <v>0.1820022159757861</v>
+        <v>0.181230275610628</v>
       </c>
       <c r="M19">
-        <v>1.42473165658859</v>
+        <v>1.425473510706959</v>
       </c>
       <c r="N19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O19">
         <v>0.204560421762222</v>
       </c>
       <c r="P19" t="s">
+        <v>111</v>
+      </c>
+      <c r="S19" t="s">
         <v>114</v>
-      </c>
-      <c r="S19" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -5005,52 +5953,58 @@
         <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F20">
-        <v>0.01473429951690822</v>
+        <v>0.01043478260869565</v>
       </c>
       <c r="G20">
-        <v>0.006376811594202901</v>
+        <v>0.01811594202898551</v>
       </c>
       <c r="H20">
-        <v>0.008357487922705319</v>
+        <v>-0.007681159420289864</v>
       </c>
       <c r="I20">
-        <v>-0.03937699896679999</v>
+        <v>-0.08681275054350658</v>
       </c>
       <c r="J20">
-        <v>0.05950336880945854</v>
+        <v>0.09128877870612474</v>
       </c>
       <c r="K20">
-        <v>0.7482</v>
+        <v>0.8618</v>
+      </c>
+      <c r="L20">
+        <v>0.2388921310381965</v>
+      </c>
+      <c r="M20">
+        <v>1.336772764287313</v>
       </c>
       <c r="N20" t="s">
+        <v>67</v>
+      </c>
+      <c r="O20">
+        <v>0.8618</v>
+      </c>
+      <c r="P20" t="s">
         <v>110</v>
       </c>
-      <c r="O20">
-        <v>0.9228</v>
-      </c>
-      <c r="P20" t="s">
-        <v>113</v>
-      </c>
       <c r="Q20">
-        <v>-0.05103539816859672</v>
+        <v>-0.1141871619631026</v>
       </c>
       <c r="R20">
-        <v>0.06775037401400737</v>
+        <v>0.09882484312252289</v>
       </c>
       <c r="S20" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -5058,52 +6012,58 @@
         <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F21">
-        <v>0.4014975845410628</v>
+        <v>0.4165217391304348</v>
       </c>
       <c r="G21">
-        <v>0.4215458937198068</v>
+        <v>0.4256521739130435</v>
       </c>
       <c r="H21">
-        <v>-0.02004830917874395</v>
+        <v>-0.009130434782608721</v>
       </c>
       <c r="I21">
-        <v>-0.06341673548373197</v>
+        <v>-0.09398305560858214</v>
       </c>
       <c r="J21">
-        <v>0.02278842149249139</v>
+        <v>0.07321618921121935</v>
       </c>
       <c r="K21">
-        <v>0.3648</v>
+        <v>0.8304</v>
+      </c>
+      <c r="L21">
+        <v>0.3271451061470259</v>
+      </c>
+      <c r="M21">
+        <v>1.26766664491409</v>
       </c>
       <c r="N21" t="s">
+        <v>67</v>
+      </c>
+      <c r="O21">
+        <v>0.8304</v>
+      </c>
+      <c r="P21" t="s">
         <v>110</v>
       </c>
-      <c r="O21">
-        <v>0.3648</v>
-      </c>
-      <c r="P21" t="s">
-        <v>113</v>
-      </c>
       <c r="Q21">
-        <v>-0.07233878000738253</v>
+        <v>-0.1101837620501105</v>
       </c>
       <c r="R21">
-        <v>0.03224216164989475</v>
+        <v>0.0919228924848931</v>
       </c>
       <c r="S21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -5111,46 +6071,52 @@
         <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F22">
-        <v>0.4993498188103143</v>
+        <v>0.5201170436838566</v>
       </c>
       <c r="G22">
-        <v>0.5350976252975095</v>
+        <v>0.5374321662622487</v>
       </c>
       <c r="H22">
-        <v>-0.03574780648719517</v>
+        <v>-0.01731512257839207</v>
       </c>
       <c r="I22">
-        <v>-0.08117500431921684</v>
+        <v>-0.1164926751154171</v>
       </c>
       <c r="J22">
-        <v>0.01103192398107171</v>
+        <v>0.08380091829685227</v>
       </c>
       <c r="K22">
-        <v>0.1386</v>
+        <v>0.7464</v>
+      </c>
+      <c r="L22">
+        <v>0.1949057415254287</v>
+      </c>
+      <c r="M22">
+        <v>1.374108209799784</v>
       </c>
       <c r="N22" t="s">
+        <v>67</v>
+      </c>
+      <c r="O22">
+        <v>0.9228</v>
+      </c>
+      <c r="P22" t="s">
         <v>110</v>
       </c>
-      <c r="O22">
-        <v>0.2192</v>
-      </c>
-      <c r="P22" t="s">
+      <c r="S22" t="s">
         <v>113</v>
-      </c>
-      <c r="S22" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -5158,52 +6124,52 @@
         <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F23">
-        <v>0.3599999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="G23">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="H23">
-        <v>-0.01000000000000012</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="I23">
-        <v>-0.09999999999999987</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="J23">
-        <v>0.05999999999999994</v>
+        <v>0.09500000000000003</v>
       </c>
       <c r="K23">
-        <v>0.6612</v>
+        <v>0.8336</v>
       </c>
       <c r="N23" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="O23">
-        <v>0.7706</v>
+        <v>0.8766</v>
       </c>
       <c r="P23" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q23">
-        <v>-0.1038971985921919</v>
+        <v>-0.09734129388236519</v>
       </c>
       <c r="R23">
-        <v>0.08389719859219168</v>
+        <v>0.1173412938823652</v>
       </c>
       <c r="S23" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5211,46 +6177,46 @@
         <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F24">
-        <v>0.5003424089040717</v>
+        <v>0.5238220251826913</v>
       </c>
       <c r="G24">
-        <v>0.5363567435512407</v>
+        <v>0.5410617974988647</v>
       </c>
       <c r="H24">
-        <v>-0.03601433464716908</v>
+        <v>-0.01723977231617346</v>
       </c>
       <c r="I24">
-        <v>-0.08128862160672953</v>
+        <v>-0.117765501818481</v>
       </c>
       <c r="J24">
-        <v>0.01090263065652809</v>
+        <v>0.08218194600946505</v>
       </c>
       <c r="K24">
-        <v>0.1346</v>
+        <v>0.751</v>
       </c>
       <c r="N24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O24">
-        <v>0.2062</v>
+        <v>0.9198</v>
       </c>
       <c r="P24" t="s">
+        <v>110</v>
+      </c>
+      <c r="S24" t="s">
         <v>113</v>
-      </c>
-      <c r="S24" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5258,46 +6224,52 @@
         <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F25">
-        <v>0.714975845410628</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G25">
-        <v>0.6473429951690821</v>
+        <v>0.7101449275362319</v>
       </c>
       <c r="H25">
-        <v>0.06763285024154586</v>
+        <v>-0.0434782608695653</v>
       </c>
       <c r="I25">
-        <v>-0.004830917874396135</v>
+        <v>-0.1486789027833803</v>
       </c>
       <c r="J25">
-        <v>0.1400966183574879</v>
+        <v>0.05714285714285714</v>
       </c>
       <c r="K25">
-        <v>0.08782509563019504</v>
+        <v>0.4104456923623511</v>
+      </c>
+      <c r="L25">
+        <v>-0.01013513513513513</v>
+      </c>
+      <c r="M25">
+        <v>1.568181818181818</v>
       </c>
       <c r="N25" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="O25">
-        <v>0.1756501912603901</v>
+        <v>0.8208913847247021</v>
       </c>
       <c r="P25" t="s">
+        <v>111</v>
+      </c>
+      <c r="S25" t="s">
         <v>114</v>
-      </c>
-      <c r="S25" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5305,52 +6277,58 @@
         <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F26">
-        <v>0.01473429951690822</v>
+        <v>0.01043478260869565</v>
       </c>
       <c r="G26">
-        <v>0.002318840579710145</v>
+        <v>0.06304347826086956</v>
       </c>
       <c r="H26">
-        <v>0.01241545893719808</v>
+        <v>-0.05260869565217391</v>
       </c>
       <c r="I26">
-        <v>-0.05180369647565036</v>
+        <v>-0.1879810138775782</v>
       </c>
       <c r="J26">
-        <v>0.07238411204395538</v>
+        <v>0.05830076237802242</v>
       </c>
       <c r="K26">
-        <v>0.6962</v>
+        <v>0.3848</v>
+      </c>
+      <c r="L26">
+        <v>-0.03098345436095269</v>
+      </c>
+      <c r="M26">
+        <v>1.568181818181818</v>
       </c>
       <c r="N26" t="s">
+        <v>67</v>
+      </c>
+      <c r="O26">
+        <v>0.6546</v>
+      </c>
+      <c r="P26" t="s">
         <v>110</v>
       </c>
-      <c r="O26">
-        <v>0.9156</v>
-      </c>
-      <c r="P26" t="s">
-        <v>113</v>
-      </c>
       <c r="Q26">
-        <v>-0.06168545131060543</v>
+        <v>-0.2000900155857261</v>
       </c>
       <c r="R26">
-        <v>0.08651636918500157</v>
+        <v>0.09487262428137828</v>
       </c>
       <c r="S26" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5358,52 +6336,58 @@
         <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F27">
-        <v>0.4014975845410628</v>
+        <v>0.4165217391304348</v>
       </c>
       <c r="G27">
-        <v>0.4694685990338164</v>
+        <v>0.4534782608695653</v>
       </c>
       <c r="H27">
-        <v>-0.06797101449275361</v>
+        <v>-0.0369565217391305</v>
       </c>
       <c r="I27">
-        <v>-0.1150446795079015</v>
+        <v>-0.1201436004796208</v>
       </c>
       <c r="J27">
-        <v>-0.01980502496348764</v>
+        <v>0.05199748898995496</v>
       </c>
       <c r="K27">
-        <v>0.0066</v>
+        <v>0.39</v>
+      </c>
+      <c r="L27">
+        <v>-0.2695103572946947</v>
+      </c>
+      <c r="M27">
+        <v>1.568181818181818</v>
       </c>
       <c r="N27" t="s">
+        <v>67</v>
+      </c>
+      <c r="O27">
+        <v>0.6682</v>
+      </c>
+      <c r="P27" t="s">
         <v>110</v>
       </c>
-      <c r="O27">
-        <v>0.0182</v>
-      </c>
-      <c r="P27" t="s">
-        <v>113</v>
-      </c>
       <c r="Q27">
-        <v>-0.1263846722789996</v>
+        <v>-0.1410315331593855</v>
       </c>
       <c r="R27">
-        <v>-0.009557356706507911</v>
+        <v>0.06711848968112478</v>
       </c>
       <c r="S27" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5411,46 +6395,52 @@
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F28">
-        <v>0.4993498188103143</v>
+        <v>0.5201170436838566</v>
       </c>
       <c r="G28">
-        <v>0.5841530472476332</v>
+        <v>0.5544640969283843</v>
       </c>
       <c r="H28">
-        <v>-0.08480322843731886</v>
+        <v>-0.03434705324452769</v>
       </c>
       <c r="I28">
-        <v>-0.1392818727626998</v>
+        <v>-0.1272371763235338</v>
       </c>
       <c r="J28">
-        <v>-0.02765282063164901</v>
+        <v>0.06288154246470519</v>
       </c>
       <c r="K28">
-        <v>0.004</v>
+        <v>0.5024</v>
+      </c>
+      <c r="L28">
+        <v>-0.1848791046335549</v>
+      </c>
+      <c r="M28">
+        <v>1.568181818181818</v>
       </c>
       <c r="N28" t="s">
+        <v>67</v>
+      </c>
+      <c r="O28">
+        <v>0.7744</v>
+      </c>
+      <c r="P28" t="s">
         <v>110</v>
       </c>
-      <c r="O28">
-        <v>0.0112</v>
-      </c>
-      <c r="P28" t="s">
+      <c r="S28" t="s">
         <v>113</v>
-      </c>
-      <c r="S28" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5458,52 +6448,52 @@
         <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F29">
-        <v>0.3599999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="G29">
-        <v>0.4199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="H29">
-        <v>-0.06000000000000005</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="I29">
-        <v>-0.15</v>
+        <v>-0.145</v>
       </c>
       <c r="J29">
-        <v>-1.110223024625157E-16</v>
+        <v>0.06999999999999995</v>
       </c>
       <c r="K29">
-        <v>0.044</v>
+        <v>0.5732</v>
       </c>
       <c r="N29" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="O29">
-        <v>0.3118</v>
+        <v>0.7028</v>
       </c>
       <c r="P29" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q29">
-        <v>-0.1500000000000001</v>
+        <v>-0.1700413668805986</v>
       </c>
       <c r="R29">
-        <v>0.03000000000000003</v>
+        <v>0.09004136688059849</v>
       </c>
       <c r="S29" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5511,46 +6501,46 @@
         <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F30">
-        <v>0.5003424089040717</v>
+        <v>0.5238220251826913</v>
       </c>
       <c r="G30">
-        <v>0.5855645643413213</v>
+        <v>0.5549040837833944</v>
       </c>
       <c r="H30">
-        <v>-0.08522215543724965</v>
+        <v>-0.03108205860070312</v>
       </c>
       <c r="I30">
-        <v>-0.1400943073214456</v>
+        <v>-0.1262655503625984</v>
       </c>
       <c r="J30">
-        <v>-0.02918989008947918</v>
+        <v>0.06957054598927924</v>
       </c>
       <c r="K30">
-        <v>0.006</v>
+        <v>0.5556</v>
       </c>
       <c r="N30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O30">
-        <v>0.0176</v>
+        <v>0.8274</v>
       </c>
       <c r="P30" t="s">
+        <v>110</v>
+      </c>
+      <c r="S30" t="s">
         <v>113</v>
-      </c>
-      <c r="S30" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5558,46 +6548,52 @@
         <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F31">
-        <v>0.714975845410628</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G31">
-        <v>0.6038647342995169</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="H31">
-        <v>0.111111111111111</v>
+        <v>0.01449275362318836</v>
       </c>
       <c r="I31">
-        <v>0.03381642512077294</v>
+        <v>-0.1475963668586618</v>
       </c>
       <c r="J31">
-        <v>0.1835748792270532</v>
+        <v>0.1803392531876139</v>
       </c>
       <c r="K31">
-        <v>0.006357215082587968</v>
+        <v>0.8633641527524397</v>
+      </c>
+      <c r="L31">
+        <v>0.08860617399438728</v>
+      </c>
+      <c r="M31">
+        <v>1.473567895472554</v>
       </c>
       <c r="N31" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="O31">
-        <v>0.0190716452477639</v>
+        <v>0.8633641527524397</v>
       </c>
       <c r="P31" t="s">
+        <v>111</v>
+      </c>
+      <c r="S31" t="s">
         <v>114</v>
-      </c>
-      <c r="S31" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5605,52 +6601,58 @@
         <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F32">
-        <v>0.006376811594202901</v>
+        <v>0.01811594202898551</v>
       </c>
       <c r="G32">
-        <v>0.002318840579710145</v>
+        <v>0.06304347826086956</v>
       </c>
       <c r="H32">
-        <v>0.004057971014492756</v>
+        <v>-0.04492753623188404</v>
       </c>
       <c r="I32">
-        <v>-0.06646966441868675</v>
+        <v>-0.1754659154641391</v>
       </c>
       <c r="J32">
-        <v>0.07049753251267667</v>
+        <v>0.08188536834779539</v>
       </c>
       <c r="K32">
-        <v>0.9026</v>
+        <v>0.4786</v>
+      </c>
+      <c r="L32">
+        <v>-0.04383859438246455</v>
+      </c>
+      <c r="M32">
+        <v>1.568181818181818</v>
       </c>
       <c r="N32" t="s">
+        <v>67</v>
+      </c>
+      <c r="O32">
+        <v>0.7151999999999999</v>
+      </c>
+      <c r="P32" t="s">
         <v>110</v>
       </c>
-      <c r="O32">
-        <v>0.9228</v>
-      </c>
-      <c r="P32" t="s">
-        <v>113</v>
-      </c>
       <c r="Q32">
-        <v>-0.07685225067811854</v>
+        <v>-0.2027351339597176</v>
       </c>
       <c r="R32">
-        <v>0.08496819270710404</v>
+        <v>0.1128800614959495</v>
       </c>
       <c r="S32" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5658,52 +6660,58 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F33">
-        <v>0.4215458937198068</v>
+        <v>0.4256521739130435</v>
       </c>
       <c r="G33">
-        <v>0.4694685990338164</v>
+        <v>0.4534782608695653</v>
       </c>
       <c r="H33">
-        <v>-0.04792270531400966</v>
+        <v>-0.02782608695652178</v>
       </c>
       <c r="I33">
-        <v>-0.1024447384258064</v>
+        <v>-0.1214282966917444</v>
       </c>
       <c r="J33">
-        <v>0.005401149152844641</v>
+        <v>0.07867450219518883</v>
       </c>
       <c r="K33">
-        <v>0.0788</v>
+        <v>0.5806</v>
+      </c>
+      <c r="L33">
+        <v>-0.03481933654805834</v>
+      </c>
+      <c r="M33">
+        <v>1.568181818181818</v>
       </c>
       <c r="N33" t="s">
+        <v>67</v>
+      </c>
+      <c r="O33">
+        <v>0.7912</v>
+      </c>
+      <c r="P33" t="s">
         <v>110</v>
       </c>
-      <c r="O33">
-        <v>0.1346</v>
-      </c>
-      <c r="P33" t="s">
-        <v>113</v>
-      </c>
       <c r="Q33">
-        <v>-0.111707487254363</v>
+        <v>-0.1503432645023226</v>
       </c>
       <c r="R33">
-        <v>0.01586207662634324</v>
+        <v>0.09469109058927928</v>
       </c>
       <c r="S33" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5711,46 +6719,52 @@
         <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E34" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F34">
-        <v>0.5350976252975095</v>
+        <v>0.5374321662622487</v>
       </c>
       <c r="G34">
-        <v>0.5841530472476332</v>
+        <v>0.5544640969283843</v>
       </c>
       <c r="H34">
-        <v>-0.04905542195012369</v>
+        <v>-0.01703193066613562</v>
       </c>
       <c r="I34">
-        <v>-0.1111569370207811</v>
+        <v>-0.1356648710020678</v>
       </c>
       <c r="J34">
-        <v>0.01275237325302565</v>
+        <v>0.100814865669678</v>
       </c>
       <c r="K34">
-        <v>0.1238</v>
+        <v>0.8066</v>
+      </c>
+      <c r="L34">
+        <v>-0.03807315394614937</v>
+      </c>
+      <c r="M34">
+        <v>1.568181818181818</v>
       </c>
       <c r="N34" t="s">
+        <v>67</v>
+      </c>
+      <c r="O34">
+        <v>0.9228</v>
+      </c>
+      <c r="P34" t="s">
         <v>110</v>
       </c>
-      <c r="O34">
-        <v>0.2192</v>
-      </c>
-      <c r="P34" t="s">
+      <c r="S34" t="s">
         <v>113</v>
-      </c>
-      <c r="S34" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5758,52 +6772,52 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F35">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="G35">
-        <v>0.4199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="H35">
-        <v>-0.04999999999999993</v>
+        <v>-0.05000000000000004</v>
       </c>
       <c r="I35">
-        <v>-0.1400000000000001</v>
+        <v>-0.17</v>
       </c>
       <c r="J35">
-        <v>0.02999999999999992</v>
+        <v>0.06</v>
       </c>
       <c r="K35">
-        <v>0.224</v>
+        <v>0.4592</v>
       </c>
       <c r="N35" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="O35">
-        <v>0.4476</v>
+        <v>0.6756</v>
       </c>
       <c r="P35" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q35">
-        <v>-0.1519260792971539</v>
+        <v>-0.1850000000000001</v>
       </c>
       <c r="R35">
-        <v>0.05192607929715401</v>
+        <v>0.08500000000000002</v>
       </c>
       <c r="S35" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5811,46 +6825,46 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F36">
-        <v>0.5363567435512407</v>
+        <v>0.5410617974988647</v>
       </c>
       <c r="G36">
-        <v>0.5855645643413213</v>
+        <v>0.5549040837833944</v>
       </c>
       <c r="H36">
-        <v>-0.04920782079008057</v>
+        <v>-0.01384228628452966</v>
       </c>
       <c r="I36">
-        <v>-0.1114327077564691</v>
+        <v>-0.1354366941567308</v>
       </c>
       <c r="J36">
-        <v>0.01244135367620838</v>
+        <v>0.1085662294439589</v>
       </c>
       <c r="K36">
-        <v>0.1184</v>
+        <v>0.8346</v>
       </c>
       <c r="N36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O36">
-        <v>0.2062</v>
+        <v>0.9198</v>
       </c>
       <c r="P36" t="s">
+        <v>110</v>
+      </c>
+      <c r="S36" t="s">
         <v>113</v>
-      </c>
-      <c r="S36" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5858,46 +6872,52 @@
         <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D37" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F37">
-        <v>0.6473429951690821</v>
+        <v>0.7101449275362319</v>
       </c>
       <c r="G37">
-        <v>0.6038647342995169</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="H37">
-        <v>0.04347826086956519</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="I37">
-        <v>-0.03381642512077294</v>
+        <v>-0.07142857142857142</v>
       </c>
       <c r="J37">
-        <v>0.1159420289855072</v>
+        <v>0.1940298507462687</v>
       </c>
       <c r="K37">
-        <v>0.3134999455835852</v>
+        <v>0.3988546137823287</v>
+      </c>
+      <c r="L37">
+        <v>-0.01065246338215713</v>
+      </c>
+      <c r="M37">
+        <v>1.568181818181818</v>
       </c>
       <c r="N37" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="O37">
-        <v>0.3134999455835852</v>
+        <v>0.7977092275646573</v>
       </c>
       <c r="P37" t="s">
+        <v>111</v>
+      </c>
+      <c r="S37" t="s">
         <v>114</v>
-      </c>
-      <c r="S37" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5905,52 +6925,58 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F38">
-        <v>0.02648241206030149</v>
+        <v>0.01693277310924369</v>
       </c>
       <c r="G38">
-        <v>0.05065326633165827</v>
+        <v>0.01974789915966386</v>
       </c>
       <c r="H38">
-        <v>-0.02417085427135678</v>
+        <v>-0.002815126050420166</v>
       </c>
       <c r="I38">
-        <v>-0.07938859663334021</v>
+        <v>-0.05748818465674033</v>
       </c>
       <c r="J38">
-        <v>0.03473953972963441</v>
+        <v>0.05012159164749841</v>
       </c>
       <c r="K38">
-        <v>0.3916</v>
+        <v>0.9176</v>
+      </c>
+      <c r="L38">
+        <v>0.1943278172079755</v>
+      </c>
+      <c r="M38">
+        <v>1.359032548719953</v>
       </c>
       <c r="N38" t="s">
+        <v>67</v>
+      </c>
+      <c r="O38">
+        <v>0.982</v>
+      </c>
+      <c r="P38" t="s">
         <v>110</v>
       </c>
-      <c r="O38">
-        <v>0.4768</v>
-      </c>
-      <c r="P38" t="s">
-        <v>113</v>
-      </c>
       <c r="Q38">
-        <v>-0.0908680477437257</v>
+        <v>-0.06625616770219352</v>
       </c>
       <c r="R38">
-        <v>0.0425263392010121</v>
+        <v>0.06062591560135315</v>
       </c>
       <c r="S38" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -5958,52 +6984,58 @@
         <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F39">
-        <v>0.4006532663316583</v>
+        <v>0.3740756302521008</v>
       </c>
       <c r="G39">
-        <v>0.4056281407035176</v>
+        <v>0.3876470588235295</v>
       </c>
       <c r="H39">
-        <v>-0.004974874371859284</v>
+        <v>-0.01357142857142862</v>
       </c>
       <c r="I39">
-        <v>-0.05070529366418342</v>
+        <v>-0.06071090006005311</v>
       </c>
       <c r="J39">
-        <v>0.04187065486244625</v>
+        <v>0.03126504210044222</v>
       </c>
       <c r="K39">
-        <v>0.8314</v>
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="L39">
+        <v>0.2103450236458073</v>
+      </c>
+      <c r="M39">
+        <v>1.345653477740814</v>
       </c>
       <c r="N39" t="s">
+        <v>67</v>
+      </c>
+      <c r="O39">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="P39" t="s">
         <v>110</v>
       </c>
-      <c r="O39">
-        <v>0.8314</v>
-      </c>
-      <c r="P39" t="s">
-        <v>113</v>
-      </c>
       <c r="Q39">
-        <v>-0.06040181445148433</v>
+        <v>-0.06891405825293671</v>
       </c>
       <c r="R39">
-        <v>0.05045206570776576</v>
+        <v>0.04177120111008013</v>
       </c>
       <c r="S39" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -6011,46 +7043,52 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E40" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F40">
-        <v>0.5074703248991672</v>
+        <v>0.4805271090386144</v>
       </c>
       <c r="G40">
-        <v>0.5017647249418594</v>
+        <v>0.4957262730732819</v>
       </c>
       <c r="H40">
-        <v>0.005705599957307794</v>
+        <v>-0.01519916403466753</v>
       </c>
       <c r="I40">
-        <v>-0.0437486940349788</v>
+        <v>-0.05959981574711692</v>
       </c>
       <c r="J40">
-        <v>0.05394448983572651</v>
+        <v>0.02961214099715429</v>
       </c>
       <c r="K40">
-        <v>0.8202</v>
+        <v>0.503</v>
+      </c>
+      <c r="L40">
+        <v>0.1856703660766267</v>
+      </c>
+      <c r="M40">
+        <v>1.366375422058099</v>
       </c>
       <c r="N40" t="s">
+        <v>67</v>
+      </c>
+      <c r="O40">
+        <v>0.503</v>
+      </c>
+      <c r="P40" t="s">
         <v>110</v>
       </c>
-      <c r="O40">
-        <v>0.8202</v>
-      </c>
-      <c r="P40" t="s">
+      <c r="S40" t="s">
         <v>113</v>
-      </c>
-      <c r="S40" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -6058,52 +7096,52 @@
         <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F41">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="G41">
-        <v>0.3500000000000001</v>
+        <v>0.335</v>
       </c>
       <c r="H41">
-        <v>-0.01000000000000012</v>
+        <v>-0.04500000000000004</v>
       </c>
       <c r="I41">
-        <v>-0.08000000000000018</v>
+        <v>-0.105</v>
       </c>
       <c r="J41">
-        <v>0.05999999999999994</v>
+        <v>0.03999999999999998</v>
       </c>
       <c r="K41">
-        <v>0.6392</v>
+        <v>0.3164</v>
       </c>
       <c r="N41" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="O41">
-        <v>0.764</v>
+        <v>0.3292</v>
       </c>
       <c r="P41" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q41">
-        <v>-0.09925482790573971</v>
+        <v>-0.131897207526139</v>
       </c>
       <c r="R41">
-        <v>0.07925482790573947</v>
+        <v>0.04189720752613892</v>
       </c>
       <c r="S41" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -6111,46 +7149,46 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E42" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F42">
-        <v>0.5080569923909963</v>
+        <v>0.4812407527715649</v>
       </c>
       <c r="G42">
-        <v>0.5004604701660993</v>
+        <v>0.4963766811552734</v>
       </c>
       <c r="H42">
-        <v>0.00759652222489704</v>
+        <v>-0.01513592838370859</v>
       </c>
       <c r="I42">
-        <v>-0.04136267558648257</v>
+        <v>-0.05940962551562724</v>
       </c>
       <c r="J42">
-        <v>0.05592181985989171</v>
+        <v>0.02955483342924571</v>
       </c>
       <c r="K42">
-        <v>0.761</v>
+        <v>0.5008</v>
       </c>
       <c r="N42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O42">
-        <v>0.761</v>
+        <v>0.5008</v>
       </c>
       <c r="P42" t="s">
+        <v>110</v>
+      </c>
+      <c r="S42" t="s">
         <v>113</v>
-      </c>
-      <c r="S42" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -6158,46 +7196,52 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C43" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F43">
-        <v>0.6683417085427136</v>
+        <v>0.7394957983193278</v>
       </c>
       <c r="G43">
-        <v>0.6683417085427136</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>0.06302521008403361</v>
       </c>
       <c r="I43">
-        <v>-0.07537688442211055</v>
+        <v>-0.008298755186721992</v>
       </c>
       <c r="J43">
-        <v>0.07537688442211055</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="K43">
-        <v>1</v>
+        <v>0.0785432549942764</v>
+      </c>
+      <c r="L43">
+        <v>0.06937498713753575</v>
+      </c>
+      <c r="M43">
+        <v>1.473305902152329</v>
       </c>
       <c r="N43" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="O43">
-        <v>1</v>
+        <v>0.1570865099885528</v>
       </c>
       <c r="P43" t="s">
+        <v>111</v>
+      </c>
+      <c r="S43" t="s">
         <v>114</v>
-      </c>
-      <c r="S43" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -6205,52 +7249,58 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F44">
-        <v>0.02648241206030149</v>
+        <v>0.01693277310924369</v>
       </c>
       <c r="G44">
-        <v>0.09015075376884421</v>
+        <v>0.01130252100840337</v>
       </c>
       <c r="H44">
-        <v>-0.06366834170854271</v>
+        <v>0.005630252100840326</v>
       </c>
       <c r="I44">
-        <v>-0.134711306615152</v>
+        <v>-0.06081467861304428</v>
       </c>
       <c r="J44">
-        <v>0.005948065860233304</v>
+        <v>0.07283379687072547</v>
       </c>
       <c r="K44">
-        <v>0.08019999999999999</v>
+        <v>0.862</v>
+      </c>
+      <c r="L44">
+        <v>0.2479815712178917</v>
+      </c>
+      <c r="M44">
+        <v>1.315229181497365</v>
       </c>
       <c r="N44" t="s">
+        <v>67</v>
+      </c>
+      <c r="O44">
+        <v>0.982</v>
+      </c>
+      <c r="P44" t="s">
         <v>110</v>
       </c>
-      <c r="O44">
-        <v>0.1878</v>
-      </c>
-      <c r="P44" t="s">
-        <v>113</v>
-      </c>
       <c r="Q44">
-        <v>-0.1488692935139442</v>
+        <v>-0.0744154556769744</v>
       </c>
       <c r="R44">
-        <v>0.02153261009685876</v>
+        <v>0.08567595987865505</v>
       </c>
       <c r="S44" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -6258,52 +7308,58 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F45">
-        <v>0.4006532663316583</v>
+        <v>0.3740756302521008</v>
       </c>
       <c r="G45">
-        <v>0.4757788944723618</v>
+        <v>0.4584453781512605</v>
       </c>
       <c r="H45">
-        <v>-0.0751256281407035</v>
+        <v>-0.08436974789915969</v>
       </c>
       <c r="I45">
-        <v>-0.1310229499051968</v>
+        <v>-0.1398838651624345</v>
       </c>
       <c r="J45">
-        <v>-0.02007745571459697</v>
+        <v>-0.0295327372730704</v>
       </c>
       <c r="K45">
-        <v>0.008200000000000001</v>
+        <v>0.0034</v>
+      </c>
+      <c r="L45">
+        <v>0.2617227998154008</v>
+      </c>
+      <c r="M45">
+        <v>1.304461201119753</v>
       </c>
       <c r="N45" t="s">
+        <v>67</v>
+      </c>
+      <c r="O45">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="P45" t="s">
         <v>110</v>
       </c>
-      <c r="O45">
-        <v>0.024</v>
-      </c>
-      <c r="P45" t="s">
-        <v>113</v>
-      </c>
       <c r="Q45">
-        <v>-0.1420685129346101</v>
+        <v>-0.1507495494343032</v>
       </c>
       <c r="R45">
-        <v>-0.008182743346796903</v>
+        <v>-0.01798994636401634</v>
       </c>
       <c r="S45" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:19">
@@ -6311,46 +7367,52 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D46" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F46">
-        <v>0.5074703248991672</v>
+        <v>0.4805271090386144</v>
       </c>
       <c r="G46">
-        <v>0.5911278717875009</v>
+        <v>0.5806744123080022</v>
       </c>
       <c r="H46">
-        <v>-0.08365754688833371</v>
+        <v>-0.1001473032693878</v>
       </c>
       <c r="I46">
-        <v>-0.1420902483200672</v>
+        <v>-0.1606451278002748</v>
       </c>
       <c r="J46">
-        <v>-0.02184629191013983</v>
+        <v>-0.03734422411782519</v>
       </c>
       <c r="K46">
-        <v>0.0086</v>
+        <v>0.0032</v>
+      </c>
+      <c r="L46">
+        <v>0.2003745902317424</v>
+      </c>
+      <c r="M46">
+        <v>1.353950574887211</v>
       </c>
       <c r="N46" t="s">
+        <v>67</v>
+      </c>
+      <c r="O46">
+        <v>0.0058</v>
+      </c>
+      <c r="P46" t="s">
         <v>110</v>
       </c>
-      <c r="O46">
-        <v>0.0188</v>
-      </c>
-      <c r="P46" t="s">
+      <c r="S46" t="s">
         <v>113</v>
-      </c>
-      <c r="S46" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:19">
@@ -6358,52 +7420,52 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C47" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E47" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F47">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="G47">
-        <v>0.3900000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="H47">
-        <v>-0.05000000000000016</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="I47">
-        <v>-0.1199999999999999</v>
+        <v>-0.16</v>
       </c>
       <c r="J47">
-        <v>0.02000000000000002</v>
+        <v>0</v>
       </c>
       <c r="K47">
-        <v>0.1548</v>
+        <v>0.0716</v>
       </c>
       <c r="N47" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="O47">
-        <v>0.2654</v>
+        <v>0.125</v>
       </c>
       <c r="P47" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q47">
-        <v>-0.1364378623663957</v>
+        <v>-0.1748543278868911</v>
       </c>
       <c r="R47">
-        <v>0.03643786236639536</v>
+        <v>0.01485432788689105</v>
       </c>
       <c r="S47" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:19">
@@ -6411,46 +7473,46 @@
         <v>43</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D48" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F48">
-        <v>0.5080569923909963</v>
+        <v>0.4812407527715649</v>
       </c>
       <c r="G48">
-        <v>0.5856865757701022</v>
+        <v>0.581787933214607</v>
       </c>
       <c r="H48">
-        <v>-0.07762958337910586</v>
+        <v>-0.1005471804430421</v>
       </c>
       <c r="I48">
-        <v>-0.1370381777191461</v>
+        <v>-0.1598467389143226</v>
       </c>
       <c r="J48">
-        <v>-0.01531069818067748</v>
+        <v>-0.03791708938899847</v>
       </c>
       <c r="K48">
-        <v>0.0224</v>
+        <v>0.0042</v>
       </c>
       <c r="N48" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O48">
-        <v>0.0424</v>
+        <v>0.0114</v>
       </c>
       <c r="P48" t="s">
+        <v>110</v>
+      </c>
+      <c r="S48" t="s">
         <v>113</v>
-      </c>
-      <c r="S48" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -6458,46 +7520,52 @@
         <v>43</v>
       </c>
       <c r="B49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C49" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D49" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F49">
-        <v>0.6683417085427136</v>
+        <v>0.7394957983193278</v>
       </c>
       <c r="G49">
-        <v>0.6180904522613065</v>
+        <v>0.6386554621848739</v>
       </c>
       <c r="H49">
-        <v>0.05025125628140703</v>
+        <v>0.1008403361344539</v>
       </c>
       <c r="I49">
-        <v>-0.03517587939698492</v>
+        <v>0.02574557059535602</v>
       </c>
       <c r="J49">
-        <v>0.135678391959799</v>
+        <v>0.1769547325102881</v>
       </c>
       <c r="K49">
-        <v>0.3018984444285246</v>
+        <v>0.01051393361055575</v>
+      </c>
+      <c r="L49">
+        <v>0.2828519996869374</v>
+      </c>
+      <c r="M49">
+        <v>1.288243537854977</v>
       </c>
       <c r="N49" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="O49">
-        <v>0.6037968888570493</v>
+        <v>0.03154180083166726</v>
       </c>
       <c r="P49" t="s">
+        <v>111</v>
+      </c>
+      <c r="S49" t="s">
         <v>114</v>
-      </c>
-      <c r="S49" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:19">
@@ -6505,52 +7573,58 @@
         <v>43</v>
       </c>
       <c r="B50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D50" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F50">
-        <v>0.05065326633165827</v>
+        <v>0.01974789915966386</v>
       </c>
       <c r="G50">
-        <v>0.09015075376884421</v>
+        <v>0.01130252100840337</v>
       </c>
       <c r="H50">
-        <v>-0.03949748743718594</v>
+        <v>0.008445378151260492</v>
       </c>
       <c r="I50">
-        <v>-0.114302675420823</v>
+        <v>-0.06093731332680365</v>
       </c>
       <c r="J50">
-        <v>0.03372151397468764</v>
+        <v>0.07706069689774481</v>
       </c>
       <c r="K50">
-        <v>0.2944</v>
+        <v>0.8086</v>
+      </c>
+      <c r="L50">
+        <v>0.1799810231676754</v>
+      </c>
+      <c r="M50">
+        <v>1.371244234613271</v>
       </c>
       <c r="N50" t="s">
+        <v>67</v>
+      </c>
+      <c r="O50">
+        <v>0.9704</v>
+      </c>
+      <c r="P50" t="s">
         <v>110</v>
       </c>
-      <c r="O50">
-        <v>0.4768</v>
-      </c>
-      <c r="P50" t="s">
-        <v>113</v>
-      </c>
       <c r="Q50">
-        <v>-0.1270242150164059</v>
+        <v>-0.07491254037785042</v>
       </c>
       <c r="R50">
-        <v>0.04802924014203403</v>
+        <v>0.09180329668037143</v>
       </c>
       <c r="S50" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:19">
@@ -6558,52 +7632,58 @@
         <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E51" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F51">
-        <v>0.4056281407035176</v>
+        <v>0.3876470588235295</v>
       </c>
       <c r="G51">
-        <v>0.4757788944723618</v>
+        <v>0.4584453781512605</v>
       </c>
       <c r="H51">
-        <v>-0.07015075376884422</v>
+        <v>-0.07079831932773106</v>
       </c>
       <c r="I51">
-        <v>-0.1301497201187742</v>
+        <v>-0.1273640479129107</v>
       </c>
       <c r="J51">
-        <v>-0.01301543821783446</v>
+        <v>-0.0154243638359112</v>
       </c>
       <c r="K51">
-        <v>0.0186</v>
+        <v>0.0158</v>
+      </c>
+      <c r="L51">
+        <v>0.2066823974584756</v>
+      </c>
+      <c r="M51">
+        <v>1.348689562693561</v>
       </c>
       <c r="N51" t="s">
+        <v>67</v>
+      </c>
+      <c r="O51">
+        <v>0.0308</v>
+      </c>
+      <c r="P51" t="s">
         <v>110</v>
       </c>
-      <c r="O51">
-        <v>0.0348</v>
-      </c>
-      <c r="P51" t="s">
-        <v>113</v>
-      </c>
       <c r="Q51">
-        <v>-0.1390395629729493</v>
+        <v>-0.1394101766616208</v>
       </c>
       <c r="R51">
-        <v>-0.001261944564739118</v>
+        <v>-0.002186461993842218</v>
       </c>
       <c r="S51" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:19">
@@ -6611,46 +7691,52 @@
         <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C52" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D52" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E52" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F52">
-        <v>0.5017647249418594</v>
+        <v>0.4957262730732819</v>
       </c>
       <c r="G52">
-        <v>0.5911278717875009</v>
+        <v>0.5806744123080022</v>
       </c>
       <c r="H52">
-        <v>-0.08936314684564151</v>
+        <v>-0.08494813923472028</v>
       </c>
       <c r="I52">
-        <v>-0.1519342158815156</v>
+        <v>-0.1446335592384758</v>
       </c>
       <c r="J52">
-        <v>-0.02445697967964856</v>
+        <v>-0.02545425540213038</v>
       </c>
       <c r="K52">
-        <v>0.008999999999999999</v>
+        <v>0.0092</v>
+      </c>
+      <c r="L52">
+        <v>0.09316285966893136</v>
+      </c>
+      <c r="M52">
+        <v>1.450093471617067</v>
       </c>
       <c r="N52" t="s">
+        <v>67</v>
+      </c>
+      <c r="O52">
+        <v>0.0178</v>
+      </c>
+      <c r="P52" t="s">
         <v>110</v>
       </c>
-      <c r="O52">
-        <v>0.0188</v>
-      </c>
-      <c r="P52" t="s">
+      <c r="S52" t="s">
         <v>113</v>
-      </c>
-      <c r="S52" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:19">
@@ -6658,52 +7744,52 @@
         <v>43</v>
       </c>
       <c r="B53" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C53" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D53" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F53">
-        <v>0.3500000000000001</v>
+        <v>0.335</v>
       </c>
       <c r="G53">
-        <v>0.3900000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="H53">
-        <v>-0.04000000000000004</v>
+        <v>-0.03499999999999998</v>
       </c>
       <c r="I53">
-        <v>-0.1000000000000003</v>
+        <v>-0.13</v>
       </c>
       <c r="J53">
-        <v>0.0399999999999997</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="K53">
-        <v>0.3536</v>
+        <v>0.454</v>
       </c>
       <c r="N53" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="O53">
-        <v>0.4588</v>
+        <v>0.4868</v>
       </c>
       <c r="P53" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q53">
-        <v>-0.13</v>
+        <v>-0.145</v>
       </c>
       <c r="R53">
-        <v>0.04999999999999993</v>
+        <v>0.07500000000000001</v>
       </c>
       <c r="S53" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:19">
@@ -6711,46 +7797,46 @@
         <v>43</v>
       </c>
       <c r="B54" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D54" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E54" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F54">
-        <v>0.5004604701660993</v>
+        <v>0.4963766811552734</v>
       </c>
       <c r="G54">
-        <v>0.5856865757701022</v>
+        <v>0.581787933214607</v>
       </c>
       <c r="H54">
-        <v>-0.0852261056040029</v>
+        <v>-0.08541125205933353</v>
       </c>
       <c r="I54">
-        <v>-0.1485120228288059</v>
+        <v>-0.1444532979412127</v>
       </c>
       <c r="J54">
-        <v>-0.01921195482153516</v>
+        <v>-0.0259623222200178</v>
       </c>
       <c r="K54">
-        <v>0.0134</v>
+        <v>0.0078</v>
       </c>
       <c r="N54" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O54">
-        <v>0.0322</v>
+        <v>0.0204</v>
       </c>
       <c r="P54" t="s">
+        <v>110</v>
+      </c>
+      <c r="S54" t="s">
         <v>113</v>
-      </c>
-      <c r="S54" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:19">
@@ -6758,46 +7844,1024 @@
         <v>43</v>
       </c>
       <c r="B55" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C55" t="s">
+        <v>94</v>
+      </c>
+      <c r="D55" t="s">
+        <v>46</v>
+      </c>
+      <c r="E55" t="s">
+        <v>47</v>
+      </c>
+      <c r="F55">
+        <v>0.6764705882352942</v>
+      </c>
+      <c r="G55">
+        <v>0.6386554621848739</v>
+      </c>
+      <c r="H55">
+        <v>0.03781512605042026</v>
+      </c>
+      <c r="I55">
+        <v>-0.04166666666666666</v>
+      </c>
+      <c r="J55">
+        <v>0.1174456345342423</v>
+      </c>
+      <c r="K55">
+        <v>0.3611297063274773</v>
+      </c>
+      <c r="L55">
+        <v>0.23582236229011</v>
+      </c>
+      <c r="M55">
+        <v>1.324906792740472</v>
+      </c>
+      <c r="N55" t="s">
+        <v>70</v>
+      </c>
+      <c r="O55">
+        <v>0.3611297063274773</v>
+      </c>
+      <c r="P55" t="s">
+        <v>111</v>
+      </c>
+      <c r="S55" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19">
+      <c r="A56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" t="s">
+        <v>88</v>
+      </c>
+      <c r="C56" t="s">
+        <v>89</v>
+      </c>
+      <c r="D56" t="s">
+        <v>45</v>
+      </c>
+      <c r="E56" t="s">
+        <v>46</v>
+      </c>
+      <c r="F56">
+        <v>0.03606060606060607</v>
+      </c>
+      <c r="G56">
+        <v>0.05505050505050505</v>
+      </c>
+      <c r="H56">
+        <v>-0.01898989898989898</v>
+      </c>
+      <c r="I56">
+        <v>-0.08862496046271545</v>
+      </c>
+      <c r="J56">
+        <v>0.05388728593976482</v>
+      </c>
+      <c r="K56">
+        <v>0.6018</v>
+      </c>
+      <c r="L56">
+        <v>-0.2904474668586193</v>
+      </c>
+      <c r="M56">
+        <v>1.546875</v>
+      </c>
+      <c r="N56" t="s">
+        <v>67</v>
+      </c>
+      <c r="O56">
+        <v>0.6018</v>
+      </c>
+      <c r="P56" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q56">
+        <v>-0.1041717788624654</v>
+      </c>
+      <c r="R56">
+        <v>0.06619198088266737</v>
+      </c>
+      <c r="S56" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19">
+      <c r="A57" t="s">
+        <v>44</v>
+      </c>
+      <c r="B57" t="s">
+        <v>88</v>
+      </c>
+      <c r="C57" t="s">
+        <v>90</v>
+      </c>
+      <c r="D57" t="s">
+        <v>45</v>
+      </c>
+      <c r="E57" t="s">
+        <v>46</v>
+      </c>
+      <c r="F57">
+        <v>0.4552525252525252</v>
+      </c>
+      <c r="G57">
+        <v>0.4681818181818182</v>
+      </c>
+      <c r="H57">
+        <v>-0.01292929292929296</v>
+      </c>
+      <c r="I57">
+        <v>-0.07435904196308235</v>
+      </c>
+      <c r="J57">
+        <v>0.055124609713654</v>
+      </c>
+      <c r="K57">
+        <v>0.6848</v>
+      </c>
+      <c r="L57">
+        <v>-0.106425305850861</v>
+      </c>
+      <c r="M57">
+        <v>1.546875</v>
+      </c>
+      <c r="N57" t="s">
+        <v>67</v>
+      </c>
+      <c r="O57">
+        <v>0.6848</v>
+      </c>
+      <c r="P57" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q57">
+        <v>-0.09169388423036738</v>
+      </c>
+      <c r="R57">
+        <v>0.06583529837178102</v>
+      </c>
+      <c r="S57" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19">
+      <c r="A58" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" t="s">
+        <v>88</v>
+      </c>
+      <c r="C58" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58" t="s">
+        <v>45</v>
+      </c>
+      <c r="E58" t="s">
+        <v>46</v>
+      </c>
+      <c r="F58">
+        <v>0.543478322353971</v>
+      </c>
+      <c r="G58">
+        <v>0.559177787452075</v>
+      </c>
+      <c r="H58">
+        <v>-0.01569946509810405</v>
+      </c>
+      <c r="I58">
+        <v>-0.08072115640039265</v>
+      </c>
+      <c r="J58">
+        <v>0.05111977716054127</v>
+      </c>
+      <c r="K58">
+        <v>0.6614</v>
+      </c>
+      <c r="L58">
+        <v>-0.1555075394087764</v>
+      </c>
+      <c r="M58">
+        <v>1.546875</v>
+      </c>
+      <c r="N58" t="s">
+        <v>67</v>
+      </c>
+      <c r="O58">
+        <v>0.6614</v>
+      </c>
+      <c r="P58" t="s">
+        <v>110</v>
+      </c>
+      <c r="S58" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19">
+      <c r="A59" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" t="s">
+        <v>92</v>
+      </c>
+      <c r="D59" t="s">
+        <v>45</v>
+      </c>
+      <c r="E59" t="s">
+        <v>46</v>
+      </c>
+      <c r="F59">
+        <v>0.45</v>
+      </c>
+      <c r="G59">
+        <v>0.44</v>
+      </c>
+      <c r="H59">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="I59">
+        <v>-0.11</v>
+      </c>
+      <c r="J59">
+        <v>0.11</v>
+      </c>
+      <c r="K59">
+        <v>0.9892</v>
+      </c>
+      <c r="N59" t="s">
+        <v>68</v>
+      </c>
+      <c r="O59">
+        <v>0.9892</v>
+      </c>
+      <c r="P59" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q59">
+        <v>-0.114656049457789</v>
+      </c>
+      <c r="R59">
+        <v>0.134656049457789</v>
+      </c>
+      <c r="S59" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19">
+      <c r="A60" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" t="s">
+        <v>88</v>
+      </c>
+      <c r="C60" t="s">
         <v>93</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D60" t="s">
         <v>45</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E60" t="s">
         <v>46</v>
       </c>
-      <c r="F55">
-        <v>0.6683417085427136</v>
-      </c>
-      <c r="G55">
-        <v>0.6180904522613065</v>
-      </c>
-      <c r="H55">
-        <v>0.05025125628140703</v>
-      </c>
-      <c r="I55">
-        <v>-0.04020100502512563</v>
-      </c>
-      <c r="J55">
-        <v>0.135678391959799</v>
-      </c>
-      <c r="K55">
-        <v>0.3018984444285246</v>
-      </c>
-      <c r="N55" t="s">
+      <c r="F60">
+        <v>0.5450403807953941</v>
+      </c>
+      <c r="G60">
+        <v>0.5592932379303726</v>
+      </c>
+      <c r="H60">
+        <v>-0.01425285713497848</v>
+      </c>
+      <c r="I60">
+        <v>-0.08059016955817802</v>
+      </c>
+      <c r="J60">
+        <v>0.05341654811530116</v>
+      </c>
+      <c r="K60">
+        <v>0.6748</v>
+      </c>
+      <c r="N60" t="s">
+        <v>69</v>
+      </c>
+      <c r="O60">
+        <v>0.6748</v>
+      </c>
+      <c r="P60" t="s">
+        <v>110</v>
+      </c>
+      <c r="S60" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19">
+      <c r="A61" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" t="s">
+        <v>94</v>
+      </c>
+      <c r="D61" t="s">
+        <v>45</v>
+      </c>
+      <c r="E61" t="s">
+        <v>46</v>
+      </c>
+      <c r="F61">
+        <v>0.5959595959595959</v>
+      </c>
+      <c r="G61">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="H61">
+        <v>0.02020202020202011</v>
+      </c>
+      <c r="I61">
+        <v>-0.09900990099009901</v>
+      </c>
+      <c r="J61">
+        <v>0.1320754716981132</v>
+      </c>
+      <c r="K61">
+        <v>0.7329150910757301</v>
+      </c>
+      <c r="L61">
+        <v>-0.07978330658105939</v>
+      </c>
+      <c r="M61">
+        <v>1.546875</v>
+      </c>
+      <c r="N61" t="s">
+        <v>70</v>
+      </c>
+      <c r="O61">
+        <v>0.7329150910757301</v>
+      </c>
+      <c r="P61" t="s">
+        <v>111</v>
+      </c>
+      <c r="S61" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19">
+      <c r="A62" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" t="s">
+        <v>88</v>
+      </c>
+      <c r="C62" t="s">
+        <v>89</v>
+      </c>
+      <c r="D62" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" t="s">
+        <v>47</v>
+      </c>
+      <c r="F62">
+        <v>0.03606060606060607</v>
+      </c>
+      <c r="G62">
+        <v>0.1149494949494949</v>
+      </c>
+      <c r="H62">
+        <v>-0.07888888888888887</v>
+      </c>
+      <c r="I62">
+        <v>-0.1770903863284953</v>
+      </c>
+      <c r="J62">
+        <v>0.01515153893145468</v>
+      </c>
+      <c r="K62">
+        <v>0.1058</v>
+      </c>
+      <c r="L62">
+        <v>0.02059518934996596</v>
+      </c>
+      <c r="M62">
+        <v>1.52467233255561</v>
+      </c>
+      <c r="N62" t="s">
+        <v>67</v>
+      </c>
+      <c r="O62">
+        <v>0.2266</v>
+      </c>
+      <c r="P62" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q62">
+        <v>-0.1930728623380932</v>
+      </c>
+      <c r="R62">
+        <v>0.03529508456031522</v>
+      </c>
+      <c r="S62" t="s">
         <v>112</v>
       </c>
-      <c r="O55">
-        <v>0.6037968888570493</v>
-      </c>
-      <c r="P55" t="s">
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63" t="s">
+        <v>90</v>
+      </c>
+      <c r="D63" t="s">
+        <v>45</v>
+      </c>
+      <c r="E63" t="s">
+        <v>47</v>
+      </c>
+      <c r="F63">
+        <v>0.4552525252525252</v>
+      </c>
+      <c r="G63">
+        <v>0.5197979797979798</v>
+      </c>
+      <c r="H63">
+        <v>-0.06454545454545457</v>
+      </c>
+      <c r="I63">
+        <v>-0.1304029636920622</v>
+      </c>
+      <c r="J63">
+        <v>-0.005277721363423381</v>
+      </c>
+      <c r="K63">
+        <v>0.045</v>
+      </c>
+      <c r="L63">
+        <v>-0.1754230967541944</v>
+      </c>
+      <c r="M63">
+        <v>1.546875</v>
+      </c>
+      <c r="N63" t="s">
+        <v>67</v>
+      </c>
+      <c r="O63">
+        <v>0.119</v>
+      </c>
+      <c r="P63" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q63">
+        <v>-0.1428151845382822</v>
+      </c>
+      <c r="R63">
+        <v>0.01372427544737288</v>
+      </c>
+      <c r="S63" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
+      <c r="A64" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" t="s">
+        <v>88</v>
+      </c>
+      <c r="C64" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64" t="s">
+        <v>45</v>
+      </c>
+      <c r="E64" t="s">
+        <v>47</v>
+      </c>
+      <c r="F64">
+        <v>0.543478322353971</v>
+      </c>
+      <c r="G64">
+        <v>0.6253112356372157</v>
+      </c>
+      <c r="H64">
+        <v>-0.08183291328324471</v>
+      </c>
+      <c r="I64">
+        <v>-0.1462367376518515</v>
+      </c>
+      <c r="J64">
+        <v>-0.01656233111272169</v>
+      </c>
+      <c r="K64">
+        <v>0.0324</v>
+      </c>
+      <c r="L64">
+        <v>-0.2623026064131282</v>
+      </c>
+      <c r="M64">
+        <v>1.546875</v>
+      </c>
+      <c r="N64" t="s">
+        <v>67</v>
+      </c>
+      <c r="O64">
+        <v>0.0764</v>
+      </c>
+      <c r="P64" t="s">
+        <v>110</v>
+      </c>
+      <c r="S64" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19">
+      <c r="A65" t="s">
+        <v>44</v>
+      </c>
+      <c r="B65" t="s">
+        <v>88</v>
+      </c>
+      <c r="C65" t="s">
+        <v>92</v>
+      </c>
+      <c r="D65" t="s">
+        <v>45</v>
+      </c>
+      <c r="E65" t="s">
+        <v>47</v>
+      </c>
+      <c r="F65">
+        <v>0.45</v>
+      </c>
+      <c r="G65">
+        <v>0.49</v>
+      </c>
+      <c r="H65">
+        <v>-0.03999999999999998</v>
+      </c>
+      <c r="I65">
+        <v>-0.12</v>
+      </c>
+      <c r="J65">
+        <v>0.04999999999999999</v>
+      </c>
+      <c r="K65">
+        <v>0.6532</v>
+      </c>
+      <c r="N65" t="s">
+        <v>68</v>
+      </c>
+      <c r="O65">
+        <v>0.7156</v>
+      </c>
+      <c r="P65" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q65">
+        <v>-0.14</v>
+      </c>
+      <c r="R65">
+        <v>0.06000000000000004</v>
+      </c>
+      <c r="S65" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19">
+      <c r="A66" t="s">
+        <v>44</v>
+      </c>
+      <c r="B66" t="s">
+        <v>88</v>
+      </c>
+      <c r="C66" t="s">
+        <v>93</v>
+      </c>
+      <c r="D66" t="s">
+        <v>45</v>
+      </c>
+      <c r="E66" t="s">
+        <v>47</v>
+      </c>
+      <c r="F66">
+        <v>0.5450403807953941</v>
+      </c>
+      <c r="G66">
+        <v>0.6177830240223103</v>
+      </c>
+      <c r="H66">
+        <v>-0.07274264322691626</v>
+      </c>
+      <c r="I66">
+        <v>-0.1326539191798262</v>
+      </c>
+      <c r="J66">
+        <v>-0.01153379621125429</v>
+      </c>
+      <c r="K66">
+        <v>0.029</v>
+      </c>
+      <c r="N66" t="s">
+        <v>69</v>
+      </c>
+      <c r="O66">
+        <v>0.0992</v>
+      </c>
+      <c r="P66" t="s">
+        <v>110</v>
+      </c>
+      <c r="S66" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19">
+      <c r="A67" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" t="s">
+        <v>94</v>
+      </c>
+      <c r="D67" t="s">
+        <v>45</v>
+      </c>
+      <c r="E67" t="s">
+        <v>47</v>
+      </c>
+      <c r="F67">
+        <v>0.5959595959595959</v>
+      </c>
+      <c r="G67">
+        <v>0.5252525252525253</v>
+      </c>
+      <c r="H67">
+        <v>0.07070707070707061</v>
+      </c>
+      <c r="I67">
+        <v>-0.0396039603960396</v>
+      </c>
+      <c r="J67">
+        <v>0.1747572815533981</v>
+      </c>
+      <c r="K67">
+        <v>0.2080477461314518</v>
+      </c>
+      <c r="L67">
+        <v>-0.1782954165272666</v>
+      </c>
+      <c r="M67">
+        <v>1.546875</v>
+      </c>
+      <c r="N67" t="s">
+        <v>70</v>
+      </c>
+      <c r="O67">
+        <v>0.6241432383943554</v>
+      </c>
+      <c r="P67" t="s">
+        <v>111</v>
+      </c>
+      <c r="S67" t="s">
         <v>114</v>
       </c>
-      <c r="S55" t="s">
-        <v>117</v>
+    </row>
+    <row r="68" spans="1:19">
+      <c r="A68" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" t="s">
+        <v>88</v>
+      </c>
+      <c r="C68" t="s">
+        <v>89</v>
+      </c>
+      <c r="D68" t="s">
+        <v>46</v>
+      </c>
+      <c r="E68" t="s">
+        <v>47</v>
+      </c>
+      <c r="F68">
+        <v>0.05505050505050505</v>
+      </c>
+      <c r="G68">
+        <v>0.1149494949494949</v>
+      </c>
+      <c r="H68">
+        <v>-0.05989898989898989</v>
+      </c>
+      <c r="I68">
+        <v>-0.1734529329899067</v>
+      </c>
+      <c r="J68">
+        <v>0.04550799786446531</v>
+      </c>
+      <c r="K68">
+        <v>0.2758</v>
+      </c>
+      <c r="L68">
+        <v>0.3926960711657209</v>
+      </c>
+      <c r="M68">
+        <v>1.210705736991787</v>
+      </c>
+      <c r="N68" t="s">
+        <v>67</v>
+      </c>
+      <c r="O68">
+        <v>0.4524</v>
+      </c>
+      <c r="P68" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q68">
+        <v>-0.1906136501021066</v>
+      </c>
+      <c r="R68">
+        <v>0.07081567030412667</v>
+      </c>
+      <c r="S68" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19">
+      <c r="A69" t="s">
+        <v>44</v>
+      </c>
+      <c r="B69" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" t="s">
+        <v>90</v>
+      </c>
+      <c r="D69" t="s">
+        <v>46</v>
+      </c>
+      <c r="E69" t="s">
+        <v>47</v>
+      </c>
+      <c r="F69">
+        <v>0.4681818181818182</v>
+      </c>
+      <c r="G69">
+        <v>0.5197979797979798</v>
+      </c>
+      <c r="H69">
+        <v>-0.05161616161616162</v>
+      </c>
+      <c r="I69">
+        <v>-0.1467751922665724</v>
+      </c>
+      <c r="J69">
+        <v>0.02086892772980065</v>
+      </c>
+      <c r="K69">
+        <v>0.224</v>
+      </c>
+      <c r="L69">
+        <v>0.2988823474395362</v>
+      </c>
+      <c r="M69">
+        <v>1.277004435911887</v>
+      </c>
+      <c r="N69" t="s">
+        <v>67</v>
+      </c>
+      <c r="O69">
+        <v>0.3428</v>
+      </c>
+      <c r="P69" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q69">
+        <v>-0.1526720041364751</v>
+      </c>
+      <c r="R69">
+        <v>0.04943968090415207</v>
+      </c>
+      <c r="S69" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19">
+      <c r="A70" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" t="s">
+        <v>91</v>
+      </c>
+      <c r="D70" t="s">
+        <v>46</v>
+      </c>
+      <c r="E70" t="s">
+        <v>47</v>
+      </c>
+      <c r="F70">
+        <v>0.559177787452075</v>
+      </c>
+      <c r="G70">
+        <v>0.6253112356372157</v>
+      </c>
+      <c r="H70">
+        <v>-0.06613344818514066</v>
+      </c>
+      <c r="I70">
+        <v>-0.1528966205025178</v>
+      </c>
+      <c r="J70">
+        <v>0.01365989588905082</v>
+      </c>
+      <c r="K70">
+        <v>0.1566</v>
+      </c>
+      <c r="L70">
+        <v>0.2015912523625502</v>
+      </c>
+      <c r="M70">
+        <v>1.35389219565621</v>
+      </c>
+      <c r="N70" t="s">
+        <v>67</v>
+      </c>
+      <c r="O70">
+        <v>0.2464</v>
+      </c>
+      <c r="P70" t="s">
+        <v>110</v>
+      </c>
+      <c r="S70" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19">
+      <c r="A71" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" t="s">
+        <v>88</v>
+      </c>
+      <c r="C71" t="s">
+        <v>92</v>
+      </c>
+      <c r="D71" t="s">
+        <v>46</v>
+      </c>
+      <c r="E71" t="s">
+        <v>47</v>
+      </c>
+      <c r="F71">
+        <v>0.44</v>
+      </c>
+      <c r="G71">
+        <v>0.49</v>
+      </c>
+      <c r="H71">
+        <v>-0.04999999999999999</v>
+      </c>
+      <c r="I71">
+        <v>-0.16</v>
+      </c>
+      <c r="J71">
+        <v>0.08500000000000002</v>
+      </c>
+      <c r="K71">
+        <v>0.6528</v>
+      </c>
+      <c r="N71" t="s">
+        <v>68</v>
+      </c>
+      <c r="O71">
+        <v>0.7156</v>
+      </c>
+      <c r="P71" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q71">
+        <v>-0.1935531761552672</v>
+      </c>
+      <c r="R71">
+        <v>0.09355317615526718</v>
+      </c>
+      <c r="S71" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19">
+      <c r="A72" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" t="s">
+        <v>88</v>
+      </c>
+      <c r="C72" t="s">
+        <v>93</v>
+      </c>
+      <c r="D72" t="s">
+        <v>46</v>
+      </c>
+      <c r="E72" t="s">
+        <v>47</v>
+      </c>
+      <c r="F72">
+        <v>0.5592932379303726</v>
+      </c>
+      <c r="G72">
+        <v>0.6177830240223103</v>
+      </c>
+      <c r="H72">
+        <v>-0.05848978609193778</v>
+      </c>
+      <c r="I72">
+        <v>-0.1360691728962422</v>
+      </c>
+      <c r="J72">
+        <v>0.01505136763452953</v>
+      </c>
+      <c r="K72">
+        <v>0.148</v>
+      </c>
+      <c r="N72" t="s">
+        <v>69</v>
+      </c>
+      <c r="O72">
+        <v>0.2186</v>
+      </c>
+      <c r="P72" t="s">
+        <v>110</v>
+      </c>
+      <c r="S72" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19">
+      <c r="A73" t="s">
+        <v>44</v>
+      </c>
+      <c r="B73" t="s">
+        <v>88</v>
+      </c>
+      <c r="C73" t="s">
+        <v>94</v>
+      </c>
+      <c r="D73" t="s">
+        <v>46</v>
+      </c>
+      <c r="E73" t="s">
+        <v>47</v>
+      </c>
+      <c r="F73">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="G73">
+        <v>0.5252525252525253</v>
+      </c>
+      <c r="H73">
+        <v>0.0505050505050505</v>
+      </c>
+      <c r="I73">
+        <v>-0.0721930646672914</v>
+      </c>
+      <c r="J73">
+        <v>0.1739552553820179</v>
+      </c>
+      <c r="K73">
+        <v>0.4273643299212784</v>
+      </c>
+      <c r="L73">
+        <v>0.1555398671096345</v>
+      </c>
+      <c r="M73">
+        <v>1.393609099133894</v>
+      </c>
+      <c r="N73" t="s">
+        <v>70</v>
+      </c>
+      <c r="O73">
+        <v>0.7329150910757301</v>
+      </c>
+      <c r="P73" t="s">
+        <v>111</v>
+      </c>
+      <c r="S73" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -6807,7 +8871,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6821,55 +8885,55 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" t="s">
         <v>118</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>119</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" t="s">
         <v>120</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>121</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>122</v>
       </c>
-      <c r="H1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>123</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>124</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>125</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>126</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>127</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>128</v>
-      </c>
-      <c r="P1" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>130</v>
-      </c>
-      <c r="R1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -6880,19 +8944,16 @@
         <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F2" t="s">
         <v>135</v>
-      </c>
-      <c r="E2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G2" t="s">
-        <v>122</v>
       </c>
       <c r="H2">
         <v>406</v>
@@ -6916,16 +8977,16 @@
         <v>42</v>
       </c>
       <c r="O2" t="s">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="P2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -6933,37 +8994,34 @@
         <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" t="s">
         <v>133</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3" t="s">
         <v>135</v>
       </c>
-      <c r="E3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G3" t="s">
-        <v>122</v>
-      </c>
       <c r="H3">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="I3">
-        <v>207</v>
+        <v>44</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="L3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3">
         <v>4999</v>
@@ -6972,16 +9030,16 @@
         <v>42</v>
       </c>
       <c r="O3" t="s">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="P3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -6989,37 +9047,34 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" t="s">
         <v>134</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>135</v>
       </c>
-      <c r="E4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G4" t="s">
-        <v>122</v>
-      </c>
       <c r="H4">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="I4">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4">
         <v>4999</v>
@@ -7028,16 +9083,69 @@
         <v>42</v>
       </c>
       <c r="O4" t="s">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="P4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4" t="s">
-        <v>139</v>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H5">
+        <v>99</v>
+      </c>
+      <c r="I5">
+        <v>64</v>
+      </c>
+      <c r="J5">
+        <v>35</v>
+      </c>
+      <c r="K5">
+        <v>0.546875</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>4999</v>
+      </c>
+      <c r="N5">
+        <v>42</v>
+      </c>
+      <c r="O5" t="s">
+        <v>136</v>
+      </c>
+      <c r="P5" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
